--- a/server/data/rss/RSS_FullText.xlsx
+++ b/server/data/rss/RSS_FullText.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="973">
   <si>
     <t>Source</t>
   </si>
@@ -35,6 +35,646 @@
   </si>
   <si>
     <t>TheHindu</t>
+  </si>
+  <si>
+    <t>A.P. Tenant Farmers’ Association questions government’s credibility ahead of State-wide outreach tour</t>
+  </si>
+  <si>
+    <t>The Andhra Pradesh Tenant Farmers’ Association has launched a sharp attack on the ruling coalition, questioning with what “face or moral right” the government plans to approach farmers during its upcoming State-wide outreach programme scheduled from November 24 to December 2.
+In a statement on Sunday (November 23), association State president E. Katamayya and general secretary P. Jamalayya accused the government of completely abandoning the promises it made to tenant farmers during the election campaign. They said coalition leaders had repeatedly assured that, once in power, they would repeal the earlier Tenant Farming Act, issue identity cards easily to tenant farmers, and extend the Annadata Sukhibhava scheme to all landless tenant cultivators. “Eighteen months have passed, and not a single promise has been implemented,” they alleged.
+The leaders said tenant farming has become central to the State’s agriculture, with nearly 80% of land being cultivated by tenant farmers. Despite the Chief Minister’s announcement at the State-Level Bankers’ Committee meeting that banks would offer low-interest crop loans to tenants, three agricultural seasons have passed without any progress, they said.
+They further charged the government with scrapping the free crop insurance scheme and burdening tenant farmers with high premiums, while failing to ensure minimum support price (MSP), forcing farmers to sell produce at distress prices. Calling the government’s attitude “negligent and insensitive,” the association leaders questioned why the promised new law for tenant farmers’ welfare had not materialised. They also criticised the distribution of Annadata Sukhibhava benefits to non-cultivating landowners while excluding actual tenant cultivators.
+Demanding accountability, the leaders said the government should visit farmers’ homes not for publicity but to apologise for failing to deliver on its commitments.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/andhra-pradesh/ap-tenant-farmers-association-questions-governments-credibility-ahead-of-state-wide-outreach-tour/article70314075.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 16:52:27 +0530</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/theme/images/og-image.png</t>
+  </si>
+  <si>
+    <t>Forty students fall ill due to suspected food poisoning in Kasaragod</t>
+  </si>
+  <si>
+    <t>Around 40 students from Kakkat Government Higher Secondary School, Nileshwaram, were hospitalised due to suspected food poisoning after returning from an excursion to Wayanad on Saturday (November 22, 2025).
+The students, all from the upper primary section, were admitted to the Nileswaram Taluk Hospital and other private hospitals. Four teachers who accompanied them also sought medical attention. Hospital authorities said none of the affected children are in critical condition.
+The incident occurred after the group reportedly consumed chicken curry at a hotel near Banasura Sagar in Wayanad. Several students started experiencing stomach pain and began vomiting on their return journey and continued to show symptoms after reaching home on Saturday night.
+More children arrived at hospitals on Sunday morning (November 23, 2025) as the discomfort persisted. Health officials are monitoring the situation and assessing the cause of the suspected contamination.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/kerala/forty-students-fall-ill-due-to-suspected-food-poisoning-in-kasaragod/article70313677.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 16:25:31 +0530</t>
+  </si>
+  <si>
+    <t>Nearly half of Tamil Nadu’s contingent for ‘Khelo India University Games 2025’ drawn from University of Madras</t>
+  </si>
+  <si>
+    <t>Nearly half of the Tamil Nadu contingent at the Khelo India University Games 2025 has been drawn from the University of Madras and its affiliated colleges.
+The contingent of nearly 200 athletes left for Rajasthan on Saturday (November 22, 2025). The 82-strong contingent from the University of Madras (UoM) would participate in nine disciplines of both individual and team events at the Games that begin on November 24.
+Citing past records, V. Mahadevan, Director, Physical Education Department of University of Madras, exuded confidence that the contingent will do well. “Our athletes have always done well and have won medals in the past. Also, we have been sending 80 to 90 athletes to all the four previous Khelo Indian University Games,” he said. The contingent also includes over 50 athletes from Annamalai University and close to 20 from Anna University.
+Working on a paltry annual budget of around ₹60 lakh, the University of Madras is having to balance its priorities. This is apart from the ₹10 lakh that the university allocates the Physical Education Department towards kit and uniform of the students.
+The system works thus: Athletes from the 130-odd affiliate colleges and the university departments attend a special camp where the potential representatives are selected. The potential representatives are then put through a special coaching camp to develop better coordination among them before being sent for inter-university competitions. The attendees are reportedly paid ₹100 a day as allowance during the camps. The practice of daily training for athletes is conspicuously absent.
+So, how many of these athletes have the goal of pushing themselves to reach the next level? Very few, replies Mr. Mahadevan. “Most of the students who enter colleges or the university under sports quota aren’t that well-to-do. They mostly look for securing jobs under the sports quota,” he observes.
+The university has a working collaboration with the Sports Development Authority of Tamil Nadu for using its facilities during the selection and coaching camps. That, to some extent, addresses the infrastructure issue. Question remains, however, on how such a financially strained system is able to support the requirements of athletes and push their performance levels up a few notches.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/tamil-nadu/nearly-half-of-tamil-nadus-contingent-for-khelo-india-university-games-2025-drawn-from-university-of-madras/article70311735.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 16:14:31 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/o4petv/article70314040.ece/alternates/LANDSCAPE_1200/DSC_2671.JPG</t>
+  </si>
+  <si>
+    <t>Shivamogga agri-horticultural varsity develops new variety of rice, receives good response</t>
+  </si>
+  <si>
+    <t>The fine-grain red rice variety – Sahyadri Sindhura – recently introduced by the Keladi Shivappa Nayaka University of Agricultural and Horticultural Sciences in Shivamogga has been in high demand.
+The rice variety developed by a team headed by Dr. B.M. Dushyantha Kumar, Director of Research of the university, was launched by Agriculture Minister N. Cheluvarayaswamy earlier this month.
+After the university revealed the salient features of the rice, including high protein, iron and zinc content, and a low glycaemic index, requests have poured in from the public. The officials from the Governor’s office in Bengaluru, ministers and many elected representatives too have reached out to the university.
+Rigorous research
+The research team has spent five years coming up with this variety after a rigorous experiment at different levels. This rice variety is a cross between popular Jyothi and Biliya varieties. They cultivated the variety, which matures in 120 days, in the demonstration plots of the university in Shivamogga initially. They then expanded to the irrigated area in the Bhadra command area and also the Malnad area. Later, they cultivated it in Davangere. In the third stage, they cultivated it in different research centres spread across the State. The variety has been registered with the National Bureau of Plant Genetic Resources in New Delhi.
+Mr. Dushyanth Kumar told The Hindu, “The trial results recorded an impressive yield of 53-54 quintals per hectare in the irrigated land. The farmers get anywhere up to 50 quintals per acre, which is better than the traditional varieties that yield around 40-45 quintals per hectare,” the scientist said.
+The variety, according to the research team, is resistant to blast disease and tolerant to insects and pests, including leaf folders and stem borers. The growers benefit because of the high-quality straw, which serves as fodder.
+Good price
+The university and the farmers, who have already cultivated the rice variety, are selling the rice at ₹70 to ₹80 per kilo. “The response from consumers is very impressive. The taste is good, and it is also healthy. We are getting requests from the Governor’s office, ministers and many elected representatives. There are a few farmers who have already grown the variety,” he said. The university has sent the seeds to Tamil Nadu, Goa and other places, where farmers were keen to grow the variety.
+Sitaram Bhat, a native of Sagar Taluk, who has grown the variety organically in Hosanagara, said that he had been satisfied with the yield. “When traditional varieties of rice are grown organically, the yield is only around 11-12 quintals per acre. However, the new variety’s yield is anywhere between 18 and 21 quintals. We have been selling rice at ₹75 per kilo, and demand continues to rise,” he stated.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/karnataka/shivamogga-agri-horticultural-varsity-develops-new-variety-of-rice-receives-good-response/article70311043.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 15:58:59 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/kzolgn/article70314019.ece/alternates/LANDSCAPE_1200/9911_7_11_2025_15_35_24_2_KRISHIMELA04.JPG</t>
+  </si>
+  <si>
+    <t>UNSC reforms no longer an option, but a necessity: PM Modi at IBSA meet</t>
+  </si>
+  <si>
+    <t>Prime Minister Narendra Modi on Sunday (November 23, 2025) said the reform of the UN Security Council was no longer an option, but a necessity and asserted that the India-Brazil-South Africa troika should send a clear message for changes to institutions of global governance.
+Addressing the India-Brazil-South Africa (IBSA) leaders summit, Mr. Modi said at a time when the world appears fragmented and divided, IBSA can provide a message of unity, cooperation, and humanity.
+Follow the G20 summit LIVE
+He also proposed institutionalising the IBSA NSA-level meeting to strengthen security cooperation among the three countries.
+“In the fight against terrorism, we must move forward in close coordination. There is no place for any double standards on such a serious issue,” Mr. Modi said at the meeting attended by South African President Cyril Ramaphosa and Brazilian President Luiz Inacio Lula da Silva.
+Highlighting technology's crucial role in ensuring human-centric development, the Prime Minister also proposed establishing an 'IBSA Digital Innovation Alliance' to facilitate the sharing of Digital Public Infrastructure like UPI, health platforms like CoWIN, cybersecurity frameworks and women-led tech initiatives among the three countries.
+Appreciating the IBSA Fund's work in supporting projects across 40 countries in sectors like education, health, women empowerment and solar energy, he proposed the IBSA Fund for Climate Resilient Agriculture to further advance South-South cooperation.
+Mr. Modi called the IBSA meeting as timely as it coincided with the first G20 Summit on African soil and marked the culmination of four consecutive G20 presidencies by Global South countries, out of which the last three were by the IBSA members.
+This has resulted in several important initiatives focused on human-centric development, multilateral reform and sustainable growth, he said.
+The Prime Minister said IBSA was not just a group of three countries but an important platform connecting three continents, three major democratic nations, and three major economies.
+Mr. Modi also invited IBSA leaders to the AI Impact Summit to be held in India next year, even as he emphasised the grouping's potential to contribute to the development of safe, trustworthy and human-centric AI norms.
+The Prime Minister said IBSA can complement each other's development and become an example for sustainable growth.
+He highlighted cooperation opportunities in areas such as millets, natural farming, disaster resilience, green energy, traditional medicines and health security.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/unsc-reforms-no-longer-an-option-but-a-necessity-pm-modi-at-ibsa-meet/article70314001.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 15:57:54 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/wuf2vh/article70314016.ece/alternates/LANDSCAPE_1200/PTI11_23_2025_000282B.jpg</t>
+  </si>
+  <si>
+    <t>Tamil Nadu government deputes SDRF teams to Thoothukudi, Tirunelveli districts over heavy rain prediction</t>
+  </si>
+  <si>
+    <t>In view of the weather advisory predicting heavy rains in a few districts, the Tamil Nadu government has deputed three teams of State Disaster Response Force (SDRF) to Thoothukudi and Tirunelveli districts.
+The India Meteorological Department (IMD) has predicted heavy rains in Cuddalore, Ariyalur, Mayiladuthurai, Nagapattinam, Tiruvarur, Thanjavur, Pudukottai, Sivaganga, Madurai, Virudhunagar and Ramanathapuram districts, an official release said.
+The State government has instructed Collectors of these districts to ensure that precautionary measures are taken, in view of the weather advisory. While two SDRF teams have been deputed to Thoothukudi district, one SDRF team has been positioned in Tirunelveli district.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/tamil-nadu/tamil-nadu-government-deputes-sdrf-teams-to-thoothukudi-tirunelveli-districts-over-heavy-rain-prediction/article70313909.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 15:50:01 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/vrs1f1/article70313995.ece/alternates/LANDSCAPE_1200/DSC_5810.jpg</t>
+  </si>
+  <si>
+    <t>Over 5,000 Congress workers from Jharkhand to take part in Delhi rally against 'vote chori'</t>
+  </si>
+  <si>
+    <t>Jharkhand Congress president Keshav Mahato Kamlesh on Sunday (November) said over 5,000 party workers from the State would take part in a rally next month at Ramlila Maidan in Delhi to protest against the alleged vote theft.
+He said, “They would also hold a demonstration against the Special Intensive Revision (SIR) of electoral rolls in various States.”
+The Congress on Friday (November 23, 2025) announced that it would hold 'Vote Chor Gaddi Chhod' rally on December 14 at Ramlila Maidan in the national capital to send a message across the nation against the alleged attempts to "destroy" the Constitution, a party functionary said.
+"Over 5,000 Congress workers from all divisions of Jharkhand will participate in the proposed rally. All district presidents have been asked to prepare the list of members who will take part in the rally," Mr. Kamlesh told reporters.
+He also alleged that the NDA Governments in several States were being formed by "stealing votes".
+"The Election Commission, acting on the directives of those in power, has disregarded the dignity of the entire electoral process. Therefore, to save democracy, we must keep raising the voice of the people loudly," Mr. Kamlesh claimed.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/jharkhand/over-5000-congress-workers-from-jharkhand-to-take-part-in-delhi-rally-against-vote-chori/article70313951.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 15:39:02 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/8mlk4o/article70313970.ece/alternates/LANDSCAPE_1200/PTI11_10_2025_000023B.jpg</t>
+  </si>
+  <si>
+    <t>Rathnakar reaffirms faith in Sathya Sai Baba’s continuous legacy</t>
+  </si>
+  <si>
+    <t>Managing trustee of the Sri Sathya Sai Central Trust R. J. Rathnakar said that Sri Sathya Sai Baba had personally imparted to him several valuable lessons, and narrated instances of how Sathya Sai Baba guided his destiny at every step, shaping both his life and path of service.
+Addressing a massive gathering of devotees at the centenary celebrations of Sri Sathya Sai Baba here on Sunday (November 23), Mr. Rathnakar said that Baba’s work should be publicised extensively. “Do we need to tell the world that there is light when the sun rises? When good is done, it shines on its own.” Mr. Rathnakar recalled Baba’s words, and the promise he made to his mother that he would remain in Prasanthi Nilayam and dedicate his life to spread the message of Baba.
+Reaffirming Sathya Sai Baba’s continuing presence, he said the mission remains vibrant because devotees across the world experience Baba’s guidance and protection every moment. Drawing an analogy, he recalled Baba’s teaching that just as bathing in the Ganga does not sanctify the river but purifies the individual, service through Sai institutions transforms the devotee more than the organisation itself. With this conviction, he noted, 7.5 lakh members of the Sri Sathya Sai Organisation are engaged in continuous service activities with dedication and faith.
+Mr. Rathnakar expressed gratitude to all the dignitaries who attended despite their demanding schedules, saying their presence added special significance to the centenary celebrations.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/andhra-pradesh/rathnakar-reaffirms-faith-in-sathya-sai-babas-continuous-legacy/article70313938.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 15:35:24 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/9okofz/article70313976.ece/alternates/LANDSCAPE_1200/PTI11_23_2025_000007B.jpg</t>
+  </si>
+  <si>
+    <t>Political pressures prevent SUDA from taking up ₹20 crore worth developmental activities</t>
+  </si>
+  <si>
+    <t>Srikakulam Urban Development Authority (SUDA) is unable to take up ₹20 crore worth works with the reported delay in finalisation of tenders for the provision of street lights, beautification, and others in Visakhapatnam-Amadalavalasa stretch and other places like Pathapatnam, Narasannapeta and Tekkali.
+According to sources, the public representatives and their confidants have been putting pressure on SUDA officials for sanction of works under the nomination process so that they can select the contractors on their own. Some of them sought relaxation in tender norms so that their chosen contractors would get the works from the SUDA.
+SUDA authorities feared that the delay in finalisation of tenders would lead to lapse of the funds allocated for the financial year 2025-26. They have urged senior officials of Municipal Administration to find out a solution since they were sandwiched between the pressures from local leaders and rules and regulations.
+“Many departments that don’t have funds have not taken up any developmental activity in the last one and a half years. SUDA has funds, but pressures from local public representatives prevented the organisation from taking up beautification, street lighting and other works in several Assembly segments,” said a senior official on condition of anonymity.
+A few officials of SUDA are expected to go to Amaravati to explain the situation in Srikakulam district to higher authorities. They are hopeful that the Municipal Administration senior officials might release fresh guidelines for taking up the works.
+“We are also planning to propose execution of the works with our own team from SUDA on the lines of Visakhapatnam Metropolitan Region Development Authority (VMRDA), which takes up works on its own due to its vast experience,” he added.
+The local public representatives defended themselves, saying that their opinions should be considered by SUDA since they would know the right contractors who can complete the works as per the schedule.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/andhra-pradesh/political-pressures-prevent-suda-from-taking-up-20-crore-worth-developmental-activities/article70313820.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 15:11:45 +0530</t>
+  </si>
+  <si>
+    <t>Grandeur marks Sathya Sai Baba’s centenary; Vice President, Chief Minister, TG Chief Minister pay tributes</t>
+  </si>
+  <si>
+    <t>Puttaparthi witnessed a historic spiritual gathering on Sunday as thousands assembled at the Sri Sathya Sai Hill View Stadium to celebrate the 100th birth anniversary of Sri Sathya Sai Baba.
+Vice President C. P. Radhakrishnan, Andhra Pradesh Chief Minister N. Chandrababu Naidu, Telangana Chief Minister A. Revanth Reddy and several other dignitaries participated in the global event, with speakers reflecting on the appeal of Sathya Sai Baba’s message of love and service.
+Vice President Radhakrishnan paid glowing tributes to the spiritual leader, recalling Sathya Sai Baba’s large-scale humanitarian initiatives, particularly drinking water projects that uplifted lakhs across multiple States. He fondly remembered Baba as the only saint who had visited the residence of former Tamil Nadu Chief Minister M. Karunanidhi, calling it a testament to his boundless compassion that transcended political and social barriers.
+“At a time when society is challenged by division, Baba’s teachings of love, unity and service hold greater urgency. His mission lives vibrantly here,” he said, urging devotees to honour his legacy through purposeful action rather than symbolic celebration.
+Chief Minister Chandrababu Naidu described November 23, 1926, as the divine advent of a figure who transformed millions through unconditional love. Calling Prasanthi Nilayam a “divine energy centre,” he said people from across the world were drawn to Sathya Sai Baba without any outreach, purely by the power of his message. He reiterated Baba’s universal declarations — “Love All, Serve All” and “Help Ever, Hurt Never” — and highlighted the 75th anniversary of Prasanthi Nilayam’s inauguration. Mr. Naidu lauded the immense educational, medical and drinking water projects undertaken by Sai institutions and urged devotees to carry Swami’s message across the world.
+Telangana Chief Minister Revanth Reddy said it was an honour to participate both as a devotee and as a constitutional head. He praised Sathya Sai Baba for achieving what even governments struggle to accomplish, citing free education from kindergarten to postgraduate level, life-saving medical services, and major drinking water schemes benefiting Palamuru, Anantapur, and Tamil Nadu. Though physically absent, he said, Baba’s philosophy continues to inspire lakhs of people.
+Earlier, the celebrations opened with the spectacular Swarna Rathotsavam, featuring chanting of Vedas, Nadaswaram, contingents from several countries, Bal Vikas cultural presentations and offerings from various wings of the Sai Organisation.
+Dignitaries, including the Governor of Tripura N. Indrasena Reddy, and a special message from Tamil Nadu Chief Minister M. K. Stalin, added to the solemnity of the occasion.
+The session concluded with Mangala Harathi and the National Anthem, as Prasanthi Nilayam basked in devotion, gratitude and celebration.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/andhra-pradesh/grandeur-marks-sathya-sai-babas-centenary-vice-president-chief-minister-tg-chief-minister-pay-tributes/article70313899.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 15:08:32 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/58g8dq/article70313961.ece/alternates/LANDSCAPE_1200/PTI11_23_2025_000254B.jpg</t>
+  </si>
+  <si>
+    <t>Man held for threatening BLO over dispute in filling up voter's SIR form</t>
+  </si>
+  <si>
+    <t>A man was arrested for allegedly threatening a booth-level officer (BLO) over a dispute in filling up the enumeration form of a 97-year-old voter in West Bengal's North 24 Parganas district, as part of the ongoing Special Intensive Revision (SIR) of electoral rolls in the State, police said on Sunday (November 23, 2025).
+The accused, identified as Jamirul Islam Molla, considered an active TMC worker at Nazat in Basirhat, had allegedly threatened the BLO with dire consequences after the nonagenarian's name was found missing in the voters' list of 2002, the year when the last SIR was conducted in the State, a senior officer said.
+BLO Deepak Mahato had first submitted a written complaint to the Block Development Officer and later lodged a complaint at Nazat Police Station, alleging that Molla threatened him over the phone, he said.
+"Molla was arrested on Saturday night, and a case has been registered for threatening a government official and obstructing him from performing his duties. The accused has been produced before a Basirhat court," the officer said.
+Also Read | Two BLOs die across two districts in M.P.; kin allege SIR survey work pressure
+Locals claimed that the accused is close to the TMC panchayat pradhan of the area and was also working as a booth-level agent appointed by the ruling party.
+A purported audio clip of the telephonic conversation between Molla and the BLO went viral on social media.
+Mr. Mahato also claimed that Mr. Molla repeatedly pressured him to somehow add the name of the 97-year-old voter to the electoral roll, and threatened him with vandalising his house and setting it on fire.
+The BLO claimed that he felt intimidated and feared, the officer said.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/west-bengal/man-held-for-threatening-blo-over-dispute-in-filling-up-voters-sir-form/article70313901.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 15:01:25 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/2sy3de/article70313906.ece/alternates/LANDSCAPE_1200/IMG_vbk-HANDCUFF-arrest_2_1_46C98QUC.jpg</t>
+  </si>
+  <si>
+    <t>ITBP to establish 10 all-women border outposts along India-China LAC</t>
+  </si>
+  <si>
+    <t>The Indo-Tibetan Border Police force, which guards the 3,488 km-long India-China LAC, is establishing 10 all-women border posts along this arduous and icy frontier, the director general of the paramilitary said.
+The force, as part of its ambitious "forwardisation" plan, initiated post the 2020 military clash in Ladakh, has also moved its 215 border posts forward along the front on India's north and eastern flank so far.
+Indo-Tibetan Border Police (ITBP) DG Praveen Kumar said this during the 64th Raising Day parade of the force held in Jammu on Saturday (November 22, 2025).
+"We have worked on the forwardisation plan and, as a result, the number of forward-deployed BOPs (border outposts) is now 215 as compared to 180.
+"The establishment of seven new battalions and a sector headquarters has not only strengthened this plan (forwardisation) but has also enhanced our reach and supervision of the forward areas...," the DG said.
+The Centre had sanctioned seven more battalions and a sector office comprising about 9,400 personnel for the ITBP in 2023.
+The DG said the force will establish 41 more such forward bases along the India-China Line of Actual Control (LAC) in the near future in order to "strengthen security and coordination".
+As part of enhancing the role of women combatants, the ITBP is in the process of establishing two all-women BOPs in Ladakh's Lukung and Thangi in Himachal Pradesh.
+Eight more all-women BOPs will be made operational on this front, the DG said.
+The ITBP chief said the training institutions of the force have been "reorganised" and five new skilling modules have been launched for the troops, including on subjects like mountain warfare and tactical survival.
+The ITBP, with a manpower of more than one lakh personnel, has its border posts ranging between the height of 9,000 feet and over 14,000 feet, affected by inclement weather and low levels of oxygen.
+The force, raised in 1962, functions under the command of the Union Home Ministry.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/itbp-to-establish-10-all-women-border-outposts-along-india-china-lac/article70313892.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 14:53:39 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/r7cqyn/article70313896.ece/alternates/LANDSCAPE_1200/PTI11_22_2025_000452B.jpg</t>
+  </si>
+  <si>
+    <t>Bengaluru ATM van robbery: Home Minister warns of dismissal of police personnel involved in crime</t>
+  </si>
+  <si>
+    <t>Home Minister G. Parameshwara, who on one hand congratulated the Bengaluru city police team for cracking the ATM van robbery case in record time, also bemoaned the involvement of a police constable as a prime accused in the case.
+Taking strong exception while meeting after the senior police officials, Dr. Parameshwara said police personnel involved in such criminal acts will be dismissed followed by strict legal action.
+He said that he has issued strict instructions to senior police officers to remain vigilant and ensure discipline within the department.
+Speaking to reporters after holding a review meeting with senior officials at his Sadashivanagar residence, the minister said Bengaluru Police have arrested seven accused in the ₹7.11 crore cash-van robbery case, while a few more suspects are yet to be traced.
+The minister congratulated the Commissioner, two Joint Commissioners, two DCPs and more than 200 staff members involved in the investigation.
+He said the robbery had brought disrepute to Bengaluru and posed a major challenge to the police department.
+So far, ₹6.29 crore of the stolen cash has been recovered. The remaining amount will also be traced. The accused had executed the plan with extreme caution, but the police have solved the case using advanced technical methods, he said.
+The government will also examine whether the agency handling the cash-van followed RBI guidelines, and action will be taken if violations are found.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/karnataka/bengaluru-atm-van-robbery-home-minister-warns-of-dismissal-of-police-personnel-involved-in-crime/article70313801.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 14:51:32 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/doc84b/article70313888.ece/alternates/LANDSCAPE_1200/20251007072L.jpg</t>
+  </si>
+  <si>
+    <t>Hasty SIR implementation reminiscent of demonetisation, Covid lockdown: Congress after BLO deaths</t>
+  </si>
+  <si>
+    <t>Attacking the Bharatiya Janata Party (BJP) over the death of some Booth Level Officers (BLOs) in various states, the Congress on Sunday (November 23, 2025) alleged that the workload is forcing BLOs and polling officers to end their lives, and claimed that the "hasty" implementation of SIR is reminiscent of demonetisation and the COVID-19 lockdown.
+Congress president Mallikarjun Kharge said the BJP's "vote chori" has now taken a deadly turn.
+Mr. Kharge shared on X a media report which claimed that in 19 days, there have been deaths of 16 BLOs during the Special Intensive Revision (SIR) of electoral rolls.
+The workload is forcing BLOs and polling officers to end their lives, the Congress chief said.
+"My deepest condolences to every family who has lost a loved one. Based on ground reality, this number is far higher than reported, which is extremely worrying. Who will provide justice to these families?" Mr. Kharge said in his post in Hindi.
+"The BJP is busy enjoying the fruits of stolen power, while the Election Commission of India is watching as a mute spectator," he charged.
+"The hasty, unplanned forced implementation of SIR is reminiscent of demonetisation and the COVID-19 lockdown," Mr. Kharge claimed.
+The BJP's hunger for power is driving institutions to force deaths, shredding of the Constitution, and weakening of democracy through misuse of power, he alleged.
+"Enough is enough! If we still don't wake up, no one can save the last pillars of democracy from collapsing. Those who remain silent on SIR and vote theft are responsible for the deaths of these innocent BLOs. Raise your voice, save democracy!" Mr. Kharge said.
+A woman working as a Booth Level Officer (BLO) in West Bengal's Nadia district was found dead at her residence on Saturday (November 22, 2025), with her family members claiming that she was under considerable SIR work-related stress and ended her life, police said.
+West Bengal Chief Minister Mamata Banerjee expressed shock over the BLO's death and said this has become "truly alarming now".
+The CM shared a note left behind by the deceased. In the note, the deceased held the ECI responsible for this consequence. Senior BJP leader Rahul Sinha, however, claimed that note is 'fake'.
+Also, two teachers-cum-BLOs tasked with conducting a voter list survey for SIR died of "illness" in Raisen and Damoh districts of Madhya Pradesh on Friday (November 21, 2025), officials said.
+(Suicide Prevention Helpline: Disha - 1056, 0471-2552056)</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/hasty-sir-implementation-reminiscent-of-demonetisation-covid-lockdown-congress-after-blo-deaths/article70313841.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 14:41:54 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/3deza8/article70313930.ece/alternates/LANDSCAPE_1200/PTI09_01_2025_000133B.jpg</t>
+  </si>
+  <si>
+    <t>PM Modi holds talks with South African President Ramaphosa, discusses cooperation in trade, critical minerals</t>
+  </si>
+  <si>
+    <t>Prime Minister Narendra Modi on Sunday (November 23, 2025) met South African President Cyril Ramaphosa on the sidelines of the G20 Summit in Johannesburg and the two leaders discussed cooperation in various areas, including trade, investment, mining, critical minerals, AI and food security.
+“PM @narendramodi held a warm and productive meeting with President @CyrilRamaphosa of South Africa,” Ministry of External Affairs Spokesperson Randhir Jaiswal posted on social media after the meeting.
+G20 summit LIVE updates
+He said the discussions focused on further cooperation in trade, investment, mining, critical minerals, AI, Digital Public Infrastructure, skill development and food security.
+"The leaders discussed initiating exchange of youth delegations for enhancing technology and people to people ties,” Jaiswal added.
+PM @narendramodi held a warm and productive meeting with President @CyrilRamaphosa of South Africa.
+PM congratulated President Ramaphosa &amp; South Africa for the successful presidency of @G20. Discussions focused on further cooperation in trade, investment, mining, critical… pic.twitter.com/2VBZUZ7Xhh — Randhir Jaiswal (@MEAIndia) November 23, 2025
+Mr. Modi also congratulated the South African leader on the successful presidency of the G20 summit this year.
+“PM congratulated President Ramaphosa &amp; South Africa for the successful presidency of @G20,” Jaiswal added.
+South Africa is hosting the first G20 Summit being held in Africa. The African Union became a member of the G20 during India’s presidency in 2023.
+This is PM Modi's fourth official visit to South Africa, following his bilateral visit in 2016 and later for the two BRICS summits in 2018 and 2023.
+South Africa is the largest trading partner of India in the African region. Bilateral trade between India and South Africa stood at $19.25 billion in 2023-24.
+Indian businesses have invested over $1.3 billion in South Africa from April 2000 to September 2024. These investments traverse diverse sectors, encompassing pharmaceuticals, IT, automotive, banking, and mining.
+On Saturday (November 22, 2025), upon reaching the G20 Summit venue in Johannesburg, Mr. Modi thanked South African President Cyril Ramaphosa “for the warm welcome and for organising this important Summit”.
+Addressing the opening session of the G20 Leaders’ Meeting, Modi called for a profound rethink of global development parameters and proposed the establishment of a G20 initiative to counter the drug-terror nexus and a global healthcare response team.
+Mr., Modi is visiting Johannesburg from November 21 to 23 to attend the 20th G20 Leaders' Summit.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/pm-modi-south-africa-president-cyril-ramaphosa-meeting-g20/article70313865.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 14:39:07 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/news/national/gfuywn/article70313873.ece/alternates/LANDSCAPE_1200/Modi-Ramaphosa.jpg</t>
+  </si>
+  <si>
+    <t>Seventh accused in Bengaluru ATM van robbery case arrested</t>
+  </si>
+  <si>
+    <t>The Bengaluru city police on Sunday (November 23, 2025) arrested a seventh suspect in the ₹7.11 crore cash van robbery reported on November 19.
+The accused, identified as Rakesh, was related to one of the suspects arrested earlier. He was arrested in Bengaluru late on Saturday night and further recovery is yet to be made, a police officer part of the probe team said.
+The police had earlier arrested six persons involved in the heist and recovered a total of ₹6.2 crore from them.
+Among those arrested earlier were former employees of CMS Info Systems, a man working as fleet incharge responsible for operating the cash-transport vehicles, and Annappa Naik, a police constable attached to the Govindapura police station.
+It was a combined effort of over 200 police personnel deployed to crack the case.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/cities/bangalore/seventh-accused-in-bengaluru-atm-van-robbery-case-arrested/article70313599.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 14:37:09 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/qxgz6d/article70313863.ece/alternates/LANDSCAPE_1200/DSC03447%20copy.JPG</t>
+  </si>
+  <si>
+    <t>A Bengal Vinayagar idol with snake as sacred thread in Tamil Nadu’s Nageswaran temple</t>
+  </si>
+  <si>
+    <t>On the left side of the entrance to the sanctum sanctorum of the Nageswaran Temple in Kumbakonam of Thanjavur district stands an unusual statue of Pillaiyar (Lord Vinayagar), adorned with a serpent worn as a sacred thread. Worshipped as Gangaikonda Vinayagar, the idol was brought to the Nageswaran Temple — known as Kudanathi Keezhkottam — by the Chola king Rajendra I following his conquest of Bengal.
+“The deity, depicted in a standing posture, is a creation of the Pala dynasty, which ruled in Bihar and Bengal from the eighth to the twelfth century. It is one of the many war trophies brought to Tamil Nadu by Rajendra Chola,” notes Kudavayil Balasubramanian in his book Rajendra Cholan – Victories, Capital, Temples. Stone inscriptions and literary works record the artefacts and sculptures brought by Chola kings from various countries after their conquests.
+The Vinayagar in the Nageswaran Temple, facing north, is shown with four hands: one holding a modakam (or kolukattai, a rice-based delicacy), one a broken tusk, one a strand of rudraksha beads, and one a parasu (axe). He is depicted eating the kolukattai with his tusk, while a mouse sits at his feet.
+Mr. Balasubramanian says the beauty of the idol impressed the sculptors of the Chola Kingdom, who were renowned for their expertise in bronze casting. “A sculptor cast a copy of the Pala dynasty Vinayagar in bronze. It was found buried in Muthupet in Tiruvarur district and is now on display at the Thanjavur Art Gallery,” he writes.
+Historians R. Kalaikovan and M. Nalini, who have studied the origins of Vinayagar worship in Tamil Nadu, say the earliest literary references to the deity are found in the Thevaram hymns of Thirugnanasambandar and Thirunavukkarasar.
+“Even the Poolankurichi inscriptions, believed to belong to the period of Silapathikaram and referring to temples and worship, make no mention of Vinayagar. The Saivite minstrels, who praise Lord Muruga in forty-seven places, refer to the elephant-headed God only in a few,” they write.
+They point out that the Pallavas, pioneers in the creation of rock-cut temples, did not feature Vinayagar in those structures. “A stone mandapam in Thirukazhukundram, created by Narasimhavarman, also does not include Vinayagar. But, there is a Vinayagar in the Ramanuja rock-cut temple in Mamallapuram,” they explain in their essay Pillaiya Vazhipattin Thotramum Valarchiyum (The origin and growth of Pillaiyar worship).
+Vinayagar adorns the Dharma Ratha in Mamallapuram, belonging to the period of Rajasimha. The deity is also found in temples constructed by this king. “Keezhkudavarai in Tiruchirapalli, the Kailasanatha temple in Tirupattur, and the rock-cut temple in Vallam in Chengalpattu district also feature the deity. This clearly shows that Vinayagar began to appear in temples in northern Tamil Nadu only a century after the time of Thirunavukkarasar,” they write.
+Mr. Kalaikovan and Ms. Nalini, however, believe the worship of Vinayagar originated in southern Tamil Nadu much earlier and identify the earliest sculpture as the Pillaiyar of Pillaiyarpatti. “Although Pillaiyar is today worshipped as the main deity there, the sculpture was originally created as a kosta deivam (wall shrine deity) of a rock-cut Shiva temple,” they say, noting that it likely dates to either the sixth or seventh century.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/tamil-nadu/a-bengal-vinayagar-idol-with-snake-as-sacred-thread-in-kumbakonam-nageswaran-temple/article70313795.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 14:11:07 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/news/national/tamil-nadu/v6jk5h/article70313818.ece/alternates/LANDSCAPE_1200/Stone%20idol%20of%20Bengal%20Vinayagar%20at%20Nageswaram%20temple.jpeg</t>
+  </si>
+  <si>
+    <t>Proposal on Chandigarh doesn’t alter administrative structure, no final decision yet: MHA</t>
+  </si>
+  <si>
+    <t>The Ministry of Home Affairs (MHA) stated on Sunday (November 23, 2025) that the Centre has no intention of introducing a constitutional amendment bill to bring Chandigarh under Article 240 of the Constitution.
+It said that the proposal to simplify the Central Government’s law-making process for the Union Territory of Chandigarh is still under consideration by the Central Government.”
+The MHA said, “No final decision has been made on this proposal. The proposal in no way seeks to alter Chandigarh’s governance or administrative structure, nor does it aim to change the traditional arrangements between Chandigarh and the States of Punjab or Haryana.”
+“A suitable decision will be made only after adequate consultations with all stakeholders, keeping in mind the interests of Chandigarh. There is no need for concern regarding this matter. The Central Government has no intention of introducing any bill to this effect in the upcoming Winter Session of Parliament,” the Home Ministry further stated.
+The Constitution (131 Amendment) Bill 2025 seeks to include the Union Territory of Chandigarh in Article 240 of the Constitution of India, aligning it with other Union Territories without legislatures, such as the Andaman and Nicobar Islands, Lakshadweep, Dadra and Nagar Haveli and Daman and Diu, and Puducherry (when its Legislative Assembly is dissolved or suspended).
+“Chandigarh is the joint capital of Haryana and Punjab. Currently, the Governor of Punjab is concurrently the Administrator of Chandigarh, and if the bill is passed, the Union Territory will be governed by a Lieutenant Governor.”
+According to a bulletin of the Lok Sabha and the Rajya Sabha, the Centre has proposed to include the Union Territory (UT) of Chandigarh under the ambit of Article 240 of the Constitution, which empowers the President to make regulations for the UT and legislate directly.
+This could pave the way for the appointment of an independent administrator in Chandigarh, similar to when it had an independent Chief Secretary in the past, a move that evoked sharp reactions from the Congress, the Akali Dal and the AAP.
+(with PTI inputs)</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/proposal-on-chandigarh-doesnt-alter-administrative-structure-no-final-decision-yet-mha/article70313800.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 14:03:37 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/news/national/nhvj9z/article70313817.ece/alternates/LANDSCAPE_1200/AmitShah.jpg</t>
+  </si>
+  <si>
+    <t>Four pilgrims from Madhya Pradesh killed in road accident</t>
+  </si>
+  <si>
+    <t>As many as four pilgrims from Madhya Pradesh were killed in a fatal road accident that occurred near Etturallupadu of Kotabommali mandal of Srikakulam district on Sunday (November 23, 2025).
+According to the police, the van in which they were travelling hit a stationary lorry, leading to the ghastly incident. The police officials shifted the bodies to the Kotabommali hospital and informed their family members about the incident.
+The deceased were identified as Singh Pawar (60), Kushal Singh (62), Vijay Singh Tomar (64) and Santoshi Bhai (62).
+The passengers had darshan of important temples located in Madhya Pradesh and Odisha before leaving for darshan of temples such as Simhachalam, Srisailam and others in Andhra Pradesh. The police personnel registered a case against the lorry driver who had parked the vehicle on the road.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/andhra-pradesh/four-pilgrims-from-madhya-pradesh-killed-in-road-accident/article70313643.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 14:02:56 +0530</t>
+  </si>
+  <si>
+    <t>TVK chief Vijay accuses DMK of abandoning Annadurai’s ideals</t>
+  </si>
+  <si>
+    <t>Tamilaga Vettri Kazhagam (TVK) president Vijay, on Sunday (November 23, 2025), alleged the Dravida Munnetra Kazhagam (DMK) has forgotten the principles and ideals of its party founder C.N. Annadurai. He accused the ruling party of making “looting as its principle” and speaking about ideologies while burying them in practice.
+The actor-turned-politician was addressing party supporters from Kancheepuram district at a limited-access, indoor meeting at a private college in Sunguvarchathiram which marked the first public engagement of Mr. Vijay nearly two months after 41 persons died in a stampede at a political rally he addressed at Karur.
+The TVK leader said: “Kancheepuram is the birthplace of Anna [C.N. Annadurai]. When MGR [M.G. Ramachandran] founded his party [the AIADMK], he chose to feature Anna’s face on the party flag, as Anna had been his guiding light. But those who later captured the party founded by Anna have acted in ways that need no explanation. The people of Tamil Nadu know what has been happening.”
+He added, “Personally, we [TVK] have no problem with them [DMK]. They may hate me, but we do not hate them. But they cheated us to come to power and then pretended to do good. How can we remain silent without questioning them? We will not stop questioning them.”
+Recalling he had begun his first public outreach in support of farmers opposing the proposed greenfield airport at Parandur, he said, “After a period of great turmoil, our public outreach programme has resumed, and it begins again in Kancheepuram. We are following the path shown by Anna, who said Makkalidam Sel (reach out to the people). But those who run the party today have deviated from Anna’s principles.”
+He strongly objected to DMK functionaries calling the TVK a party without principles. “For a party that declared Pirapokkum Ella Uyrikkum (all beings are equal by birth), how can they say we have no principles? We opposed the CAA even before our party was formed. We have been advocating for a caste census to ensure social justice for everyone. We were the first to approach the Supreme Court against the Waqf (Amendment) Act,” he said.
+Problems plaguing Kancheepuram
+Speaking about issues in Kancheepuram district, Mr. Vijay said the Palar river had deteriorated because of illegal sand mining. A total of 22.7 lakh units of sand had been illegally mined, causing a loss of ₹4,730 crore. The weavers of world-renowned Kancheepuram silk continued to live in poverty, and the Tamil Nadu government had taken no measures to renovate the old bus stand in the town, he said, reiterating that his party would continue to stand with the farmers over the Parandur airport issue.
+“I have entered politics only to do good for the people. I have no other motive,” he claimed, adding, “that is why we have clearly declared our ideological and political enemies, and we stand opposed to them.”
+Mr. Vijay also objected to his party supporters being called tharkuri (nincompoop). “We are not tharkuri. We are acharyakuri (exclamation mark) and maatrathirkaana arikuri (a sign of change) in Tamil Nadu politics,” he believed.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/tamil-nadu/tvk-chief-vijay-accuses-dmk-of-abandoning-annadurais-ideals/article70313759.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 13:46:50 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/news/national/tamil-nadu/va3wao/article70313788.ece/alternates/LANDSCAPE_1200/TVK%20leader%20Vijay%20at%20Sunguvarchathiram%20Kancheepuram%20Nov%2023%202025.jpeg</t>
+  </si>
+  <si>
+    <t>AIADMK general council, executive committee to meet on December 10</t>
+  </si>
+  <si>
+    <t>The All India Anna Dravida Munnetra Kazhagam’s (AIADMK) general council and executive committee meetings will be held at Vanagaram near Chennai on December 10, 2025 (Wednesday).
+AIADMK presidium chairman A. Tamilmagan Hussain will chair the meeting, the party’s general secretary Edappadi K. Palaniswami said in a statement.
+The meeting assumes significance in the backdrop of key developments in the recent past including the expulsion of senior leader and Gobichettipalayam MLA K.A. Sengottiayan from the party.
+Strategies for the 2026 Assembly polls, including the electoral alliance, ways to strengthen the party are among the issues over which discussions are expected in the meeting.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/tamil-nadu/aiadmk-general-council-executive-committee-meeting-on-december-10-2025/article70313680.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 13:21:33 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/5672xa/article70313772.ece/alternates/LANDSCAPE_1200/KIKKM_28-4-2016_18-34-23_ELECTION_2.JPG</t>
+  </si>
+  <si>
+    <t>Gelatin sticks found near school in Uttarakhand’s Almora, investigation underway</t>
+  </si>
+  <si>
+    <t>About 160 gelatin sticks were found hidden in bushes near a school in ​​Almora district of Uttarakhand, police said on Sunday (November 23, 2025).
+“Preliminary investigations have ruled out any terrorist links, and it appears that the explosives were left behind by a contractor during construction of a road,” Almora Senior Superintendent of Police Devendra Pincha said.
+The incident came to light on November 21, when Subhash Singh, acting principal of the Government Higher Secondary School, Dabhra, located in the Salt area, spotted some suspicious packages in the bushes near the campus and informed the police.
+Upon receiving the information, police arrived at the scene and cordoned off the entire area. Subsequently, Bomb Detection and Disposal Squad (BDDS) and Dog Squads from Udham Singh Nagar and Nainital districts were called to the scene, assisting them in conducting a thorough search of the area.
+A few packets of gelatin sticks were first recovered from a location near the school, followed by several more packets about 15–20 feet away, police said, adding that a total of 161 cylindrical gelatin sticks were recovered from both locations.
+“The Bomb Squad transported all the packets to a safe location and sealed them,” police said. “The entire operation was videotaped and evidence was collected,” they added.
+A case has been registered against unknown individuals under Section 4(a) of the Explosive Substances Act, 1908, and Section 288 of the Bharatiya Nyaya Sanhita.
+The gelatin sticks are used by contractors to break stones and rock formations during road construction, Mr. Pincha said, adding that the police are conducting extensive inquiries with contractors and labourers in the area.
+Mr. Pincha said, "The road was constructed at this location a few years ago, and the contractor may have left the gelatin sticks in the bushes." However, he clarified that a conclusion can only be reached after a thorough investigation.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/uttarakhand/gelatin-sticks-found-near-school-in-uttarakhands-almora-investigation-underway/article70313748.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 13:19:23 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/aapx00/article70313771.ece/alternates/LANDSCAPE_1200/PTI11_23_2025_000122B.jpg</t>
+  </si>
+  <si>
+    <t>White collar terror module: Haryana preacher pleads with police to collect rent from doctors</t>
+  </si>
+  <si>
+    <t>The atmosphere in the police interrogation room at Srinagar is tense, but a Haryana preacher detained in connection with a 'white-collar’ terror module remains focused on unpaid rent from arrested doctors.
+Maulvi Ishtiyaq, the religious preacher from Mewat in Haryana, was picked up by Jammu and Kashmir Police after the recovery of 2,500 kg of explosive material, including ammonium nitrate, potassium chlorate, and sulphur, from his rented residence located outside Faridabad's Al Falah University, which has emerged as the epicentre of the terror module.
+His name surfaced during the interrogation of Dr. Muzammil Ganaie, a key member of the 'white-collar' terror module arrested from the University. At his instance, the police team recovered explosives from the residence of the preacher.
+This white-collar module was busted on November 10 after an intense investigation by Srinagar police and led to the arrest of eight persons, including three doctors. But one, Dr. Umar-un-Nabi, had managed to give a slip and was driving the explosive-laden car that blasted outside Red Fort, killing 15 people on November 10.
+Maulvi Ishtiyaq told his interrogators a shockingly different story, claiming that Ganaie and Umar approached him earlier this year, asking him to store what they called "fertilisers" at his home and allegedly agreed upon a monthly storage fee of ₹2,500, according to officials.
+Maulvi Ishtiyaq was not concerned about the gravity of the situation and his concern was about the outstanding rent owed by Ganaie and Umar which was pending for the last six months, they said.
+Living below the poverty line and struggling to support his four children and family, the religious preacher told the officials of the National Investigation Agency, Srinagar Police and others from central security agencies to recover the outstanding rent from Ganaie so that he could send the money back home.
+The officials recalled that the disparity between the heinous crime of storing enough material for a massive terror attack and the detainee's immediate, desperate concern for the rent payment was enough to briefly break the tension in the interrogation room.
+The incident provides a bizarre and tragicomic look into the lives entangled on the fringes of major terror plots, said a senior police official.
+His story was supported by Ganaie during interrogation, the officials said, adding Maulvi Ishtiyaq has been handed over to the State Investigation Agency for further action.
+The preacher was detained on November 12 after a series of raids conducted by Jammu and Kashmir police along with their Haryana counterparts.
+Jammu and Kashmir police on November 10 along with their counterparts in Haryana and Uttar Pradesh carried out the operation to unravel a 'white-collar' terror network of banned Jaish-e-Mohammed (JeM) and Ansar Ghazwat-ul-Hind and arrested eight people.
+Investigations led to the Al Falah University where 2,900 kg of explosives was recovered.
+It all started on the intervening night of October 18-19, when posters of the banned JeM surfaced on walls just outside Srinagar city. The posters warned of attacks on police and security forces in the Valley.
+Three people — Arif Nisar Dar alias Sahil, Yasir-ul-Ashraf and Maqsood Ahmad Dar alias Shahid — were arrested after CCTV footage showed them pasting the posters.
+During interrogation, they named former paramedic turned preacher Maulvi Irfanas the one who had supplied the posters. He was arrested.
+This was the thread that led to the unravelling of the plot. Ganaie and Dr Shaheen Saeed were held from Faridabad. Later, Adeel Rather was picked up from Saharanpur in Uttar Pradesh.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/white-collar-terror-module-haryana-preacher-pleads-with-police-to-collect-rent-from-doctors/article70313747.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 13:09:15 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/5kch7u/article70313764.ece/alternates/LANDSCAPE_1200/PTI11_22_2025_000118B.jpg</t>
+  </si>
+  <si>
+    <t>Tamil Nadu government announces police honours for poet Erode Tamilanban's funeral</t>
+  </si>
+  <si>
+    <t>The Tamil Nadu government, on Sunday (November 23, 2025), announced that police honours would be accorded during the funeral of poet and Sahitya Akademi award-winner Erode Tamilanban who passed away at the age of 92 on Saturday.
+Chief Minister M.K. Stalin has issued directions for according police honours to the scholar's funeral, to honour his immense contributions to the Tamil language in various forms throughout his long life, an official release said.
+Born N. Jagadeesan at Chennimalai in Erode district, Tamilanban was part of the Vanambadi poetry movement launched in the 1970s, which is regarded as an extension of a long tradition of Tamil poetry and is credited with ushering in a renaissance in Tamil literary expression.
+A Tamil teacher at New College, Chennai, he was also a newsreader with Doordarshan, and was known for his flawless pronunciation and intonation.
+He won the Sahitya Akademi Award in 2004 for Vanakkam Valluva, a collection of poems based on the Tirukkural. Tamilanban had said in a media interview that the poems were intended to seek clarifications from Tiruvalluvar himself.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/tamil-nadu/tamil-nadu-government-announces-police-honours-for-poet-erode-tamilanbans-funeral/article70313682.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 13:06:00 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/46ruo5/article70313756.ece/alternates/LANDSCAPE_1200/PTI11_6_2017_000084A.JPEG-0edb1.jpg</t>
+  </si>
+  <si>
+    <t>SC to hear on November 24 plea challenging climate activist Sonam Wangchuk's detention</t>
+  </si>
+  <si>
+    <t>The Supreme Court is scheduled to hear on Monday (November 24, 2025) a plea filed by Sonam Wangchuk's wife which termed the climate activist's detention under the stringent National Security Act as illegal and an arbitrary exercise violating his fundamental rights.
+The top court had on October 29 sought response of the Centre and the Ladakh administration on the amended plea of Mr. Wangchuk's wife Gitanjali J. Angmo.
+As per the apex court's cause list of November 24, the plea is slated to come up for hearing before a Bench of Justices Aravind Kumar and N.V. Anjaria.
+Mr. Wangchuk was detained under the National Security Act (NSA) on September 26, two days after violent protests demanding statehood and Sixth Schedule status for Ladakh left four people dead and 90 injured in the Union Territory. The government had accused him of inciting the violence.
+The amended plea has said, "The detention order is founded upon stale FIRs, vague imputations, and speculative assertions, lacks any live or proximate connection to the purported grounds of detention and is thus devoid of any legal or factual justification".
+"Such arbitrary exercise of preventive powers amounts to a gross abuse of authority, striking at the core of constitutional liberties and due process, rendering the detention order liable to be vitiated by this court," it said.
+The plea said it is wholly preposterous that after over three decades of being recognized at the state, national, and international levels for his contributions to grassroots education, innovation, and environmental conservation in Ladakh and across India, Mr. Wangchuk would suddenly be targeted.
+"Merely two months before the elections and the final rounds of dialogue between ABL (Apex Body of Leh), KDA (Kargil Democratic Alliance), and the Ministry of Home Affairs, he was served with notices for land lease cancellation, FCRA cancellation, initiation of a CBI investigation, and summons from the Income Tax Department," it said.
+The plea claimed these coordinated actions, taken in close temporal proximity, make it prima facie evident that the order of detention is not based on genuine concerns of public order or security but is instead a calculated attempt to silence a respected citizen exercising his democratic and constitutional right to dissent.
+The plea said the unfortunate events of violence in Leh on September 24 cannot be attributed to the actions or statements of Mr. Wangchuk in any manner.
+It said Mr. Wangchuk himself condemned the violence through his social media handles and categorically stated that violence would lead to the failure of Ladakh's "tapasya" and peaceful pursuit of five years and stated that "it is the saddest day of his life".
+It further stated that complete grounds of detention were only supplied to Mr. Wangchuk after a flagrant delay of 28 days, which is in clear violation of the statutory timeline prescribed under section 8 of the NSA.
+The plea said under section 8 of the NSA the detaining authority shall as soon as may be, but ordinarily not later than five days and, in exceptional circumstances and for reasons to be recorded in writing, not later than ten days, communicate to the detenu the complete grounds of detention.
+The NSA empowers the Centre and states to detain individuals to prevent them from acting in a manner "prejudicial to the defence of India". The maximum detention period is 12 months, though it can be revoked earlier.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/sc-to-hear-on-november-24-plea-challenging-climate-activist-sonam-wangchuks-detention/article70313745.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 13:00:31 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/6wmbsl/article70313753.ece/alternates/LANDSCAPE_1200/PTI08_05_2025_000300B.jpg</t>
+  </si>
+  <si>
+    <t>After Akhilesh's charge on voter deletions, Maurya predicts Opposition setbacks in Bengal, U.P.</t>
+  </si>
+  <si>
+    <t>A day after Samajwadi Party (SP) chief Akhilesh Yadav accused the BJP government and the Election Commission of plotting to remove voters from select constituencies, Uttar Pradesh Deputy Chief Minister Keshav Prasad Maurya suggested that the next electoral setbacks for the Opposition would come in West Bengal and Uttar Pradesh.
+Taking to X on Sunday, Mr. Maurya posted, "During the Bihar elections, with Rahul Gandhi diving in and dragging Tejashwi Yadav along, the fate of the Mahagathbandhan was sealed."
+Mr. Maurya, who served as the BJP's co-incharge for the Bihar Assembly polls, added, "The next number is that of Mamata Didi (West Bengal Chief Minister Mamata Banerjee) and then SP's brave Akhilesh Yadav."
+In the recent Bihar Assembly elections, the BJP-led National Democratic Alliance (NDA) secured a two-thirds majority, leaving the INDIA bloc far behind.
+Akhilesh had alleged on Saturday (November 23, 2025) that the BJP and the Election Commission were conspiring to delete more than 50,000 votes in assembly segments where the SP and the INDIA bloc had won during the 2024 Lok Sabha polls.
+He claimed the Special Intensive Revision (SIR) of voter lists was being misused for this purpose.
+Akhilesh said, "We expect the Election Commission to remain impartial and address our complaints. But we are hearing that after losing in 2024, the BJP and the commission are focusing heavily on West Bengal and Uttar Pradesh."
+He further alleged that the SP had received information that major "preparations" were underway jointly by the BJP and the Election Commission in both States.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/uttar-pradesh/after-akhileshs-charge-on-voter-deletions-maurya-predicts-opposition-setbacks-in-bengal-up/article70313744.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 12:57:19 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/ekn6us/article70313754.ece/alternates/LANDSCAPE_1200/PTI04_15_2024_RPT236B.jpg</t>
+  </si>
+  <si>
+    <t>Justice Surya Kant to take oath as 53rd Chief Justice of India on November 24</t>
+  </si>
+  <si>
+    <t>Justice Surya Kant, who has been part of several landmark verdicts and orders on abrogation of Article 370 removing Jammu and Kashmir's special status, Bihar electoral rolls revision and Pegasus spyware case, will on Monday (November 24, 2025) take oath as the 53rd Chief Justice of India.
+He will succeed Justice B.R. Gavai, who demits office this evening.
+Justice Kant was appointed as the next CJI on October 30 and will remain in the post for nearly 15 months. He will demit office on February 9, 2027 on attaining the age of 65 years.
+Born on February 10, 1962 in Hisar district of Haryana to a middle-class family, Justice Kant went from being a small-town lawyer to the country’s highest judicial office, where he has been part of several verdicts and orders of national importance and constitutional matters. He also has the distinction of standing 'first class first' in his Master’s degree in law in 2011 from Kurukshetra University.
+Justice Kant, who penned several notable judgments in the Punjab and Haryana HC, was appointed the chief justice of Himachal Pradesh HC on October 5, 2018.
+His tenure as an SC judge is marked by verdicts on the abrogation of Article 370, free speech and citizenship rights.
+The judge was part of the recent presidential reference on the powers of the Governor and President in dealing with bills passed by a state assembly. The verdict is keenly awaited with potential ramifications across states.
+He was part of the bench that kept the colonial-era sedition law in abeyance, directing that no new FIRs be registered under it until a government review.
+Justice Kant also nudged the Election Commission to disclose the details of 65 lakh voters excluded from the draft electoral rolls in Bihar while hearing a batch of petitions challenging the poll panel’s decision to undertake Special Intensive Revision (SIR) of the voters list in the poll-bound state.
+In an order that emphasised grassroots democracy and gender justice, he led a bench that reinstated a woman sarpanch unlawfully removed from office and called out the gender bias in the matter.
+He is also credited with directing that one-third of seats in bar associations, including the Supreme Court Bar Association, be reserved for women.
+Justice Kant was part of the bench that appointed a five-member committee headed by former top court judge Justice Indu Malhotra to probe the security breach during Prime Minister Narendra Modi’s visit to Punjab in 2022, saying such matters required “a judicially trained mind”.
+He also upheld the One Rank-One Pension scheme for defence forces, calling it constitutionally valid, and continues to hear petitions of women officers in the armed forces seeking parity in permanent commission.
+Justice Kant was on the seven-judge bench that overruled the 1967 Aligarh Muslim University judgment, opening the way for reconsideration of the institution's minority status.
+He was also part of the Bench which heard the Pegasus spyware case and which appointed a panel of cyber experts to probe allegations of unlawful surveillance, famously stating that the state cannot get a "free pass under the guise of national security".</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/justice-surya-kant-to-take-oath-as-53rd-chief-justice-of-india-on-november-24/article70313733.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 12:40:29 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/yr6dc2/article70313742.ece/alternates/LANDSCAPE_1200/20251030319L.jpg</t>
+  </si>
+  <si>
+    <t>Kejriwal, Harsimrat oppose bill allowing President to make legislation for Chandigarh directly</t>
+  </si>
+  <si>
+    <t>AAP supremo Arvind Kejriwal and SAD leader Harsimrat Kaur Badal on Sunday (November 23, 2025) strongly opposed a Constitution Amendment bill set to be introduced in Parliament to include Chandigarh under Article 240, empowering the President to make regulations for the Union territory and legislate directly.
+The Centre will bring the Constitution (131st Amendment) Bill, 2025, in the upcoming Winter session of Parliament, beginning December 1, according to a Lok Sabha and Rajya Sabha bulletin.
+If the bill is passed, Chandigarh could have an independent administrator, similar to having had an independent chief secretary in the past. Chandigarh serves as the joint capital of Punjab and Haryana.
+This proposed amendment has sparked political outrage in Punjab, with the ruling AAP, Congress, and Shiromani Akali Dal (SAD) criticising the BJP-led Centre, accusing the government of attempting to "snatch" Chandigarh from Punjab.
+Aam Aadmi Party (AAP) national convener Arvind Kejriwal vehemently opposed the Centre's proposed move, calling it a "direct attack" on Punjab's identity and constitutional rights.
+"The BJP-led central government's attempt to eliminate Punjab's rights over Chandigarh through constitutional amendment is not part of a simple move, but a direct attack on Punjab's identity and constitutional rights. This mentality of undermining the federal structure and depriving Punjabis of their rights is extremely dangerous," Mr. Kejriwal said in a post on X.
+"Punjab, which has always sacrificed for the nation's security, food, water, and humanity, is today being deprived of its own share. This is not just an administrative decision, but akin to wounding the soul of Punjab.
+"History bears witness that Punjabis have never bowed before any dictatorship. Punjab will not bow even today. Chandigarh belongs to Punjab and will remain with Punjab," he further said.
+Shiromani Akali Dal (SAD) MP and former Union Minister Harsimrat Kaur Badal said that with this move, Punjab will lose its rights over Chandigarh.
+"The Shiromani Akali Dal strongly opposes the proposed Constitution (131st Amendment) Bill being brought by the Central Government in this winter session. With this amendment, Chandigarh will be converted into a state, and Punjab will completely lose its right over Chandigarh," she said.
+Ms. Badal described the proposal as a significant blow to Punjab, noting that the Congress party had initially taken Chandigarh from Punjab and asserting that the decision to make it a separate state would not be accepted.
+"This amendment bill is a robbery of the rights of Punjab and also a violation of the principles of federal structure. The Shiromani Akali Dal will not allow this to happen and will strongly oppose it in this session," she said.
+The SAD has called an emergency meeting of its core committee on November 24 to discuss this issue. SAD leader Daljit Singh Cheema said the meeting, to be chaired by SAD President Sukhbir Singh Badal, will chart out the next steps.
+Senior constitutional experts will be consulted to finalise a strong strategy to counter the Centre's move, he added.
+Congress MLA Pargat Singh said that the Centre's latest endeavour aims to "completely snatch" Chandigarh from Punjab and transform it into a separate Union territory. He described this action as "an act of sheer aggression that Punjab will never accept."
+"I urge Chief Minister Bhagwant Mann to strongly oppose this anti-Punjab move in Monday's Assembly session and pass a resolution against it. An all-party meeting must be convened so that Punjab can stand united, go to Delhi before the Parliament session, stage a protest against this unconstitutional assault, and meet the president with an all-party delegation to formally register Punjab's objection," said Mr. Singh.
+Currently, the Punjab governor serves as the Administrator of the UT of Chandigarh. It was previously administered independently by a chief secretary since November 1, 1966, when Punjab was reorganised.
+However, since June 1, 1984, Chandigarh has been administered by the Punjab governor and the chief secretary's position was converted to an adviser to the UT administrator.
+In August 2016, the Centre sought to restore the old practice of having an independent administrator by appointing former IAS officer K J Alphons for the top post.
+However, the move was withdrawn after stiff opposition from the then-Punjab chief minister, Parkash Singh Badal, who was part of the NDA, and other parties, including the Congress and AAP.
+Punjab, which has staked its claim on Chandigarh, also wants the immediate transfer of Chandigarh to it. The chief minister has reiterated this demand during a recent meeting of the Northern Zonal Council held in Faridabad.</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/news/national/punjab/kejriwal-harsimrat-oppose-bill-allowing-president-to-make-legislation-for-chandigarh-directly/article70313726.ece</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 12:37:20 +0530</t>
+  </si>
+  <si>
+    <t>https://th-i.thgim.com/public/incoming/c4hd7s/article70313737.ece/alternates/LANDSCAPE_1200/PTI10_04_2025_000401A.jpg</t>
   </si>
   <si>
     <t>Fire breaks out at district hospital in M.P.'s Betul; patients shifted to safety</t>
@@ -99,7 +739,7 @@
     <t>Sun, 23 Nov 2025 11:43:17 +0530</t>
   </si>
   <si>
-    <t>https://th-i.thgim.com/public/news/national/tamil-nadu/iynuld/article70313669.ece/alternates/LANDSCAPE_1200/Cuddalore%20ganja%20accused%20shot%20by%20police%20Nov%2023%202025.jpeg</t>
+    <t>https://th-i.thgim.com/public/news/national/tamil-nadu/u0avhm/article70313746.ece/alternates/LANDSCAPE_1200/Cuddalore%20ganja%20accused%20Naveen%20shot%20by%20police%20Nov%2023%202025.jpeg</t>
   </si>
   <si>
     <t>Delhi air quality remains 'very poor', AQI stands at 381</t>
@@ -122,11 +762,12 @@
     <t>https://th-i.thgim.com/public/incoming/lmqzmu/article70313628.ece/alternates/LANDSCAPE_1200/TH22-Nikhil-CAQGMNF733G5.3.jpg.jpg</t>
   </si>
   <si>
-    <t>Tejas crash at Dubai Air Show: Tributes paid to Wing Commander Namansh Syal at Air Force Station Sulur</t>
+    <t>Tejas crash at Dubai Air Show: Tributes paid to Wing Commander Namansh Syal at Sulur Air Force Station</t>
   </si>
   <si>
     <t>Mortal remains of Wing Commander Namansh Syal, who tragically lost his life in a Tejas aircraft crash during the Dubai Air Show, was brought to the Air Force Station, Sulur near Coimbatore on Sunday (November 23, 2025) morning.
 The Wing Commander was attached to IAF's No. 45 Squadron (Flying Daggers) based at Air Force Station, Sulur, one of the two Squadrons operating Light Compact Aircraft (LCA) HAL Tejas.
+Officials paid homage to the mortal remains of Wing Commander Namansh Syal at Sulur Air Force Station in #Coimbatore, Tamil Nadu, on Sunday. He tragically lost his life in a Tejas aircraft crash during the #DubaiAirshow 2025. @the_hindu@THChennaipic.twitter.com/nSAYPeKRg2 — Periasamy M (@peri_periasamy) November 23, 2025
 Sources said the mortal remains were brought to the IAF Hospital, Coimbatore, late on Saturday (November 22, 2025) and kept at the mortuary. The mortal remains were brought to Air Force Station, Sulur, around 7 a.m. on Sunday (November 23, 2025) and was placed on the tarmac, the home turf of the Wing Commander.
 IAF officials, Coimbatore district Collector Pavankumar G. Giriyappanavar, and Coimbatore district Superintendent of Police K. Karthikeyan paid their respects to the deceased fighter pilot.
 Sources added the mortal remains were flown to Himachal Pradesh, the deceased officer's home State on an IAF aircraft, after the homage, for the last rites.</t>
@@ -578,532 +1219,467 @@
     <t>https://th-i.thgim.com/public/incoming/o3xhru/article70312339.ece/alternates/LANDSCAPE_1200/PTI10_17_2025_000234B.jpg</t>
   </si>
   <si>
-    <t>Experts call for strengthening wetland monitoring</t>
-  </si>
-  <si>
-    <t>An expert panel discussion held as part of the Tropical BioSummit 2025 at the Kerala University of Fisheries and Ocean Studies (Kufos) here on Friday recommended the setting up of long-term monitoring programmes for wetlands across India using high-end tools, including automated data loggers, bathymetry platforms, and satellite-based remote sensing.
-The panel recommended developing interdisciplinary monitoring frameworks incorporating hydrology, biodiversity, pollution science, fisheries, ecosystem services, and socio-economic factors, according to a communication.
-The other recommendations include conducting systematic assessments of biological productivity, fisheries resources, and trophic structure in wetlands to inform sustainable harvest regulations and developing wetland-specific fishery management plans using habitat modelling, ecological carrying capacity analysis, and species recovery strategies. Experts also suggested formulating individual restoration plans for each wetland, acknowledging that hydrology, biodiversity, and socio-ecological dynamics vary across systems, it said.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/kerala/experts-call-for-strengthening-wetland-monitoring/article70311430.ece</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 02:13:37 +0530</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/theme/images/og-image.png</t>
-  </si>
-  <si>
-    <t>Are e-KYC norms excluding MGNREGA workers? | Explained</t>
-  </si>
-  <si>
-    <t>The story so far: The Mahatma Gandhi National Rural Employment Guarantee Act (MNREGA) covers 26 crore registered workers across 2.69 lakh gram panchayats. Over the last six months, about 15 lakh workers were deleted. But in just one month, between October 10 and November 14 this year, they shot up to 27 lakh — nearly double the six-month total. This far exceeds the 10.5 lakh additions during the same period. The spike in deletions coincides with the Union government’s push to conduct e-KYC (know your customer) verification of workers, to weed out ineligible workers.
-What are the government’s reasons?
-The Union Ministry of Rural Development in a statement on Friday said that verification of MGNREGA workers is a continuous process. The e-KYC is another step towards this. “It will strengthen transparency, efficiency, and ease of service delivery under MGNREGA,” the statement said. As per the statement, till date over 56% of active workers have completed their e-KYC verification across States.
-How were workers verified before?
-From time-to-time, the government has introduced several means of verification to ensure that no ineligible person draws any benefits from MNREGA. To this end the government, after running a pilot for nearly a year, from May 2022, made it mandatory that the attendance of workers is captured digitally using a mobile based application —the National Mobile Monitoring System (NMMS). The government directed that the mate or supervisor on each MNREGA worksite should click and upload geotagged pictures of the workers twice a day. In January 2023, the government made the Aadhaar Based Payment System (ABPS) mandatory. The ABPS uses the worker’s unique 12-digit Aadhaar number as their financial address. For the ABPS to work, a worker’s Aadhaar details must be seeded to her job card and her bank account. The worker’s Aadhaar must also be mapped with the National Payments Corporation of India (NPCI) database. Moreover, the bank’s Institutional Identification Number (IIN) must itself be mapped with the NPCI database.
-How does e-KYC work?
-As stated above, the attendance of MNREGA workers has been marked on the NMMS since May 2022 on all worksites. This application also has an e-KYC feature, whereby the mate or supervisor clicks a picture of the worker which is verified against the worker’s picture in the Aadhaar database.
-Is there any correlation between the e-KYC drive and deletion of MNREGA workers?
-This is not the first time that there is a surge in the deletion of MNREGA workers. Both the introduction of the NMMS and ABPS were aimed at bringing greater transparency but also contributed to exclusion. In the case of NMMS, there have been recurrent complaints of patchy network connectivity, especially in remote areas and little to no technological know-how among the workers. There have been complaints that work could not be recorded because of these issues which led to loss of wages.
-Aadhaar seeding of job cards is the foundational step towards ABPS. But this has thrown several challenges. Often the demographic details of Aadhaar have been found to be different from that of the job card. In many cases it was found that a change in a letter here or there, between the way the name is spelled out in the two documents, led to workers’ exclusion. Deletions rose by 247% between 2021-22 and 2022-23 during the roll out of the ABPS.
-NMMS has also failed in achieving its intended goal of “transparency.” It was discovered that irrelevant or unrelated photographs were being uploaded. In many cases, “photo-to-photo capturing instead of live work images” was being done. There was also “mismatch in actual versus recorded count.” In July this year, the Ministry issued a circular directing States to ensure that photographs and attendance of workers are verified at the gram panchayat, block, district and State level. The circular introduced a system wherein the percentage of physical verification of the uploaded photographs of workers would reduce at different levels. At the gram panchayat level, there would be 100% verification of the present workers. At block level, 20% of photos at random would need to be verified, at district level this number comes down to 10% and at the State level 5%. One of the reasons to introduce e-KYC for workers was the failure of the NMMS.
-The government has refuted the claim that e-KYC has led to deletions. The Ministry said that a detailed Standard Operating Procedure (SOP) was issued in January this year on deletion of job cards/workers. “This SOP provides clear, uniform, and transparent guidelines for States to follow, ensuring fairness, accountability, and protection of workers’ interests in the management of job card records. Adequate safeguards have been made part of the SOP to prevent arbitrary/wrongful deletion,” the ministry said. These safeguards include publication of the names of workers who are intended to be deleted from the system, and giving them adequate time to file appeals. However, the government failed to explain why States with high e-KYC completion rates are leading in deletions. Andhra Pradesh, where 78.4% of workers have completed e-KYC, recorded 15.92 lakh deletions. Tamil Nadu (67.6%) saw 30,529 deletions, and Chhattisgarh (66.6%) reported 1.04 lakh.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/are-e-kyc-norms-excluding-mgnrega-workers-explained/article70312189.ece</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 01:51:00 +0530</t>
-  </si>
-  <si>
-    <t>https://th-i.thgim.com/public/incoming/839h3x/article70312545.ece/alternates/LANDSCAPE_1200/Workers-unionsG38F33UA4.3.jpg.jpg</t>
-  </si>
-  <si>
-    <t>What is the Mekedatu dam project dispute? | Explained</t>
-  </si>
-  <si>
-    <t>The story so far: On November 18, the Karnataka government decided that it would submit a “revised” Detailed Project Report (DPR) to the Centre on the Mekedatu balancing reservoir across the inter-State river Cauvery. Five days earlier, the Supreme Court termed as “premature” the application of Tamil Nadu challenging the project proposed by Karnataka. With this development, the decks have been cleared for the Cauvery Water Management Authority (CWMA) and the Central Water Commission (CWC) to examine the upper riparian State’s proposal.
-How has Tamil Nadu reacted?
-While the Opposition in Tamil Nadu has blamed the Dravida Munnetra Kazhagam government for the top Court’s ruling, the lower riparian State’s Water Resources Minister Durai Murugan rebutted reports of the Court having permitted the construction of the dam and asserted that his government would resist Karnataka’s every attempt to proceed with the project. Karnataka Deputy Chief Minister D.K. Shivakumar called the Court’s order “justice to the State.”
-What are the main features of the project?
-Karnataka is planning to build a ₹9,000-crore balancing reservoir at Mekedatu, about 100 km from Bengaluru, for impounding 67.16 thousand million cubic ft (TMC) of water. It will have a 400 MW hydro power component too. The project will submerge around 4,996 hectares of land, including about 4,800 hectares of forest and wildlife land. It is expected to help Karnataka utilise an additional 4.75 TMC of water allotted by the Supreme Court, in its judgment in February 2018 on the Cauvery dispute, to meet the growing drinking water needs of Bengaluru. Though the project was mooted as early as 1948, it acquired momentum only in recent years with the capital city of the upper riparian State experiencing severe water shortages in the summer.
-Why is the project controversial?
-The history of the dispute over the sharing of the Cauvery has led to a serious trust deficit between Tamil Nadu and Karanataka. The lower riparian State’s grievance against the upper riparian State acquires more intensity as the track record of the latter in releasing water during the first four months of the water year (June to May) is viewed as being far from satisfactory. This is why Tamil Nadu is apprehensive that the project, when fructified, may lead to Karnataka storing water excessively and releasing it at its will. However, Mr. Shivakumar contends that the project, to be carried out within Karnataka and out of the State’s own resources, would help his State supply water to Tamil Nadu as per the Cauvery Water Disputes Tribunal’s final order “even during poor rain years.”
-How important is the project?
-As per information furnished by Karnataka Chief Minister Siddaramaiah in March 2024 during Bengaluru’s acute water shortage, the city requires 2,600 million litres a day (MLD) while the available quantum was 2,100 MLD, leaving a shortfall of 500 MLD. The Cauvery river meets the demand for 1,450 MLD with 650 MLD sourced from groundwater. The population of Bengaluru, which is now 13 million, is expected to touch the 20-million mark in six years; then the city will need 4,000 MLD. It is against this backdrop that Mr. Shivakumar justified the early implementation of the Mekedatu project. But, the top Court awarded only 4.75 TMC per year to Bengaluru (equivalent to about 370 MLD).
-However, there are other ways to tackle the water problem. T.V. Ramachandra, veteran academician in the Centre for Ecological Sciences, Indian Institute of Science, Bengaluru, has been saying that the city gets annual rainfall of 700-850 mm, which, in turn, yields about 15 TMC (around 1,160 MLD), apart from the reuse of treated wastewater likely to provide about 16 TMC annually (1,240 MLD).
-How does the Centre view the issue?
-In January 2019, Karnataka submitted the DPR to the CWC, which, in turn, had forwarded it to the CWMA. When it had sought approval from the Union Ministry of Environment, Forest and Climate Change on the terms of reference to conduct the Environmental Impact Assessment study, the Ministry’s Expert Appraisal Committee, in July 2019, concluded that in view of inter-State issues, an “amicable solution” is needed between the two States. On February 1, 2024, the CWMA, after a “detailed deliberation” decided to refer the project back to the CWC.
-Now, the Authority and the CWC can provide a platform to the two States for a discussion, if possible, an understanding, on the project.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/karnataka/what-is-the-mekedatu-dam-project-dispute-explained/article70312196.ece</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 01:36:00 +0530</t>
-  </si>
-  <si>
-    <t>https://th-i.thgim.com/public/incoming/w6k1bm/article70312369.ece/alternates/LANDSCAPE_1200/IMG_IMG_MEKEDATU_RESERVO_2_1_D7A17DGD.jpg</t>
-  </si>
-  <si>
-    <t>Registration open for Bharathi Pasarai competitions</t>
-  </si>
-  <si>
-    <t>Registrations are open for competitions to held as part of the 41st Bharathi-Nehru National Art Festival, organised by the Tiruvottiyur-based Bharathi Pasarai. The competitions will include singing, drawing, oration, and poetry writing. According to a press release from Ma. Ki. Ramanan, founder-secretary, Bharathi Pasarai, school students should send their applications either via their schools or individually with a bona fide certificate from the institution. The last date for entries is November 26. The competitions will be held from 2 p.m. onwards at Mangadu Ellappa Chettiyar Kalyana Mandapam on Sannidhi Street in Tiruvottiyur on November 29. For further details, contact 9444182153.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/cities/chennai/registration-open-for-bharathi-pasarai-competitions/article70310718.ece</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 01:12:03 +0530</t>
-  </si>
-  <si>
-    <t>Kin of policeman killed in road accident to get ₹30 lakh</t>
-  </si>
-  <si>
-    <t>Chief Minister M.K Stalin announced Rs 30 lakh financial relief to the family of head constable Alagesan, who was killed in a road accident.
-Alagesan worked in the Koovathur police station and was hit by a car on his way to duty.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/kin-of-policeman-killed-in-road-accident-to-get-30-lakh/article70312198.ece</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 00:50:47 +0530</t>
-  </si>
-  <si>
-    <t>SI, two others booked for alleged blackmailing, extortion of money in Kochi</t>
-  </si>
-  <si>
-    <t>A sub-inspector (SI) posted at the Palarivattom police station was booked for allegedly extorting ₹4 lakh from a colleague in collusion with two accomplices. Baiju K.K., sub-inspector, Shiham, and Ramya were named as accused in a case registered on the basis of a complaint filed by a civil police officer at the AR camp, Kochi City.
-According to the first information report (FIR) registered on Friday (November 21, 2025), the accused extorted the money from the complainant after accusing him of stealing a gold necklace from a wellness spa in the city.
-According to the FIR, the complainant had reportedly visited the spa where Ms. Ramya works for a body massage on September 8. The next day, she informed him that a necklace was missing and asked him to return it or pay ₹6.5 lakh. He refused and suggested filing a police complaint. Following this, she allegedly involved Shiham and, with the purported assistance of the accused sub-inspector, recovered ₹4 lakh by October 1.
-The accused was charged with extortion under Section 308(2) of the Bharatiya Nyaya Sanhita. District Police Chief (Kochi City) Putta Vimaladitya has sought an internal report on the incident.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/kerala/si-two-others-booked-for-alleged-blackmailing-extortion-of-money-in-kochi/article70311706.ece</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 00:47:26 +0530</t>
-  </si>
-  <si>
-    <t>Ernakulam Revenue District School Kalolsavam to start on Nov. 25</t>
-  </si>
-  <si>
-    <t>The Ernakulam revenue district school arts festival for the academic year 2025-26 will begin on Tuesday (November 25, 2025).
-The festival will see the participation of over 8,000 students. Subin Paul, Deputy Director of Education, Ernakulam, will hoist the flag at St. Antony’s Higher Secondary School here on Wednesday (November 26, 2025) at 9 a.m. District Collector G. Priyanka will inaugurate the festival. The Collector will present an award to Binsil Biju Mathew, the student who created the logo of the festival, on the occasion.
-Registration will begin at 2 p.m. on Monday (November 24, 2025). The venues include St. Albert’s Higher Secondary School, St. Mary’s Higher Secondary School, St. Teresa’s Higher Secondary School, and Darul Uloom Vocational Higher Secondary School. The competitions will be held at 16 venues, and students will compete in over 300 categories. Along with the arts fest, a Sanskrit festival and an Arabic arts festival will also be held. Food will be provided to contestants, escorting teachers, volunteers, and others during the five-day event. The festival will be held in compliance with the green protocol.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/kerala/ernakulam-revenue-district-school-kalolsavam-to-start-on-nov-25/article70311931.ece</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 00:44:26 +0530</t>
-  </si>
-  <si>
-    <t>Kerala local body polls: Battle for the ballot a burden on the pocket</t>
-  </si>
-  <si>
-    <t>Election expenditure is often only talked about in the backrooms of political parties, but Mathew Jose, the Aam Aadmi Party’s (AAP) candidate from the Munnar division in the Idukki district panchayat, is making it a part of his campaign. Among the many campaign talking points he is raising are issues such as the insufficiency of the ₹1.5 lakh limit on campaigning expenses in district panchayats as well as the widely seen trend of candidates overshooting this limit and later underreporting it.
-“I am trying to contest the election within the stipulated expenditure limit, using contributions from the public alone. Although there are over a 100 resorts in my division, I have decided not to take contributions from them. The Election Commission’s limits are sufficient if you are doing just the traditional door-to-door campaigning and inexpensive social media posts. Although I have contested in four elections, in recent years I have seen that the expenses overshot all limits, a trend which does not bode well for democracy,” Mr. Jose, who had earlier won as a Congress candidate and as an Independent, tells The Hindu.
-Ahead of the local body elections this year, the State Election Commission chose not to revise the expenditure limits that it had last enhanced before the 2020 elections. While the candidates contesting in grama panchayat can spend only up to ₹25,000, those in block panchayats and municipalities can spend up to ₹75,000. The candidates in district panchayat divisions and Corporation wards have a ceiling of ₹1.5 lakh.
-The candidates are supposed to provide the SEC with an account of their expenses after the elections. As per a draft list put out by the SEC in 2022, a total of 9,202 out of the 74,899 candidates who contested across the State in the 2020 local body elections failed either to furnish details of their election expenses or exceeded the expense limits.
-Above ₹7 lakh
-Many who are involved in hectic campaigning, especially in the urban areas, say that the limits are a bit unrealistic. In district panchayats with each division spreading over a vast expanse, even putting up posters in all regions can stretch the spending limits. The arrival of professional public relations agencies on the campaigning scene has added to the costs. According to information shared by the campaign team of a major political front, the expense of some of the candidates in the Thiruvananthapuram Corporation could go even above ₹7 lakh.
-“Organising a ward-level convention would cost around ₹1 lakh, including the money spent to bring people to the venue. The booth-level conventions for 10 or 11 booths will also require considerable spending. The parties contribute only a part of these expenses, while in most cases the candidates are expected to spend considerably. This has also led to a situation in which candidates who do not have deep pockets end up not getting seats or choosing to stay away,” says a former Congress councillor from a coastal ward in Thiruvananthapuram.
-Stature-based funding
-The expenditure of the parties for the candidates also vary based on their relative stature. The district-level leaders get added funding and campaigning support from the district committees. The same is the case with the leaders of youth organisations. The major fronts also make considerable allocations to the smaller constituent parties.
-“We have concentrated mostly on door-to-door campaigning, while cutting down needless expenses. The Left Democratic Front (LDF) is taking care of collecting contributions from the ward and spending it for the campaign,” says Congress (S) leader and five-time councillor Palayam Rajan, who will be contesting from the Nanthancode ward of the Thiruvananthapuram Corporation.
-Sabu M. Jacob, chief coordinator of Twenty20, the political outfit backed by corporate major Kitex Group, says that his party takes care of the campaign expenses of all its candidates.
-Friends’ support
-The Independent candidates, who are on their own, do not necessarily dig deep into their own pockets as some of them bank on their network of friends and acquaintances.
-“Most of my old friends are working in West Asian countries. Quite a few of them sponsored my campaign last time that I didn’t have to ask for contributions from commercial establishments,” says M. Nissamudeen, currently an Independent councillor in the Thiruvananthapuram Corporation.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/kerala/battle-for-the-ballot-a-burden-on-the-pocket/article70303608.ece</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 00:29:13 +0530</t>
-  </si>
-  <si>
-    <t>https://th-i.thgim.com/public/incoming/d3ssou/article70312398.ece/alternates/LANDSCAPE_1200/Poll-Expenditure.jpg</t>
-  </si>
-  <si>
-    <t>Kerala local body polls: Munnar hopes for stability after a term of defections, power struggle</t>
-  </si>
-  <si>
-    <t>The Munnar grama panchayat is hoping for a rare stretch of stability. The last five years have been marked by political turbulence, with five different presidents taking turns at the helm.
-Munnar is a popular tourist destination, but the panchayat regularly witnesses hours-long traffic jams and lacks parking facilities. The absence of a bus stand and inconvenience to tourists are among the major concerns.
-“Even though there are hundreds of hotels and resorts here,there are no proper waste treatment plants or sewage plants. Wild elephants eating plastic-mixed waste at a panchayat-managed waste treatment plant at Kallar is a regular occurrence,” says a tourism stakeholder. The waste treatment plant at Kallar is not yet full-fledged.
-The number of wards in the panchayat has decreased to 20 from 21 after delimitation. Most of the voters here are tea plantation workers, with Tamil voters being the decisive factor.
-In the 2020 local body elections, the United Democratic Front (UDF) secured the majority by winning 11 of the 21 seats, and the Left Democratic Front (LDF) 10 seats. However, in January 2022, two UDF members, Praveena Ravikumar and M. Rajendran, defected to the LDF tipping the balance of power. Ms. Ravikumar then became president and Mr. Rajendran vice-president.
-No-trust motion
-This was followed by a series of defections. In August 2022, Thankamudy of the Communist Party of India (CPI) joined the UDF, and in February 2023, V. Balachandran, a Communist Party of India (Marxist) [CPI(M)] member, followed suit. The UDF, sensing an opportunity, called for a no-confidence motion. But just before the motion, the panchayat secretary received Mr. Rajendran’s resignation letter. Later, Mr. Rajendran alleged that his signature had been forged. The State Election Commission (SEC) allowed him to retain his post while the matter was under review.
-In October 2023, the SEC officially disqualified Ms. Ravikumar and Mr. Rajendran for switching parties, following which the Congress won the no-trust motion. However, its one vote became invalid, resulting in a tie. Then, the Congress’ Deepa Rajkumar became president through a draw.
-Later, she was disqualified after lapses was found in the draw, resulting in the LDF’s Jyothy Satheeshkumar becoming the panchayat chief. Six months later, theUDF reclaimed power with Ms. Rajkumar as president.
-Later, Ms. Rajkumar submitted resignation. However, she soon retracted, alleging coercion. She submitted a second letter, claiming that her resignation was made under duress and that the signature had been forged by Congress workers.
-The panchayat secretary forwarded both the letters to the SEC, which allowed her to continue in office. Subsequently, the Congress members moved a no-trust motion, forcing Ms. Rajkumar to step down. In May 2025, Congress’ M. Manimozhi became the president.
-CPI(M) district secretariat member K.V. Sasi says “the LDF aims to gain power in the panchayat with a strong margin. If it comes to power, the front will improve amenities and take steps to control the rush in the town.”
-Congress block committee president S. Vijayakumar says “the Congress aims to provide development-oriented administration in Munnar. Proper waste treatment plants and parking facilities are our main concerns.”
-Bharatiya Janata Party Munnar panchayat in-charge Balamurukan says “bus stands, parking facilities, and waste management systems are our priority.”</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/kerala/munnar-hopes-for-stability-after-a-term-of-defections-power-struggle/article70280576.ece</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 00:19:26 +0530</t>
-  </si>
-  <si>
-    <t>https://th-i.thgim.com/public/incoming/d1m17j/article70304116.ece/alternates/LANDSCAPE_1200/Munnar_Grama%20Panchayat.jpg</t>
-  </si>
-  <si>
-    <t>Stamp of election on T-shirts, caps</t>
-  </si>
-  <si>
-    <t>Demand is rife for political merchandise, including T-shirts and caps, having the pictures of leaders and party symbols as the campaigning for local body polls shifts to the top gear. Printers and traders are cashing in on the poll fever in Kochi by undertaking orders given by various political parties. Traders have also kept the campaign materials on sale in areas including the Broadway. A T-shirt with the photo of leaders or the candidate is being sold in the range of ₹100 to ₹200. Caps, which are in high demand, are being sold in the range of ₹15 to ₹25. Shop owners said that the demand for flags of varying sizes has also shot up over the last one week. They hope that the orders may go up as the key fronts are pulling out all the stops to woo the attention of the voters.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/kerala/stamp-of-election-on-t-shirts-caps/article70311583.ece</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 00:17:13 +0530</t>
-  </si>
-  <si>
-    <t>https://th-i.thgim.com/public/incoming/ltwwbn/article70311592.ece/alternates/LANDSCAPE_1200/80968_22_11_2025_18_31_45_1_IMG_8690.JPEG</t>
-  </si>
-  <si>
-    <t>Student leaders give a campus vibe for local body elections in Kerala</t>
-  </si>
-  <si>
-    <t>Student power, in all colours, is flying high in the ongoing local body elections in the State with political parties fielding a considerable number of candidates from their campus wings, marking a significant change in poll traditions.
-The CPI(M) has fielded 48 leaders of the Students’ Federation of India (SFI) in the polls while the Congress has found 79 candidates from the Kerala Students’ Union (KSU). The Muslim Students Federation (MSF) of the Indian Union Muslim League has fielded 47 leaders, while 14 from the All India Students’ Federation (AISF), the CPI’s student wing, are also in the fray.
-The student wings say they have all been given due consideration by their party leaderships this time compared to previous polls. Among the student leaders, KSU Thiruvananthapuram district vice-president Vyshna Suresh’s candidature has already grabbed wide attention following the controversy over her voting right which she had to get reinstated through a High Court intervention amid her campaign.
-Of the 79 candidates from the KSU, 22 are its State office-bearers. KSU’s State leaders in the fray include general secretaries Mubas Odakkaly and Arunima M. Kurup, the latter being one of the two transgender candidates of the Congress.
-KSU leaders have been given tickets in nine district panchayat divisions, 29 block panchayat divisions, and 31 grama panchayat wards. Among them are four district presidents of the organisation.
-KSU State president Aloshious Xavier said that in the previous local body polls, tickets were given to only 23 from the student wing. “We consider the rise in the number this time as an acknowledgement for the electoral gains the KSU has made in the campus elections over the past few years,” he said. Mr. Xavier said that the leadership of the KSU had placed its demand for due consideration in candidate selection to the Kerala Pradesh Congress Committee and the District Congress Committees as the number of seats allotted to his colleagues was low in the initial stages of electoral talks.
-‘No pressure tactics’
-Leaders of the SFI and AISF, meanwhile, said that they did not have to play any pressure tactics to be considered in candidate selection as it was against the norms of the Left parties. Prominent SFI leaders in the fray include its central committee member P. Thajudheen and State joint secretary Syed Muhammed Sadik, both contesting to the Kozhikode district panchayat. SFI leaders are contesting in nine district panchayat divisions, 14 block panchayat divisions, 29 grama panchayat wards, five municipal wards and one corporation ward. SFI State president M. Sivaprasad said the organisation will be highlighting the LDF government’s achievements in the education sector during the campaign.
-From AISF, State president Bibin Abraham is contesting as a CPI candidate in Pathanamthitta district panchayat while 10 State committee members are also in the fray.
-The Akhil Bharatiya Vidyarthi Parishad, affiliated to the RSS, meanwhile, said its office-bearers don’t contest as BJP candidates in the elections.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/kerala/student-leaders-give-a-campus-vibe-for-local-body-elections-in-kerala/article70311534.ece</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 00:13:30 +0530</t>
-  </si>
-  <si>
-    <t>https://th-i.thgim.com/public/news/national/kerala/sfy8ri/article70311836.ece/alternates/LANDSCAPE_1200/facebook_1763822540230_7398007935778943633.jpg</t>
-  </si>
-  <si>
-    <t>Tamil Nadu government finds itself in a tight corner over Code on Social Security</t>
-  </si>
-  <si>
-    <t>With the Union government notifying the enforcement of the four Labour Codes all over the country, the Tamil Nadu government has found itself in a tight corner with regard to the Code on Social Security, as it has been entertaining reservations on the issue.
-Ever since the Centre enacted the four Codes five years ago in the place of 29 laws, it had held discussions with the State government over the implementation of the Code on Social Security (CSS), 2020. But, no consensus was arrived at, according to a policymaker.
-Of the four Codes, the State government, in April 2022, published draft rules for the three — the Code on Wages, 2019, the Industrial Relations Code, 2020, and the Occupational Safety, Health, and Working Conditions Code, 2020. As consultations with stakeholders have been held, the government can notify the final rules anytime now. Only in respect of the CSS, no draft rules have been framed so far.
-Existing law
-Fundamentally, the CSS does not give liberty to the State government to retain its existing law — the Tamil Nadu Manual Workers (Regulation of Employment and Conditions of Work) Act, 1982. But, the Unorganised Workers’ Social Security Act, 2008, one of the nine laws subsumed by the latest Code, had allowed States to have any corresponding law, providing welfare schemes more beneficial to the unorganised workers than those provided for them under it.
-The main reason behind the State government’s reservation is that Tamil Nadu, being a “pioneer” in labour welfare measures for the unorganised sector, has been having 18 unorganised workers’ welfare boards, covering those engaged in 70 (manual) and 54 (construction) categories of works specified in the 1982 law. These boards are implementing a number of schemes pertaining to education, marriage, maternity, natural and accidental death, accident disability, and monthly and family pension.
-The concern expressed by activists and trade unionists, apart from the State government, is that the present framework of schemes may get disturbed after implementation of the CSS. For example, in the Code, it is for the Union government to frame welfare schemes for unorganised workers in respect of life and disability cover, health and maternity benefits, old age protection, and education, while it is for the State governments to come up with schemes for provident fund, employment injury benefit, housing, educational schemes for children, upgrading skills of workers, funeral assistance, and old age homes.
-This has raised questions over how to continue with the existing schemes of the State government and welfare boards in areas designated for the Union government. Besides, the possibility exists in respect of overlapping of certain functions, as stipulated by the Code. Notwithstanding the prevalence of challenges inherent in the implementation of the CSS, the Tamil Nadu government is particular that the interests of workers are safeguarded and strengthened, explains a senior official.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/tamil-nadu/tamil-nadu-government-finds-itself-in-a-tight-corner-over-code-on-social-security/article70310891.ece</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 00:07:58 +0530</t>
-  </si>
-  <si>
-    <t>https://th-i.thgim.com/public/incoming/gjyk61/article70312405.ece/alternates/LANDSCAPE_1200/MAY_DAY_WORKER_2.jpg</t>
-  </si>
-  <si>
-    <t>Harish Rao demands Assembly debate on sale of prime lands at throwaway rates</t>
-  </si>
-  <si>
-    <t>HYDERABAD
-The Bharat Rashtra Samithi (BRS) has alleged that the Congress Government was conspiring to dispose of valuable land chunks of 9,300 acres in the industrial estates at throwaway prices and agreements were done for the lands already.
-Addressing a press conference here on Saturday, former minister T. Harish Rao said the Hyderabad Industrial Land Transformation Policy (HILTP) was indeed a land looting policy aimed at transforming the fortunes of those close to Chief Minister A. Revanth Reddy, as the government was heavily subsidising the land sale to its “near and dear” ones.
-Ridiculing the argument of Minister for Industries and IT D. Sridhar Babu that the government was merely following the GO (policy) brought in by the previous BRS government, Mr. Harish Rao said the BRS government had disposed of some chunks of industrial lands for dual use - 50% each for IT/employment generation and residential/other - with the price fixed at 200% of the SRO (sub-registrar office/registration) value.
-However, the Congress government was planning to give away the lands at only 30% of the SRO value for multi-purpose use without any condition for employment generation. Further, they had also decided to waive the HMDA Non-Agricultural Land Assessment (NALA) and Conversion of Land Use (CLU) fee, which would otherwise bring in another ₹13,500 crore to the exchequer for multi-purpose use.
-Quoting Mr. Sridhar Babu’s statement that the land sale would get only up to ₹5,000 crore revenue to the government, Mr. Harish Rao sought to know how the government could dispose of lands valued at around ₹4 lakh crore to ₹5 lakh crore to such a meagre value.
-He saw a conspiracy as agreements for the lands to be disposed off were already signed much before operationalising the policy (HILTP). He demanded that the government convene the Assembly session to discuss the issue.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/telangana/harish-rao-demands-assembly-debate-on-sale-of-prime-lands-at-throwaway-rates/article70311571.ece</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 00:06:40 +0530</t>
-  </si>
-  <si>
-    <t>https://th-i.thgim.com/public/news/national/telangana/mvu99p/article70311564.ece/alternates/LANDSCAPE_1200/WhatsApp%20Image%202025-11-22%20at%205.33.20%20PM.jpeg</t>
-  </si>
-  <si>
-    <t>Had there been Operation Sindoor after 26/11, nobody would have dared to attack India: CM Fadnavis</t>
-  </si>
-  <si>
-    <t>Maharashtra Chief Minister Devendra Fadnavis on Saturday (November 22, 2025) said had India taken an Operation Sindoor-like action after the November 2008 Mumbai terror attack, no one would have dared to target the country again.
-Speaking at an event at the Gateway of India to mark the 17th anniversary of the 26/11 attack that is coming up, Mr. Fadnavis said it was not merely an attack on Taj and Trident hotels. Mumbai is the economic capital of India, and an attack on the city was an attack on the sovereignty of the country, he said.
-Also read: Mumbai terror attack a turning point in India-Pakistan ties: Jaishankar; ‘Pakistan stuck in bad habits’
-“Had we understood this and shown the courage to conduct an ‘Operation Sindoor’ then, nobody would have dared to attack us again,” he said.
-India carried out military action under Operation Sindoor, targeting terror infrastructure in Pakistan in the aftermath of the Pahalgam terror attack of April 2025.
-The Mumbai terror attack, during which Pakistani terrorists entered the city by sea route on November 26, 2008, and caused mayhem, claimed at least 166 lives.
-Though 17 years have passed, “there is still pain in our hearts,” Mr. Fadnavis further said.
-“We have gathered here to honour the martyrs and the brave-hearts, and remember that the threat of terror still persists and we need to be alert. We need to be the eyes and ears of our country and speak in one language. We are safe if we are united,” the Chief Minister said.
-Pakistan knows it cannot defeat India in a straightforward war, and hence the terrorist attack in Pahalgam and the recent blast in Delhi took place, Mr. Fadnavis said.
-He lauded security agencies for managing to seize 3,000 kg of RDX which was to be used to conduct terror strikes in Mumbai and other cities.
-“PM (Narendra) Modi has said terror and talks cannot go together, and gave freedom to the armed forces to take action. Through Operation Sindoor, the world saw India’s might. India is a strong country, and the war (against terror) is not over,” the Chief Minister added.
-The event ‘Global Peace Honours: Remembering the Heroes of 26/11 and Victims of Pahalgam Attack’ had been organised by the Divyaj Foundation headed by Mr. Fadnavis’s wife Amruta Fadnavis.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/maharashtra/had-there-been-operation-sindoor-after-2611-nobody-would-have-dared-to-attack-india-cm-fadnavis/article70312361.ece</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 00:03:00 +0530</t>
-  </si>
-  <si>
-    <t>https://th-i.thgim.com/public/incoming/bo9h2e/article70312388.ece/alternates/LANDSCAPE_1200/PTI11_22_2025_000475B.jpg</t>
-  </si>
-  <si>
-    <t>Real-life ‘Manjummel Boy’ in the fray in Kerala local body polls</t>
-  </si>
-  <si>
-    <t>Subhash Chandran, who faced a near-death experience in an accident at the Guna Caves in Kodaikanal, an incident that inspired the blockbuster Malayalam movie Manjummel Boys, is testing his electoral luck in this local body polls. He is contesting from Ward 27 of the Eloor municipality as the Congress candidate. It was on September 3, 2006, that he went to the Guna Caves along with his nine friends from Manjummel. He fell into a deep pit while crossing a crevice. A heart-wrenching rescue act led by his friend Siju David had brought him back to life. “I have been active in social and welfare activities in Manjummel for many years and feels that my candidature is an extension of such works,” says Mr. Chandran, whose family has been active supporters of the Congress for long.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/kerala/real-life-manjummel-boy-in-the-fray-in-kerala-local-body-polls/article70311308.ece</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 00:00:42 +0530</t>
-  </si>
-  <si>
-    <t>https://th-i.thgim.com/public/incoming/7txy7e/article70311597.ece/alternates/LANDSCAPE_1200/IMG-20251122-WA0065.jpg</t>
-  </si>
-  <si>
-    <t>iTNT Hub starts operations in Coimbatore</t>
-  </si>
-  <si>
-    <t>Minister for Information Technology and Digital Services Palanivel Thiaga Rajan inaugurated on Saturday the Tamil Nadu Technology (iTNT), Coimbatore regional hub.
-The hub, located at the Government College of Technology, is the first regional centre of iTNT Hub in western Tamil Nadu and third in the State to support deep and emerging tech startups and researchers.
-There is more monopolistic control by technology majors, be it platform providers or internet companies. It is starting to reach its limits, mainly for regulatory reasons. Historically, the big employers that used to recruits thousands of freshers are under pressure to employ AI engines and reduce the number of employees. All of this comes back to a phase of cycle where there should be a lot more startups, innovators, ideas, and MSMEs for solving problems felt daily in local communities.
-The government efforts are to bring as many IPs (new ideas and innovations) together with resources to convert them into functional products by providing access to labs, resources, mentorship, and capital to nurture the ideas so that there are meaningful outcomes. The government has a big role to play in this. “We are striving to expand our network, facilities,” he said.
-The Minister also launched the “Bosch Innovation Challenge”, which is organised jointly by iTNT Hub and Bosch Global Software Technologies, to support breakthrough ideas from researchers, innovators and startups that can build a “Foundational Security Strategy for IoT Products” for easy adoption by startups and MSMEs.
-He also launched the “IP Nexus 2026” jointly organised by Karpagam Innovation and Incubation Council and iTNT Hub to bring together Intellectual Property Rights holders, industry partners, and incubation networks to promote commercialisation, technology transfer, and explore opportunities to turn their ideas into market-ready solutions.
-The PSG-STEP exchanged a MoU with iTNT Hub to establish the Hub’s satellite office in Coimbatore. A co-incubation agreement was exchanged between iTNT Hub and Karpagam Innovation and Incubation Council, making it the Hub’s 27 th co-incubation partner in the State.
-iTNT Hub CEO Vanitha Venugopal said, “The Regional Hub will extend the benefits of the iTNT Hub to a wider range of researchers, startups, academia, industry and other stakeholders. In addition to the co-working spaces and physical infrastructure, startups and researchers will gain access to all the programmes and initiatives of the hub, including technology transfer,” she said.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/cities/Coimbatore/itnt-hub-starts-operations-in-coimbatore/article70311825.ece</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 23:57:46 +0530</t>
-  </si>
-  <si>
-    <t>https://th-i.thgim.com/public/incoming/vxx6ej/article70312394.ece/alternates/LANDSCAPE_1200/IT%20Minister.jpg</t>
-  </si>
-  <si>
-    <t>Arrested couple accused of ₹23 crore fraud brought to city by CCS on transit warrant</t>
-  </si>
-  <si>
-    <t>The Central Crime Station (CCS) Detective department arrested two alleged white collar offenders in connection with a ₹23 crore investment fraud case and brought them to Hyderabad on Saturday on a transit warrant.
-The accused, identified as Vuppalapati Satish Kumar and his wife Shilpa Banda also known as Vuppalapati Shilpa Rao, were picked up from Dharwad in Karnataka on November 20 following what police described as a dramatic operation based on credible information.
-According to the complaint filed on September 18 by P. Vinay Kumar, son of P. Shiva Shankar, 67, a resident of Mamidipalli in Ranga Reddy district, the couple allegedly persuaded him, his family members and several others to invest in their firm by promising attractive returns. Police said that after paying small initial amounts, the accused stopped making further payments and absconded, allegedly cheating investors to the tune of ₹23 crore.
-Investigators said the couple, along with associates, floated multiple shell companies and diverted deposits into different entities. A case was subsequently registered under by CCS Hyderabad.
-Since then, the accused allegedly evaded arrest and did not cooperate with the investigation.
-Police said Satish Kumar and Shilpa Rao were previously involved in cases investigated by the CBI, the Enforcement Directorate and the GST authorities.
-The operation was carried out under the supervision of DCP N Swetha of the CCS Detective Department. Officers from CCS and the Task Force jointly executed the arrests. Both accused were produced before a Hyderabad court on Saturday for judicial remand.
-The case is being investigated by Inspector C. Parasuram of the EOW Team VI of CCS Hyderabad.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/telangana/arrested-couple-accused-of-23-crore-fraud-brought-to-city-by-ccs-on-transit-warrant/article70312281.ece</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 23:54:31 +0530</t>
-  </si>
-  <si>
-    <t>Eight, including constable, arrested for abducting CEO of BPO for ransom</t>
-  </si>
-  <si>
-    <t>In a late-night operation, the Southeast Division Police rescued the owner of a BPO company in Koramangala who was abducted by a gang posing as police officers and extorted ₹18.90 lakh from him.
-Eight persons, including a police constable serving in the Kolar district, have been arrested.
-The incident took place around midnight on Friday when the accused barged into a call centre operated by Pavan. They claimed to be police personnel conducting a cybercrime inspection.
-The BPO, which works with US-based clients, functions throughout the night.
-According to police, the gang accused the employees of cyber fraud, threatened them, and forced Pavan into a vehicle on the pretext of taking him for inquiry. Instead, they drove him to Malur, where he was held hostage for nearly three hours. The suspects demanded money, and when Pavan was unable to withdraw cash, they forced him to transfer ₹18.90 lakh into certain bank accounts they provided to Pavan.
-Meanwhile, employees at the call centre grew suspicious alerted the police. Pavan also managed to send a distress message. Around 3 a.m., the city’s emergency helpline 112 received the complaint.
-Police teams tracked the movement of the accused and managed to locate both the abductors and the victim within hours. All eight accused were arrested, and two cars used in the crime were seized.
-Police have said further investigation is on to determine whether the gang was involved in similar offences earlier.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/karnataka/eight-including-constable-arrested-for-abducting-ceo-of-bpo-for-ransom/article70312236.ece</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 23:46:11 +0530</t>
-  </si>
-  <si>
-    <t>CAG exposed lies of Revanth Reddy govt. on debt, monthly interest payments: KTR</t>
-  </si>
-  <si>
-    <t>HYDERABAD
-Working president of the Bharat Rashtra Samithi (BRS) K.T. Rama Rao (KTR) has criticised Chief Minister A. Revanth Reddy for repeatedly exaggerated figures on Telangana’s debt and interest payments.
-Quoting the latest CAG report for October, he said it has completely exposed the Congress government’s “mathematical manipulation” and deceptive claims. In a statement issued on Saturday, Mr. Rama Rao demanded that the Congress government release full details of the ₹2.23 lakh crore borrowed beyond FRBM limits in the last 23 months and explain which schemes or projects benefited from the massive loans. He insisted that the government disclose details of loans raised through various corporations in the last seven months.
-He said that Congress leaders repeatedly claim that Telangana is paying ₹6,000 core to ₹7,000 crore every month just towards interest. But the CAG’s latest report has proved this to be an utter lie.
-According to the statistics in the CAG report from April 2025 to October 2025, the total interest payment made by the Congress government is ₹16,529.88 crore or ₹2,361.41 crore per month on average. He claimed that during 10 years of BRS governance, the total borrowing was ₹2.80 lakh crore and every rupee was invested into productive assets such as Mission Bhagiratha, Kaleshwaram, Palamuru-Rangareddy Lift Irrigation, Mission Kakatiya, and development projects. In contrast, within just 23 months, the Congress government has already borrowed ₹2.23 lakh crore without initiating even a single major project.
-He demanded that the Chief Minister tender a public apology and release details regarding the ₹2.23 lakh crore borrowed over the last 23 months and loan details of various corporations over the past seven months.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/telangana/cag-exposed-lies-of-revanth-reddy-govt-on-debt-monthly-interest-payments-ktr/article70311918.ece</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 23:46:07 +0530</t>
-  </si>
-  <si>
-    <t>‘A courtesy call’</t>
-  </si>
-  <si>
-    <t>Speaking to reporters after a meeting with AICC president Mallikarjun Kharge, which lasted close to 90 minutes, Chief Minister Siddaramaiah said it was “only a courtesy call”.
-Asked about the Cabinet reshuffle and power sharing, he said, “It’s only a speculation you [media] are making. Ultimately, the high command’s decision will be accepted by me and D.K. Shivakumar also.”</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/karnataka/a-courtesy-call/article70312271.ece</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 23:44:06 +0530</t>
-  </si>
-  <si>
-    <t>Adversary making desperate attempts to disrupt peace: J&amp;K L-G Manoj Sinha</t>
-  </si>
-  <si>
-    <t>J&amp;K Lieutenant Governor Manoj Sinha on Saturday (November 22, 2025) said the adversary was making desperate attempts to disrupt peace and hinder India’s progress.
-“The Jammu and Kashmir Police unearthed and dismantled a pan-India terror network that was planning to carry out a series of terrorist attacks across the country. In such a situation, we must remain alert to protect the nation’s honour, protect our borders, and preserve our unity and integrity,” said Mr. Sinha.
-He was speaking at the closing ceremony of the eye camp ‘Op Drishti’ for veterans, Veer Naris and civilians organised at Command Hospital Northern Command, Udhampur.
-He said the Army contributed in creating a conducive environment for sustainable peace and overall development of the J&amp;K U.T. as well as the growth of our country.
-“I am proud of the selfless service and supreme sacrifices by the Indian Army, the symbol of unity and national integration. The army has contributed in creating a conducive environment for sustainable peace and overall development of the J&amp;K U.T. as well as the growth of our country,” Mr. Sinha said.
-He stressed that the armed forces should continually adapt to and remain vigilant against the rapidly changing security environment.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/jammu-and-kashmir/adversary-making-desperate-attempts-to-disrupt-peace-jk-l-g-manoj-sinha/article70312129.ece</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 23:43:20 +0530</t>
-  </si>
-  <si>
-    <t>https://th-i.thgim.com/public/incoming/d28et0/article70312199.ece/alternates/LANDSCAPE_1200/20251122317L.jpg</t>
-  </si>
-  <si>
-    <t>Congress appoints new DCC presidents</t>
-  </si>
-  <si>
-    <t>After a long wait, the new District Congress Committee (DCC) presidents have been appointed on Saturday with five MLAs getting an opportunity to serve as presidents, while five women have also been accommodated in the new team.
-The five MLAs who were appointed as DCC presidents are Beerla Ilaiah (Bhongir), Medipally Sathyam (Karimnagar), Chikkudu Vamshi Krishna (Nagarkurnool), Vedma Bhojju (Nirmal) and M.S. Raj Thakur (Peddapalli).
-Others include Naresh Jadhav (Adilabad), Athram Suguna (Asifabad), Thota Devi Prasanna (Badradri Kothagudem), M. Rajeev Reddy (Gadwal), Engala Venkat Ram Reddy (Hanmakonda), Syed Khalid Saifullah (Hyderabad), Gajengi Nandaiah (Jagitial), Lakavath Dhanvanthi (Jangaon), Battu Karunakar (Jayashankar Bhupalpalle), Mallikarjun Ale (Kamareddy).
-V. Anjan Kumar (Karimnagar Corporation), Motha Rohit Mudiraj (Khairatabad), Nuthi Satyanarayana (Khammam), Deepak Chowdary (Khammam Corporation), Bhukhya Uma (Mahabubabad), A. Sanjeev Mudiraj (Mahbubnagar), Pinninti Raghunath Reddy (Mancherial), Shivannagari Anjaneyulu Goud (Medak), Thotakura Vajresh Yadav (Medchal Malkajgiri), Paidakula Ashok (Mulugu).
-Deepak John (Secunderabad), Thumkunta Anksha Reddy (Siddipet), Gudipati Narsaiah (Suryapet), Dhara Singh Jadav (Vikarabad), Mohammed Ayub (Warangal), Punna Kailash Netha (Nalgonda), Kollukuduru Prashanth Kumar Reddy (Narayanpet), Katpally Nagesh Reddy (Nizamabad), Bobbili Ramakrishna (Nizamabad Corporation) and Sangeetham Srinivas (Rajanna Sircilla)., Shivsena Reddy (Wanaparthy).
-According to AICC general secretary (Organisation) K.C. Venugopal, AICC observers appointed for each district which conducted extensive reviews, interacted with district-level leaders, office-bearers and stakeholders, and submitted detailed reports. The list was finalised based on their reports and views of senior leaders.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/telangana/new-dcc-presidents-appointed/article70312095.ece</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 23:40:45 +0530</t>
-  </si>
-  <si>
-    <t>Gandhian ideals regain relevance, says Hassan</t>
-  </si>
-  <si>
-    <t>Those who once dismissed Gandhian ideals as outdated are now beginning to recognise their relevance, senior Congress leader M.M. Hassan has said.
-He was inaugurating a memorial meeting for Kalpatta Balakrishnan, who was a prominent presence in the State’s academic, cultural, and literary spheres for decades, here on Saturday. The event was held at the M.T. Hall of the Kerala Sahitya Akademi and presided over by writer and orator P.V. Krishnan Nair.
-Mr. Hassan said that at a time when writers like poet K. Satchidanandan and many others did not view Gandhi as a progressive thinker, Kalpatta Balakrishnan had the courage to stand alone and assert that Gandhi was right. “When Gandhian philosophy had little representation in Malayalam literature, it was Kalpatta who took the initiative to highlight it,” he said.
-Mr. Hassan added that Gandhi and his ideas are being discussed more today. Since the change of regime at the Cenre in 2014, there have been attempts to push Gandhi into obscurity. Now, even those who once opposed him are starting to realise the value of Gandhian principles, he said. This is the time to rise above political differences and implement Gandhian ideals collectively.
-The Dr. Kalpatta Balakrishnan Memorial Awards were presented to K. Raghunathan, N. V. Janardhanan, and Vishwajith. Former Speaker Therambil Ramakrishnan, former Director of the State Institute of Languages M.R. Thampan; P. Balachandran, MLA; and T.V. Chandramohan, former MLA, spoke.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/kerala/gandhian-ideals-regain-relevance-says-hassan/article70311624.ece</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 23:35:10 +0530</t>
-  </si>
-  <si>
-    <t>https://th-i.thgim.com/public/incoming/mf5yii/article70312368.ece/alternates/LANDSCAPE_1200/80688_22_11_2025_20_29_13_3_HASSAN_KKN.JPG</t>
-  </si>
-  <si>
-    <t>LDF claims win in 10 wards in Kannur, Kasaragod</t>
-  </si>
-  <si>
-    <t>The Left Democratic Front (LDF) is jubilant about a potential win in 10 wards in Kannur and Kasaragod districts nearly two weeks before the voting day in the local body elections.
-On Friday, the last day for filing nominations, LDF candidates stood unopposed in six wards across Anthoor municipality and Malapattam and Kannapuram grama panchayats in Kannur district. Their victories will be officially declared once the deadline for withdrawal of nominations expires.
-The LDF claimed to have won four additional wards on Saturday after the nominations of United Democratic Front (UDF) candidates were rejected during scrutiny in one ward in Malapattam and two wards in Kannapuram panchayat. In a ward in Kasaragod’s Madikkai grama panchayat, the Bharatiya Janata Party (BJP) candidate’s nomination was rejected.
-While the LDF celebrated the outcomes, Kannur District Congress Committee (DCC) president Martin George criticised the rejections in Anthoor and Malapattam, alleging foul play to favour LDF candidates.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/kerala/ldf-claims-win-in-10-wards-in-kannur-kasaragod/article70312266.ece</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 23:33:27 +0530</t>
-  </si>
-  <si>
-    <t>HC deserves credit for probe by SIT into Sabarimala gold theft, says Chennithala</t>
-  </si>
-  <si>
-    <t>Senior Congress leader Ramesh Chennithala on Saturday said the High Court deserved credit for the arrest of two former Travancore Devaswom Board presidents in the Sabarimala gold misappropriation case.
-He said that without the High Court’s supervision, the case would have ended with the arrest of just three or four lower-level officials. It was only due to the court’s intervention that an impartial investigation was taking place.
-Mr. Chennithala, a permanent invitee to the Congress Working Committee, urged Chief Minister Pinarayi Vijayan to break his silence, which he described as mysterious, especially since two important CPI(M) leaders had been arrested and remanded in judicial custody in the case.
-“It’s the turn of the Ministers now. Media reports suggest that former Devaswom Minister Kadakampally Surendran will soon be in the dock. But that is not enough. The present Devaswom Minister V.N. Vasavan should also be questioned to uncover the whole truth,” he said.
-Accusing the CPI(M)-led government of trying to destroy Sabarimala, Mr. Chennithala said they had earlier attempted to do so by pushing for the entry of women of all ages into the temple. Now, they were doing it by misappropriating gold belonging to the temple.
-He further alleged that no adequate preparations had been made ahead of the Mandalam-Makaravilakku season, resulting in unending queues and immense hardship for devotees.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/kerala/hc-deserves-credit-for-probe-by-sit-into-sabarimala-gold-theft-says-chennithala/article70312046.ece</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 23:24:34 +0530</t>
-  </si>
-  <si>
-    <t>Over 200 students take part in neurology conference in Vijayawada</t>
-  </si>
-  <si>
-    <t>Over 200 people, including doctors and students, participated in the neurology and neurosurgery scientific conference, organised by the A.P. Neuroscientists’ Association at Siddhartha Medical College (SMC) in Vijayawada on Saturday (November 22).
-Director of Medical Education G. Raghunandan, Dr. NTR University of Health Sciences registrar V. Radhika Reddy, SMC principal A.Y. Rao, Neurological Society of India national president Manas Panigrahi, SMC neurosurgery HoD I. Babji Shyam Kumar were present in the inaugural event.
-Later, speaking on the occasion, Dr. Raghunandan pointed out that such sessions help students grasp the subjects better. A presentation was made on neurology and neuro surgery cases, and experts discussed Cervical compressive myelopathy.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/andhra-pradesh/over-200-students-take-part-in-neurology-conference-in-vijayawada/article70312104.ece</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 23:24:30 +0530</t>
-  </si>
-  <si>
-    <t>International chess tournament inaugurated at Stella College</t>
-  </si>
-  <si>
-    <t>The Ecoren International Below 1800 FIDE Rating Chess Tournament was inaugurated at Maris Stella College in Vijayawada on Saturday (November 22).
-Recipient of Dronacharya Award Koneru Ashok, vice-chairperson and managing director of Sports Authority of Andhra Pradesh (SAAP) S. Bharani, Ecoren advisor Ch. Snigdha, Stella College correspondent Sr. Leena Quadras, principal G. Insyamma, coach V. Rajkumar and Andhra Chess Association chief advisor K.V. Sharma were among those present at the three-day event.
-A total of 600 players drawn from across the country have registered for this tournament.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/andhra-pradesh/international-chess-tournament-inaugurated-at-stella-college/article70312041.ece</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 23:17:48 +0530</t>
-  </si>
-  <si>
-    <t>Cong., AAP, Akalis oppose Chandigarh plan of Central govt.</t>
-  </si>
-  <si>
-    <t>The Centre’s proposal to include the Union Territory (UT) of Chandigarh under the ambit of Article 240 of the Constitution, which empowers the President to make regulations for the UT and legislate directly, has raised a political furore in Punjab. The government will bring the Constitution (131st Amendment) Bill, 2025 in the upcoming Winter Session of Parliament, beginning December 1, 2025, as per a bulletin of the Lok Sabha and Rajya Sabha.
-Political parties, including the Congress, the Shiromani Akali Dal (SAD) and the Aam Aadmi Party (AAP), hit out at the Bharatiya Janata Party (BJP) over the proposed introduction of the Bill, which would bring Chandigarh in alignment with other UTs without legislatures. The claim over Chandigarh, the joint capital of Punjab and Haryana, has been a sensitive political issue ever since the Punjab Reorganisation Act of1966.
-Punjab’s Leader of the Opposition and Congress leader Partap Singh Bajwa took to social media to criticise the move. “Chandigarh was created in 1966 as Punjab’s capital, with the Punjab Governor serving as its Administrator for decades. Now the Centre’s 131st Amendment move to pull Chandigarh under Article 240 is nothing short of snatching the city away from Punjab – an open attack on history, federalism, and Punjab’s rights. The BJP govt is pushing a politically loaded Constitution (131st Amendment) Bill to recast Chandigarh like any other UT,” he posted on X.
-SAD president Sukhbir Singh Badal asked the Union government not to introduce the Bill, pointing out that doing so would amount to “betraying and discriminating against brave Punjabis who had sacrificed the most for the country” and going back on all commitments made to Punjab to hand over Chandigarh to it. “It seeks to end Punjab’s claim to Chandigarh as its capital city,” he said in a statement.
-AAP’s Lok Sabha MP Malvinder Kang termed the move as a “daylight robbery”. “This moment demands unity. Every MP from Punjab, across all political lines, must stand together, forge a common front, and defeat this amendment in the Winter Session,” he posted on X.</t>
-  </si>
-  <si>
-    <t>https://www.thehindu.com/news/national/punjab/cong-aap-akalis-oppose-chandigarh-plan-of-central-govt/article70311775.ece</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 23:16:37 +0530</t>
-  </si>
-  <si>
     <t>TOI</t>
+  </si>
+  <si>
+    <t>'Withdraw your son': Woman recalls Delhi boy’s last words; alleges teachers torture him</t>
+  </si>
+  <si>
+    <t>Delhi Student Suicide Case: Massive Protest Outside School After Note Alleges Harassment By Teachers
+(With agency inputs)
+NEW DELHI: Deepshikha, the woman who saw the school student last time, before he headed to the Rajendra Place Metro Station and allegedly died by suicide, said that he looked disturbed and told her that the teachers "tortured" him.On Saturday, Deepshikha said she was travelling in the same rickshaw as the victim on November 18.She said, "I bring my ward home from school in a rickshaw every day. But on the afternoon of November 18, when I had just sat in the rickshaw with my son, he (the victim) suddenly came running and quickly got in. He kept telling the driver to go faster. He looked very disturbed.""I asked him what had happened, and he replied, 'You should withdraw your son from the school.' He further said, 'My board exams are coming up, and the teachers torture me a lot. I can't even explain how much. My parents are called to school again and again'," the woman added.A class 10 student who allegedly died by suicide near Rajendra Place Metro Station left behind a note accusing his school teachers of harassment and demanding strict action against them.According to the FIR, the student is believed to have jumped from Platform No.2 of the Rajendra Place Metro Station.Even as parents and students continued their protest outside the private school on Saturday, Delhi education minister Ashish Sood said on Friday that the state government had constituted an inquiry committee to investigate the incident.Speaking to reporters, Sood said that the school had also taken certain actions in the matter. He added that he would be writing to schools to check whether they are monitoring students’ mental health and overall well-being as mandated under CBSE guidelines."We have formed an investigation committee, and the school has also taken action. I see this not only as the education minister, but also as a concerned parent. Soon, I will be writing to schools to ask whether they are monitoring students' mental health and overall well-being in accordance with CBSE guidelines. The state government is ready to provide handholding and support. We are deeply concerned about our children's mental health and well-being," the Delhi education minister said.Meanwhile, the school, located in central Delhi, has suspended four of its staff members.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/city/delhi/you-should-withdraw-your-son-from-school-woman-who-saw-delhi-school-student-before-he-died-by-suicide/articleshow/125517964.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 14:49:06 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125518061,width-1070,height-580,imgsize-36982,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>Shocking! Mandhana–Muchhal wedding postponed</t>
+  </si>
+  <si>
+    <t>Palash Muchhal and Smriti Mandhana at their mehendi ceremony (X)
+Smriti Mandhana &amp; Palash Muchhal’s Haldi Ceremony Begins!
+The much-anticipated wedding of Indian cricket star Smriti Mandhana and music composer-filmmaker Palash Muchhal, scheduled for this Sunday in Sangli, has been indefinitely postponed.Mandhana’s manager Tuhin Mishra confirmed that her father is unwell and the family has decided to put the ceremony on hold."This morning, while they were having breakfast, Smriti’s father, Shriniwas Mandhana, suddenly started feeling unwell. We waited for a while, hoping he might feel better, but his condition kept worsening. So we decided not to take any risk, called an ambulance, and took him to the hospital. He is currently under observation," Mishra told news agency PTI.Mandhana, one of Indian cricket’s most prominent faces and a recent World Cup champion, was set to marry Muchhal in an intimate ceremony attended only by close family and friends.The celebrations in Sangli had been underway through the week, with fans catching rare glimpses of the usually reserved opener enjoying her pre-wedding festivities.Mandhana and Muchhal’s relationship goes back to 2019, when they met through mutual friends in Mumbai’s creative circles.The couple kept their bond private for years while balancing demanding careers — Mandhana leading India’s charge on the global stage and Muchhal expanding his footprint in films and music.They made their relationship public only in July 2024, on their fifth anniversary.Since then, the couple has shared limited but cherished glimpses of their journey, including Muchhal’s widely discussed proposal at DY Patil Stadium following India’s World Cup triumph.Leading a blindfolded Mandhana onto the very pitch where she had made history, Muchhal went down on one knee with a ring, later cementing the moment with a tattoo of “SM18” on his forearm.The couple was to formalise their union on November 23, 2025, a date they had chosen to mark the beginning of their next chapter. With the ceremony now postponed indefinitely, the family is prioritising Mandhana’s father’s health.The couple has not issued a public statement yet.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/sports/cricket/news/smriti-mandhanapalash-muchhal-wedding-indefinitely-postponed-cricketers-father-unwell/articleshow/125518823.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 16:24:23 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125518837,width-1070,height-580,imgsize-1286969,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>From Bihar to Bengal: How SIR is reshaping voter rolls; a deep dive into how it works</t>
+  </si>
+  <si>
+    <t>Photo: Generative AI
+The SIR and the Constitution
+Laws behind electoral revision
+SIR evolution
+SIR timeline
+How's SIR different from Special Revision
+SIR vs Special Revision
+What's the political controversy?
+INDIA bloc against SIR
+Why does it matter?
+West Bengal CM Mamata Banerjee led a rally protesting against the SIR exercise, in Kolkata. (ANI Photo)
+What happened in Bihar SIR?
+Congress MP Priyanka Gandhi Vadra, Samajwadi Party MP Akhilesh Yadav, TMC MP Mahua Moitra and others at a protest by INDIA bloc parliamentarians against the Election Commission's Special Intensive Revision (SIR) of electoral rolls in Bihar, during the Monsoon session of Parliament in New Delhi. (PTI Photo)
+What does the Election Commission say?
+CEC Gyanesh Kumar on SIR
+Tech-driven SIR
+NEW DELHI: Across India, from big metros to small towns and remote settlements, a quiet but significant exercise is under way to refresh the country’s voter rolls. The Special Intensive Revision, or SIR, has Booth Level Officers visiting homes with updated lists, seeking confirmations and corrections as they work through one of the world’s largest electoral databases.What began as routine verification has unexpectedly drawn intense national attention, sparking debate and renewed curiosity about how India’s most fundamental democratic document is kept accurate.As the Election Commission races to update the rolls ahead of crucial elections, political parties are sounding the alarm. They argue that SIR, instead of merely removing duplication, could alter electoral equations by disproportionately affecting certain voter groups.With the Supreme Court in the loop, opposition concerns mounting and millions engaging with the process, the political mood is one of cautious anticipation. A question is now beginning to surface as the exercise unfolds.Backing the poll body's decision to carry out this intensive exercise, Chief Election Commissioner (CEC) Gyanesh Kumar has said that "pure electoral rolls are inevitable for strengthening democracy.""The world's biggest voter list purification exercise was conducted in Bihar alone, and once the drive is extended to 51 crore voters in 12 states, it will mark a historic achievement for the Election Commission and the nation," Gyanesh Kumar added.However, more than a technical administrative task, it has become a political saga, carrying legal, constitutional and social implications that go to the heart of India’s most elemental democratic right. The vote.SIR rests on one of the most powerful lines in the Indian Constitution. Article 324 hands the Election Commission the sweeping authority to run the country’s elections. Not just the voting day spectacle, but everything that makes it possible.This single provision gives the Commission the right to step in whenever it believes the integrity of the process needs attention, including the upkeep of the voter list.That constitutional muscle is reinforced by the Representation of the People Act, 1950, which doesn’t just permit revisions of the electoral roll but explicitly allows the Commission to go beyond the usual annual updates. The law opens the door for deeper, more exhaustive exercises when the situation demands it, and the Registration of Electors Rules lay out the procedures to follow.In other words, SIR isn’t an improvisation but a legally grounded tool designed for moments when the regular maintenance of the rolls isn’t enough.While most years witness a “summary revision” focusing on new eligibles and basic updates, SIR is distinct. It combines a full-fledged house-to-house enumeration, rigorous document verification, and mass data audits.India’s first major enumeration drives date to the early post-independence years, under the Representation of the People Acts of 1950 and 1951. The earliest “intensive” revisions built the foundational voter rolls, but as the population grew and people’s mobility increased, summary revisions became the norm.While a Summary Revision focuses on new eligibles and routine corrections, SIR goes far deeper, involving statewide house-to-house verification, detailed scrutiny of entries, and large-scale data audits.For instance, under a Summary Revision, a voter who has shifted homes must file a form to update their address. Under SIR, the Booth Level Officer visits that address, confirms whether the voter still lives there, checks if anyone new has become eligible, and updates the roll based on physical verification rather than waiting for the voter to initiate the change.The political storm around the Special Intensive Revision (SIR) has intensified, with the Congress preparing a major protest rally in Delhi in the first week of December to oppose what it called a “politically motivated” overhaul of voter rolls.Congress leader KC Venugopal alleged that the Election Commission was acting “at the behest of the BJP,” while Rahul Gandhi has described SIR as an attempt to “institutionalise vote theft.”The confrontation has also shifted to the courts, with both the Trinamool Congress and the DMK moving the Supreme Court against the ongoing revision in West Bengal and Tamil Nadu, arguing that compressed timelines and inconsistencies in the process risk disenfranchising genuine voters.Opposition parties collectively claim that the timing of the SIR, the scale of proposed deletions in states like Bihar, and alleged procedural lapses point to an attempt to skew the electoral field ahead of crucial polls, particularly impacting migrants, minorities and other vulnerable voter groups.Poll-bound states are sharply split over the SIR of electoral rolls, with three chief ministers from West Bengal, Tamil Nadu and Kerala, attacking the process, while Assam has been kept out of the exercise this year.In Assam, chief minister Himanta Biswa Sarma said the Election Commission "could not" conduct SIR because “the NRC has not yet been notified.”He said SIR requires NRC data to verify citizenship and added that “in Assam’s case, notification is still pending.” The ECI has instead ordered a Special Summary Revision, which the state “fully supports.”Sarma said the aim is an “error-free and foreigner-free” voters’ list and that SIR will be taken up next year after the NRC notification.Union home minister Amit Shah has also said that the Bharatiya Janata Party (BJP) fully supports the Election Commission’s Special Intensive Revision, describing it as an essential exercise to cleanse the electoral rolls, PTI reported. Shah also took aim at the Congress’ ‘Voter Adhikar Yatra’ in Bihar, claiming the opposition launched the campaign to “save infiltrators,” and alleging that the party “wants to win elections with their help. ”West Bengal chief minister Mamata Banerjee has been the strongest critic, calling the process dangerous and rushed. Referring to the deaths of booth-level officers, she asked: “How many more lives will be lost? How many more need to die for this SIR?” She has termed the rollout “unplanned, chaotic and dangerous.”Mamata Banerjee has also written a strongly worded letter to CEC Gyanesh Kumar, urging him to stop the SIR.Tamil Nadu chief minister M.K. Stalin called SIR “flawed, confusing, and dangerous,” warning that forms are so complex that “even well-educated people will have their heads spinning.” He alleged political intent, saying, “If you cannot defeat us, you seek to delete us.”Kerala CM Pinarayi Vijayan called the EC’s move “a challenge to the democratic process,” criticising the use of old data formats and warning it could “undermine the public mandate.”With three states objecting to the process and Assam opting out due to pending NRC notification, the SIR rollout has emerged as one of the most politically charged administrative exercises ahead of the 2026 electoral season.Before the Bihar polls, CEC Gyanesh Kumar claimed the first phase of the Special Intensive Revision (SIR) in Bihar had concluded “without a single appeal,” signalling what the Election Commission views as a smooth and uncontested verification process.The state’s electorate now stands at 7.42 crore, down from 7.89 crore before SIR, a reduction of nearly 47 lakh from the old rolls. However, compared to the draft roll published on August 1, which had removed 65 lakh names on grounds such as death, migration and duplication, the final tally actually shows an increase.A total of 21.53 lakh new voters were added after the draft publication, while 3.66 lakh names were removed, resulting in a net gain of 17.87 lakh electors between the draft and final lists. The EC said the final numbers reflected corrections made during claims and objections and demonstrate the scale of the verification process undertaken under SIR.The Election Commission has defended the Special Intensive Revision as a routine but essential clean-up of the country’s electoral rolls, insisting the exercise is aimed at making voter lists “transparent, accurate and fully inclusive.”In a detailed press brief, the Commission said the purpose of SIR is to ensure that all eligible citizens are added and no ineligible names remain, describing it as part of a broader effort to create “error-free” rolls across states.Responding to criticism from opposition parties, the Chief Election Commissioner Gyanesh Kumar told reporters that “misinformation” was being spread about the process, accusing some leaders of “firing from the Election Commission’s shoulder.”The EC had also clarified discrepancies flagged in Bihar, saying that additions made after the draft roll were within rules that allow updates until ten days before nominations.The Election Commission is leaning heavily on digital tools to execute the Special Intensive Revision, with a mix of citizen-facing apps and backend platforms supporting the massive house-to-house verification exercise.Voters can use the Voter Helpline app and the ECI portal to check their registration status, download or submit forms, correct entries and, in some cases, even book a call with their Booth Level Officer (BLO). These tools allow electors to view pre-filled details pulled from legacy rolls and upload missing documents online, reducing duplication and easing the administrative burden during the nationwide verification drive.On the field side, officials rely on the BLO App (formerly Garuda), a mobile platform used for house-to-house verification, confirming voter residence, updating addresses, and capturing photographs and GPS-tagged data.The app also lets BLOs record polling-station facilities and track verification progress in real time, feeding directly into supervisory dashboards.The Special Intensive Revision has emerged as more than an administrative exercise. It now sits at the intersection of politics, perception and democratic trust.Whether SIR ultimately strengthens the integrity of India’s voter rolls or deepens existing doubts will depend not only on the Election Commission’s execution, but also on how transparently the process is communicated and how responsibly political parties engage with it.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/india/from-bihar-to-bengal-how-sir-is-reshaping-voter-rolls-a-deep-dive-into-how-it-works/articleshow/125517788.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 15:44:22 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125518373,width-1070,height-580,imgsize-94492,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>Chandigarh under Article 240: No bill this Winter Session; what the change would mean</t>
+  </si>
+  <si>
+    <t>File photo
+What's The Constitution (131st Amendment) Bill, 2025
+What's the political row?
+NEW DELHI: The ministry of home affairs, issuing a clarification over the Constitution (131st Amendment) Bill, said on Sunday that the central government has "no intention" of introducing the Bill in the upcoming Winter Session of Parliament.The ministry said the intent behind the legislation is to "simplify the Central Government’s law-making process" for the Union Territory of Chandigarh and that the Bill is "still under consideration with the Central Government".The Bill reportedly aims to bring the Union Territory of Chandigarh under the ambit of Article 240 of the Constitution, a provision that empowers the president to issue regulations and legislate directly for certain Union territories."The proposal only to simplify the Central Government’s law-making process for the Union Territory of Chandigarh is still under consideration with the Central Government. No final decision has been taken on this proposal. The proposal in no way seeks to alter Chandigarh’s governance or administrative structure, nor does it aim to change the traditional arrangements between Chandigarh and the States of Punjab or Haryana," the ministry said."A suitable decision will be taken only after adequate consultations with all stakeholders, keeping in mind the interests of Chandigarh. There is no need for any concern on this matter. The Central Government has no intention of introducing any Bill to this effect in the upcoming Winter Session of Parliament," the MHA said.According to bulletins issued by the Lok Sabha and Rajya Sabha, the government will introduce The Constitution (131st Amendment) Bill, 2025 in the Winter Session of Parliament beginning December 1.The Bill proposes to place Chandigarh in the same constitutional category as Union territories without legislatures, including the Andaman &amp; Nicobar Islands, Lakshadweep, Dadra &amp; Nagar Haveli and Daman &amp; Diu, and Puducherry when its assembly is suspended or dissolved.If enacted, the move could pave the way for Chandigarh to once again have an independent administrator, similar to the arrangement that existed when the UT had its own chief secretary.​The government has also listed a provisional set of 10 Bills for the coming session, the bulletin noted.Article 240 currently empowers the president to make regulations for specified UTs “for the peace, progress and good governance” of these territories. However, once a legislative body is set up under Article 239A, as in Puducherry, the president’s power to issue such regulations ceases from the date of the legislature’s first sitting. Regulations issued under Article 240 may amend or repeal parliamentary laws applicable to the UT and carry the same authority as an Act of Parliament.AAP MP Vikramjit Singh urged an intervention on the issue, calling the amendment "politically sensitive" and asking all MPs from Punjab to meet Union home minister Amit Shah.Citing media reports, he posted on X that the proposal seeks to bring Chandigarh under Article 240 "like several other UTs". He also warned that "Chandigarh is currently administered by the Punjab governor, and with the new law, it is likely to be administered by an independent administrator.""Punjab claims on Chandigarh have historical significance. Chandigarh was made capital of Punjab after partition as Lahore went to Pakistan,” he said, recalling that after the 1966 reorganisation of Punjab, the city became the joint capital of Punjab and Haryana. He noted that under multiple accords, the Centre “promised to make Chandigarh the capital of Punjab.” Singh added, “I request all MPs from Punjab to immediately call upon the home minister. ”Chandigarh’s administration has shifted over the decades. Initially run by an independent chief secretary after its creation in 1966, the UT came under the administration of the Punjab governor from June 1, 1984, with the chief secretary’s role recast as Adviser to the Administrator.In 2016, the Centre attempted to restore the old model by appointing former IAS officer K J Alphons as administrator, but withdrew the move following protests from then Punjab chief minister Parkash Singh Badal and opposition parties including the Congress and AAP.Punjab continues to assert its claim over Chandigarh, with chief minister Bhagwant Mann reiterating the demand for its immediate transfer during the recent Northern Zonal Council meeting in Faridabad.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/india/chandigarh-under-article-240-no-bill-this-winter-session-what-the-change-would-mean/articleshow/125518088.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 15:41:08 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125518333,width-1070,height-580,imgsize-192338,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>Meta under fire: Filings allege adult strangers contacted minors; Elon Musk responds</t>
+  </si>
+  <si>
+    <t>“Terrible”
+.
+“trafficking of humans for sex.”
+What Meta said about these allegations
+“We strongly disagree with these allegations, which rely on cherry-picked quotes and misinformed opinions in an attempt to present a deliberately misleading picture. The full record will show that for over a decade, we have listened to parents, researched issues that matter most, and made real changes to protect teens – like introducing Teen Accounts with built-in protections and providing parents with controls to manage their teens’ experiences. We’re proud of the progress we’ve made and we stand by our record.”
+What former Instagram executive said about user safety on Meta’s sites
+“You could incur 16 violations for prostitution and sexual solicitation, and upon the 17th violation, your account would be suspended,”
+“a very, very high strike threshold.”
+Tesla CEO Elon Musk has responded to filings that allege Facebook parent Meta was aware that millions of adult strangers were contacting minors on its sites. Replying to a post by Time that reported these serious accusations against the Mark Zuckerberg-led social media giant, the world’s richest man wrote:The report cited a court filing, which was unsealed this week, also claimed that sex trafficking on Meta platforms was difficult to report and often left unaddressed. The filing includes testimony from Instagram’s former head of safety and well-being, Vaishnavi Jayakumar, who said she was shocked to learn that Meta had a “17x” strike policy for accounts allegedly involved inIn a statement to Time, a Meta spokesperson said:In her testimonial, Jayakumar said,calling itPlaintiffs also argued that internal documents supported her statements.The brief, submitted in the Northern District of California, also alleged that Meta knew about significant harms affecting young users and engaged in efforts to downplay those risks.According to the filing, Meta was aware that millions of adult strangers were contacting minors on its sites and that its products worsened mental health challenges in teens.That content involving eating disorders, suicide, and child sexual abuse was repeatedly detected but rarely removed. The report claims Meta did not disclose these harms to the public or Congress and declined to adopt safety measures that may have protected young users.The brief comes from a large multidistrict lawsuit involving more than 1,800 plaintiffs, including families, school districts, and state attorneys general. The suit alleges that the companies behind Instagram, TikTok, Snapchat, and YouTube “relentlessly pursued a strategy of growth at all costs” while overlooking risks to children’s health. The newly unsealed claims about Meta represent only a portion of the wider case.According to the filing, the allegations are based on depositions of current and former Meta executives, as well as internal communications, research, and presentations obtained during discovery. The brief quotes from these materials, though the underlying documents remain sealed and were not independently reviewed by TIME.Even so, the brief describes internal discussions and research indicating that Meta pursued young users since 2017 despite evidence that its platforms could be harmful or potentially addictive for kids. The filing states that employees proposed various safety measures, but executives often rejected them due to concerns that certain protections might reduce teen engagement or hinder user growth.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/technology/social/elon-musks-one-word-reaction-to-filings-alleging-mark-zuckerbergs-meta-was-aware-about-adult-strangers-contacting-minors-on-its-sites/articleshow/125516932.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 12:44:25 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125516958,width-1070,height-580,imgsize-811625,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>'Fake news': French navy on Pak media reports on Op Sindoor; calls Rafale claims fabricated</t>
+  </si>
+  <si>
+    <t>French navy slams Pakistan's misinformation campaign
+'Objective Is To Destroy The Enemy': Op Sindoor Echoes As Indian Army Vows Stronger Response to Pak
+(With inputs from agencies)
+NEW DLEHI: The French Navy on Sunday criticised Pakistani media for publishing what it described as “misinformation and disinformation” about India’s Operation Sindoor , after one outlet claimed a French officer had confirmed Pakistani air superiority and the shooting down of Indian Rafale jets during a border confrontation earlier this year in May.In a statement issued on its official X handle, the ‘Marine Nationale’ said the article had fabricated comments and even misidentified the officer involved.“FAKENEWS: These statements were attributed to Captain Launay who never gave his consent for any form of publication. The article contains extensive misinformation and disinformation,” the post said. Pakistan based broadcaster Geo TV’s November 21 report had quoted a “Jacques Launay” as allegedly praising the Pakistan air force during a supposed May 6–7 aerial engagement involving over 140 fighters, and claiming Indian Rafales were downed with Chinese support. The French Navy said the officer’s real name is Captain Yvan Launay - and none of the comments attributed to him were genuine.Clarifying his actual role, the Navy said: “First name is Yvan, not Jacquis. Contrary to what has been established in the article, his responsibilities are limited to commanding the organic naval air station where the French Rafale Marine aircraft are stationed.”According to the statement, Captain Launay’s presentation at the Indo-Pacific conference was strictly technical.“Captain Yvan Launay presented the assets of his naval air base, the missions of the Rafale fighter jet, and the French carrier strike group concept,” it said.Responding to questions at the event, Launay “neither confirmed nor denied that Indian aircrafts had been shot down” during Operation Sindoor and “refused to comment on possible jamming of the Indian Rafale by Chinese systems.” The Navy added that “he never mentioned the Chinese J10.”These clarifications directly contradicted another claim published by the Pakistani outlet, which had said Launay linked alleged Rafale performance issues to operational shortcomings and compared the jet with the Chinese J-10C. The Navy reiterated that such references were never made.The BJP spokesperson and its IT cell chief Amit Malviya reacting to the post by French navy called out the Geo TV's report as "same old, fabricated claims." He also took a dig at the journalist behind it Hamid Mir.In a post on X he said, "The French Navy has called out Pakistan’s Geo TV and its correspondent Hamid Mir for spreading “misinformation and disinformation.” In his report, Hamid Mir peddled the same old, fabricated claims about Rafales and the so-called May conflict and has now been publicly exposed. When official institutions start debunking their propaganda, you know how desperate Pakistan’s misinformation machinery has become. Incidentally Hamid Mir has several friends in Indian media. Spot them."France’s rebuttal comes days after a US report by US-China Economic and Review Commission exposed how in aftermath of Operation Sindoor, China initiated a “disinformation campaign” to “hinder the sales of French Rafale aircraft in favour of its own J-35s, using fake social media accounts to propagate AI images of supposed debris from the planes that China’s weapon destroyed.”The Operation Sindoor was launched in response to the dastardly Pahalgam terror attack in Jammu &amp; Kashmir on April 22 earlier this year, in which 26 civilians were killed - the incident later prompted Indian response targeting Pakistan-sponsored terrorist sites.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/india/fake-news-french-navy-slams-pakistan-media-over-misinformation-on-operation-sindoor-calls-rafale-claims-fabricated/articleshow/125518149.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 15:24:51 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125518187,width-1070,height-580,imgsize-688549,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>Epstein controversy: Andrew makes rare public appearance since losing titles</t>
+  </si>
+  <si>
+    <t>Image credit: AP
+Live
+Andrew Windsor Slammed For 'No Response' Over Epstein-Links Interview Letter From U.S.
+The Times
+Mirror
+Daily Mail
+Entitled: The Rise and Fall of the House of York
+Mirror
+Britain's former prince Andrew Mountbatten-Windsor has been spotted in public for the first time since being stripped of his royal titles and asked to leave the Royal Lodge, marking a rare outing amid ongoing scrutiny over his past associations with convicted sex offender Jeffrey Epstein, Birminghamreported.The former Duke of York was photographed horse-riding on the Windsor estate, an outing that royal experts say has drawn mixed feelings from his neighbours, Prince William and Princess Kate. The couple, who recently moved into the Grade II-listed Forest Lodge just a few miles from Andrew, are reportedly maintaining a sense of responsibility for his welfare despite ongoing family tensions.Former prince Andrew has faced growing pressure over his links to Epstein. In a statement, he said, “I vigorously deny the accusations against me.” Meanwhile, his failure to respond to the US House Oversight and Government Reform Committee’s interview request has drawn criticism from its members, who are conducting their own inquiry into Epstein’s associates. According to, Democratic committee members recently wrote to Andrew requesting a transcribed interview regarding his long-standing association with Epstein, but he has yet to comply, fueling mounting frustration.Speaking to the, former BBC Royal correspondent Jennie Bond noted, “While there is no love lost between William, Catherine and Andrew, my understanding is that they, and the rest of the royal family, believe they still have a duty of care for his welfare and mental health. Andrew has reportedly become isolated, depressed, and solitary. It’s not his fault if photographers are ready to pounce when he ventures out, and I don’t think the Prince and Princess would begrudge him a ride around the park for some fresh air.Andrew is preparing to leave the Royal Lodge after more than two decades and move to a smaller residence on the Sandringham estate in Norfolk, a change that experts say will ease tensions for the Prince and Princess of Wales. “Obviously it would be more convenient if it wasn’t on their doorstep, but they know this is temporary,” Bond added.Royal commentators suggest that King Charles may be displeased with the publicity surrounding Andrew’s outing. Bond said, “It is unfortunate that pictures of Andrew are in the press again, drawing attention away from the work the rest of the family are doing. It would be preferable if he were seen engaging in charity work or some other productive activity.”A royal insider told thethat the photographs of Andrew riding on Windsor Castle grounds, which are taxpayer-funded, do not present a favourable image.Prince William is believed to have played a key role in the decision to remove Andrew’s titles. Andrew Lownie, author of the biography, told the, “From what I know of him and his father, William would have played quite an active role in stiffening Charles’ resolve. Andrew’s voluntary surrender of titles was deemed insufficient, and Charles realised the gravity of the situation, particularly after continued press coverage distracted from other royal duties.”Kate Middleton is believed to have fully supported King Charles III’s decision, distancing from Andrew in bid to protect the monarchy’s reputation. Lownie added, “They do not want further reputational damage from being linked to him.”</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/world/uk/epstein-controversy-andrew-makes-rare-public-appearance-since-losing-titles-william-and-kate-maintain-duty-of-care/articleshow/125515796.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 10:44:40 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125515840,width-1070,height-580,imgsize-921611,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>US arrests tech company CTO and three others for selling Nvidia's banned chips to China</t>
+  </si>
+  <si>
+    <t>America has banned Nvidia from selling its high-end H200 GPUs to China. The US government release further said that the government will also seek forfeiture of 50 Nvidia H200 GPUs that were intended to be exported unlawfully.
+Nvidia H20 Chips for China: What’s Really Going On?
+Two American citizens and two nationals of the People’s Republic of China (PRC) -- all residing in the United States -- have been charged with a conspiracy to illegally export cutting-edge Nvidia Graphics Processing Units (GPUs) to the PRC. John Eisenberg, assistant attorney general for the Justice Department’s National Security Division, said in a press release.Those arrested include Hon Ning Ho, aka “Mathew Ho,” an American citizen born in Hong Kong, 34, residing in Tampa, Florida; Brian Curtis Raymond, American citizen, 46, Huntsville, Alabama; Cham Li, aka “Tony Li,” PRC national, 38, San Leandro, California, and Jing Chen, aka “Harry Chen,” PRC national on F-1 nonimmigrant student visa, 45, Tampa, Florida. On November 19, 2025, Ho and Chen were arrested and appeared in court in the Middle District of Florida, while Raymond was arrested and appeared in the Northern District of Alabama.Raymond was briefly the chief technology officer (CTO) of the Virginia-based Corvex, which describes itself as an AI cloud computing company and is planning to go public. Corvex listed Raymond as its CTO and part of its leadership team in a press release on November 10.Corvex told CNBC yesterday that it “had no part in the activities cited in the Department of Justice’s indictment,” and that “the person in question is not an employee of Corvex. Previously a consultant to the company, he was transitioning into an employee role but that offer has been rescinded.”“The indictment unsealed yesterday alleges a deliberate and deceptive effort to transship controlled Nvidia GPUs to China by falsifying paperwork, creating fake contracts, and misleading U.S. authorities,” said John A. Eisenberg, Assistant Attorney General for National Security. “The National Security Division is committed to disrupting these kinds of black markets of sensitive U.S. technologies and holding accountable those who participate in this illicit trade. ”“As demonstrated by this indictment, the US Attorney's Office for the Middle District of Florida is firmly committed to safeguarding our country’s national security,” said U.S. Attorney Gregory W. Kehoe for the Middle District of Florida. “Thanks to the dedicated investigative work by our law enforcement partners, these defendants who wrongfully exported this sensitive technology are facing justice.”According to the indictment, the PRC seeks to become the world leader in AI by 2030 and seeks to use AI for its military modernization efforts and in connection with the design and testing of weapons of mass destruction and deployment of advanced AI surveillance tools. The PRC seeks cutting-edge U.S. technology in furtherance of that goal, including Nvidia GPUs. To protect U.S. national security, beginning in October 2022, the Department of Commerce implemented new license requirements for the export of these technologies to the PRC.As alleged, from September 2023 to November 2025, Ho, Raymond, Li, and Chen conspired to violate these critical U. export controls, by illegally exporting advanced GPUs to the PRC through Malaysia and Thailand. In furtherance of the conspiracy, the conspirators used Janford Realtor, LLC—a Tampa, Florida-based company owned and controlled by Ho and Li—as a front to purchase and then illegally export controlled GPUs to the PRC. Despite its name, Janford Realtor, LLC, was never involved in any real estate transactions. Raymond, though his Alabama-based electronics company, supplied NVIDIA GPUs to Ho and others for illegal export to the PRC as part of the conspiracy.As further alleged in the indictment, the conspiracy encompassed four separate exports of Nvidia GPUs to the PRC. The first and second exports resulted in 400 Nvidia A100 GPUs being exported to the PRC between October 2024 and January 2025. The third and fourth exports to the PRC were disrupted by law enforcement and therefore not completed. These attempted exports related to ten Hewlett Packard Enterprises supercomputers containing Nvidia H100 GPUs and 50 separate Nvidia H200 GPUs.Despite knowing that licenses were required to export these items to the PRC, none of the conspirators ever sought or obtained a license for any of these exports. Instead, they lied about the intended destination of the GPUs to evade U.S. export controls. The indictment further alleges that the conspirators received over $3.89 million in wire transfers from the PRC to fund this unlawful scheme.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/technology/tech-news/tech-company-cto-and-three-others-arrested-for-exporting-nvidia-chips-that-are-banned-to-china/articleshow/125511701.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 02:24:14 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125511699,width-1070,height-580,imgsize-256718,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>Can arterial plaque be reversed? Top US doc says...</t>
+  </si>
+  <si>
+    <t>CREDIT: CANVA
+The hidden reality:
+What really works
+Daily habits that make all the difference, Dr. Vassily suggests:
+Every thing takes time, nothing is a magic cure
+What this means for us
+For decades, many of us have been told that arterial plaque buildup, that is, the sticky fatty deposits that line our arteries, is a permanent condition. The common belief is that once these plaques form, invasive procedures like stenting or bypass surgery are the only ways to manage the risks of heart attack and stroke. But Dr. Vassily Eliopoulos, a Cornell-educated longevity specialist and emergency medicine physician in New York, challenges this idea with a hopeful message: plaque can often be reduced and arteries healed without surgery.What most people don’t realize, says Dr. Eliopoulos, is that the majority of heart attacks are caused by “soft plaques” rupturing inside the arteries, not by the hard blockages that show up on traditional scans. These soft plaques are far more dangerous because their sudden rupture causes clots that block blood flow abruptly.This means you can pass a standard stress test and still be at high risk for a heart attack because those tests only detect flow limitations caused by calcified plaques. Stents and bypass surgery address the immediate blockage and can save your life in an emergency, but they don’t fix the root cause—the chronic disease process that causes these plaques to form and inflame your arteries.According to Dr. Eliopoulos, the secret to reversing plaque lies in a comprehensive, root-cause strategy that targets the underlying inflammation and metabolic dysfunction driving the disease.The first step is precision testing. Advanced blood markers such as APOB measure the number of atherogenic lipoprotein particles-those tiny, sticky cholesterol carriers that actually form plaques. Inflammatory markers like high-sensitivity CRP and Lp-PLA2 reveal active inflammation fueling plaque growth. Imaging technology like coronary CT angiography (CCTA) or Cleerly scans show exactly where plaques are forming and whether they are stable or vulnerable.Next comes targeted nutrition. Dr. Eliopoulos strongly promotes a Mediterranean-style diet rich in polyphenols, omega-3 fatty acids (from wild fish, flaxseed), fiber, and antioxidants. Avoiding added sugars and ultra-processed foods is crucial because they damage the vessel linings and promote inflammation.It’s not just what you eat, but how you move and rest that shapes heart. The doctor recommends:Taking a 5-10 minute walk after every meal to improve blood sugar control and circulation.Engaging in zone 2 cardio workouts (moderate intensity where you can still talk) at least three times a week to enhance cardiovascular fitness.Prioritizing restful sleep of at least seven and a half hours per night to lower stress hormones and inflammation.In some cases, supplements and advanced therapies enhance the healing process. Niacin and berberine help reduce the harmful lipid particles. Peptides like BPC-157 and Mod-C show promise in calming vascular inflammation and supporting mitochondrial function. Intravenous nutrients such as glutathione and arginine boost nitric oxide production, which relaxes blood vessels and improves their health.However, Dr. Eliopoulos emphasizes that no pill or procedure alone can replace lifestyle changes as the foundation of arterial healing.Plaque reversal is a marathon, not a sprint. Meaningful change usually takes six to twelve months of strict adherence to this protocol. But patients often notice improvements in energy, mental clarity, and cardiovascular health as they go.The “root cause” approach aligns with the latest cardiovascular research showing that focusing solely on blockages without addressing inflammation and metabolic health only treats the symptoms, not the disease itself.If you think heart disease and plaque buildup are irreversible, Dr. Eliopoulos’ message brings fresh hope. Modern cardiology is evolving beyond emergency interventions toward precision diagnostics and lifestyle-oriented therapies that target disease drivers.If you have any concerns about your heart health or plaque burden, consider seeking care from a physician who uses advanced testing and supports a comprehensive lifestyle strategy.This approach empowers you to take control of your heart health and possibly avoid invasive interventions altogether. Remember, every small change in diet, movement, sleep, and stress management can move the needle on arterial plaque and put you on the path to longer, healthier living.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/life-style/health-fitness/can-arterial-plaque-be-reversed-top-u-s-doc-says-/articleshow/125502158.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 07:00:00 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125502196,width-1070,height-580,imgsize-988832,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>Inside job: How a police constable 'trained' gang for Bengaluru's biggest cash van robbery; 6 held</t>
+  </si>
+  <si>
+    <t>(R-L) Police constable Annappa Naik, Xavier
+Bengaluru Cash Van Robbed Of ₹7 Crore After Fake RBI Officers Trick Staff In A Filmy-Style Heist
+3 nabbed from Hyd lodge
+BENGALURU: Six states, 200 cops, a mountain of phone data and CCTV footage dump, and 72 hours of massive hunt. Plus human intelligence. With this, Bengaluru police have arrested six persons, including a police constable, and recovered Rs 6.29 crore of the Rs 7.11 crore spirited away from a bank van on Nov 19.The arrested include Annappa Naik of Govindapura police station in the east division; Xavier, a former employee of CMS Cash Management Services, which runs cash vans; Gopal Prasad, in charge of transport vehicle; their friends Naveen, Nelson and Ravi.The gang had executed a near-flawless, insider-assisted daring daylight heist: Three months of planning, 15-day recce, chose spots outside CCTV coverage, multiple vehicles with fake number plates, and communicated in different languages via WhatsApp calls to avoid detection.Police commissioner Seemant Kumar Singh said the crime — committed on Dairy Circle flyover, a shadow police jurisdiction — was reported two hours later with wrong coordinates, robbing cops of the golden-hour advantage.Personnel from Bengaluru’s Central Crime Branch and South division were sent out to Kerala, Tamil Nadu, Goa, Andhra Pradesh, and Telangana.The three conspirators Annappa, Xavier and Gopal Prasad — all from Bengaluru — were arrested based on CCTV analysis and Rs 5.76 crore was recoveredfrom them.Based on their information, their three other accomplices were nabbed from a lodge in Hyderabad and Rs 53 lakh was recovered. Police are on the trail of two more suspects believed to be part of a sixto eight-member gang and are yet to recover Rs 82 lakh, the last missing tranche.Constable Naik allegedly trained the group in executing the crime without leaving easy clues, while the CMS transport in-charge provided realtime movement details of the cash van. Xavier received the cash once the gang exited the city. An SUV used in the crime was found in Chittoor district, containing broken cash chests.Commissioner Singh flagged lapses at CMS, stating RBI guidelines for cash transportation were violated. He said he would recommend cancellation of the firm’s licence.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/city/bengaluru/inside-job-how-a-police-constable-trained-gang-for-bengalurus-biggest-cash-van-robbery-6-arrested/articleshow/125514482.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 07:10:22 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125514484,width-1070,height-580,imgsize-29015,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>'No intention to ... ': MHA offers big clarification on Chandigarh bill</t>
+  </si>
+  <si>
+    <t>Also Read |
+Why the controversy erupted?
+NEW DELHI: The ministry of home affairs on Sunday clarified that the central government had no intention to introduce any bill to "alter Chandigarh’s governance or administrative structure" in the upcoming Winter Session of Parliament.This came after a political row erupted over its plans to place Chandigarh under Article 240 of the Constitution through the 131st Amendment Bill in the upcoming winter session, bringing it in line with UTs such as the Andaman and Nicobar Islands, Lakshadweep, Dadra and Nagar Haveli, and Daman and Diu."The proposal only to simplify the Central Government’s law-making process for the Union Territory of Chandigarh is still under consideration with the Central Government. No final decision has been taken on this proposal. The proposal in no way seeks to alter Chandigarh’s governance or administrative structure, nor does it aim to change the traditional arrangements between Chandigarh and the States of Punjab or Haryana," MHA said in a statement."A suitable decision will be taken only after adequate consultations with all stakeholders, keeping in mind the interests of Chandigarh.There is no need for any concern on this matter. The Central Government has no intention of introducing any Bill to this effect in the upcoming Winter Session of Parliament," it added.The BJP-led Centre had proposed bringing the Union Territory of Chandigarh under Article 240 of the Constitution. This would allow the President to appoint a lieutenant governor for the city and make regulations directly. The MHA, however, clarified that the proposal would "simplify the Central Government’s law-making process Chandigarh" and it was "still under consideration with the Central Government."The move triggered sharp reactions across Punjab’s political spectrum, with several leaders calling it an attack on Punjab’s rights over Chandigarh.Punjab chief minister Bhagwant Mann strongly criticised the move, calling it “a conspiracy to snatch” Punjab’s capital. In his statement, he said “Chandigarh was, is and will always remain an integral part of the state.” Mann argued that Punjab, as the “parent state,” has full rights over Chandigarh and accused the Centre of acting unjustly.If cleared, the proposal could allow the Centre to appoint an independent administrator for Chandigarh, similar to how the UT earlier had its own chief secretary. The idea already met strong opposition from the ruling Aam Aadmi Party, Congress, and Shiromani Akali Dal.AAP supremo Arvind Kejriwal also launched a sharp attack on the central government. In a post on X, he said the proposed amendment was “a direct assault on Punjab’s identity and its constitutional rights” and accused the Centre of “tearing apart the federal structure”. He added that Punjab was being deprived of its rightful share, writing that it amounted to “wounding the very soul of Punjab”. He declared that “Chandigarh belongs to Punjab and shall remain Punjab’s”.Chandigarh currently serves as the shared capital of Punjab and Haryana. For decades, both states have claimed full rights over the city, but it has remained a Union Territory since 1966.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/india/no-intention-to-mha-offers-big-clarification-on-chandigarh-article-240-move-after-political-row/articleshow/125517315.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 13:29:26 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125517522,width-1070,height-580,imgsize-642692,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>$1 trillion squad: Musk, Zuckerberg, Pichai, and fellow billionaires break the internet</t>
+  </si>
+  <si>
+    <t>Why the '$1 trillion squad' image is everywhere
+EXPOSED: Mark Zuckerberg Embarrassed on Hot Mic Admitting Total Confusion During Trump Dinner
+Top social media reactions to the viral “$1 trillion squad” photo
+“The Avengers in real life. So is Elon channeling Nick Fury, Tony Stark or Captain America”
+“The Great Round Tech Talk Without a Round Table”
+“Quick, here comes my mom. Put it out”
+“You wanna go and get high or have a beer”
+“Seven of the brokest dudes on the planet”
+“World’s wealthiest hacky-sack circle”
+“Elon, please don’t get us thrown in jail”
+“They all got the same shoes”
+“What are half of them wearing the same shoes”
+“Picture missing the real legend… me”
+“Four men of stature and three clowns”
+“Tech gangs of back street”
+“All bases covered”
+“At least three of these dudes are sociopaths and would never spend a second with the others”
+“Who is going back to finish his bachelor’s degree”
+A meme that says everything about 2025
+An image of the world’s most powerful tech titans standing in a dimly lit parking lot has become the internet’s favourite new obsession. The so-called “$1 trillion squad” photo featuring Elon Musk Sundar Pichai , Jensen Huang, Sam Altman, Tim Cook and Jeff Bezos has blown up across X, triggering a wave of memes, jokes, edits and conspiracy-tier commentary. The image racked up hundreds of thousands of views in under two days, turning into one of the biggest viral moments of late 2025. Although the picture is not real, its cultural impact absolutely is.The picture taps perfectly into the cultural mood of 2025, a year dominated by AI arms races, compute shortages, billionaire influence battles and Chip War gossip. Seeing the most influential CEOs of the decade lined up like GTA villains or Marvel bosses felt almost too on the-nose for the internet to resist.The exaggerated cinematic lighting, the luxury cars in the background, Jensen Huang in his trademark leather jacket and Musk puffing a cigar created a visual that looked less like a business meeting and more like a poster for a dystopian tech thriller. The absurdity of the scenario, powerful billionaires casually hanging out as if plotting the next chapter of the AI revolution, made it instantly iconic.Adding to the surreal energy of the shot is the lineup of cars behind them.The Cybertruck looming on one side, a row of glossy supercars parked like getaway vehicles, and even a vintage off-road truck sitting proudly in the corner make the scene feel staged for a Hollywood heist. Each car feels like a character: the stealth-black hypercars matching the CEOs’ “final boss” vibe, the Cybertruck reinforcing Musk’s unmistakable presence, and the retro truck injecting an oddly charming contrast. Together, they create a backdrop so dramatic and overpowered that the internet couldn’t help but treat the whole thing as a film still waiting for its plot.Even funnier, the sequel image showing them inside a cheap, cramped motel-style room with a microwave, plastic chairs and mismatched furniture. The contrast between trillion-dollar influence and a 50 dollar a night room only intensified the meme storm.A large chunk of the audience initially wondered if the photo was genuine. Its hyper-real yet slightly uncanny style fits the chaotic spirit of 2025, where AI generated content often circulates faster than fact checks. Despite confirmations that the image is synthetic, the debate only fuelled the meme machine.People remixed the image with boss fight music, created comic panels and even asked AI tools like Grok and Mid journey to generate sequels, spin-offs and alternate universes. It was no longer just a viral picture, it was turning into a multi-format franchise.Here are some of the funniest and most creative reactions that flooded X after the image went viral:The “$1 trillion squad” photo works because it captures a simple truth: tech leaders have become the cultural superheroes or supervillains of our time. Their influence spans AI, chips, space, communications, politics and markets. Seeing them together, even artificially, taps into fascination, fear and humour all at once.And because the image is AI generated, it also symbolises something bigger: AI is no longer just reshaping technology, it is reshaping culture, imagination and the way we interpret power.If Musk reacts to it, which he often does with memes, expect this moment to double in reach and spawn countless remixes. The internet might not be ready for the “$1 trillion squad” cinematic universe, but it is definitely asking for it.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/technology/social/1-trillion-squad-musk-zuckerberg-pichai-and-fellow-billionaires-break-the-internet-with-viral-photo/articleshow/125508025.cms</t>
+  </si>
+  <si>
+    <t>Sat, 22 Nov 2025 21:53:05 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125508048,width-1070,height-580,imgsize-97592,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>Tejas crash: IAF pilot Namansh Syal’s mortal remains reach native village; last rites in Kangra</t>
+  </si>
+  <si>
+    <t>Mortal remains of Wing Commander Namansh Syal reach his native village in Kangra (ANI image)
+IAF Officer Namansh Syal Flown Back to India After Tejas Jet Crash in Dubai Air Show
+Who was Wing Commander Namansh Syal?
+Wing Commander Namansh Syal (ANI image)
+How the tragic mishap occurred?
+NEW DELHI: The mortal remains of Wing Commander Namansh Syal, who lost his life in the Tejas fighter jet crash during the Dubai Air Show 2025, were brought to his native village of Patialkar in Himachal Pradesh’s Kangra district on Sunday.Villagers, family members and officials gathered to pay emotional tributes as his last rites are set to be performed.The Indian Air Force (IAF) confirmed the pilot’s demise after the aircraft crashed and burst into flames during a low-level aerobatic demonstration at Al Maktoum International Airport, Dubai on Friday.Local residents and friends described Syal as a “gem” and the pride of their village and school.Sandeep Kumar, a local, said, “"We are from the same village as Namansh, Patialkar. Everyone in our village is sad. He was like our younger brother. This should not have happened. We do not have words. We met him 3-4 months ago when he visited our village.”Pankaj Chadha, who studied alongside Wing Commander Namansh Syal, recalled their school days and how he was a gem."I have also studied in the same school as Namansh, Sainik School Sujanpur Tira. We have lost one of our gems. He was the pride of our school.We will go to his native village, Patialkar. He made all of us very proud," Chadha said.The mortal remains were flown from Dubai to Sulur Air Base in Coimbatore earlier in the day, where Coimbatore District Collector Pavankumar G. Giriyappanavar, Superintendent of Police Dr K Karthikeyan and IAF officials paid floral tributes. The Emirati Defence Forces also accorded Syal a ceremonial guard of honour in recognition of his bravery and service.Wing Commander Namansh Syal, 37, hailed from Patialkar village in Nagrota Bagwan tehsil of Kangra district, Himachal Pradesh. He was posted at Sulur Air Force Station in Tamil Nadu and was attached to No 45 Squadron, the “Tejas Daggers” of the IAF.Syal, an experienced fighter pilot, was a graduate of Sainik School Sujanpur Tira, Hamirpur and the National Defence Academy (NDA). He trained with the Hunter Squadron at the Air Force Academy and earned his wings with distinction.His father, Jagannath Syal, is an ex-armyman who later became a teacher, while his wife, Afsaan, also serves as a Wing Commander at Sulur Air Base. The couple has a seven-year-old daughter.Himachal Pradesh chief minister Sukhvinder Singh Sukhu paid tribute, calling Syal a “courageous, dutiful, and valiant pilot”. He added that “the nation has lost a brave son of Kangra district.”Defence minister Rajnath Singh expressing his grief wrote in a post on X, “Deeply anguished at the loss of a brave and courageous IAF pilot during an aerial display in Dubai Air Show. My heartfelt condolences to the bereaved family. The nation stands firmly with the family in this tragic hour.”Chief of Defence Staff General Anil Chauhan also offered condolences, affirming the armed forces’ solidarity with the family.The Tejas Mark-1 fighter jet was performing an eight-minute aerobatic demonstration when it could not recover from a low-altitude “negative G-turn,” plunging to the ground and erupting into flames in front of a large audience.Visuals from the Dubai Air Show showed the jet crashing and sending thick black smoke into the sky. Emergency teams rushed to the site, but Wing Commander Syal could not eject in time and sustained fatal injuries.This was the second crash involving the lightweight multi-role Tejas since its induction into the IAF a decade ago. The first crash, near Jaisalmer in March last year, saw the pilot safely eject. The IAF has ordered a court of inquiry to ascertain the cause of the crash, coordinating with Dubai aviation authorities and recovering the aircraft’s black box.Veteran pilots highlight that such accidents can occur due to sudden loss of power, control malfunction or spatial disorientation during negative G maneuvers.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/india/teary-farewell-heartfelt-tributes-wing-commander-namansh-syals-mortal-remains-reach-native-village-last-rites-in-kangra/articleshow/125518191.cms</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125518362,width-1070,height-580,imgsize-953947,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>Pant says 'maarne de usko', Muthusamy sends next ball over long-on - Watch</t>
+  </si>
+  <si>
+    <t>Rishabh Pant press conference: On Shubman Gill injury, India Playing XI, pitch and more
+NEW DELHI: Senuran Muthusamy showed patience to bring up his first Test century while Marco Jansen scored freely at the other end, as South Africa scored a strong first-innings total of 489 on day two of the second Test in Guwahati.India’s stand-in captain Rishabh Pant was seen guiding his bowlers throughout the day. At times he gave direct instructions, at times he encouraged his teammates, and at times he told them to stay calm, saying he would handle the field. One such moment involved Washington Sundar, when Pant told him to let the batter go for a big shot, and the batter responded by hitting a six.In the 124th over of the South African innings, Senuran Muthusamy, who did not play the first Test, was facing Washington Sundar. One run had already come from Marco Jansen in that over. Before the last ball, Pant said, "marne de usko." (let him hit.)Sundar tossed the ball outside off, and Muthusamy hit it over long-on for six.Muthusamy was later dismissed by Mohammed Siraj in the 139th over. He scored 109 off 206 balls with 10 fours and 2 sixes. He became the third South African batter to score a Test century at number seven or below against India in India.Muthusamy played cautiously in the morning session with occasional boundaries, and then played more freely after tea, taking a cue from Jansen.Their 97-run stand between Muthusamy and Jansen, with Muthusamy reaching his first Test hundred and Jansen scoring his fourth Test fifty, strengthened South Africa’s push for a first Test series win in India in 25 years. South Africa scored 489 in their first innings.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/sports/cricket/india-vs-south-africa/ind-vs-sa-rishabh-pant-says-marne-de-usko-senuran-muthusamy-sends-next-ball-over-long-on-watch/articleshow/125518104.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 15:20:04 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125518669,width-1070,height-580,imgsize-4941604,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>Cyclone 'Senyar' likely to form over Bay of Bengal: 10 key points</t>
+  </si>
+  <si>
+    <t>Representative Image
+Here are 10 key points you need to know:
+The low-pressure area, currently well-marked, is expected to move west-northwestwards and intensify into a depression over the southeast Bay of Bengal around Nov 24.
+It may further strengthen into a cyclonic storm over the southeast Bay of Bengal within 48 hours after forming as a depression.
+The IMD issued a Special Message on Saturday, a protocol followed when there is significant likelihood of cyclone formation.
+IMD Director General Mrutyunjay Mohapatra said once the system becomes a depression, bulletins will be issued every six hours, and every three hours after it turns into a cyclone.
+The warnings are anticipatory, advising fishermen to avoid venturing into the sea and cautioning about heavy rain over the Andaman &amp; Nicobar Islands .
+. Skymet Weather also flagged the system’s potential to develop into a cyclonic storm next week but said the track remains uncertain.
+Skymet president GP Sharma suggested the system may bypass Tamil Nadu and Andhra Pradesh, potentially moving towards West Bengal or Bangladesh, but exact paths are difficult to predict at this stage.
+IMD forecast isolated very heavy rainfall over Andaman &amp; Nicobar Islands from Nov 22 to 27, with squally winds of 40-50 kmph.
+Wind speeds are expected to increase further as the system intensifies into a depression and possibly a cyclone.
+Officials said it is too early to predict landfall or rainfall zones for mainland India; impacts will become clearer once the system consolidates over the Bay of Bengal.
+CHENNAI: A low-pressure area over the Strait of Malacca and adjoining south Andaman Sea is likely to intensify into a cyclonic storm over the Bay of Bengal next week, the India Meteorological Department (IMD) said.If named, the cyclone will be called Senyar — meaning "lion" — a name submitted by the United Arab Emirates. The Bay of Bengal has historically produced intense cyclones in the September–October season, including Montha in late October, which left two dead and damaged over 80,000 hectares of crops.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/city/chennai/cyclone-senyar-likely-to-form-over-bay-of-bengal-10-key-points/articleshow/125516130.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 11:27:23 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125516226,width-1070,height-580,imgsize-38158,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>How much water should you be drinking every day: Risks of dehydration</t>
+  </si>
+  <si>
+    <t>Why is water important for kidneys
+How water should you drink every day
+How to reach the ideal number
+Signs of dehydration
+How overhydration affects kidneys
+Tips for staying hydrated and protecting
+kidney health
+Disclaimer: This article is informational only and not a substitute for medical advice
+We all know that water is extremely important for our body, and especially our kidneys, since it helps the organ remove extra waste and fluid from the body. However, when it comes to how much water should one drink in the day, the consensus is not always clear – while the general rule of thumb is to drink 8 glasses, this can hugely vary due to age, weight, activity levels, climate etc. On the other hand, staying dehydrated is a sure shot sign to invite kidney trouble. So, how much water should one drink to not tire out our kidneys ? Let’s take a look…Kidneys balance the fluids and the salts in the bod, and keeps the urine clear. Clear urine means a lower chance of kidney stones and urinary infections. When you do not drink enough water, the kidneys have to work harder to make the urine more concentrated. That extra work can strain the kidneys over time. Good water intake helps the kidney function smoothly, and may also lower the risk of long-term kidney disease. Hence, drinking enough water is crucial for the kidneys Health authorities such as the U.S. National Academies of Sciences, recommend that men drink 3.7 liters of fluids each day, while women should drink 2.7 liters of fluids each day. However, this translates into fluids from all sources, such as water, juice, other beverages, and food. Studies show that most adults meet these recommendations, though it can be less in older adults, or those with limited physical activity.On the other hand, this is, in no way, a magic number, since water needs change with age, weight, climate and exercise. For example, water needs of people who live in hot places, or who do intense physical labour are higher, because they lose more fluid. This apart, pregnant and breastfeeding women also need to drink more water.In a nutshell, there is no magic number, but rather a magic trick - the trick is to listen to your body. The body tells you when water is needed, so drink when you feel thirsty. However, do not drink too water, because it can lead kidney strain as well. If you live in a cold climate, or are not used to drinking too much water, you might have to set reminders to drink, since it is important to reach the minimum limit of water consumption at least.Not many know that even mild dehydration can make the kidneys feel tired. Warning signs of this include less urine, dry mouth, headache and fatigue. On the other hand, long term dehydration raises the chance of kidney stones, and can damage kidney function. Drinking enough water each day helps the kidneys flush out toxins, and prevents kidney stones and kidney function problems. To test, observe your urine. A dark color means you are likely dehydrated, while a colorless one means you are overhydrated. A light color urine is perfect when it comes to gauging ideal water consumption.Even though it is rare, drinking a lot of water quickly, can cause water intoxication or hyponatremia. Water intoxication or hyponatremia lowers the sodium in the blood, and can be dangerous. The condition stresses the kidneys, and can even affect the brain. To counter this, most adults should drink water when they are thirsty, apart from a couple of glasses here and there.• Eat water-rich foods like fruits and vegetables.• Limit the sugary drinks. The caffeinated and sugary drinks may cause dehydration.• Monitor urine color as a simple hydration check.• Adjust the water intake when you exercise, or it is too hot/cold. If you have underlying health conditions such as diabetes and heart issues, let your doctor recommend your daily intake.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/life-style/health-fitness/kidney-health-how-much-water-should-you-be-drinking-every-day-symptoms-and-risks-of-dehydration-and-over-hydration/articleshow/125412800.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 15:00:00 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125412799,width-1070,height-580,imgsize-510327,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>Mass kidnappings: Over 300 missing in Nigeria after armed raid on catholic school</t>
+  </si>
+  <si>
+    <t>AP file photo
+A week marked by escalating abductions
+Churches also targeted
+Why mass kidnappings are on the rise
+Gunmen have abducted more than 300 students and teachers from a Catholic co-educational school in Niger state, in one of Nigeria’s largest mass kidnappings, a Christian group said on Saturday.The attackers stormed St Mary’s School early Friday, days after gunmen raided a secondary school in neighbouring Kebbi state and seized 25 girls, deepening security fears in Africa’s most populous nation.The Christian Association of Nigeria (CAN), which initially reported 227 people abducted, said the figure rose to 303 students and 12 teachers after a “verification exercise,” as cited by AFP.The victims, boys and girls aged eight to 18, account for nearly half of St. Mary’s total enrolment of 629 students.Bago, whose administration had already shut several schools, announced a statewide closure as efforts intensify to rescue the abducted students and teachers. Neighbouring states have also suspended classes as a precaution.At the national level, the education ministry has ordered 47 boarding secondary schools across the country to close temporarily.The attack capped a week of kidnappings across Nigeria that targeted both Christians and Muslims, with several incidents appearing to be financially motivated.On Monday, 25 Muslim schoolgirls were abducted during an armed assault on a school in Kebbi, where the vice principal was killed. Local media also reported that 64 people were seized from their homes in neighbouring Zamfara state, as cited by Time Magazine.Earlier this week, a live stream captured a gunman attacking the Christ Apostolic Church in Oke Isegun, Kwara State, killing two people and abducting more than 30. A church official told Reuters the kidnappers had demanded “around $69,000 in ransom per person.” The latest attacks on Christian communities are expected to heighten pressure on the Nigerian government and could prompt the Trump Administration to consider more direct involvement.The recent surge in kidnappings is driven by complex motives and not necessarily religious divisions, experts warn. A report released last year by the Africa Centre for Strategic Studies noted a sharp rise in abductions by “criminal gangs,” known locally as “bandits.”The report also highlighted a shift toward large-scale abductions because they “increase the possibility of government ransom payments, which are more substantial than what can be cobbled together by individual ransoms.”Schools also remain particularly vulnerable, as they often lack the security needed to prevent coordinated mass attacks.Nigeria remains scarred by the abduction of nearly 300 schoolgirls by Boko Haram in Chibok, Borno state, more than a decade ago. Some victims are yet to return.US defence secretary Pete Hegseth urged Abuja to “take both urgent and enduring action to stop violence against Christians” during talks with Nigerian National Security Advisor Nuhu Ribadu, the Pentagon said Friday, as cited by AFP.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/world/rest-of-world/mass-kidnappings-over-300-missing-in-nigeria-after-armed-raid-on-catholic-school-what-we-know-so-far/articleshow/125518457.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 15:53:28 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125518473,width-1070,height-580,imgsize-1086233,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>Explained: How new labour laws may cut take-home salary; raise PF &amp;amp; gratuity contributions</t>
+  </si>
+  <si>
+    <t>Currently, PF contributions are set at 12% of the basic salary. (AI image)
+.
+New Labour Codes: Why will your take home pay go down?
+Mandatory retirement contributions, including provident fund and gratuity payments, are set to rise following the implementation of the Code on Wages.
+and payments, are set to rise following the implementation of the Code on Wages. The new regulation requires that an employee's basic salary must constitute at least 50% of their total CTC, or meet the government-specified percentage.
+This adjustment will lead to higher contributions as both PF and gratuity calculations are based on an individual’s basic pay .
+. Whilst this change ensures enhanced retirement benefits for workers, it also means reduced take-home pay, as the increased contributions will come from the existing CTC.
+The regulation concerning basic salary aims to stop organisations from intentionally maintaining low basic salary whilst increasing allowances to reduce their obligations towards retirement benefits and gratuity.
+Currently, PF contributions are set at 12% of the basic salary, whilst gratuity payments are determined by the final basic pay and tenure at an organisation.
+New labour Codes: Impact on Take-Home Salary
+.
+New Labour Codes: Top points to know
+.
+New labour codes 2025: The government has notified new labour laws that may require companies to ensure basic salary makes up at least 50% of the total cost-to-company (CTC), potentially prompting changes in how pay packets are structured. As a result, for many employees, take-home pay could come down over time as contributions to retirement savings are likely to rise.The government has unified 29 labour-related central laws into four extensive Labour Codes: the Code on Wages (2019), Industrial Relations Code (2020), Code on Social Security (2020), and Occupational Safety, Health and Working Conditions (OSHWC) Code (2020). Starting November 21, 2025, these Codes seek to simplify regulatory compliance, enhance worker safeguards, and modernise India's workforce regulations in accordance with contemporary economic conditions.The Code on Wages became operational on Friday, with the government expected to announce detailed rules within the next 45 days. Companies will need to restructure their salary frameworks to comply with these new regulations.According to experts, employees might receive reduced take-home pay under the new rules, as both provident fund and gratuity contributions would increase within the existing CTC framework."The new labour codes unify the definition of 'wages' under the Code on Wages and Social Security. This would mean better retirement security through higher gratuity and provident fund but a possible dip in take-home pay if employers restructure allowances downward to offset costs," Suchita Dutta, executive director of the Indian Staffing Federation was quoted as saying by ET.The standardisation of wage definitions across labour codes ensures uniformity in computing social security benefits."Wages now include basic pay, dearness allowance and retaining allowance; 50% of the total remuneration (or such percentage as may be notified) shall be added back to compute wages, ensuring consistency in calculating gratuity, pension and social security benefits," explains Anjali Malhotra, partner at professional services firm Nangia Group.According to Puneet Gupta, partner, People Advisory Services at EY India, the implementation of labour codes could result in increased gratuity payments since calculations will be based on "wages", encompassing basic salary and all allowances, excluding HRA and conveyance allowance.The new labour codes introduce universal minimum wages for all employees across organised and unorganised sectors, replacing the earlier system that covered only about 30% of workers.A statutory floor wage will be set by the government based on minimum living standards, and no state can fix wages below this benchmark.A uniform definition of wages now applies, where basic pay, dearness allowance, and retaining allowance together must account for at least 50% of total remuneration.The codes mandate gender equality, prohibiting discrimination in hiring, wages, or employment terms for similar work, along with universal wage payment coverage that ensures timely payments and prevents unauthorised deductions for employees earning up to ₹24,000 per month. Overtime compensation must be paid at twice the normal rate.Several compliance and enforcement reforms are included as well. Decriminalisation of offences replaces imprisonment with monetary penalties for first-time violations, and compounding of offences allows certain fines to be settled without prosecution.The threshold for government approval of lay-offs, retrenchment, or closure has increased from 100 to 300 workers, with states allowed to raise it further.Work-from-home is formally recognised in services sectors based on mutual agreement, while dispute resolution will be handled by two-member tribunals for faster outcomes.A mandatory 14-day strike notice aims to prevent sudden disruptions and includes mass casual leave within the definition of a strike.The codes extend social protections to new categories, requiring aggregators to contribute 1–2% of annual turnover towards gig and platform workers’ social security (capped at 5% of their payments).Fixed-term employees become eligible for gratuity after just one year of continuous service instead of five.The inspector-cum-facilitator system introduces randomised, technology-driven inspections to reduce harassment and improve transparency. Compliance is simplified through digitisation of records, as well as a streamlined one license, one registration, one return system.Employers must issue formal appointment letters detailing job roles, wages, and social security.The codes also expand labour flexibility and reduce burdens on small units.Night shifts for women are permitted in all establishments with their consent and safety measures. Contract labour rules include an all-India licence valid for five years.Factory thresholds have been raised to 20 workers for units using power and 40 for those without, reducing compliance requirements for smaller factories.Finally, working hours remain capped at 8 hours per day and 48 hours per week, with flexible weekly structures allowed through mutual consent.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/business/india-business/explained-how-new-labour-laws-could-hit-your-take-home-salary-increase-your-provident-fund-gratuity-contributions/articleshow/125515961.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 13:10:18 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125516988,width-1070,height-580,imgsize-41896,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>Bengaluru shocker: Pilot 'sexually assaults' cabin crew member at hotel; booked</t>
+  </si>
+  <si>
+    <t>(The victim's identity has not been revealed to protect her privacy as per Supreme Court directives on cases related to sexual assault)
+(With agency inputs)
+HYDERABAD: A case has been filed against the pilot of a chartered flight for allegedly sexually assaulting a 26-year-old cabin crew member at a hotel in Bengaluru, police said on Sunday.Although the incident took place in Bengaluru on November 18, the victim lodged a complaint at Begumpet Police Station in the city, leading to the registration of a ‘Zero FIR’ under relevant sections of the BNS, officials added."After returning to Hyderabad, the crew member reported the incident here and we registered a case and it was transferred to Halasuru police station in Bengaluru. They are investigating the case," a police official at Begumpet Police Station said.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/city/hyderabad/bengaluru-pilot-sexually-assaults-cabin-crew-member-at-hotel-booked/articleshow/125517291.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 13:19:20 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125517480,width-1070,height-580,imgsize-12048,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>'You're not dumb, I am the one who trusted you': Bowler recalls what Dhoni said</t>
+  </si>
+  <si>
+    <t>MS Dhoni (PTI Photo/R Senthilkumar)
+Indian pacer Deepak Chahar recently appeared on Big Boss and shared a memorable incident from the 2019 Indian Premier League (IPL) involving MS Dhoni . The incident occurred during a match between Chennai Super Kings and Punjab Kings at the MA Chidambaram Stadium.Chennai Super Kings had set a target of 160 runs for 3 wickets in their 20 overs. Sarfaraz Khan was batting well, who went on to score 67 runs off 59 balls with four fours and two sixes that day.This was Chahar's first experience bowling in the death overs, as he typically bowled with the new ball. MS Dhoni had given him this responsibility after careful consideration."In that game, for the very first time, I was bowling at the death. Before that, I had the responsibility of bowling with the new ball. So after lots of consideration, Mahi bhai threw me the ball in the death, and Sarfaraz was the batter. In the preparation, we discussed the type of deliveries we need to bowl to a certain batter. The plan was to bowl a slow delivery, and I went with a leg cutter," Chahar said.The situation became tense when Chahar's execution didn't go as planned. His first two deliveries resulted in no-balls, leading to eight runs without a legal delivery being bowled."Now, my feet stopped on the first ball, and it went full toss. So, he smashed a four, and it ended up being a no-ball. The plan was right, but the execution was wrong. So, I repeated the same ball and it was again a no-ball. Eight runs came without a ball being bowled. Now, Mahi Bhai came furiously and said something to me.""Mahi bhai said that 'you are not dumb; I am the one who trusted you.' I thought that this was the last time I got the chance to bowl in the death overs. In the same five balls, I gave away five runs and picked up a wicket. We won the game at the end."Despite this incident, CSK went on to win the match by 22 runs.Chahar had an impressive season in 2019. He finished as the third-highest wicket-taker with 22 wickets in 17 innings, maintaining an average of around 22 and an economy rate under seven.The video of Chahar sharing this story on Big Boss has gained significant attention on social media platforms.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/sports/cricket/ipl/top-stories/ms-dhoni-said-you-are-not-dumb-i-am-the-one-who-trusted-you-india-pacer-recalls-during-his-latest-big-boss-appearance/articleshow/125518000.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 15:10:18 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125518111,width-1070,height-580,imgsize-243428,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>From Article 370 to Pegasus: Justice Kant set to take oath as CJI tomorrow; key cases</t>
+  </si>
+  <si>
+    <t>File photo
+'No Remorse, God Provoked Me': Lawyer Rakesh Kishore Defends His Shoe Attack On CJI BR Gavai
+Article 370 verdict
+Sedition law on hold
+Pegasus spyware case
+Bihar electoral rolls revision
+Gender justice and local governance
+Governor–president powers reference
+Security breach in PM Modi’s convoy
+One rank-one pension (OROP)
+AMU minority status reconsideration
+Justice Surya Kant, a judge known for his role in several landmark constitutional and civil liberties rulings, will on Monday be sworn in as the 53rd Chief Justice of India. He succeeds Justice BR Gavai, who demits office on Sunday evening.Appointed as the next CJI on October 30, Justice Kant will have a relatively long tenure of nearly 15 months, serving until February 9, 2027, when he turns 65.Born on February 10, 1962, in Haryana’s Hisar district, Justice Surya Kant rose from a modest background to the country’s highest judicial office. Before his elevation, he practised as a lawyer in Hisar and subsequently at the Punjab and Haryana High Court, where he delivered several influential judgments. In 2018, he was appointed Chief Justice of the Himachal Pradesh high court.His time in the Supreme Court has been defined by involvement in key cases that shaped national policy, constitutional interpretation and civil liberties.Justice Kant was part of the historic bench that upheld the abrogation of Article 370, which removed Jammu &amp; Kashmir’s special status. The judgment remains one of the most consequential constitutional rulings of recent times.He was on the bench that effectively suspended the colonial-era sedition law, directing states and the Centre not to register new FIRs under Section 124A IPC until the government completed a reconsideration of the provision. The order was widely viewed as a major push for free speech.Justice Kant was also part of the bench that heard the Pegasus surveillance allegations. The court appointed a committee of cyber experts to investigate the claims, remarking that the state cannot be given a “free pass in the name of national security.”In another significant order, Justice Kant asked the Election Commission to disclose details of 65 lakh voters dropped from Bihar’s draft rolls during a Special Intensive Revision, stressing the importance of transparency in electoral processes.He led a bench that reinstated a woman sarpanch removed from office unlawfully, calling out gender bias in the decision. He later directed that one-third of seats in bar associations, including the Supreme Court Bar Association, be reserved for women—an unprecedented push for gender equity within the legal fraternity.Justice Kant was part of the Constitution Bench hearing the presidential reference on the powers of Governors and the President in dealing with state legislation—an issue with wide political and federal implications. The verdict is awaited.He was also on the bench that appointed a panel headed by Justice Indu Malhotra to probe the 2022 security lapse during Prime Minister Narendra Modi’s visit to Punjab, noting that such sensitive matters require judicial scrutiny.Justice Kant upheld the One Rank-One Pension (OROP) scheme as constitutionally valid, while continuing to hear matters related to women officers seeking parity in permanent commission in the armed forces.On a seven-judge bench, Justice Kant helped overturn the 1967 Aligarh Muslim University ruling, paving the way for a fresh examination of AMU’s minority status.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/india/from-article-370-to-pegasus-justice-surya-kant-set-to-take-oath-as-53rd-cji-on-monday-key-judgments-he-was-a-part-of/articleshow/125516612.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 13:03:22 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125517157,width-1070,height-580,imgsize-461344,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>Grand Udaipur wedding today: Trump Jr, Bollywood celebs to attend</t>
+  </si>
+  <si>
+    <t>Parents of the bride, Raj and Padmaja Mantena (in pastel jacket and saree, respectively), with Donald Trump Jr. and girlfriend Bettina Anderson (centre, holding hands), and (2nd from left) Lakshyaraj Singh Mewar, at the City Palace in Udaipur
+B town Celebs Light Up Netra Mantena’s Star Studded Udaipur Wedding!
+UDAIPUR/VIJAYAWADA: US President Donald Trump's son Donald Trump Jr has landed, as have Jennifer Lopez and Justin Bieber. Kriti Sanon, Madhuri Dixit and Shahid Kapoor joined in. All are here for the Sunday wedding of Andhra-origin US baron Rama Raju Mantena's daughter Netra in Udaipur, sending ripples far beyond the erstwhile Rajasthan royal hub also known as the City of Lakes.Not surprisingly, attention has been riveted on Trump Jr, who arrived late Friday accompanied by his girlfriend and proceeded to Leela Palace hotel. He is likely to be under spotlight Sunday, too, when Netra ties the knot with Vamsi Gadiraju against the backdrop of historic Jag Mandir Island Palace.Columbia University alumnus Vamsi is co-founder of Superorder, a New York-based tech firm that aims to revolutionise the food delivery industry. He also has Telugu roots and was part of Forbes' list of Under 30 prodigies. Netra completed her undergraduate studies in pharmacology and works in New York.On Saturday, Trump Jr. and Rama Raju -- also known as Raj -- visited Udaipur City Palace and met Lakshyaraj Singh Mewar of the former Mewar royal family.The meeting was steeped in tradition, with discussions on Mewar's rich history. Singh presented the two symbolic emblems, which Trump Jr called "special and memorable" and expressed admiration for the region's historical figures such as Maharana Kumbha, Maharana Sanga, and Maharana Pratap.Udaipur has also turned into a fortress. Security is extensive, involving coordination between local police and US Secret Service. Drones monitor the skies. Lake jetties and hotel perimeters are under close watch, with VIP movements facilitated through dedicated corridors and tight entry checks.Wedding festivities kicked off late Friday with performances by Kriti, Madhuri and Shahid. The celebrations continued Saturday with shows by Lopez --- who flew in on a chartered flight from Ireland --- and Bieber. The wedding will be followed by a "grand reception" on Nov 24.The Mantenas trace their roots to Vijayawada. Rama Raju moved to the US in 1984, starting seven companies there. His latest is Integra Connect, which offers value-based, precision medicine, leading the industry in real-world data, analytics, and AI capabilities for speciality care organisations.Rama Raju made his fortune by selling the companies he founded in the pharmacy and IT sectors by unlocking their true value. A pharmacy graduate from Vijayawada, Rama Raju is the nephew of Gokaraju Gangaraju, former BJP MP and entrepreneur. Rama Raju made his fortune by selling the companies he founded in the pharmacy and IT sectors by unlocking their true value.In the process of selling his firms, Rama Raju made high-profile connections with global entrepreneurs and celebrities. The connection with the US President's family happened during the years they both lived in Florida as neighbours."Raj has a long-standing friendship with Trump's family. He really wants to bring qualitative change in the lives of cancer patients and has big plans to invest in India's pharma sector," said a close friend.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/city/jaipur/trump-jr-bieber-lopez-bollywood-line-up-for-wedding-of-andhra-origin-us-barons-daughter/articleshow/125511388.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 04:15:26 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125515408,width-1070,height-580,imgsize-1541189,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
   </si>
   <si>
     <t>Relief for Indian-origin families: Canada to overhaul citizenship-by-descent rules; check details</t>
@@ -1140,6 +1716,58 @@
     <t>https://static.toiimg.com/thumb/msid-125515280,width-1070,height-580,imgsize-1142569,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
   </si>
   <si>
+    <t>Ladakh violence: SC to hear plea against Sonam Wangchuk's detention on Nov 24</t>
+  </si>
+  <si>
+    <t>Images/Agencies
+NEW DELHI: The Supreme Court is set to hear on Monday a plea filed by Sonam Wangchuk ’s wife, Gitanjali J Angmo. The plea challenges the climate activist’s detention under the stringent National Security Act (NSA) as illegal and an arbitrary exercise violating his fundamental rights.The matter will be heard before a bench comprising Justices Aravind Kumar and NV Anjaria. The top court had earlier, on October 29, sought responses from the Centre and the Ladakh administration on the amended plea filed by Angmo.Wangchuk was detained on September 26, two days after violent protests in Leh demanding statehood and Sixth Schedule status for Ladakh resulted in four deaths and over 90 injuries.Authorities have alleged that Wangchuk incited the unrest. He was transferred to a jail in Jodhpur, Rajasthan and booked under the NSA, which allows preventive detention of individuals deemed a threat to national security for a maximum of 12 months.The amended plea filed by Gitanjali Angmo contends that Wangchuk’s detention is “founded upon stale FIRs, vague imputations, and speculative assertions, lacks any live or proximate connection to the purported grounds of detention and is thus devoid of any legal or factual justification".The plea further highlights that Wangchuk, a recognized educator and climate activist for over three decades, has been subjected to a series of coordinated actions including notices for land lease cancellation, FCRA cancellation, a CBI investigation and summons from the Income Tax Department.According to the petition, these actions appear to be aimed at silencing a citizen exercising his democratic right to dissent rather than addressing genuine security concerns.The petition also highlights Wangchuk’s condemnation of the violence on social media. It quotes him saying it was “the saddest day of his life” and that such unrest would undermine Ladakh's ongoing five-year peaceful pursuit, or "tapasya," for development.Moreover, the plea points out that the complete grounds of Wangchuk’s detention were only supplied after 28 days. This, it says, is in clear violation of Section 8 of the NSA, which mandates communication within five days, extendable to ten in exceptional circumstances.Earlier, on October 6, the Supreme Court had issued notice to the Centre and Ladakh administration on a habeas corpus plea filed by Gitanjali Angmo, seeking Wangchuk’s immediate release.Solicitor General Tushar Mehta, representing the government, maintained that “law has been followed and grounds of detention supplied to Wangchuk.” However, the bench refused to pass any order on providing the grounds at the time and posted the matter for further hearing.Gitanjali Angmo has also approached President Droupadi Murmu seeking intervention, alleging a “witch-hunt” against her husband for advocating the people of Ladakh and raising concerns over police actions in the Union Territory after the September 24 violence.She compared the situation to colonial-era oppression, claiming misuse of Ladakh police by the Union home ministry."Is India really free? In 1857, 24,000 Britishers used 135,000 Indian sepoys to oppress 300 million Indians under orders from the Queen. Today, a dozen administrators are misusing 2400 Ladakhi police to oppress and torture 3 lakh Ladakhis under the orders of the MHA," Gitanjali wrote on X.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/india/ladakh-violence-sc-to-hear-plea-against-sonam-wangchuks-detention-on-nov-24-wife-terms-it-illegal/articleshow/125517212.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 13:56:23 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125517336,width-1070,height-580,imgsize-1012788,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>'India backs early end to conflict': Jaishankar speaks to Ukraine counterpart</t>
+  </si>
+  <si>
+    <t>ANI photo
+No Division Of Ukraine Or Limiting Military: EU 'Offers' 4 Changes To Trump For Zelensky’s Surrender
+NEW DELHI: External affairs minister S Jaishankar spoke to Ukraine’s foreign minister Andrii Sybiha on Saturday and discussed the latest developments in the Ukraine conflict.After the call, Jaishankar posted X, “Had a telecon with FM Andrii Sybiha last evening. Appreciate his briefing on the ongoing developments related to the Ukraine conflict. Reiterated India’s support for an early end to this conflict and the establishment of an enduring peace. ”The two leaders had last met in Canada in November during the G7 foreign ministers’ outreach session, where they reviewed bilateral ties and the situation on the battlefield. India has repeatedly said that only dialogue and diplomacy can lead to a fair and lasting settlement.The call came at a sensitive moment, as US president Donald Trump said he expects Zelenskyy to respond by next Thursday on the new 28-point plan to end the war, although he later said he “would like to get to peace”.The proposal also caused a storm in Washington on Saturday. Hours after Trump’s remarks, some Republican senators said secretary of state Marco Rubio told them that the document resembled a “Russian wish list”.The state department rejected that account, and Rubio later said the plan was drafted by the US.The episode, however, raised questions about the plan’s clarity and future. For Ukraine, the moment is even more difficult as Zelenskyy is facing a corruption scandal involving $100 million in alleged kickbacks linked to the state nuclear energy company, leading to cabinet resignations.Zelenskyy warned Friday that Ukraine is entering “perhaps the most difficult choice in its history”. Ukraine’s battlefield challenges and energy shortages ahead of winter have also increased pressure.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/india/india-backs-early-end-to-conflict-jaishankar-speaks-to-ukraine-counterpart-call-amid-trumps-peace-plan-looming-over-kyiv/articleshow/125515662.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 12:49:28 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125515875,width-1070,height-580,imgsize-25500,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>'Mazak bana rakha hai Test cricket ko': Pant's fiery message for Team IND star - watch</t>
+  </si>
+  <si>
+    <t>Rishabh Pant made his frustration clear with his teammates during Day 2 of the 2nd Test in Guwahati. (Agencies)
+Go Beyond The Boundary with our YouTube channel. SUBSCRIBE NOW!
+Rishabh Pant press conference: On Shubman Gill injury, India Playing XI, pitch and more
+Poll Was South Africa's lower middle order's performance surprising? Yes, unexpected strength No, they are capable players
+Stand-in captain Rishabh Pant ’s voice dominated Day 2 of the second Test in Guwahati, with several stump-mic moments revealing India’s rising frustration as South Africa strengthened their position. With Shubman Gill unavailable due to injury, Pant took charge on the field, and his constant instructions, reminders and corrections became one of the major talking points as India struggled to control the game.India’s over-rate issues and inability to take wickets only added to the pressure. Pant repeatedly demanded urgency from his bowlers and fielders between deliveries. In one clip, he said, "Yaar 30 seconds ka timer hai" (There’s a 30-second timer), followed by "Ghar pe khel rahe ho kya? Ek ball daal jaldi." (Are you playing at home? Bowl one quickly.)He also reminded Kuldeep Yadav about the two warnings India had already received, saying, "Yaar Kuldeep, dono baar warning le li" (Kuldeep, we’ve already taken two warnings).As delays continued, Pant grew sharper in tone, telling his team, "Pura ek over thodi na chahiye. Mazak bana rakha hai Test cricket ko." (We don’t need a whole over. You’ve made a joke out of Test cricket.)While organising the field, Pant insisted on handling the placements himself, saying, "Field mere ko karne de. Tu tappe se daalne ko dekh. Baaki ho jaayega kaam." (Let me set the field. You just focus on bowling quickly. The rest will fall in place.)At another moment, urging his side not to drop intensity, he said, "Bhai kal poori din mehnat kari hai yaar. Chhodenge nahi. Kaam karte raho." (We worked hard all day yesterday. We can’t let it slip now. Keep at it.)When Washington Sundar prepared to bowl, Pant again referred to the timer, saying, "Guys play with the timer, there's 1 minute timer for every over. come on yaar" (Play according to the timer, there’s a one-minute limit for every over, come on.)Pant’s comments reflected the tense phase India found themselves in, especially after South Africa’s lower middle order continued to frustrate the hosts. Senuran Muthusamy and Kyle Verreynne put on an 88-run stand for the seventh wicket before Ravindra Jadeja finally broke through.At lunch, South Africa reached 428 for 7 in 137 overs. Muthusamy was unbeaten on 107 from 203 balls, while Marco Jansen moved to 51 off 57 deliveries.Pant’s on-field exchanges became a key storyline on a day when South Africa controlled the contest and India searched for breakthroughs.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/sports/cricket/india-vs-south-africa/mazak-bana-rakha-hai-test-cricket-ko-rishabh-pants-fiery-message-for-team-india-star-caught-on-stump-mic-watch/articleshow/125517240.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 13:38:22 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125517372,width-1070,height-580,imgsize-63756,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
     <t>Last-minute air ticket cancellation? Up to 80% refund likely soon</t>
   </si>
   <si>
@@ -1155,6 +1783,21 @@
     <t>https://static.toiimg.com/thumb/msid-125514650,width-1070,height-580,imgsize-492063,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
   </si>
   <si>
+    <t>TVK resumes poll campaign: Vijay challenges SIR rollout; targets DMK for 'loot' in TN</t>
+  </si>
+  <si>
+    <t>NEW DELHI: Tamilaga Vettri Kazhgam chief Vijay on Sunday resumed its poll campaign in election-bound state on Tamil Nadu after a break of nearly two months following the tragic stampede. The newly-formed party challenged the challenged the Election Commission over its decision to rollout Special Intensive Revision (SIR).It further targeted the MK Stalin government in the state for "loot and dynasty politics", PTI reported.He said the TVK doesn’t make “empty promises” like the DMK on scrapping NEET, and instead was pushing to move education from the concurrent list to the state list, the news agency cited the actor-politician saying."Kancheepuram is the land of former Chief Minister Annadurai. Even former CM MGR placed Annadurai’s symbol on his party flag as a mark of respect for his guidance. The DMK holds a personal vendetta against our TVK party. We don’t carry such grudges, but we will question them because they have deceived the very people who trusted and voted for them. Their actions are nothing but drama. We will not remain silent about it.We have a natural connection with Kanchipuram, as our first public outreach campaign began in Parandur, right here in this district," ANI quoted him saying.Vijay criticised DMK for raising doubts about TVK’s ideology, insisting his party rests on strong ideological foundations rooted in equality and has, among other demands, called for a caste census.This was Vijay’s first address to party workers and the public since the September 27 Karur stampede, effectively restarting his campaign for next year’s state election.He spoke to party cadres, supporters and local residents at an indoor hall of an educational institution in Sunguvarchattiram, Kanchipuram district.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/india/tvk-resumes-poll-campaign-vijay-challenges-sir-rollout-in-sc-targets-dmk-for-loot-dynasty-politics-in-tamil-nadu/articleshow/125516698.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 12:38:56 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125516918,width-1070,height-580,imgsize-576442,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
     <t>'Won't shut down': Al-Falah University to worried parents amid ED probe, NAAC notice</t>
   </si>
   <si>
@@ -1168,21 +1811,6 @@
   </si>
   <si>
     <t>https://static.toiimg.com/thumb/msid-125503925,width-1070,height-580,imgsize-115496,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>Google faces 'break-up' fears again, this time for its $3 trillion-plus business</t>
-  </si>
-  <si>
-    <t>A federal judge is considering breaking up Google's dominant advertising technology business, a move that could reshape the internet's ad landscape. The Justice Department is pushing for a forced sale of key units, arguing it's necessary to restore competition. However, the judge expressed concerns about the lengthy process and potential appeals, suggesting quicker behavioral changes might be more practical. This case could mark the first major tech breakup in years, impacting Google's vast revenue streams.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/technology/tech-news/google-faces-break-up-fears-again-this-time-for-its-3-trillion-plus-business/articleshow/125515531.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 10:04:57 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125515539,width-1070,height-580,imgsize-496431,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
   </si>
   <si>
     <t>'Hand on shoulder, kiss on cheek': Gujarat cop named in teen's molestation complaint</t>
@@ -1199,6 +1827,23 @@
   </si>
   <si>
     <t>https://static.toiimg.com/thumb/msid-125515047,width-1070,height-580,imgsize-541952,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
+    <t>Smriti and Palash’s wedding: What’s the net worth of the power couple? - Find Out</t>
+  </si>
+  <si>
+    <t>Smriti Mandhana &amp; Palash Muchhal
+Palash Muchhal Proposes Cricketer Smriti Mandhana At DY Patil Stadium!
+Vice-captain Smriti Mandhana , one of India’s most celebrated and consistent women cricketers, is all set to marry music composer Palash Muchhal on November 23. The engagement itself was nothing short of cinematic: Palash proposed to Smriti at Mumbai’s DY Patil Stadium, the very venue where India clinched the Women’s World Cup earlier this month. Fans are now curious not just about their love story but also about the combined wealth of this power couple.Smriti’s earnings on the cricket field are substantial. She holds a Grade A contract with the BCCI , which comes with an annual retainer of Rs 50 lakh. On top of that, she receives match fees for every international appearance: Rs 15 lakh per Test, Rs 6 lakh per ODI, and Rs 3 lakh per T20I. Coupled with her growing list of endorsements and Women’s Premier League income, her net worth is estimated at around Rs 34 crore.The Women’s Premier League has been a major boost for Smriti’s finances. During the inaugural WPL auction, Royal Challengers Bengaluru acquired her for Rs 3.4 crore per season, making her one of the highest-paid female cricketers globally. Leading RCB to a WPL title further enhanced her brand value, reportedly increasing it by nearly 30%.Smriti’s brand endorsements add significantly to her wealth. Over the years, she has collaborated with major brands including Hyundai, Hero Motocorp, Red Bull, Garnier, Nike, Mastercard, Havells, Wrangler, Gulf Oil, Herbalife, Bata Power, and UNICEF India.Each campaign reportedly earns her between Rs 50 lakh and Rs 75 lakh, depending on its scale, contributing to her estimated net worth of Rs 32-34 crore.Palash Muchhal, meanwhile, has carved a successful path in music and filmmaking. Born in Indore in 1995 into a musical family, with sister Palak Muchhal already a known playback singer, Palash honed his talent early in Hindustani classical music and performed in charity concerts during his childhood.He has composed songs for films, television, and independent singles, with hits like “Party Toh Banti Hai” (Bhoothnath Returns), “Tu Hi Hai Aashiqui” (Dishkiyaoon), and “Musafir.” Beyond composing, he has directed over 40 music videos for major labels like T-Series and Zee Music, and has even acted in the film Khelein Hum Jee Jaan Sey. His net worth is estimated between Rs 20 crore and Rs 41 crore, coming from royalties, film projects, live shows, and music composition.Together, Smriti and Palash form one of cricket and entertainment’s wealthiest couples, with a combined net worth estimated between Rs 50 crore and Rs 75 crore. The duo has been dating since 2019 but maintained a low profile for years, only hinting at their relationship publicly in October 2025 when Palash teased that Smriti would soon become the “daughter-in-law of Indore.”</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/sports/cricket/news/smriti-mandhana-and-palash-muchhals-wedding-whats-the-net-worth-of-the-power-couple/articleshow/125517213.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 13:24:44 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125517214,width-1070,height-580,imgsize-920606,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
   </si>
   <si>
     <t>‘Don’t feel safe in Goa’: Russian DJ says 'rude cop abused us'</t>
@@ -1217,23 +1862,6 @@
   </si>
   <si>
     <t>https://static.toiimg.com/thumb/msid-125514959,width-1070,height-580,imgsize-28412,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>US arrests tech company CTO for exporting Nvidia's banned chips to China</t>
-  </si>
-  <si>
-    <t>America has banned Nvidia from selling its high-end H200 GPUs to China. The US government release further said that the government will also seek forfeiture of 50 Nvidia H200 GPUs that were intended to be exported unlawfully.
-Nvidia H20 Chips for China: What’s Really Going On?
-Two American citizens and two nationals of the People’s Republic of China (PRC) -- all residing in the United States -- have been charged with a conspiracy to illegally export cutting-edge Nvidia Graphics Processing Units (GPUs) to the PRC. John Eisenberg, assistant attorney general for the Justice Department’s National Security Division, said in a press release.Those arrested include Hon Ning Ho, aka “Mathew Ho,” an American citizen born in Hong Kong, 34, residing in Tampa, Florida; Brian Curtis Raymond, American citizen, 46, Huntsville, Alabama; Cham Li, aka “Tony Li,” PRC national, 38, San Leandro, California, and Jing Chen, aka “Harry Chen,” PRC national on F-1 nonimmigrant student visa, 45, Tampa, Florida. On November 19, 2025, Ho and Chen were arrested and appeared in court in the Middle District of Florida, while Raymond was arrested and appeared in the Northern District of Alabama.Raymond was briefly the chief technology officer (CTO) of the Virginia-based Corvex, which describes itself as an AI cloud computing company and is planning to go public. Corvex listed Raymond as its CTO and part of its leadership team in a press release on November 10.Corvex told CNBC yesterday that it “had no part in the activities cited in the Department of Justice’s indictment,” and that “the person in question is not an employee of Corvex. Previously a consultant to the company, he was transitioning into an employee role but that offer has been rescinded.”“The indictment unsealed yesterday alleges a deliberate and deceptive effort to transship controlled Nvidia GPUs to China by falsifying paperwork, creating fake contracts, and misleading U.S. authorities,” said John A. Eisenberg, Assistant Attorney General for National Security. “The National Security Division is committed to disrupting these kinds of black markets of sensitive U.S. technologies and holding accountable those who participate in this illicit trade. ”“As demonstrated by this indictment, the US Attorney's Office for the Middle District of Florida is firmly committed to safeguarding our country’s national security,” said U.S. Attorney Gregory W. Kehoe for the Middle District of Florida. “Thanks to the dedicated investigative work by our law enforcement partners, these defendants who wrongfully exported this sensitive technology are facing justice.”According to the indictment, the PRC seeks to become the world leader in AI by 2030 and seeks to use AI for its military modernization efforts and in connection with the design and testing of weapons of mass destruction and deployment of advanced AI surveillance tools. The PRC seeks cutting-edge U.S. technology in furtherance of that goal, including Nvidia GPUs. To protect U.S. national security, beginning in October 2022, the Department of Commerce implemented new license requirements for the export of these technologies to the PRC.As alleged, from September 2023 to November 2025, Ho, Raymond, Li, and Chen conspired to violate these critical U. export controls, by illegally exporting advanced GPUs to the PRC through Malaysia and Thailand. In furtherance of the conspiracy, the conspirators used Janford Realtor, LLC—a Tampa, Florida-based company owned and controlled by Ho and Li—as a front to purchase and then illegally export controlled GPUs to the PRC. Despite its name, Janford Realtor, LLC, was never involved in any real estate transactions. Raymond, though his Alabama-based electronics company, supplied NVIDIA GPUs to Ho and others for illegal export to the PRC as part of the conspiracy.As further alleged in the indictment, the conspiracy encompassed four separate exports of Nvidia GPUs to the PRC. The first and second exports resulted in 400 Nvidia A100 GPUs being exported to the PRC between October 2024 and January 2025. The third and fourth exports to the PRC were disrupted by law enforcement and therefore not completed. These attempted exports related to ten Hewlett Packard Enterprises supercomputers containing Nvidia H100 GPUs and 50 separate Nvidia H200 GPUs.Despite knowing that licenses were required to export these items to the PRC, none of the conspirators ever sought or obtained a license for any of these exports. Instead, they lied about the intended destination of the GPUs to evade U.S. export controls. The indictment further alleges that the conspirators received over $3.89 million in wire transfers from the PRC to fund this unlawful scheme.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/technology/tech-news/tech-company-cto-and-three-others-arrested-for-exporting-nvidia-chips-that-are-banned-to-china/articleshow/125511701.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 02:24:14 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125511699,width-1070,height-580,imgsize-256718,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
   </si>
   <si>
     <t>Watch: PM Modi shares G20 highlights; calls discussions with leaders 'productive'</t>
@@ -1302,40 +1930,6 @@
     <t>https://static.toiimg.com/thumb/msid-125516203,width-1070,height-580,imgsize-139536,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
   </si>
   <si>
-    <t>$1 trillion squad: Musk, Zuckerberg, Pichai, and fellow billionaires break the internet</t>
-  </si>
-  <si>
-    <t>Why the '$1 trillion squad' image is everywhere
-EXPOSED: Mark Zuckerberg Embarrassed on Hot Mic Admitting Total Confusion During Trump Dinner
-Top social media reactions to the viral “$1 trillion squad” photo
-“The Avengers in real life. So is Elon channeling Nick Fury, Tony Stark or Captain America”
-“The Great Round Tech Talk Without a Round Table”
-“Quick, here comes my mom. Put it out”
-“You wanna go and get high or have a beer”
-“Seven of the brokest dudes on the planet”
-“World’s wealthiest hacky-sack circle”
-“Elon, please don’t get us thrown in jail”
-“They all got the same shoes”
-“What are half of them wearing the same shoes”
-“Picture missing the real legend… me”
-“Four men of stature and three clowns”
-“Tech gangs of back street”
-“All bases covered”
-“At least three of these dudes are sociopaths and would never spend a second with the others”
-“Who is going back to finish his bachelor’s degree”
-A meme that says everything about 2025
-An image of the world’s most powerful tech titans standing in a dimly lit parking lot has become the internet’s favourite new obsession. The so-called “$1 trillion squad” photo featuring Elon Musk Sundar Pichai , Jensen Huang, Sam Altman, Tim Cook and Jeff Bezos has blown up across X, triggering a wave of memes, jokes, edits and conspiracy-tier commentary. The image racked up hundreds of thousands of views in under two days, turning into one of the biggest viral moments of late 2025. Although the picture is not real, its cultural impact absolutely is.The picture taps perfectly into the cultural mood of 2025, a year dominated by AI arms races, compute shortages, billionaire influence battles and Chip War gossip. Seeing the most influential CEOs of the decade lined up like GTA villains or Marvel bosses felt almost too on the-nose for the internet to resist.The exaggerated cinematic lighting, the luxury cars in the background, Jensen Huang in his trademark leather jacket and Musk puffing a cigar created a visual that looked less like a business meeting and more like a poster for a dystopian tech thriller. The absurdity of the scenario, powerful billionaires casually hanging out as if plotting the next chapter of the AI revolution, made it instantly iconic.Adding to the surreal energy of the shot is the lineup of cars behind them.The Cybertruck looming on one side, a row of glossy supercars parked like getaway vehicles, and even a vintage off-road truck sitting proudly in the corner make the scene feel staged for a Hollywood heist. Each car feels like a character: the stealth-black hypercars matching the CEOs’ “final boss” vibe, the Cybertruck reinforcing Musk’s unmistakable presence, and the retro truck injecting an oddly charming contrast. Together, they create a backdrop so dramatic and overpowered that the internet couldn’t help but treat the whole thing as a film still waiting for its plot.Even funnier, the sequel image showing them inside a cheap, cramped motel-style room with a microwave, plastic chairs and mismatched furniture. The contrast between trillion-dollar influence and a 50 dollar a night room only intensified the meme storm.A large chunk of the audience initially wondered if the photo was genuine. Its hyper-real yet slightly uncanny style fits the chaotic spirit of 2025, where AI generated content often circulates faster than fact checks. Despite confirmations that the image is synthetic, the debate only fuelled the meme machine.People remixed the image with boss fight music, created comic panels and even asked AI tools like Grok and Mid journey to generate sequels, spin-offs and alternate universes. It was no longer just a viral picture, it was turning into a multi-format franchise.Here are some of the funniest and most creative reactions that flooded X after the image went viral:The “$1 trillion squad” photo works because it captures a simple truth: tech leaders have become the cultural superheroes or supervillains of our time. Their influence spans AI, chips, space, communications, politics and markets. Seeing them together, even artificially, taps into fascination, fear and humour all at once.And because the image is AI generated, it also symbolises something bigger: AI is no longer just reshaping technology, it is reshaping culture, imagination and the way we interpret power.If Musk reacts to it, which he often does with memes, expect this moment to double in reach and spawn countless remixes. The internet might not be ready for the “$1 trillion squad” cinematic universe, but it is definitely asking for it.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/technology/social/1-trillion-squad-musk-zuckerberg-pichai-and-fellow-billionaires-break-the-internet-with-viral-photo/articleshow/125508025.cms</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 21:53:05 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125508048,width-1070,height-580,imgsize-97592,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
     <t>Adorable! Smriti Mandhana’s viral dance with Palash Muchhal steals spotlight - Watch</t>
   </si>
   <si>
@@ -1373,6 +1967,7 @@
   </si>
   <si>
     <t>Punjab CM Bhagwant Mann
+Nov 23 Chandigarh - AI City News
 Non-BJP parties join hands to oppose Centre’s move
 CHANDIGARH: Central govt seeks to bring Union Territory of Chandigarh under Article 240 of Constitution by tabling the 131st Amendment Bill in winter session of Parliament, similar to other UTs like Andaman and Nicobar Islands, Lakshadweep, Dadra and Nagar Haveli, and Daman and Diu.The politically sensitive move has sparked a storm of protest in Punjab, from governing AAP to opposition Congress and Shiromani Akali Dal.“This amendment is against the interests of Punjab. We strongly oppose it and won’t allow this conspiracy being hatched by central govt against Punjab to succeed. Only Punjab has the right over Chandigarh, which was built by destroying the villages of our Punjab. We will not give up our rights. We will take whatever steps are necessary for that,” CM Bhagwant Mann posted on X.Chandigarh is administered by the Punjab governor. With the new law, it is likely to be administered by an independent administrator. The move is being seen as a bid to delink Chandigarh from Punjab. It may open another Punjab vs Delhi war soon after the skirmish over restructuring of Panjab University senate in which Centre took a U-turn.Chandigarh was designated a Union Territory in 1966 and has since been governed directly by central govt rather than Punjab or Haryana, even though it serves as the two states’ joint capital. The role of Chandigarh administrator has been held by the Punjab governor since 1984. Earlier this year, Centre abolished the post of “advisor to administrator” and redesignated it as “chief secretary”.The Article 240 move has brought together non-BJP parties who see it as an attempt to “snatch” Chandigarh from Punjab.Punjab LoP Partap Singh Bajwa urged political parties in Punjab to unite against BJP-led Union govt’s “highly sensitive amendment”. “This Bill is a clear attempt to weaken Punjab’s historical, constitutional, and emotional claim over its own capital,” he said, accusing Centre of eroding Punjab’s rights “whether on Chandigarh, river waters, or Panjab University”.“BJP-led Centre’s antiPunjab agenda is now out in the open.Because Punjabis do not elect BJP, Centre seems intent on penalising state. This mindset is discriminatory, divisive, and completely unacceptable,” he asserted. Bajwa sought to remind Centre of the farmers’ movement and Panjab University Bachao Morcha as recent examples of Punjab’s collective strength.Punjab Congress president Amrinder Singh Raja Warring warned Centre against the proposed 131st Constitutional Amendment. Calling the move “totally uncalled for”, he expressed hope better sense would prevail in Centre and that it would refrain from legislating such a provision. “Chandigarh belongs to Punjab, and any attempt to snatch it away will have serious repercussions,” he cautioned, adding central govt should not make such a misadventure and must make necessary amendments in the proposed Bill.Senior Congress functionary Pargat Singh saw it as “part of a pattern”, and said, “The assault has been years in the making — pushing for a separate Haryana assembly inside Chandigarh, plotting to convert Panjab University into a central university, reducing Punjab-cadre officers in Chandigarh administration, dissolving Panjab University’s elected senate, and now using Article 240 to turn Chandigarh into a regular UT, completely severed from Punjab. It’s a blatant, unconstitutional attack on Punjab’s capital and federal rights.”Rajya Sabha MP Vikramjit Singh Sahney stressed Punjab’s claim on Chandigarh had historical significance as it became Punjab’s capital after Partition when Lahore went to Pakistan. Following the 1966 Punjab Reorganisation, the city became the shared capital of Punjab and Haryana and, under multiple accords, Centre promised to transfer Chandigarh to Punjab. Sahney urged all MPs from Punjab to immediately meet the Union home minister.</t>
   </si>
@@ -1384,25 +1979,6 @@
   </si>
   <si>
     <t>https://static.toiimg.com/thumb/msid-125515238,width-1070,height-580,imgsize-994736,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>Stefon Diggs' lady love Cardi B raves about hospital stay after giving birth</t>
-  </si>
-  <si>
-    <t>(Image via Getty: Cardi B)
-Fans react as NFL WAG Cardi B praises opulent hospital catering so much that she suggests another pregnancy
-Cardi B Debuts Newborn Son in Patriots Gear as She and Stefon Diggs Melt the Internet
-More coverage on Cardi B:
-Remedy Blog illuminated Instagram with two videos from Grammy-winning rapper and newest mommy in NFL town, Cardi B . In the first, Cardi gushed over her hospital stay, captioning it with heart emojis and raving, ‘Yall this hospital was to tea …like I did not wanted to leave.’ Filming the impressive spread of hospital food on her phone, she joked that if every birth came with this kind of treatment, she might be back in six months for another baby. “If they’re gonna treat me like this every time I give birth,” Cardi said. “I might get pregnant in six more months (chuckles).” Lifting dish after dish, Cardi could only say, ‘Wow. Wow. Wow.’ The second video, titled ‘Noo like foreal..next time I get a cold imma go over there,’ showed her marveling again at the hospital’s cuisine. She declared it the best hospital food she’d ever had, even better than what one would find in restaurants or hotels. “The best hospital ever! This hospital has better food than restaurants and hotels,” she said, excitedly pointing out, “Look at this. This is crab stuff.”Fans flooded Remedy Blog’s Cardi-praising-hospital-food post with a hurricane of reactions. One nodded in agreement, reminiscing about their own hospital stay and meals: “Same oh the way I enjoy my stay and food at the hospital after giving birth 😍.”Another joked about a possible pregnancy in the next six months: “She Said She Will Get Pregnant Again in The Next Six Months 😂😂😂😂😂😂.”, while someone else teased that the feast would surely show up on the bill: “It will be added to her bills 😂😂😂😂😂 we know how we run it. ” Some doubted the food was even from a hospital: “That’s definitely not hospital food 😂😂😂😂.”, and others brutally critiqued Cardi’s English, sending their congratulations: “I love cardi but this her English is giving me a migraine,which one is i did not wanted to leave 😂congrats cardi ❤️.” Many simply drooled over the delicious spread: “That's some yummy goodness😂😍.”My Mixtapez posted the same two videos on their X platform, and fans, without further ado, shared their strong opinions. One fan clapped back at Cardi’s critics, pointing out, “Yall calling her slow. But she figured out how to make millions. While yall taking out a loan to pay rent 😅.” Another chimed in, “Probaly cus you rich duhhh.” Someone else added, “Cardi funny… she’s not the first woman to think like this, especially when you actually enjoy having children &amp; a had good delivery experience. ” Another fan joked, “Breakfast,lunch, dinner, dessert all in one.” Someone else reminded everyone, “She has a tour to tend to.” Stefon Diggs ’ girlfriend, Cardi B, is set to kick off her “Little Miss Drama Tour” in February 2026, following the September 19 release of her album, “Am I The Drama?”</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/sports/nfl/news/if-they-treat-me-like-this-stefon-diggs-lady-love-cardi-b-raves-about-hospital-stay-after-giving-birth-considers-another-pregnancy/articleshow/125505266.cms</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 17:43:43 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125505261,width-1070,height-580,imgsize-57974,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
   </si>
   <si>
     <t>Toxic smog chokes Delhi: Air quality turns 'severe' as AQI reading soars to 435</t>
@@ -1440,6 +2016,28 @@
     <t>https://static.toiimg.com/thumb/msid-125497581,width-1070,height-580,imgsize-49856,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
   </si>
   <si>
+    <t>From better digestion to relaxation: Why you should drink clove water at night</t>
+  </si>
+  <si>
+    <t>CREDIT: CANVA
+Improves digestion, reduces night-time discomfort
+Consume cloves for these health benefits
+Promotes relaxation and supports better sleep
+Liver health and detoxification are supported
+Anti-inflammatory benefits for overall health
+How to prepare and use clove water
+Drinking clove water at night is one of those highly effective nighttime habits, linked with traditional medicine, now supported by scientific studies. Due to some key health benefits associated with this intake, which manifest much more in these nighttime hours when the human body usually rests and undergoes repair, various experts prescribe bedtime consumption of clove water. Clove water helps improve digestion and enhances relaxation, boosts immunity, and supports liver detoxification during nighttime. Herein is a detailed explanation of why drinking clove water at night is so useful, based on recent research findings.The reason people drink clove water at night is because it helps with their digestion. Cloves contain eugenol, a chemical compound that has very powerful digestive benefits. Scientific studies show eugenol promotes the secretion of digestive enzymes that help in food digestion quicker and gives soothing effects to the digestive tract. These reduce common problems such as bloating, gas, and indigestion, which disturb one's sleep.The majority of the population experiences indigestion right after dinner, which turns into discomfort if left untreated, thereby perturbing sleep quality. A study published in the Journal of Pharmacognosy and Phytochemistry has clearly explained that clove works effectively in soothing gastrointestinal irritation and subsequently reducing the symptoms of diarrhea and nausea.Clove water before bed helps your digestive system relax and function optimally during sleep, preparing you for a good night's sleep.Clove water acts soothingly not only on the digestive system but on the nervous system, too. Cloves are a natural source of phytochemicals, including eugenol, which possesses anxiolytic actions. According to studies conducted by NIH , eugenol demonstrated a reduction in the levels of stress and anxiety. Because of this, warm clove water taken at night can act as a soft, natural relaxant.Clove water works by soothing the nervous system, easing the transition into sleep. It is an important period of rest that gives the body the chance to repair tissues, regulate hormones, and refuel energy stores. Clove water helps support normal melatonin rhythms, the hormone responsible for regulating the sleep-wake cycle. Another great part to this nighttime routine is the act of sipping on warm flavored water prepares the body to wind down, signaling it is time to rest. These all will contribute to help improve sleep onset, quality, and duration.The peak period of liver detoxification is at night; when sleeping, the liver is working hard to filter out toxins, metabolize waste, and repair cells that might be damaged. Clove extract, especially eugenol, has been found to have liver-protective effects in research that included studies published in the Journal of Food Biochemistry. Eugenol reduces liver inflammation and oxidative stress, two factors involved in the impairment of liver function. Clove water taken before going to bed may enhance this natural detoxification process, supplying the liver with phytochemicals that aid in cellular repair. Continuous intake is thus considered very good for people exposed to environmental toxins or with minor liver issues, and helps maintain liver health, promoting smooth toxin clearance.Clove water possesses strong anti-inflammatory activity along with other health benefits. Most of the degenerative diseases, including arthritis, cardiovascular disease, and neurodegeneration, have chronic inflammation as their basis. Various studies published in Food Chemistry wrote of clove water extract reducing pro-inflammatory markers like IL-6 and TNF-α, helping in lowering systemic inflammation. Drinking clove water at night can support the body in its effort to control inflammation, especially after a day that has exposed one to environmental stressors or was filled with unhealthy foods and physical strain. This continued lowering of inflammation contributes to healthy aging and a reduced risk of chronic diseases.Clove water can be prepared easily. Typically, 3 to 5 whole cloves are boiled in hot water for about 10 to 15 minutes. After that, the warm infusion is strained and consumed. Experts claim that taking clove water about 30 minutes before retiring to bed will significantly improve digestion and sleep while enabling it to support detoxification processes. In fact, most of the people who take it in moderation do not suffer from any harm, though sensitive people may face an irritated digestive system due to its excessive consumption, so it is better to start gradually.</t>
+  </si>
+  <si>
+    <t>https://timesofindia.indiatimes.com/life-style/health-fitness/from-better-digestion-to-relaxation-why-you-should-drink-clove-water-at-night/articleshow/125482643.cms</t>
+  </si>
+  <si>
+    <t>Sun, 23 Nov 2025 12:22:48 +0530</t>
+  </si>
+  <si>
+    <t>https://static.toiimg.com/thumb/msid-125482723,width-1070,height-580,imgsize-1409009,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+  </si>
+  <si>
     <t>Ashes: 'Two years ago you silenced India'- Shastri’s hard-hitting tribute to Travis Head</t>
   </si>
   <si>
@@ -1489,502 +2087,1545 @@
     <t>https://static.toiimg.com/thumb/msid-125515794,width-1070,height-580,imgsize-1286969,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
   </si>
   <si>
-    <t>Smriti Mandhana set to tie the knot with Palash Muchhal today: All you need to know</t>
-  </si>
-  <si>
-    <t>Smriti Mandhana is all set to marry music composer and filmmaker Palash Muchhal in an intimate afternoon ceremony on Sunday (Image credit: X)
-Go Beyond The Boundary with our YouTube channel. SUBSCRIBE NOW!
-Palash Muchhal Proposes Cricketer Smriti Mandhana At DY Patil Stadium!
-Smriti will marry music composer Palash Muchhal on November 23, 2025, in Sangli, Maharashtra.
-The couple met in 2019 and kept their relationship private until July 2024.
-Palash proposed at DY Patil Stadium and got a tattoo of Smriti’s initials and jersey number, ‘SM18’.
-Pre-wedding celebrations reveal a more expressive side of Smriti, while the couple balances their high-profile careers.
-NEW DELHI: Indian cricket star and World Cup winner Smriti Mandhana is all set to marry music composer and filmmaker Palash Muchhal in an intimate afternoon ceremony on Sunday, in her hometown of Sangli, Maharashtra. The private wedding comes shortly after India’s triumphant Women’s World Cup campaign and will be attended by close friends and family following a week of pre-wedding festivities that celebrated the couple’s journey together.Mandhana and Muchhal first crossed paths in 2019 through mutual friends in Mumbai’s creative circles. Despite their busy and high-profile careers, the pair managed to keep their relationship largely private, away from the media spotlight. Their romance became public in July 2024 on their five-year anniversary via a social media post, highlighting the strong bond they had nurtured while continuing to focus on their respective professional commitments.The proposal was a romantic affair at DY Patil Stadium in Navi Mumbai, where Palash blindfolded Smriti and led her to the very cricket pitch where she had played a pivotal role in India’s World Cup victory.There, on one knee, he proposed, creating a memorable moment the couple will cherish forever. To symbolize his dedication, Palash also got a tattoo of Smriti’s initials and jersey number, ‘SM18’, on his forearm.Breaking from tradition, the wedding will be held as an afternoon event. The pre-wedding celebrations have revealed a more expressive and playful side of Smriti, often known for her reserved nature. Choosing Sangli as the venue adds a personal touch, celebrating her roots and marking a significant milestone in her life, following her recent cricketing achievements.The couple has successfully balanced demanding careers—Smriti in international cricket and Palash in Bollywood music—while maintaining a strong personal connection. Their relationship reflects both love and mutual support, proving that it is possible to nurture a meaningful bond even amidst the pressures of fame and professional life.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/sports/cricket/news/smriti-mandhana-set-to-tie-the-knot-with-palash-muchhal-today-all-you-need-to-know/articleshow/125516088.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 11:24:20 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125516156,width-1070,height-580,imgsize-51550,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>Delhi blast: Accused doctors bought Russian weapon, freezer for explosives</t>
-  </si>
-  <si>
-    <t>Delhi Blast Probe
-ED Cracks Down On ‘White-Collar Terror Module’, Conducts 25 Raids Linked To Al-Falah University
-LUCKNOW: Fresh revelations in the probe into the Jaish-e-Mohammed (JeM) module busted in Faridabad have exposed a sophisticated weapons procurement and explosive-manufacturing network involving arrested suspects Dr Muzammil, Dr Shaheen, Dr Adeel and Amir.Investigators said Muzammil purchased a Russian assault rifle for Rs 5 lakh through a contact linked to co-accused Dr Shaheen. The weapon was later recovered from a locker belonging to Dr Adeel, marking a breakthrough in mapping the module's arms routes.Another Russian-origin rifle, an AK Krinkov, along with a Chinese star pistol, a Beretta pistol and nearly 2,900 kg of explosive precursor material, was earlier seized in Faridabad.Also Read | Chilling revelation in Delhi car blast: AK-47 bought for more than Rs 5 lakh, deep freezer used for explosives Officials said Lucknow-based Dr Shaheen arranged for the Russian assault rifles and deep freezer—after discreet negotiations with suppliers to avoid suspicion—on Umar's request and purchases were done by Muzzamil.The agencies are also tracking the suppliers. Overall, Rs 26 lakh was raised by the suspects, majority of the share through Shaheen.The freezer was allegedly used to store temperature-sensitive precursor chemicals essential for fabricating powerful improvised explosive devices (IEDs).Forensic teams are examining the recovered samples to identify the compounds.Intelligence sources said Shaheen not only helped arrange the rifle and freezer but also tapped her network to mobilise funds for the purchase of arms and ammunition. Sources added that the possible links could be through Afirah Bibi, the wife of Jaish commander and Pulwama attack mastermind Umar Farooq.Umar Farooq, the nephew of Jaish chief Masood Azhar, was killed in an encounter in the wake of the 2019 Pulwama attack that claimed the lives of 40 personnel of the Central Reserve Police Force (CRPF)."The AK-56 recovery from Adeel's locker is a crucial link. It highlights the level of planning, financing and operational readiness of the module," an official said.The probe also revealed that Umar had extensively studied bomb-making tutorials, manuals and open-source content online and was given directions by handlers from Turkiye.He allegedly sourced chemical ingredients from Nuh, electronic components from Bhagirath Palace in Delhi and Faridabad's NIT Market and used the freezer to stabilise and process the explosive mixture.Sources added that tensions had erupted between the accused inside Al-Falah University premises over money matters, an altercation witnessed by several students. After the clash, Umar reportedly handed over his red EcoSport—already loaded with explosive material—to Muzammil.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/city/lucknow/accused-docs-bought-russian-weapon-freezer-for-explosives/articleshow/125510925.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 00:30:26 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125514593,width-1070,height-580,imgsize-1577157,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>Ind vs Sa: KL Rahul set to return as India’s ODI captain; Gill doubtful for T20Is as well</t>
-  </si>
-  <si>
-    <t>KL Rahul will captain India in the upcoming ODI series against South Africa, replacing Shubman Gill who is out with a serious neck injury. With vice-captain Shreyas Iyer also sidelined, Rahul steps in. Gill's recovery timeline is extended, raising doubts about his availability for the T20Is as well.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/sports/cricket/india-vs-south-africa/kl-rahul-set-to-return-as-indias-captain-shubman-gill-doubtful-for-odis-and-t20is/articleshow/125514876.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 08:21:11 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125514870,width-1070,height-580,imgsize-89622,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>Uttarakhand on alert: 20kg explosives, 161 gelignite sticks found near Almora schools</t>
-  </si>
-  <si>
-    <t>Image Credit: TOI
-'Objective Is To Destroy The Enemy': Op Sindoor Echoes As Indian Army Vows Stronger Response to Pak
-BAGESHWAR: A major security alert was sounded in Almora district after 161 gelignite sticks, over 20 kg of highly explosive material, were recovered from bushes near two schools in the Salt area.As the recovery came days after nearly 2,900 kg of explosive materials allegedly part of the terror plot behind the blast near Delhi's Red Fort were seized in Haryana, district authorities launched a massive operation with dog squads and forensic teams combing the area.Police said the gelignite sticks were first spotted by school children on Thursday when they went into the bushes to look for their cricket ball and found the explosives stacked there.After school authorities alerted police, a team from Bhikiyasain carried out the recovery on Friday. An FIR was registered against unknown persons under section 4(A) of the Explosive Substances Act, 1908, and BNS section 288 (negligent conduct with respect to explosive substance)."Samples have been collected, and a detailed probe is underway to identify who brought the gelatin rods and for what purpose," Almora SSP Devendra Pincha told TOI.He added that the material is commonly used for stone-breaking in road construction, though police were "investigating all angles."Dabhra village head Arjun Singh said the location suggested the material may have been left behind by workers involved in a PMGSY road project completed in the village last year. "The workers' camp was just 30m from where the explosives were found. It is possible the material was brought for breaking hard rock and later abandoned after becoming unusable," he told TOI.On Saturday morning, Provincial Armed Constabulary (PAC) personnel and additional police units also joined the operation. Teams from the bomb disposal unit, local intelligence unit (LIU) and the Indian Reserve Battalion (IRB) carried out a combing operation in the forested area, bushes, school campus and nearby footpaths to ensure no additional material remained.Forensic experts were conducting a second round of testing on Sat to trace the source and nature of the gelatin sticks. Investigators had mapped the spot and collected soil samples and other evidence from multiple locations.SSP Pincha said the explosives will be disposed of safely after court approval.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/city/dehradun/over-20kg-of-explosives-found-near-almora-school-massive-security-probe-launched/articleshow/125509426.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 03:39:49 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125514995,width-1070,height-580,imgsize-100050,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>Trump Jr, Bollywood line up for wedding of US baron’s daughter in Udaipur</t>
-  </si>
-  <si>
-    <t>Parents of the bride, Raj and Padmaja Mantena (in pastel jacket and saree, respectively), with Donald Trump Jr. and girlfriend Bettina Anderson (centre, holding hands), and (2nd from left) Lakshyaraj Singh Mewar, at the City Palace in Udaipur
-B town Celebs Light Up Netra Mantena’s Star Studded Udaipur Wedding!
-UDAIPUR/VIJAYAWADA: US President Donald Trump's son Donald Trump Jr has landed, as have Jennifer Lopez and Justin Bieber. Kriti Sanon, Madhuri Dixit and Shahid Kapoor joined in. All are here for the Sunday wedding of Andhra-origin US baron Rama Raju Mantena's daughter Netra in Udaipur, sending ripples far beyond the erstwhile Rajasthan royal hub also known as the City of Lakes.Not surprisingly, attention has been riveted on Trump Jr, who arrived late Friday accompanied by his girlfriend and proceeded to Leela Palace hotel. He is likely to be under spotlight Sunday, too, when Netra ties the knot with Vamsi Gadiraju against the backdrop of historic Jag Mandir Island Palace.Columbia University alumnus Vamsi is co-founder of Superorder, a New York-based tech firm that aims to revolutionise the food delivery industry. He also has Telugu roots and was part of Forbes' list of Under 30 prodigies. Netra completed her undergraduate studies in pharmacology and works in New York.On Saturday, Trump Jr. and Rama Raju -- also known as Raj -- visited Udaipur City Palace and met Lakshyaraj Singh Mewar of the former Mewar royal family.The meeting was steeped in tradition, with discussions on Mewar's rich history. Singh presented the two symbolic emblems, which Trump Jr called "special and memorable" and expressed admiration for the region's historical figures such as Maharana Kumbha, Maharana Sanga, and Maharana Pratap.Udaipur has also turned into a fortress. Security is extensive, involving coordination between local police and US Secret Service. Drones monitor the skies. Lake jetties and hotel perimeters are under close watch, with VIP movements facilitated through dedicated corridors and tight entry checks.Wedding festivities kicked off late Friday with performances by Kriti, Madhuri and Shahid. The celebrations continued Saturday with shows by Lopez --- who flew in on a chartered flight from Ireland --- and Bieber. The wedding will be followed by a "grand reception" on Nov 24.The Mantenas trace their roots to Vijayawada. Rama Raju moved to the US in 1984, starting seven companies there. His latest is Integra Connect, which offers value-based, precision medicine, leading the industry in real-world data, analytics, and AI capabilities for speciality care organisations.Rama Raju made his fortune by selling the companies he founded in the pharmacy and IT sectors by unlocking their true value. A pharmacy graduate from Vijayawada, Rama Raju is the nephew of Gokaraju Gangaraju, former BJP MP and entrepreneur. Rama Raju made his fortune by selling the companies he founded in the pharmacy and IT sectors by unlocking their true value.In the process of selling his firms, Rama Raju made high-profile connections with global entrepreneurs and celebrities. The connection with the US President's family happened during the years they both lived in Florida as neighbours."Raj has a long-standing friendship with Trump's family. He really wants to bring qualitative change in the lives of cancer patients and has big plans to invest in India's pharma sector," said a close friend.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/city/jaipur/trump-jr-bieber-lopez-bollywood-line-up-for-wedding-of-andhra-origin-us-barons-daughter/articleshow/125511388.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 04:15:26 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125515408,width-1070,height-580,imgsize-1541189,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>'Hamas-terror network in Europe': Mossad makes bold claim; arms prepped ‘when ordered’</t>
-  </si>
-  <si>
-    <t>Image credit: AP
-'Resistance Our Right': Hamas Rejects Gaza Stabilisation Force Proposal; Slams US Resolution At UNSC
-Turkey, Qatar named in the statement
-Israel’s intelligence agency Mossad has claimed that it uncovered a major Hamas-linked terror network operating across Europe, alleging that elements of the group’s leadership in Qatar were involved in steering the operations.Mossad, in a statement, said that the network was designed by Hamas to activate “on the day the order is given,” with European raids revealing weapons stockpiles that included handguns and explosive devices. One such cache was discovered last September during a joint operation by Austria’s State Security and Intelligence Directorate (DSN) in Vienna."The investigation into the Hamas terror network in Europe is currently examining the possible involvement of Hamas elements in Turkey in promoting the intention to carry out attacks, some of which have been exposed," the statement said."Law and enforcement authorities in Europe, including in Germany and Austria, have conducted a series of complex counter-terrorism operations, resulting in the arrest of terrorist operatives and the discovery of weapons caches intended for use by terrorist cells to harm innocent people 'on the day the order is given'," it added.The investigation has also drawn attention to suspected Hamas activity in Turkey, which Mossad described as a longstanding “convenient operational arena.”German authorities arrested another alleged operative, Barah al-Khatib, last November after he reportedly travelled from Turkey following his activities in Europe."This is due to Turkey being a convenient operational arena for Hamas operatives in the past and present. As part of the investigation by European security and enforcement bodies, a prominent operative in the infrastructure, Barah al-Khatib, was arrested in Germany last November, after having stayed in Turkey, apparently after completing his operational activity on European soil," it said.Investigators linked the weapons seized to Hamas operative Muhammad Na’im, son of senior Hamas political bureau member Basem Na’im. Mossad claimed the pair held a meeting in Qatar around the same period, suggesting that senior leadership based there had authorised the expansion of terror activity into Europe. It asserted that this contradicted public denials by Hamas leaders who reject accusations of external operations."The involvement of the organization's leadership from Qatar in promoting terrorist activities is not being exposed for the first time, even though the movement's senior officials have repeatedly denied it publicly, as part of their effort to protect the image of the Hamas organization in the eyes of international public opinion," it said.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/world/europe/hamas-terror-network-in-europe-mossad-makes-bold-claim-arms-prepped-for-use-when-order-is-given/articleshow/125514720.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 08:47:53 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125515050,width-1070,height-580,imgsize-1259412,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>Delhi school admissions 2026-27: Schedule for nursery, KG in private schools out</t>
-  </si>
-  <si>
-    <t>Delhi private school admissions for 2026-27 to begin soon
-Applications from December 4, first list on January 23
-IMPORTANT DATES AT A GLANCE
-Event / Milestone
-Date
-Uploading of criteria &amp; point system by schools
-28 November 2025 (Friday)
-Admission process begins; forms available
-4 December 2025 (Thursday)
-Last date to submit application forms
-27 December 2025 (Saturday)
-Schools upload list of all applicants
-9 January 2026 (Friday)
-Schools upload marks/points allotted to each applicant
-16 January 2026 (Friday)
-First list of selected candidates (with waiting list)
-23 January 2026 (Friday)
-Query-redressal window for first list
-24 January–3 February 2026
-Second list of selected candidates (if any)
-9 February 2026 (Monday)
-Query-redressal window for second list
-10–16 February 2026
-Subsequent list (if any)
-5 March 2026 (Thursday)
-Closure of the admission process
-19 March 2026 (Thursday)
-The notice says,
-Age requirements for Nursery, KG and Class 1
-Nursery (Balvatika 1): 3 to 4 years
-KG: 4 to 5 years
-Class 1: 5 to 6 years
-Proof of residence
-“Regarding documents valid as proof of address”
-Registration fee capped at ₹25
-“shall be optional.”
-25% EWS/DG/CWSN quota to continue
-Highest number of entry-level seats to be maintained
-Mandatory draw of lots for oversubscribed schools
-The Directorate of Education (DoE), Delhi, has issued a detailed circular announcing the admission schedule for entry-level classes—Nursery, KG and Class 1—in private unaided recognised schools for the academic session 2026–27. The order, dated 22 November 2025, lays out timelines, age limits, documentation requirements, prohibited criteria, and mandatory transparency measures for schools. The circular applies only to open-category seats and excludes EWS/DG/CWSN admissions.According to the circular, schools must first upload their admission criteria and point system on the DoE module by 28th November 2025. The admission process and availability of forms for parents will begin on 4th December 2025, with the last date for submission of application forms set as 27th December 2025.By 9th January 2026, schools are required to upload details of all children who applied under open seats, followed by uploading marks as per the points system for each applicant on 16th January 2026. The first list of selected children, including the waiting list, along with marks allotted under the points system, will be displayed on 23rd January 2026.The second list of selected children, if any (including waiting list, with marks) will be displayed on 9 FebruaryThe DoE has explicitly forbidden any deviation from the notified timeline.“No deviation from the above schedule shall be permitted. Each school shall display the aforesaid admission schedule on its notice board and website.” It also requires schools to ensure forms remain available until the final date of submission.The circular specifies age limits as on 31 March 2026:The notice states, “A child must have attained the prescribed minimum age as on 31st March 2026.” It also formalises the shift to 6+ years for Class 1, in line with NEP changes.Parents may submit any one of several listed documents as proof of residence, including ration or smart cards, domicile certificates, voter ID cards, utility bills, passports, or Aadhaar cards. The circular lists these underReiterating long-standing DoE norms, the notice caps all admission-related charges. It states clearly, “Only Rs. 25/- (Non-refundable) can be charged… as admission registration fee.”Schools are also barred from forcing parents to buy prospectuses, with the circular noting that the purchase of printed materialThey must also keep application forms available until the last submission date and publicly display the full schedule on their noticeboards and websites.The circular reaffirms the statutory requirement of reserving 25% seats for EWS, DG, and Children with Disabilities at entry level. It reads, “All private unaided recognized schools… shall reserve 25% seats for EWS/DG category students &amp; Child with Disability…”It further clarifies that schools are not allowed to admit these categories on their own.“No private unaided recognized schools shall process the admission of EWS/DG/CWSN free-ship category students manually.” The DoE will handle the full process centrally, including the draw of lots for these seats.To prevent seat cuts, the notice requires schools to keep at least the highest intake from recent years. It states, “The number of seats at entry level… shall not be less than the highest number of seats… during the previous three years.”If the number of applications exceeds the number of available seats, schools must conduct a transparent draw of lots. The circular lays out strict requirements. “The draw of lots… shall be conducted in a transparent manner in presence of parents… videography of the draw shall be maintained/retained by the school,” it reads. It adds that slips must be demonstrated openly. Parents must be notified at least two days prior to the draw date.Check the official notice here</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/education/news/delhi-school-admissions-2026-27-schedule-for-nursery-kg-and-class-1-in-private-schools-out-important-dates-here/articleshow/125515400.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 09:57:59 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125515490,width-1070,height-580,imgsize-1889410,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>'Searching for videos of son': Tejas pilot Syal’s father reveals how he found about crash</t>
-  </si>
-  <si>
-    <t>(File Photo) Wg Cdr Namansh Syal, who lost his life in the Tejas fighter aircraft crash at the Dubai Airshow, on Saturday. (@IAF_MCC on X)
-'We Fly For You': Russian Fighter Pilot's Heartfelt Note For Indian Tejas Pilot After Dubai Crash
-SHIMLA: Wing Commander Namansh Syal, who perished in the Tejas crash at Dubai Air Show on Friday, was a high flyer all his life - house captain in Sainik School, Academy Cadet Adjutant (ACC) at National Defence Academy (NDA), and an instructor with Indian Air Force (IAF), training the next generation of combat pilots.The air warrior will be cremated at his ancestral village, Patialkar, in Kangra district's Nagrota Bagwan tehsil, on Sunday, his father Naib Subedar Jagan Nath (retd), an Army Medical Corps veteran, told TOI. In a tragic twist, the 71-year-old said he was searching for videos of his son's aerial acrobatics at the air show when news reports of the crash popped up. Speaking to TOI over phone from Sulur, the grief-stricken father said, "Then, officers from my son's squadron arrived to convey the tragic news. "When the family got the news, Namansh's wife, Wing Commander Afshan, was in Kolkata on a training course. Their six-year-old daughter was with her grandparents in Sulur, where Namansh was serving with No. 3 Squadron.The high-achiever was an inspiration for hundreds not only in his hometown but also his alma mater, Sainik School Sujanpur Tira in Hamirpur district, and NDA. The school held a remembrance meet Saturday.He was part of the school's 21st batch, passing out in 2005. Group Captain Rachna Joshi, the school's principal, said: "Teachers here tell me he was exceptionally well in academics. Joining the school in Class IX and becoming the captain of Chenab House speaks volumes about him. He will continue to remain in our hearts forever as a braveheart," said the principal. His 'home' at NDA - Hunter Squadron - also held a remembrance meet.After his Class XII, Namansh enrolled in National Institute of Technology , Hamirpur, but his heart was set on NDA. After his first semester, he cleared SSB and joined NDA 115th course in 2006. He was appointed academic cadet captain, and commanded NDA's passing-out parade in Nov 2008, earning the President's Silver Medal in overall merit. Commissioned as a fighter pilot in Dec 2009, he flew MiG-21 and Su-30MKI before getting into Tejas at Sulur AFS in Coimbatore. At Hakimpet, he was a flying instructor on the Kiran trainer.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/india/tejas-crash-father-came-to-know-of-crash-while-searching-for-videos-of-syal-at-air-show/articleshow/125511446.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 01:14:47 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125511488,width-1070,height-580,imgsize-774730,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>Gisele Bundchen says prioritising Tom Brady for years took personal toll</t>
-  </si>
-  <si>
-    <t>Supermodel Gisele Bündchen reflects on her marriage to Tom Brady, describing their split as a "death and rebirth." She details her shift from supporting his career to rediscovering her own dreams and personal fulfillment. Bündchen emphasizes that true success lies in authenticity and self-discovery, moving forward on her own terms.
-Gisele Bündchen's shifting balance between support, career and self-fulfillment
-Moving from high-stakes partnership to reinventing life on her own terms
-In her March 2023 interview with Vanity Fair, supermodel Gisele Bündchen opened up about her 13-year marriage to former NFL quarterback Tom Brady, how their lives evolved, and what she discovered in the space that followed. While details of their split had played out in headlines, Bündchen offered fresh context and a more nuanced perspective.Gisele Bündchen admitted that the marriage was “like a death and a rebirth,” and described her own shift from supporting a partner’s career to rediscovering her personal dreams. Her reflections reveal not just a high-profile breakup, but a woman reclaiming her voice and defining success on her own terms.When Gisele Bündchen first met Tom Brady at age 26, she said she was, “so ready” for family and partnership. Traditionally one of the world’s highest-earning models, she gradually scaled back her runway work after 2015 to support the family life they were building..Gisele Bündchen describes relocating to Tampa without ever having lived there before, “When we moved to Tampa, I actually had never been there before.I just arrived and that was my life.” Yet despite her enormous success, much of the public narrative painted her as “against football” or overshadowed by Brady’s career, a portrayal she calls “very hurtful” and “the craziest thing I’ve ever heard.”Gisele Bündchen underscores that marriage didn’t unravel overnight. “That takes years to happen.” As she puts it, “Sometimes you grow together; sometimes you grow apart … When you love someone, you don’t put them in a jail and say, ‘You have to live this life.’ You set them free to be who they are..”Gisele Bündchen's message: supporting someone doesn’t mean losing yourself, and that truth became clearer to her as her kids grew and her dreams quietly changed..Today, Gisele Bündchen speaks of her next act in Costa Rica, building a home, raising her children, and exploring wellness and nature far from red carpets. She asserts, “I have my own dreams..”While Tom Brady continued his historic career, Bündchen’s focus shifted inward. She embraced spiritual practices, daily rituals, and the idea that success is not just professional acclaim but authenticity and fulfillment. She says the breakup felt like both a loss and a liberation, “I believed in fairy tales when I was a kid. I think it’s beautiful to believe in that.”Gisele Bündchen's reflection on Brady is remarkably gracious. “Listen, I have always cheered for him, and I would continue forever … If there’s one person I want to be the happiest in the world, it’s him.”In doing so, Gisele Bündchen rejects reductive headlines and stereotypes, choosing instead to present a fuller picture of love, change and self-discovery. As she said, “What’s been said is one piece of a much bigger puzzle. It’s not so black and white.”In the end, this isn’t a story solely of one of fashion’s biggest icons, Gisele Bündchen stepping aside. It’s the story of a woman stepping forward, redefining when a chapter ends, a new one begins..Also Read: Gisele Bündchen’s post divorce evolution raises question: did Tom Brady underestimate what letting her go would cost him?</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/sports/nfl/news/gisele-bndchen-implied-that-prioritizing-tom-brady-for-years-took-a-personal-toll-when-you-love-someone-you-dont-put-them-in-jail/articleshow/125033119.cms</t>
-  </si>
-  <si>
-    <t>Mon, 03 Nov 2025 04:40:47 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125033119,width-1070,height-580,imgsize-60856,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>Who was Harman Sidhu? All about the Punjabi singer who passed away in road accident</t>
-  </si>
-  <si>
-    <t>Tragic news as Punjabi singer Harman Sidhu has passed away at 37 following a fatal road accident. His vehicle collided head-on with a truck on the Mansa-Patiala road, resulting in his immediate death. Sidhu rose to fame with his hit song 'Paper Ya Pyar' and was known for his relatable tracks and down-to-earth nature.
-Who was Harman Sidhu?
-Punjabi Singer Harman Sidhu Dies In Tragic Road Accident!
-More about his demise
-Punjabi singer Harman Sidhu has passed away at the very young age of 37 after meeting a fatal road accident . As per the reports, the music artist was going back to his village when his vehicle collided with a truck on the Mansa-Patiala road. Reportedly, his car got crushed in the accident due to a head-on collision. It has been reported that the singer died on the spot. Let's learn more about the departed soul.Harman Sidhu was from the village of Khiala near the Mansa district of Punjab. He discovered his love for singing early in life, growing up in a place where Punjabi music and folk traditions were a part of everyday living. And eventually, he picked it as his career.Sidhu shot to fame after his song 'Paper Ya Pyar', starring Miss Pooja , became a massive hit. As it was a chartbuster track, it resulted in making Harman popular amongst the youth. With that, the singer solidified his place in the music industry of Punjab.Harman Sidhu went on to drop several tracks, which received love and appreciation from the audience, strengthening his fanbase. His popular tracks include, 'Paper Ya Pyar' (with Miss Pooja), 'Bebe Bapu', 'Koi Chakkar Nai', 'Babbar Sher', and 'Multan VS Russia'.These tracks remain favorites of the people even now due to their catchy beats and relatable lyrics.On social media platforms, the singer had a modest fan following but loyal supporters. His Instagram account has over 3742 followers. On the other hand, his Facebook followers' count is 18000. Meanwhile, on YouTube, he has over 13.1K subscribers.The admirers of the singer always lauded him for his down-to-earth nature and his connection with his audience.For those unaware, Harman Sidhu is survived by his wife and young daughter. As of now, his family has not issued any statement. His fans and the Punjabi community have expressed their grief on social media. They grieved his loss, remembering him as a kind soul and a gifted artist who left far too soon.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/entertainment/punjabi/music/who-was-harman-sidhu-all-about-the-punjabi-singer-who-passed-away-in-fatal-road-accident-at-37/articleshow/125515975.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 11:04:02 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125515975,width-1070,height-580,imgsize-31380,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>'Too much speed for narrow lane': Teen-driven car kills 7-year-old in Gurgaon</t>
-  </si>
-  <si>
-    <t>Representative Image
-GURGAON: A seven-year-old boy playing outside his house with his father was crushed to death by a car being driven by a teenager in Maruti Kunj on Friday evening.Witnesses recalled the sudden roar of a Maruti SX4 as it sped down the narrow lane and crashed into Yohan, a Class II student. The boy was dragged for almost 20 metres on the bonnet of the car before the 15-year-old driver slammed the brakes.“It all happened in a flash. The car was going too fast for a lane as narrow as this. We heard a loud thud and rushed out to see what had happened,” said a local resident.Yohan was the only son of Ashwani Kumar, a building materials supplier and his schoolteacher wife.Residents gathered at the scene, pulled the underage driver out of the vehicle and informed police. Yohan’s family rushed him to Artemis Hospital, but he had succumbed to injuries by then.The incident left the neighbourhood shocked. “Our children play here every day. We never imagined something like this could happen right at our doorstep,” said a neighbour.An FIR was registered at Bhondsi police station under sections 106 (causing death by negligence) and 281 (rash driving) of BNS. Preliminary probe revealed that the car was not registered in the name of the minor’s father, who works for a private company.“We are trying to find out the actual owner of the car,” said an officer, adding that the vehicle could have been recently purchased second hand without updating registration records.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/city/gurgaon/too-much-speed-for-narrow-lane-7-year-old-boy-crushed-to-death-by-car-driven-by-15-year-old/articleshow/125514732.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 08:06:12 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125514770,width-1070,height-580,imgsize-9074,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>Ukraine peace plan row: Is Trump’s 28-point proposal actually Russia’s ‘wishlist’? What Rubio said</t>
-  </si>
-  <si>
-    <t>Trump with Putin; Zelenskyy (File photo)
-‘Sign NOW Or Suffer Later!’: US Threatens NATO To Pressure Ukraine Into Signing Russia Peace Deal
-The US state department on Saturday rejected claims that its 28-point plan to end the Ukraine war was a “Russian wish list.” The denial came after a group of senators said they were told by secretary of state Marco Rubio that President Donald Trump was pushing a plan shaped by Moscow.State department spokesman Tommy Pigott said on X that the allegation was “blatantly false,” adding that the plan was written by the United States with inputs from both Russia and Ukraine.Pigott was responding to Republican senator Mike Rounds' claim that secretary of state Rubio told him the document was a proposal passed on to a US representative, not a plan drafted by the US, reported News Hour.Rounds reportedly said that the plan was shared as an intermediary and later leaked, not released by lawmakers. According to Rounds, the proposal was handed over by someone claiming to represent Russia and delivered to Steve Witkoff, the US special envoy to the Middle East.Senator Angus King also said the leaked document appeared to reflect Russian demands, not the administration’s position. "The leaked 28-point plan, which, according to secretary Rubio, is not of the administration's position--it is essentially the wish list of the Russians," he said.Earlier, CBS News reported that Western leaders were concerned because the proposal contained several Russian conditions and provided only limited assurances regarding Ukraine’s sovereignty and security.The plan has triggered concern in Kyiv and across Europe. Ukraine's President Volodymyr Zelenskyy said his country now faced a difficult choice between protecting its sovereign rights and maintaining crucial American support.President Trump has asked Zelenskyy to respond to the plan by Thursday, with the possibility of an extension. He told reporters that the proposal was not his final offer and repeated his view that the war should never have happened.On Friday, Russian President Vladimir Putin confirmed that Moscow had received the text of the 28-point plan through its usual communication channels with Washington.Ukrainian officials will meet a US delegation in Switzerland to discuss the plan.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/world/us/ukraine-peace-plan-row-is-trumps-28-point-proposal-actually-russias-wishlist-what-rubio-said/articleshow/125514590.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 08:07:58 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125514794,width-1070,height-580,imgsize-36620,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>Exclusive! Abhinav Tejrana - The Delhi boy ignored by DDCA is making waves for Goa</t>
-  </si>
-  <si>
-    <t>Abhinav Tejrana is the leading run scorer in Ranji Trophy Elite group. (GCA)
-New Delhi:
-Shubman Gill ruled out of South Africa ODIs; three captaincy candidates emerge
-Go Beyond The Boundary with our YouTube channel. SUBSCRIBE NOW!
-Poll What do you think contributed most to Abhinav Tejrana's success in Goa? Support from family Opportunities in local tournaments Coaching and mentorship in Goa
-A ‘Tejrana’ from Delhi plying his trade for Goa in the Ranji Trophy seems bizarre."I am not playing as a professional for Goa. I am a local," Abhinav Tejrana clarifies in a freewheeling chat with TimesofIndia.com from Porvorim.The 24-year-old top-order batter has set the Ranji Trophy on fire. Batting at No. 3 for Goa, the Delhi-born cricketer has amassed 651 runs in eight innings, including a double century on his first-class debut against Chandigarh. He has also smashed two centuries against Punjab and Saurashtra, and not to forget his match-saving unbeaten 73 against Karnataka.Abhinav, who has played U-19 cricket for Delhi, was given the cold shoulder by the Delhi &amp; District Cricket Association (DDCA) selectors. The thought of quitting the game initially crossed Abhinav's mind in 2021, but his father Anil Kumar, a Delhi Government employee, put his arm around his son's shoulder and said: "There's always a smile on your face whenever you pick up a bat. Never lose that, keep believing."Tejrana vividly recollects the advice he received from his father, and in 2022, he decided to move to Goa to take care of a "guest house"—a property his father had invested in years ago—and also in a quest to find a second home."Actually, I wasn't playing for 2–3 years in Delhi. I last played in under-19. And then for 2 years, I didn't play for DDCA. So I decided to shift. I had some business in Goa and residence here, so it kind of made my decision easier," shares Abhinav."I started playing the local tournaments and leagues in Goa. From there onwards, I started giving trials for the Goa Cricket Association (GCA). Then I played under-23 last season and was also in the Ranji Trophy camp. This year, finally, I made my Ranji Trophy debut," he says.Abhinav found his second home in Goa, but it came at an emotional cost."I am playing as a local here. My father works in the Delhi government, so he is based in New Delhi. My sisters and most of my family live in Delhi. My mother decided to stay with me," says an emotional Abhinav."I had a lot of people to support me. My family always believed in me, encouraged me to keep going. They always believed in my potential."In the initial days in Goa, many local people also backed me. So I kept going on. It is always tough to work hard when you don't know whether it is going to happen or not. But it is important to keep going and have that faith," he says.I have always felt at home here in Goa, and most of the credit goes to the GCA. They have helped me a lotThe faith definitely worked wonders for Tejrana as he not only found a home in Goa but his exploits have also helped Goa punch above their weight."I have always felt at home here in Goa, and most of the credit goes to the GCA. They have helped me a lot. Chetan Desai sir, Vinod Phadke sir, who are the chiefs in Goa, the secretary Tulsidas (Shetye) sir and President Mahesh Desai sir, they have all backed me. And when I wasn't getting the opportunities, Vipul Phadke sir also encouraged me in my low times. Head coach Milap Mewada—how can I forget his name. I really want to thank all of them," Tejrana shows his gratitude.No. 3 in first-class cricket is probably the most crucial number to bat at, and the southpaw eased into the role seamlessly."Actually, in red-ball cricket, the top 3 batters are mostly openers. In white-ball cricket, I don't know yet where I would bat. But I think growing up, I have played in most of the numbers. It's not like I have always opened. I have experience of playing in the middle order as well," he says.Talking about the season, the youngster, who will turn 25 in a month's time, rates his double hundred on Ranji debut as very special."I think the first one was important because it gave us a good score on the board. And we were 3 down for 115. Then me and Lalit (Yadav) bhai had a 309-run partnership. That was very important for the team to have 7 points in the first game."And after that, I think against Karnataka in Shimoga, they were going for the outright win. So we had to play in tough conditions. The ball was doing a lot. So to play those 46 overs out was helpful for the team. So those two were, I would say, helpful for the team to get some points," he says.Reflecting on the grind he went through after moving to Goa, he believes it made him a tough cookie."I think it made me more of a complete player. I am still in the process, as there is a lot to learn. But I think having this experience of playing these matches was a bit new to me. But gradually playing in the Goa Premier League Division gave me a lot of experience. And the setup that the association has is really nice," he says."We have a red-ball camp for 2–3 weeks, and I got to prepare very well for the red ball. So I didn't face any issues because I have been playing red-ball cricket for the last 3 months now. That helped me a lot," he adds.Goa is not known for cricket; it has a rich history in football. But Abhinav feels things are changing."Currently the pool of cricketers in Goa is not that big. But I think the way the leagues are conducted, they are far better. Because I have never played a three-day match in the Delhi leagues. There are no days matches there. So the type of tournament that they conduct here in Goa, I think, is much better. The structure of leagues and trials and camps—I think they have a structure that is more player-friendly. And surely you will see more young guys at under-19 level coming through the ranks because they have such a structure that is bound to improve players and produce quality players," he says.Abhinav's eyes are set on the upcoming Syed Mushtaq Ali Trophy, and he wants to continue playing cricket with a smile on his face, as he promised his father a couple of years ago."I think I have always played cricket to enjoy. That is the most important thing. And that's what my father says to me. And that is my goal ultimately—to enjoy when I am playing on the field. I don't think that much about the runs, the performances. I have a game plan which I follow, and even if I get out executing my plans, I don't mind it," he says.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/sports/cricket/news/abhinav-tejrana-the-delhi-boy-ignored-by-ddca-is-making-waves-for-goa/articleshow/125514774.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 08:34:56 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125514920,width-1070,height-580,imgsize-42618,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>G20 summit: PM Modi calls for global fight against drug-terror nexus</t>
-  </si>
-  <si>
-    <t>PM Modi at G20
-At G20 Summit, PM Modi Proposes Global Knowledge, Skills, Health And Security Initiatives For Future
-PM Modi lauds South Africa’s presidency
-In his address at the G20 summit in Johannesburg on Saturday, PM Narendra Modi pitched for sustainable and inclusive growth and made four proposals, including a coordinated global effort to combat the drug-terror nexus, calling drug trafficking a threat to public health, stability and security and a source of terror financing.He pushed for reconsidering the parameters of growth, saying the existing framework has left a vast section of the population deprived of resources and led to overexploitation of nature.Modi, who was instrumental in getting the African Union as a permanent member of G20 at the New Delhi meet of the grouping two years ago, emphasised the continent has suffered the most because of skewed growth priorities. “Today, as Africa hosts G20 Summit for the first time, it is imperative for us to reconsider the parameters of development.”The PM mentioned “integral humanism”, an idea associated with BJP’s ideologue Deen Dayal Upadhyay, as a path forward. “We will have to look at the individual, society and nature as an integrated whole. Only then can we achieve true harmony between progress and nature,” he said.He proposed creation of a global traditional knowledge repository built on Indian knowledge systems’ initiative, saying this can preserve the collective wisdom of humanity for future generationsBatting for a global healthcare response team to bring together experts from G20 countries, he said it will ensure swift measures in case of health emergencies and natural disasters.The speech was marked by an unabashed advocacy of what Modi called India’s civilisational ethos. India’s civilisational values, he said, can offer ways to reevaluate development parameters.Focusing on Africa, PM said the continent can benefit from skills transfer. He said Africa’s development and empowerment of its young talent are in the interests of the entire world and proposed a ‘G20-Africa Skills Multiplier Initiative’. This can operate under a “train-the-trainers” model across various sectors, and all G20 partners can finance and support this effort, he added.“Our collective goal will be to prepare one million certified trainers in Africa over the next decade. These trainers will, in turn, help equip millions of young people with skills. This initiative will have a powerful multiplier effect. It will strengthen local capacity and significantly contribute to Africa’s long-term development.”Turning his attention to drug trafficking, PM Modi singled out the “rapid spread of highly lethal substances like fentanyl”. “This has emerged as a serious challenge to public health, social stability and global security. It also serves as a significant channel for financing terrorism,” he said.A G20 initiative to counter this global threat can bring together various instruments relating to finance, governance and security. Only then can the drug-terror economy be effectively weakened, he said. Modi lauded South Africa’s presidency for making commendable progress on key areas such as skilled migration, tourism, food security, AI, digital economy, innovation and women’s empowerment, noting that historic initiatives undertaken at the New Delhi G20 Summit have been carried forwardPM Modi on Saturday also proposed a G20 Critical Minerals Circularity Initiative, saying that for global growth, sustainability and clean energy are essential, and critical minerals have a huge role to play.“Under this, innovations such as re-cycling, urban mining and second-life batteries can be promoted,” said PM Modi. This comes amid concerns China is leveraging its chokehold over supply of rare and critical minerals to further its strategic goals.“If there is investment in circularity, then dependence on primary mining will be less. This will also reduce the pressure on the supply chain, and it will also be good for nature. This initiative can support joint research, technology standards and pilot recycling facilities in the Global South,” PM Modi said.Resilience cannot be built in silos, stressed the PM. “The G20 should promote comprehensive strategies that combine nutrition, public health, sustainable agriculture, and disaster preparedness, to create a robust global defence,” he said.PM Modi suggested a G20 open satellite data partnership saying India believes that the entire humanity should benefit from space technology. “This will make satellite data and analysis of space agencies of G20 countries more accessible, interoperable and usable for countries in the Global South,” he said.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/india/g20-summit-pm-modi-calls-for-global-fight-against-drug-terror-nexus/articleshow/125511740.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 02:47:47 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125511744,width-1070,height-580,imgsize-874511,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>'Trusted orchestra': Army chief on Op Sindoor's 22-min, 9-target strike</t>
-  </si>
-  <si>
-    <t>Indian Army Chief Reveals How A Trusted Orchestra Crushed Nine Targets in Operation Sindoor Blitz
-NEW DELHI: Army Chief General Upendra Dwivedi talked about Operation Sindoor, drawing parallels with a "trusted orchestra" where "every musician played a simultaneous or a synergistic role. ". Speaking at an event in the national capital on Saturday, he explained how the armed forces destroyed nine targets in 22 minutes, despite the time crunch."Operation Sindoor was a trusted orchestra where every musician played a simultaneous or a synergistic role. That is how in 22 minutes, we could destroy nine terrorist targets and, we could in 80 hours make sure that the battle comes to an end. But what is more important, there was no time for decision making, had we not visualised, and had we not trusted the entire team," the Army chief said.He said that the response was not shaped "in the moment, but through years of imagining how intelligence, precision and technology could converge into action."In an earlier address, echoing Prime Minister Narendra Modi's sentiments, he had said that Operation Sindoor was just a "trailer", hinting at a 2.0 version."On Operation Sindoor 1.0, I would say that the movie had not even begun, only a trailer was shown, and after 88 hours the trailer was over," he had said.India launched Operation Sindoor on May 7, destroying several terror facilities in Pakistan and PoK. Pakistan responded with its own offensives, prompting further Indian counterstrikes under the same operation. The nearly clash between the two nuclear-armed nations ended on May 10 after both sides reached an understanding.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/india/trusted-orchestra-army-chief-on-operation-sindoor-explains-how-teamwork-crushed-nine-targets-in-22-minutes/articleshow/125514374.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 07:00:51 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125514469,width-1070,height-580,imgsize-712497,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>How handwoven silk in this tiny village of Assam has stood the test of time</t>
-  </si>
-  <si>
-    <t>Weavers work on handlooms in Assam’s Sualkuchi village; (bottom) Buyers with mekhela chador — traditional two-piece garment worn in the state — made of Pat and Muga silk
-Sualkuchi operates 12,000 handlooms, producing around 3 lakh sq m of silk fabric a year, and remains untouched by the clatter of machines
-Defying the industrial revolution
-Silk with a signature
-TOI
-Threads of history
-Struggles of continuity
-In 1946, when Mahatma Gandhi set foot in Sualkuchi, a picturesque village nestled along the Brahmaputra near Guwahati, he was spellbound by the artistry of the local weavers, particularly the women. Their looms seemed to weave not just silk, but dreams, he felt. His words — “Assamese women weave dreams on their looms”, have lingered like the rustle of silk ever since.Nearly eight decades later, those looms are still humming. Sualkuchi remains one of the rare places in India where handlooms, not machines, dictate the rhythm of daily life.While many historic silk weaving centres across India have succumbed to the lure of power looms for economic gain, Sualkuchi, located 35km from Guwahati, remains a bastion of handloom tradition. This steadfast commitment to authenticity is a bequest of the village’s dedication to preserving its cultural heritage. Despite govt’s push for mechanisation in places like Varanasi and Kancheepuram, Sualkuchi’s weavers, supported by their community and loyal customers, have resisted, ensuring that the artistry of handwoven Muga and Pat silk remains untouched by the clatter of machines.This village, with approximately 50,000 people, produces three exquisite varieties of Assam silk — the golden Muga, the warm Eri, and the lustrous Pat — each derived from different silkworms.Within its 8 sq km, 12,000 handlooms work tirelessly, producing around 3 lakh sq m of silk fabric a year, valued at Rs 300 crore. But beyond the numbers lies something more fragile: a cultural identity woven into every strand of yarn. This cottage industry supports nearly 6,000 families, all intricately woven into the fabric of Sualkuchi’s identity.Dr Nihar Ranjan Kalita, an adviser to the Sualkuchi Tat Silpa Unnayan Samiti and principal of SBMS (Sualkuchi Budram Madhab Satradhikar) College, explains that the village’s handloom industry thrives because it is deeply embedded in the local culture. He says that the younger generation, drawn by the allure of fashion and style, actively participates in this age-old craft, ensuring its continuity. “There is societal pressure in Sualkuchi and Assam to keep the textile industry handloombased. The community understands the exquisite value of handloom products.”In Sualkuchi, wearing a mekhela chador (Assam’s traditional two-piece garment) made of Pat and Muga silk is a mark of prestige at weddings and festive gatherings. The village’s commitment to the handloom is so strong that the word “powerloom” is almost taboo, seen as a threat to the originality of their textiles.Kalita, who has explored various textile hubs across India, observes that while other centres focus on exports, Sualkuchi’s products are cherished domestically. This local focus, coupled with govt support for semimechanisation in allied activities, helps maintain the village’s handloom legacy.This guardianship of tradition is not without struggle. In 2013, when powerloom textiles and counterfeit fabrics began flooding the market, threatening to dilute Sualkuchi’s reputation, villagers rose in protest. Their agitation eventually led to the establishment of the Sualkuchi Silk Testing Laboratory. In 2017, its centuries-old weaving tradition earned trademark status. Now, entrepreneurs submit their products in the lab where every piece of silk is tested, certified, and tagged — with a QR code, a 3D hologram and the Silk Mark logo — if they meet the standards.With a quick scan, buyers today can verify a garment’s authenticity, trace its fabric details, and even discover the specific handloom and artisan behind the weave. The trademark seal, ‘Sualkuchi’s’, acts as both a brand and a shield, protecting these handcrafted treasures from counterfeiting.During’s visit to the lab, the staffers were seen conducting three tests to confirm authenticity — burning analysis, microscopic crosssectional examination and chemical verification. The first test involves burning small thread samples to verify silk content; microscopic analysis identifies the specific silk variety, while chemical testing is performed when the first two examinations prove inconclusive.Assam is unique in producing all four recognised silk varieties in India — Muga, Eri, Mulberry, and Tussar. But it is Muga that sets Sualkuchi apart. The distinctive golden yellow silk, exclusive to Assam, comes from the Antheraea assamensis silkworm. It’s valued for its longevity and distinctive lustre.Eri, recognised for its even texture, is used in clothing and household items. In the Mulberry category, despite substantial demand for the yarn, the supply of the locally available Nuni pat variety is insufficient. Weavers often source Mulberry and Tussar yarn, a recent addition to the state’s silk portfolio, from Karnataka (Mulberry), Jharkhand, Odisha, and West Bengal (Tussar).Sualkuchi’s history dates back to the 11th century, when King Dharma Pala of the Pala Dynasty established it as a weavers’ village by relocating 26 weaver families from Tantikuchi in Barpeta. Royal patronage turned the village into a hub of silk weaving. During the 17th century, under Ahom rule, it had become Assam’s primary handloom centre. For centuries, its economy thrived not just on weaving but also on pottery, goldsmithing, and oil pressing — until the 1940s, when only the looms endured.Until 1930, silk weaving was concentrated within Tantipara’s Tanti community. World War II gave Sualkuchi its biggest push, as skyrocketing demand and prices prompted several Tanti families to establish commercial weaving units with hired workers.However, challenges like rising raw material costs, market instability, and limited cocoon availability have pressed Sualkuchi’s weavers hard. “Muga silk products of Sualkuchi have been the most precious. But inadequate supply of cocoons and high prices of yarn have confined the number of households producing Muga textile to about 50,” says Kalyan Kalita, an entrepreneur. “Once, Sualkuchi was known for Muga above all else. Now, few families can afford to produce them. ” The industry has seen shifts: Bodo weavers, mostly women, have returned home after peace talks, reviving traditional skills, and skilled weavers from Bengal found refuge in Sualkuchi post-Covid. This convergence of talent has reinforced the village’s handloom tradition.Weaver Binita Boro reflects on the enduring appeal of the craft: “Handloom cannot die. As a child, I watched my aunt weave dreams here in Sualkuchi. Now, as an adult, I am part of this enchanting village.”</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/india/how-handwoven-silk-in-this-tiny-village-of-assam-has-stood-the-test-of-time/articleshow/125514584.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 07:25:51 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125514594,width-1070,height-580,imgsize-1372959,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>'Long live friendship': Macron hails India-France ties; meets PM Modi on G20 sidelines</t>
-  </si>
-  <si>
-    <t>(Image credits: X @narendramodi)
-At G20 Summit, PM Modi Proposes Global Knowledge, Skills, Health And Security Initiatives For Future
-NEW DELHI: French President Emmanuel Macron and Prime Minister Narendra Modi on Sunday reaffirmed the close and growing partnership between India and France during a meeting on the sidelines of the 2025 G20 Summit in Johannesburg.After the discussion, President Macron posted on X, saying, “Thank you, my friend, dear Narendra Modi. Nations are stronger when they move forward together. Long live the friendship between our countries!”PM Modi also hailed the relationship, writing, “Delighted to meet President Macron during the Johannesburg G20 Summit. We had an engaging exchange on different issues. India-France ties remain a force for global good!”Earlier, during the second session of the G20 Leaders’ Summit, PM Modi highlighted the rising frequency of natural disasters and their growing impact on populations across the world. He stressed the need for stronger international cooperation and noted that India had created the Disaster Risk Reduction Working Group during its 2023 G20 presidency. He also commended South Africa for prioritising the issue.“Natural disasters continue to pose a major challenge to humanity. This year as well, they have impacted a large portion of the global population. These events clearly highlight the need to strengthen international cooperation for effective disaster preparedness and response.To support this idea, India formed the Disaster Risk Reduction Working Group during its G20 Presidency. I also congratulate South Africa for giving priority to this important agenda,” he said.Calling for a shift from a “response-centric” to a “development-centric” approach to resilience building, PM Modi proposed a G20 Open Satellite Data Partnership to improve access to satellite data from G20 space agencies. He said the initiative would be particularly valuable for the Global South.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/india/long-live-friendship-between-our-countries-macron-hails-india-france-ties-meets-pm-modi-on-g20-summit-sidelines/articleshow/125514523.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 07:09:58 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125514526,width-1070,height-580,imgsize-578748,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>Tharoor's post on Trump-Mamdani meeting gives BJP ammo to attack Rahul</t>
-  </si>
-  <si>
-    <t>'This Is How Democracy Should Work': Shashi Tharoor's Truth Bomb on Cong After Trump-Mamdani Meeting
-NEW DELHI: Lauding the cordial meeting between US President Donald Trump and New York City Mayor-elect Zohran Mamdani, Congress leader Shashi Tharoor Saturday said "this is how democracy should work and hoped to see this happen in India". BJP spokesperson Shehzad Poonawalla commended Tharoor for his remarks and said he hoped that Rahul Gandhi would get the message.After months of attacks against each other during the high voltage New York City mayoral election, Trump and Mamdani adopted a mutually warm tone during their first meeting at the White House in Washington DC. Reposting on X a video of a media interaction where Trump and Mamdani took questions on their meeting, Tharoor said, "This is how democracy should work. Fight passionately for your point of view in elections, with no rhetorical holds barred. But once it's over, and the people have spoken, learn to cooperate with each other in the common interests of the nation you are both pledged to serve.""I would love to see more of this in India, and I'm trying to do my part," the Congress MP from Thiruvananthapuram added.Reacting to Tharoor's remarks, BJP spokesperson Shehzad Poonawalla in a post on X said, "Once again, Shashi Tharoor reminds Congress to put India first, not Parivar.To behave democratically and not like sore losers. But will Rahul Gandhi get the message? One more Fatwa loading against Shashi?" Poonawala posed in a post on X.On November 18, Tharoor's praise for PM Narendra Modi's speech at a media function triggered a social media storm with Congress leader Sandeep Dikshit asking Tharoor to explain how BJP's policies, which are against Congress's principles, are helping the country and why he is staying on in Congress if he agrees with BJP. AICC spokesperson Supriya Shrinate also said that she did not find find any reason to praise the PM's speech.On Nov 9, Congress had "dissociated" itself from Tharoor's statement praising veteran BJP leader L K Advani and made it clear that "like always he speaks for himself and the fact that he continues to do so as a CWC member reflects the party's democratic and liberal spirit".Congress's remarks had come after Tharoor, reacting to criticism over his birthday greetings for Advani, said reducing the veteran BJP leader's long years of service to one episode, however significant, is unfair. He also said that when the totality of Jawaharlal Nehru's career cannot be judged by the China setback and Indira Gandhi's by the Emergency alone, he believes "we should extend the same courtesy to Advaniji".</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/india/shashi-tharoors-post-praising-trump-mamdani-meeting-gives-bjp-ammo-to-attack-rahul-gandhi/articleshow/125511643.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 01:52:08 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125511645,width-1070,height-580,imgsize-547184,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>Saudi bus crash: Umrah pilgrims, including 45 Indians laid to rest in Medina</t>
-  </si>
-  <si>
-    <t>Over 40 Indians From Hyderabad Travelling From Mecca To Medina Feared Killed in Saudi Bus Crash
-HYDERABAD: The last rites of the 46 Umrah pilgrims — 45 from Hyderabad — who died in the bus accident near Medina on November 17 were performed in the holy city on Saturday.Telangana minority welfare minister Mohammed Azharuddin, who was in Medina with minority welfare secretary B Shafiullah and AIMIM legislator Majid Hussain, said all religious formalities were "completed with great care and honour in one of the purest and most sacred places in Islam. "Funeral prayers were offered at Masjid-e-Nabawi after Namaz-e-Zuhar, followed by burial at Jannat al-Baqi, one of Islam's holiest graveyards. The rites were delayed by a day due to pending documentation for some of the deceased and logistical issues.The Telangana government, which announced 5 lakh ex gratia for each bereaved family, facilitated the travel of two relatives for every victim to Saudi Arabia. Azharuddin said arrangements for transportation, food and accommodation were made for all visiting relatives, while some travelled on their own.A total of 38 family members are currently in Saudi Arabia and will return to Hyderabad on November 27 after completing all formalities.Among them is Imran Sharif, nephew of Naseeruddin (70), who lost 17 family members. "The last rites were completed in presence of 13 of our family members. I reached Medina on Thursday; I didn't travel with the group of 35," he said.Rizwan Ahmed, who lost five family members including his mother and brother, said, "We are now waiting for any other additional formalities that need to be done."The accident — one of the worst involving Indian Umrah pilgrims in recent years — left several families shattered. Authorities said they will be in touch with Saudi officials for any further support needed.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/city/hyderabad/umrah-pilgrims-laid-to-rest-in-medina-families-to-return-on-nov-27/articleshow/125510420.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 00:04:41 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125511737,width-1070,height-580,imgsize-920658,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>Historic! First time since the 19th century: Perth Test breaks century-old records</t>
-  </si>
-  <si>
-    <t>Travis Head &amp; Mitchell Starc (AP)
-England’s rapid double collapse
-Shubman Gill ruled out of South Africa ODIs; three captaincy candidates emerge
-Fewest balls faced by England in Tests
-325 v Australia, Melbourne 1904
-388 v Australia, Lord’s 1888
-405 v Australia, Perth 2025*
-408 v Australia, Sydney 1895
-446 v West Indies, Edgbaston 1995
-476 v India, Ahmedabad 2021
-First Ashes Test to finish inside two days in a century
-Ashes Tests completed in under two days
-Lord’s 1888
-The Oval 1888
-Manchester 1888
-The Oval 1890
-Nottingham 1921
-Perth 2025*
-Shortest Ashes Test by balls bowled in over a century
-Shortest Ashes Tests (balls bowled)
-788 Manchester 1888
-792 Lord’s 1888
-847 Perth 2025*
-911 Sydney 1895
-Travis Head’s whirlwind century seals victory
-Australia’s commanding eight-wicket triumph over England in the first Ashes Test in Perth was more than just a dominant win — it rewrote record books, producing three rare feats not seen in over a century, with the match concluding in under two days.England’s batting woes were historic. Across both innings, they faced just 405 deliveries, their shortest combined total in a Test match since 1904. The visitors managed only 172 in the first innings and 164 in the second, marking just the third occasion in their history that a Test side has faced fewer than 410 balls.The collapse was abrupt and stark, underlining how even in the era of Bazball, England’s batting could crumble with shocking speed.Perth 2025 became the first Ashes Test in 100 years to finish in less than 48 hours, joining only a handful of historic matches from the late 19th and early 20th centuries. The last Ashes game to end this quickly was Nottingham in 1921.The match required just 847 deliveries, making it the shortest Ashes contest by balls bowled since the 19th century.Over 113 overs, fast bowlers dominated, claiming 30 wickets for 468 runs. Day one alone saw 19 wickets fall — the most in a single day in modern Ashes history. Mitchell Starc was the spearhead, taking 10 wickets in the match, including a career-best 7-58 in England’s first innings. On day two, he dismissed Zak Crawley , Joe Root, and Ben Stokes , while Scott Boland’s devastating post-lunch burst — three wickets in 11 balls — reduced England from 65-1 to 88-6. A stubborn 50-run partnership between Gus Atkinson (37) and Brydon Carse (20) was the only resistance before setting a target of 205.Australia promoted Travis Head to open in Khawaja’s absence, and he produced a counterattacking masterpiece. Head scored 123 off 83 balls, reaching his century in 69 deliveries — the fastest Ashes hundred by an opener. He struck 16 fours and four sixes, dismantling England’s short-ball strategy.Head fell with just 13 runs remaining, but Marnus Labuschagne (51*) finished the chase in style with a six, ensuring Australia’s eight-wicket victory and setting a new benchmark for rapid Ashes Test finishes.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/sports/cricket/ashes/historic-first-time-since-the-19th-century-perth-test-breaks-century-old-records/articleshow/125514355.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 06:47:21 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125514363,width-1070,height-580,imgsize-1186437,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>Mumbai twins, just a month old, battle drug-resistant TB</t>
-  </si>
-  <si>
-    <t>Representative image
-MUMBAI: A Kandivli couple's joy at having twins after IVF treatment was tinged with sadness as their boys were diagnosed with drug-resistant tuberculosis (TB) during Diwali when they were barely a month old.Their case points to a worrisome pattern of drug-resistant TB in infants. The state-run JJ Hospital's NICU, where the twins—possibly the youngest in the state—have been admitted since October 29, has seen multiple such cases. The World Health Organisation's Global TB Report released last week highlighted a 21% drop in the incidence of TB in India between 2015 and 2024, but it's clear that alarming concerns remain."One of the boys was diagnosed when he was barely a few weeks old," recalled infectious diseases specialist Dr Tanu Singhal, who suspected TB when he was first taken with pneumonia to Kokilaben Ambani Hospital. "Both are the youngest drug-resistant TB cases I have seen," she said.She directed the children to Dr Sushant Mane, who is the nodal officer (paediatrics) at the National Centre of Excellence for Tuberculosis in JJ Hospital.Four months ago, the JJ team treated a three-month-old boy who was the first infant in the state to be put on a course of newer anti-TB antibiotics, bedaquiline and delamanid.When contacted, Dr Mane confirmed that both the boys, who were admitted on October 29, have drug-resistant TB. "While the younger child had clinical and X-ray evidence of extensive TB, the elder twin's tests were non-conclusive," he said. The doctors then tested the cerebrospinal fluid of both babies and found "features of TB meningitis" in both, and started them on anti-TB medications. The older twin later developed breathing difficulty and was put on ventilator support.Doctors said the twins most likely got TB from their mother. Their father, who didn't want his family to be identified, said his wife was treated for abdominal TB before undergoing IVF, but subsequent tests showed she was clear.The reason for more infants getting treated for TB is better diagnostics, said Dr Mane. "Every year, 10 million new cases of TB are diagnosed across the world. About 10% of the cases are among paediatric patients under 15 years of age," said Dr Singhal.The boys, who were 2 kg and 1.7 kg at birth, now weigh 3.6 kg and 3 kg respectively. "As they are improving, doctors may discharge them soon," said their father. However, they have to continue with anti-TB medications until they are 18 or 24 months old.Mumbai registers over 60,000 new TB patients every year. Of these, roughly 5,000 patients have the difficult-to-treat drug-resistant variations.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/city/mumbai/one-month-old-twins-could-be-the-youngest-drug-resistant-tb-patients-in-mumbai/articleshow/125508535.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 04:12:32 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125514226,width-1070,height-580,imgsize-648131,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>When Madhuri recalled her fearless first date with Dr Nene</t>
-  </si>
-  <si>
-    <t>What she said about the first date
-Madhuri Dixit Nature Escape; Actress Shares Dreamy Pictures From Her Winter Getaway
-Celebrating 26 years together
-Madhuri Dixit Nene, one of Bollywood’s most graceful icons, has charmed audiences since her debut and later became a household name with celebrated films like Devdas, Hum Aapke Hain Koun and Beta. Beyond her illustrious career, her personal life has always warmed hearts. She married Dr Shriram Nene in 1999, stepping away from the film industry to begin a new chapter. Years later, she openly shared how nervous she felt during her very first date with him.Madhuri once spoke about that unforgettable day on Simi Garewal ’s show. She recalled that Dr Nene invited her for a mountain-biking outing — a sport she had never tried. She described the moment with honesty and humour: “The first time we met, he said, ‘Let’s go mountain biking.’ I swear I had not sat on a bicycle for the past 20 years. I am like, ‘Okay, let’s go.’ Mom was like, ‘What’s wrong with you? Do you know what it involves?’ And I am like, ‘Yeah, you just sit on a bike and you go.’ Once we went there, that was when I knew what mountain biking is. ”She remembered the fear vividly, describing how she rode down steep slopes, completely shocked at her own courage. Madhuri shared, “I literally was frightened out of my wits… ‘Did I just come down that?’” When she confessed to Dr Nene that she had never done anything like it, he admired her effort. As she recalled, he told her, “You are brave.” Their adventure became a defining moment, showing how naturally they connected.On October 17, the couple celebrated 26 years of marriage. Madhuri shared a heartfelt video on Instagram, captioned: “From moments to memories, 26 years of walking through life hand in hand. Happy anniversary.”</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/entertainment/hindi/bollywood/news/when-madhuri-dixit-recalled-her-fearless-first-date-with-dr-shriram-nene-i-swear-i-had-not-sat-on-a-bicycle-for-the-past-20-years/articleshow/125395129.cms</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 22:25:09 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125395151,width-1070,height-580,imgsize-90294,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>US warns western allies against mass migration saying it is an existential threat</t>
-  </si>
-  <si>
-    <t>US president Donald Trump (File photo)
-The TOI correspondent from from Washington:
-Trump IMPEACHMENT Announced In DC; Fury Near White House As 1000s Erupt In US | ‘REMOVE, CONVICT’
-The United States on Friday extended its campaign against mass migration to cover its European allies, warning that such inflow poses an “existential threat to Western civilization” and undermines its stability.In a series of posts, the State Department sought to expand the Trump administration’s anti-migration outlook beyond US borders, instructing American embassies in western nations to report on the human rights implications and public safety impacts of mass migration.“Western nations have endured crime waves, terror attacks, sexual assaults, and the displacement of communities. US officials will urge governments to take bold action and defend citizens against the threats posed by mass migration,” the State Department said characterising mass migration as “a human rights concern” affecting the population of its allies, rather than a concern relating to the migrants themselves as has been viewed traditionally.Asserting that issues stemming from mass migration have plagued citizens of Western nations for years, it said US officials will urge governments to “take bold action and defend citizens against the threats posed by mass migration.” Officials will also report policies that punish citizens who object to continued mass migration and document crimes and human rights abuses committed by people of a migration background, it added.The State Department cited examples of grooming gangs of migrant men victimising girls in the U.K – a decades old problem involving British-Pakistani criminals – and more recent stray incidents in Sweden and Germany to make the case against mass migration.It said US officials will now scrutinize policies in Western nations that give leniency to migrant crime and human rights abuses or that create two-tiered systems that prioritize migrants at the expense of their own citizens, citing the example of a German woman who it claimed was given a harsher sentence than rape perpetrators for insulting one of them online.Effectively, the State Department warning suggests the Trump administration not only wants to end migration into the US but also to stir up opposition in its western allies some of whom have been flooded with refugees and asylum seekers from Africa and Asia.Some analysts are concerned that the campaign against mass migration is a cover to end all immigration, including legal immigration, as demanded by MAGA nativists and isolationists. A few US allies, notably Canada and Australia, actively solicit qualified immigrants to replenish their vast land mass, stagnant or depleting population, and their coffers, without the wealthy and healthy conditionalities that Washington now insists on.While MAGA sentiment is firmly against all immigration, including legal immigration and even temporary foreign skilled workers, Canada aims to attract 500,000 immigrants annually and Germany's Skilled Immigration Act eases entry for non-EU workers. Even China, with 1.4 billion people, is opening its doors to foreign workers that the MAGA is happy to reject or dispense with.The new US anti-migration policy rolled out by Washington came on the heels of a series of posts by senior Trump officials blaming unchecked immigration for the economic decline of allies and celebrating US success in staunching migration.Responding to a chart shared by an economist that showed Canada's GDP per capita growth lagging behind other G7 nations since around 2015, US vice President J.D Vance suggested that immigration, not US policies, was the problem. "While I'm sure the causes are complicated, no nation has leaned more into 'diversity is our strength, we don't need a melting pot we have a salad bowl' immigration insanity than Canada. It has the highest foreign-born share of the population in the entire G7 and its living standards have stagnated,” he gibed.US officials also shared and celebrated a report in MAGA outlet Breitbart News about the US Foreign-Born Population declining by 2.3 Million under Trump, heralding what it called the “Golden Age” of America. “We are seeing a massive decrease in net migration in our country. What we're doing is working!” Vance exulted, while immigration advocates mused about the long-term effect of negative migration on the US economy.The official White House handle itself celebrated a report showing more than 2.5 million native-born Americans gaining employment, while 670,000 foreign-born workers lost jobs under President Trump.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/world/us/us-warns-western-allies-against-mass-migration-saying-it-is-an-existential-threat/articleshow/125509064.cms</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 23:08:25 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125509138,width-1070,height-580,imgsize-20636,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>'Brainless': 85-year-old ex-England cricketer blasts Ben Stokes-led team</t>
-  </si>
-  <si>
-    <t>England after losing the first Ashes cricket test match against Australia in Perth (Photo Credit: AP Photo/Gary Day)
-Former England cricketer Geoffrey Boycott has criticised the England team following their loss in the first Ashes Test match against Australia in Perth, which concluded in just two days.Boycott expressed his views in his column for The Telegraph UK, titled "I cannot take this stupid England team seriously anymore," where the 85-year-old criticised the team's approach."Before this series started Ben Stokes told the world that any ex-player who criticised them or had a different opinion were "has-beens" because Test cricket had changed and the past was irrelevant. Well, from this has been the message is simple: when you keep throwing away Test matches by doing the same stupid things, it is impossible to take you seriously. They never learn, because they never listen to anyone outside their own bubble, because they truly believe their own publicity," he penned."It is simple. Brainless batting and bowling lost England the match. A 40-run lead on a fast bouncy low scoring pitch was huge and with Ben Duckett and Ollie Pope together at one stage England were in charge at effectively 100 for one. But as exciting as this England team can be, they are always only a blink of an eye away from self destruction.""Bazball, bad judgement, overconfidence, whatever the reason it makes winning matches difficult. Against top teams like India and Australia, it is a huge factor in losing."The first Test match saw significant action with 19 wickets falling on the opening day.The second day witnessed 13 wickets, including England's complete second innings, where they could only set a target of 205 runs despite having a 40-run first-innings lead.Travis Head played a remarkable innings for Australia, scoring 123 runs from just 83 balls. Marnus Labuschagne contributed with a half-century as Australia successfully chased down the target.Australia secured an eight-wicket victory to take a 1-0 lead in the five-match series.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/sports/cricket/ashes/brainless-and-stupid-85-year-old-ex-england-cricketer-blasts-ben-stokes-led-team-after-1st-ashes-test-defeat-to-australia/articleshow/125508200.cms</t>
-  </si>
-  <si>
-    <t>Sun, 23 Nov 2025 05:00:00 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125508790,width-1070,height-580,imgsize-110068,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
-  </si>
-  <si>
-    <t>Brittany Mahomes stuns in red leather on date with Patrick before Chiefs–Colts game</t>
-  </si>
-  <si>
-    <t>Brittany Mahomes dazzles at 1587 Prime.
-Patrick and Brittany Mahomes enjoy personal moments at 1587 prime while gearing up for key chiefs game
-More NFL coverage
-Kansas City fans are bracing for a pivotal showdown as Patrick Mahomes and the Chiefs return to Arrowhead Stadium to face the Indianapolis Colts. After back-to-back road losses to the Bills and Broncos, Mahomes knows the margin for error has vanished. The team (5‑5) needs a win to keep its AFC playoff hopes alive, and all eyes are on the three-time Super Bowl MVP to bounce back. Beyond the pressure of the field, Mahomes also found moments of personal joy, giving fans a glimpse into life outside football.Off the field, Mahomes spent Friday evening with his wife, Brittany, enjoying a rare night out before the high-stakes matchup. Brittany shared several updates on Instagram, spotlighting her red leather outfit for dinner at 1587 Prime, the Kansas City steakhouse Mahomes opened with Travis Kelce earlier this year. The posts allowed followers to see a different side of the quarterback, one grounded in family, love, and life beyond the playbook.In one post, Brittany drew attention to a small detail in her outfit, writing, “1587 &amp; a cute bow,” with her back turned to the camera. She later shared a black-and-white photo giving her 2.1 million followers a clear look at the front of her ensemble. 1587 Prime has become a hotspot for Chiefs players and NFL personalities alike, with Travis Kelce and his fiancee, Taylor Swift, among the frequent guests.The restaurant honors both Mahomes’ No. 15 and Kelce’s No. 87, and even offers signature cocktails inspired by their partners.Patrick Mahomes didn’t appear in Brittany’s Friday night posts, but she gave him a nod earlier in the day for his thoughtful gesture. A bouquet of “just because flowers” from her high school sweetheart appeared on her Instagram story with the caption, “@patrickmahomes you are the best ever.” Moments like these show a couple enjoying each other’s company and staying grounded, even amid the demands of the NFL season.As the Chiefs prepare to take on the Colts, the Mahomes pair brings off-field positivity into a high-pressure weekend. Brittany’s style, their shared moments, and Patrick’s focus on bouncing back all contribute to the narrative heading into a crucial home game. Fans will be watching to see if that energy translates to a strong performance on the field and another stylish appearance from Brittany during gameday.</t>
-  </si>
-  <si>
-    <t>https://timesofindia.indiatimes.com/sports/nfl/news/brittany-mahomes-stuns-in-red-leather-dress-on-romantic-date-with-patrick-mahomes-before-he-leads-chiefs-into-showdown-with-colts/articleshow/125506298.cms</t>
-  </si>
-  <si>
-    <t>Sat, 22 Nov 2025 20:18:36 +0530</t>
-  </si>
-  <si>
-    <t>https://static.toiimg.com/thumb/msid-125507143,width-1070,height-580,imgsize-69204,resizemode-75,overlay-toi_sw,pt-32,y_pad-500/photo.jpg</t>
+    <t>News18_Crawler</t>
+  </si>
+  <si>
+    <t>Cricket News</t>
+  </si>
+  <si>
+    <t>India Vs South Africa ODI &amp; T20I Squad Announcement Live Updates: Selection Meeting Won't Happen In Guwahati, Shifted To... India Women Create History, Win Inaugural T20 World Cup Cricket For Blind On this day in 2009, Sachin Tendulkar created history by becoming the first player to reach 30,000 international runs during the India-Sri Lanka Test in Ahmedabad. India vs South Africa 2nd Test Day 1: Kuldeep, Bumrah Turn the Tide, South Africa Collapse to 247/6 High-Pressure Test for Rishabh Pant &amp; Gambhir | India vs South Africa 2nd Test Preview Sanju Samson’s First CSK Interview: Pride Of Wearing Yellow, MSD Connection &amp; Chennai Bond Shubman Gill Ruled Out? Predicted XI For 2nd Test Vs South Africa In Guwahati Australian Camp Worried As Josh Hazlewood's Ashes Participation In Doubt: Report When Will The 2026 T20 World Cup Schedule Be Out? Find All Details Here Smriti Mandhana's Father Suffers Heart Attack; Wedding With Palash Muchhal Deferred India Women Create History, Win Inaugural T20 World Cup Cricket For Blind Marco Jansen Misses Maiden Test Ton But Becomes 1st South African Batter To... Taijul Islam Makes History As Bangladesh Whitewash Ireland With 217-Run Win In 2nd Test 'That Is Lot Of Bowling...': Jasprit Bumrah Likely To Sit Out SA ODIs As Workload Peaks RCB Or RR: One Franchise Might Change Their IPL Home To Pune In IPL 2026 Marco Jansen Scripts History Vs India, Equals Shahid Afridi's Huge Record For.... Change In Plans! Ajit Agarkar-Led Selection Committee To Pick India's White-Ball Squad Vs SA On... First Time Ever! India Humiliated By South African Tailenders' Huge Record How David Warner Inspired Travis Head's All-Timer Ton Vs England In Ashes Opener After Losing Ashes Operner, Former England Captains Want Ben Stokes &amp; Co. To Play... 'Rahul Bhai Always Says...': R Ashwin Slams England's BazBall With Dravid Example 'Ghar Pe Khel Rahe Ho Kya?': Rishabh Pant Lashes Out At Kuldeep Yadav | Watch 17 Crores Loss! How Travis Head's Century Spelled Doom For Cricket Australia 'Travis Head, You Plunged My Country Into Silence': Ex-India Coach Pays Huge Compliment To Aussie Star 'Shreyas Iyer Recovering Well And...': PBKS Owner Preity Zinta Parties With India Batting Star Watch | Smriti Mandhana Loses All Inhibition! Dances With Palash Mucchal On 'Tenu Leke...'</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/cricket/</t>
+  </si>
+  <si>
+    <t>INDIA VS SOUTH AFRICA 2025</t>
+  </si>
+  <si>
+    <t>INDIA VS SOUTH AFRICA 2025 INDIA VS SOUTH AFRICA 2025 India Coach Reveals India's Gameplan For South Africa In 2nd Test: 'Chasing The Win...' Shubman Gill Given Injection For Nerve Injury, Likely To Return Next Year: Report IND Vs SA Highlights, 2nd Test Day 2: Jaiswal And Rahul Cautious After South Africa Post 489 Shubman Gill’s Injury More Serious Than Expected? Doubt Looms Over Participation In T20I Series Rahul or Rohit - Who'll Lead India In Gill's Absence? Selectors To Announce ODI Squad On... 'A Little Bit More...': Here's How Kuldeep Yadav Sparked South Africa's Collapse In Guwahati 'Massive Contrast From Kolkata': India Coach Calls Guwahati Pitch True Test Cricket Surface India vs South Africa 2nd Test Day 1: Bowlers Lead India’s Fightback as South Africa Slip to 247/6 Temba Bavuma Becomes 1st South African Captain In WTC To... First Time In 148 Years! India-South Africa Test In Guwahati To... India Vs South Africa ODI &amp; T20I Squad Announcement Live Updates: Selection Meeting Won't Happen In Guwahati, Shifted To... Shubman Gill OUT, 2 Players IN: India's Playing XI For 2nd Test Against South Africa Why Shubman Gill Is Not Playing 2nd India-South Africa Test In Guwahati? Rishabh Pant Becomes 2nd Wicketkeeper In 93 Years To... Rishabh Pant To MS Dhoni: Full List Of Wicketkeepers To Captain In Tests IND Vs SA Highlights, 2nd Test Day 1: South Africa Reach 247/6 At Stumps</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/cricket/series/india-vs-south-africa-2025.html</t>
+  </si>
+  <si>
+    <t>Cricket Schedule</t>
+  </si>
+  <si>
+    <t>The cricket schedule is regularly updated to reflect the latest fixtures and match details. Information on live streaming for cricket matches can be found on Cricketnext.</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/cricket/cricket-schedule/</t>
+  </si>
+  <si>
+    <t>Cricket Photos</t>
+  </si>
+  <si>
+    <t>Ashes history sees one of its most thrilling, action-packed days, featuring fireworks from the very first ball. A gripping opening day in the 2nd Test as India wrestled control with a disciplined bowling performance in Guwahati. Temba Bavuma and Tristan Stubbs looked set but threw away promising starts, while Kuldeep Yadav’s masterful spell (3/48) and Jasprit Bumrah’s precision (1/38) triggered a South African collapse from 166/2 to 247/6. Ravindra Jadeja and Mohammed Siraj also chipped in with crucial breakthroughs, leaving the Proteas ruing missed opportunities. With the pitch offering just enough assistance and India’s bowlers showing class, the stage is set for a cracking Day 2. Can India push for dominance? Watch full analysis!&lt;br&gt;A gripping opening day in the 2nd Test as India wrestled control with a disciplined bowling performance in Guwahati. Temba Bavuma and Tristan Stubbs looked set but threw away promising starts, while Kuldeep Yadav’s masterful spell (3/48) and Jasprit Bumrah’s precision (1/38) triggered a South African collapse from 166/2 to 247/6. Ravindra Jadeja and Mohammed Siraj also chipped in with crucial breakthroughs, leaving the Proteas ruing missed opportunities. With the pitch offering just enough assistance and India’s bowlers showing class, the stage is set for a cracking Day 2. Can India push for dominance? Watch full analysis! Rishabh Pant steps into the toughest leadership test of his career as India face South Africa in the series-deciding second Test in Guwahati — the first-ever Test match hosted in Assam. With Shubman Gill ruled out and Gautam Gambhir under scrutiny for questionable decisions, India enter as rare home underdogs. Can Pant inspire a turnaround and restore belief, or will South Africa tighten their grip? A high-pressure clash awaits at Barsapara, loaded with history, expectation and uncertainty.Watch the full preview, analysis and what’s at stake for Pant, Gambhir and the Indian team management.&lt;br&gt;Rishabh Pant steps into the toughest leadership test of his career as India face South Africa in the series-deciding second Test in Guwahati — the first-ever Test match hosted in Assam. With Shubman Gill ruled out and Gautam Gambhir under scrutiny for questionable decisions, India enter as rare home underdogs. Can Pant inspire a turnaround and restore belief, or will South Africa tighten their grip? A high-pressure clash awaits at Barsapara, loaded with history, expectation and uncertainty.Watch the full preview, analysis and what’s at stake for Pant, Gambhir and the Indian team management. Chennai Super Kings interview Sanju Samson on joining the team, his respect for MS Dhoni, friendship with Ruturaj Gaikwad, and connection to Tamil Nadu. India reach Guwahati bruised from the Kolkata loss, with skipper Shubman Gill’s fitness still uncertain. As Barsapara prepares for its maiden Test, the big question remains: will Gill lead, and how will India fix their fragile batting order?&lt;br&gt;India reach Guwahati bruised from the Kolkata loss, with skipper Shubman Gill’s fitness still uncertain. As Barsapara prepares for its maiden Test, the big question remains: will Gill lead, and how will India fix their fragile batting order? On November 19, 2023, Pat Cummins-led Australia defeated Rohit Sharma's India by 6 wickets at Narendra Modi Stadium in Ahmedabad to win the ODI World Cup final by 6 wickets. Rohit Sharma’s epic 140 vs Pakistan! A World Cup 2019 masterclass where the Hitman ripped apart the attack and owned the biggest rivalry in cricket. Jaw-dropping cricket catches! From Jadeja’s lightning grabs to Maxwell and Stokes defying gravity, these unreal moments redefine fielding brilliance. Sai Sudharsan and Dhruv Jurel shocked everyone by batting with just one pad during India’s optional nets at Eden Gardens. Here’s the real reason behind the risky old-school drill, what Gambhir observed, and how it ties into India’s plans for the next Test.&lt;br&gt;Sai Sudharsan and Dhruv Jurel shocked everyone by batting with just one pad during India’s optional nets at Eden Gardens. Here’s the real reason behind the risky old-school drill, what Gambhir observed, and how it ties into India’s plans for the next Test. India’s turning-pitch strategy has misfired again, with a heavy Kolkata defeat to South Africa exposing a shaky batting unit and a failed spin-first plan. As the series moves to Guwahati, big questions loom over Gambhir’s approach and India’s home Test tactics.&lt;br&gt;India’s turning-pitch strategy has misfired again, with a heavy Kolkata defeat to South Africa exposing a shaky batting unit and a failed spin-first plan. As the series moves to Guwahati, big questions loom over Gambhir’s approach and India’s home Test tactics.</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/cricket/videos/</t>
+  </si>
+  <si>
+    <t>Latest Videos</t>
+  </si>
+  <si>
+    <t>Shefali Shah is riding high on the appreciation she has been receiving for Delhi Crime 3. In an exclusive chat with CNN-News18 Showsha's Titas Chowdhury, she gets candid on her fear of letting the Delhi Crime franchise down, dealing with low self-esteem issues and being shut down on a film set. Shefali defends her choice of having fixed work hours and discusses why asking for a suite or a vanity van isn't luxury but the bare minimum. She looks back at playing Akshay Kumar's mother in Waqt and how her husband Vipul Amrutlal Shah had dissuaded her against it, and she states that she won't play a mother to an older star anymore. Shefali sheds light on maintaining her own identity in her marriage and further reveals if she congratulated Mira Nair on Zohran Mamdani's mayoral win. Watch the video for the full interview. The Family Man 3 is all set to release on Prime Video on November 21. In an exclusive chat with CNN-News18 Showsha's Titas Chowdhury, actor Jaideep Ahlawat, directors DK and Tusshar Seyth and writer Suman Kumar spill the beans on Manoj Bajpayee's wicked sense of humour. DK sheds light on the women of The Family Man, changing the gender narrative with Stree and casting a spotlight on Radhika Apte in Shor In The City which is otherwise a film about men. Jaideep recalls his earliest interaction with Manoj and reveals that he had recommended him for Gangs Of Wasseypur. The quartet further shares their stance on pay disparity in the OTT space, the super success of Lokah Chapter 1 and why Kangana Ranaut, Alia Bhatt and Deepika Padukone deserve big renumerations. Mila Kunis, Josh O’Connor, Josh Brolin, Kerry Washington and more stars lit up the red carpet at the Los Angeles premiere of their film 'Wake Up Dead Man: A Knives Out Mystery'. The cast looked spectacular as they celebrated the launch of Rian Johnson’s latest whodunit. Watch the video to know more. Aly Goni, Jasmin Bhasin, and other friends surprised Bharti Singh with a delightful baby shower, filled with fun, laughter, and heartwarming moments captured on video. Hollywood icon Tom Cruise has finally received his long-overdue Oscar recognition after 44 years of ruling Hollywood. The actor was honoured with an Academy Award at the Governors Awards on Sunday night, marking it his first-ever Oscar win. Watch the video to know more about his big moment. Veteran music composer Anu Malik, the man behind some of the most iconic hits of the ’80s and ’90s, says he is now at a stage in his career where he is struggling to get work. With over five decades in the industry and countless memorable melodies to his name, Malik opened up about the challenges he is facing. Watch the video to learn more. Internet has found its latest darling, and it is none other than Marathi actress Girija Oak Godbole, all thanks to a simple blue saree that broke the internet. What started as a candid interview moment turned into a viral sensation, with fans dubbing her the 'new national crush.' Want to know more? Watch the video as we bring you all the deets. In this candid interview, 'Madam sir' Shefali Shah talks about the upcoming season 3 of the highly anticipated show 'Delhi Crime' and why it is so close to her heart. She also talks about how the show deals with the shocking ways women are exploited in the country and working with an all-female cast.</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/videos/</t>
+  </si>
+  <si>
+    <t>Bihar Assembly Elections 2025</t>
+  </si>
+  <si>
+    <t>JDU wins by 73,572 votes against RJD JDU wins by 27 votes against RJD The Bihar Legislative Assembly, also known as the Bihar Vidhan Sabha, comprises 243 constituencies. Each constituency elects one Member of the Legislative Assembly (MLA), making a total of 243 elected representatives. This structure has been in place since the creation of the state of Jharkhand in 2000, resulting in a reduction from 324 to 243 seats in Bihar._x005F_x000D_
+_x005F_x000D_
+Bihar will vote in a two-phase election on November 6 and 11, in which all 243 seats will be contested, and the results for the high-stakes electoral battle will be announced on November 14. Dive into the election spirit — play the game for exciting challenges, fun moments, and a dose of Bihar election buzz! Go back in time and test your knowledge of Bihar election results with our very own EVM game. Elections are about winning seats (kursi in Hindi). Can you fill your ballot box with the 243 kursis of Bihar?</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/elections/</t>
+  </si>
+  <si>
+    <t>Astrology &amp; Horoscope News</t>
+  </si>
+  <si>
+    <t>Ganesha says today brings prosperity and positivity for Aries. A wonderful energy surrounds you, giving you confidence and openness to new possibilities. This is a time to strengthen personal relationships. You will thoroughly enjoy moments spent with loved ones. Open and honest conversations in relationships will deepen your bond. Your social life will also improve, leading to new friendships and connections. Openness and honesty in conversations with close friends will bring you closer. This day, filled with your positivity and energy, will not only improve your personal relationships but will also inspire those around you. Today is a great day for all that brings joy to your soul. Use this energy wisely and promote love and happiness in your life. Today will be a wonderful day for you! By Astrologer Chirag Daruwalla</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/astrology/</t>
+  </si>
+  <si>
+    <t>India Vs South Africa ODI &amp; T20I Squad Announcement Live Updates: Selection Meeting Won't Happen In Guwahati, Shifted To...</t>
+  </si>
+  <si>
+    <t>India ODI and T20I Squad against South Africa Live Updates: The Board of Control for Cricket in India (BCCI) selectors are expected to announce India’s squad for the upcoming three-match ODI and five-match T20I series against South Africa on Sunday. The three ODI matches will be played in Ranchi, Raipur and Visakhapatnam, whereas Cuttack, Mullanpur, Dharamsala, Lucknow and Ahmedabad will host the five T20I matches next month. Shubman Gill was appointed as India’s new ODI captain on October 4, and he made his ODI captaincy debut during the three-match series in Australia last month. But thanks to a neck injury that he suffered on Day 2 of the first Test against South Africa last week, there is doubt over his availability for the ODI series against the Proteas. India’s ODI vice-captain Shreyas Iyer is also out of action due to an injury that he suffered while fielding in the third India-Australia ODI, and he is all set to be rested for the home series. In the absence of Gill and Iyer, Rohit Sharma can return as India’s ODI captain for the home series. Day 2 of the India-South Africa Test in Guwahati came to an end at 4 pm IST. The visitors dominated the proceedings, setting India a mountain of a first innings score: 489. The hosts ended the day at 9/0 and will have their task cut out for Day 3. Expect updates about the selection meeting to quicken now that the day is over. However, as the meeting has been reportedly shifted to Mumbai, the final announcement might still be some time away. According to the news agency IANS, the selection committee meeting has been shifted to Mumbai. Chief selector Ajit Agarkar, RP Singh, and BCCI Secretary Devajit Saikia were in Guwahati for the second Test but flew to Mumbai on Sunday for the meeting at the BCCI headquarters. “Yes, the selection meeting is today in Mumbai, after being initially presumed that it would happen in Guwahati. It is understood that other members are also travelling to Mumbai for it,” the agency quoted sources as saying. The T20Is have been more skewed towards India. In 31 matches, the Men in Blue have won 18 while the South Africans have won only 11. However, the Proteas have a good away record, winning six T20Is in India out of 11. India and South Africa have played 94 ODIs against each other. The Indians have won only 40 of those, with the Proteas emerging victorious 51 times. Three games have ended in a no-result. Unlike Pant, Rahul has captained India in ODIs before. He led the team against South Africa, Australia, Bangladesh and Zimbabwe during the 2022-23 period, winning eight of his 12 matches. He has also led in three Tests, winning two, and won his sole T20I as the captain. According to a report in Cricbuzz, KL Rahul has a ‘slight edge’ over Pant for taking captaincy of the ODI series. However, the report said, that Rahul hasn’t been informed about the BCCI’s any such intentions. Rishabh Pant’s India captaincy career hasn’t gotten off to a good start. As the Proteas pile on runs in Guwahati, his fielding positions are being heavily criticised. “There is a fielder at mid-wicket, there is a long-on as well, there is no short leg, what is the plan here?” Aakash Chopra said on Star Sports. Taking another subtle dig, Anil Kumble then said, “On the leg side, an ODI field has been set. It is the first session of Day 1, and even then there is a deep square leg, long on and deep midwicket.” Chopra added, “Even guesswork will be failed here, because when have we ever seen Ryan Rickelton dance down the track and play over the top with the spin? Is this field planned for a short ball burst, and just for that have you set this? We have to revise how modern-day Test captaincy works.” The Indian wicketkeeper-batter has never led the team in ODIs or T20Is. The ongoing Test against South Africa in Guwahati is his first with the armband. In the IPL, he has captained Delhi Capitals and Lucknow Super Giants in a total of 57 games, winning 30 and losing 27. Yashasvi Jaiswal is likely to open alongside Rohit Sharma for the ODI series starting on November 30 in Ranchi, with Abhishek Sharma, a regular in India A’s List A set-up, serving as the reserve opener. Pace duties will be handled by Harshit Rana, Mohammed Siraj, and Arshdeep Singh, with Akash Deep as an outside contender. Jasprit Bumrah will rest after two consecutive Test series, and Hardik Pandya, currently recovering from a quadriceps injury, will focus solely on T20Is until next year’s World Cup. Kuldeep Yadav might take a break for personal reasons, leaving Axar Patel, Varun Chakravarthy, and Washington Sundar to form the spin group. On the captaincy front, Rishabh Pant is a strong contender as he is currently leading India in the second Test, although he has played only one 50-over match in the past year. KL Rahul, on the other hand, remains the first-choice keeper. For a one-off series, Rahul appears to be a more feasible option, especially with deputy Shreyas Iyer likely needing two more months to recover from his spleen injury sustained in Australia. Shubman Gill consulted Dr Abhay Nene, a spinal injury specialist based in Mumbai. The findings from the medical report have been sent to Ajit Agarkar, the chairman of selectors. “Gill has been given an injection to alleviate his symptoms and will need a period of rest before starting rehab, training and skill work. There is every chance he could also be doubtful for the T20I series,” the BCCI source said. According to reliable BCCI sources, Gill’s injury extends beyond a neck spasm and will necessitate extensive rest. Consequently, the team management has decided against taking any chances by rushing him back. Gill, who sustained a whiplash injury while batting during the opening Test in Kolkata, missed the Guwahati Test due to this injury. He is currently in Mumbai undergoing medical tests, including an MRI, to assess the full extent of the damage. “All tests are being done to ascertain whether it is a muscular injury or a nerve-related niggle that requires more rest. As of now, selectors will be hoping he gets fit for the South Africa T20Is,” a source told PTI. So, who takes over ODI captaincy? Wicketkeeper-batter Rishabh Pant and senior player KL Rahul are being considered for interim captaincy, despite veteran Rohit Sharma also being part of the squad. Not only the one-day internationals, chances of Gill playing in the upcoming T20I series against the Proteas, starting on December 9, also appear slim. Skipper Shubman Gill is expected to miss the upcoming three-match ODI series against South Africa due to a neck injury that is taking longer to heal, sources from the BCCI told PTI. According to PTI, Gill’s injury isn’t limited to neck spasm and will require extensive rest, prompting the team management to avoid any risk of rushing him back. He is currently in Mumbai undergoing medical tests, including an MRI, to determine the extent of the damage. According to reports, the selectors to meet in Guwahati after the second day’s play to pick the team for the upcoming white-ball series against South Africa. Chief selector Ajit Agarkar, selector RP Singh &amp; BCCI secretary Devajit Saikia are in Guwahati. The current ODI batting line-up is heavily right-hand dominated, prompting the management to look for left-handed options capable of shifting the tempo. With Shreyas Iyer unavailable, Rishabh Pant and Tilak Varma could be in contention for the No. 4 spot, while Yashasvi Jaiswal is set to walk into the XI in place of Shubman Gill. Shubman Gill will be unavailable for the three ODis vs South Africa starting November 30. “Unfortunately, Gill will not be available for selection for the three ODIs vs South Africa. He has been advised to get more rest by the specialists and continues to be monitored by the BCCI medical team,” a BCCI official was quoted as saying by TOI. Should Gill miss the upcoming ODI series against South Africa, three potential captaincy candidates stand out: KL Rahul – The experienced wicketkeeper-batter has captained India previously and is known for his composed leadership on the field. Rohit Sharma – The former skipper, who guided India to the 2023 ODI World Cup final, could be brought back in a temporary role. Jasprit Bumrah – If fully fit, the premier pacer is another strong option, having impressed with his leadership during earlier assignments. According to a report in Dainik Jagran, Shreyas Iyer has been advised strict rest due to discomfort in his abdominal region, which prevents him from putting strain on his body. Following an ultrasonography test, doctors recommended that he avoid any physical activity for up to five months, despite encouraging signs of recovery. The decision aims to prevent aggravating the injury during the crucial healing phase. Iyer and the BCCI have been guided by renowned orthopedic surgeon Dr. Dinshaw Pardiwala, a leading sports medicine specialist who has previously overseen major recoveries for athletes such as Rishabh Pant and Neeraj Chopra. If Gill is ruled out of the three-match ODI series against South Africa, the selectors are likely to draft in right-handed opener Ruturaj Gaikwad as his replacement. However, even with a call-up, Gaikwad may still struggle to find a spot in the Playing XI, with the team management expected to favour left-hander Yashasvi Jaiswal ahead of him. The Indian captain, Shubman Gill, suffered a neck spasm in Kolkata and was ruled out of both Tests. The BCCI medical team is still monitoring him, and he has been released from the Test squad. However, doubt looms over his participation in the ODIs. Ravindra Jadeja has retired from T20Is, but he is still active in ODIs. The Jamnagar-based all-rounder was dropped for the Australia ODIs, and it will be interesting to see if he is picked for the home series. Shubman Gill is vice-captain of India’s T20I team, but if he misses the upcoming series against South Africa, then the BCCI selectors will have to appoint a new vice-captain. Axar Patel was Surya’s deputy in the five-match T20I series against England in January-February 2025, and he could once again be considered for the role. Suryakumar Yadav is captain of India’s T20I team, and the right-handed batter from Mumbai will continue to lead the side in the 20-over format of the game. Under Surya’s leadership, India won the Asia Cup with a 100% win record in September 2025 and defeated Australia in two out of three full matches played in a five-match T20I series earlier this month. Senior men’s selection committee chairman Ajit Agarkar attended a press conference when the BCCI announced India’s ODI and T20I squads for the Australia series last month, but no such notification has been given by the BCCI for the squad announcement of the South Africa ODIs. Nitish Reddy was part of India’s ODI and T20I squad in Australia, but it will be interesting to see if he manages to retain his place in the XI after the return of Hardik Pandya. Pandya last played for India in the Asia Cup 2025 Super 4s match against Sri Lanka in Dubai on September 26. KL Rahul is India’s first-choice wicketkeeper-batter in ODIs, but it will be interesting to see who is picked as second stumper. Rishabh Pant is back in the mix along with Dhruv Jurel, who was Rahul’s backup in the Australia series. Also there’s Sanju Samson, and one must also not forget Ishan Kishan. Mohammed Shami is one of the best pacers of all time. The 35-year-old cricketer from Bengal hasn’t played for India since the ICC Champions Trophy 2025 final. He has impressed with his performances in recent Ranji Trophy matches for Bengal, and there is a possibility that Indian selectors might pick him for the ODI series. Aiden Markram (C), Ottneil Baartman, Corbin Bosch, Dewald Brevis, Quinton de Kock (WK), Tony de Zorzi, Donovan Ferreira, Reeza Hendricks, Marco Jansen, Keshav Maharaj, George Linde, Kwena Maphaka, David Miller, Lungi Ngidi, Anrich Nortje, Tristan Stubbs. Temba Bavuma (C), Ottneil Baartman, Corbin Bosch, Matthew Breetzke, Dewald Brevis, Nandre Burger, Quinton de Kock (WK), Tony de Zorzi, Rubin Hermann, Keshav Maharaj, Marco Jansen, Aiden Markram, Lungi Ngidi, Ryan Rickelton (WK), Prenelan Subrayen. Rohit Sharma has led India in 56 ODIs so far and managed to win 42 matches. Under his leadership, India reached the final of the ODI World Cup in 2023 and won the ICC Champions Trophy title in 2025 with a 100% win record. Shreyas Iyer is vice-captain of India’s ODI team, but he is out of action these days due to an injury. According to a latest report in Dainik Jagran, Iyer is unlikely to return before IPL 2026. Ruturaj Gaikwad was India A’s best batter in the recently concluded three-match unofficial ODI series against South Africa A, and there are high chances of him getting a reward for his consistent performances. Rohit Sharma, KL Rahul, Rishabh Pant, Axar Patel and Hardik Pandya are five captaincy options for Team India in Gill’s absence for the ODI series against South Africa. Jasprit Bumrah is unlikely to play for India in the three ODI matches against South Africa. He missed the ODI series against Australia as well last month but is all set to return for the five T20I matches. Hardik Pandya is in the BCCI’s CoE these days and is all set to make a comeback during the T20I series against South Africa. He is, however, expected to not be picked for the three ODI matches. Rohit Sharma was sacked as captain of India’s ODI team on October 4, 2025, despite him leading the Men in Blue to the ICC Champions Trophy title in his last assignment. But in the absence of Gill and Iyer, there is a possibility of him taking charge of the Men in Blue once again in the 50-over format of the game. Shreyas Iyer is designated vice-captain of India in ODIs, but the Mumbai-based batter is out of action these days due to an injury that he suffered while fielding in the third India-Australia ODI at Sydney Cricket Ground last month. He is undergoing recovery these days and is unlikely to be picked for the South Africa ODIs.</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/cricket/india-vs-south-africa-odi-t20i-squad-announcement-live-updates-ind-cricket-team-against-south-africa-rohit-sharma-virat-kohli-shubman-gill-bcci-liveblog-ws-l-9724098.html</t>
+  </si>
+  <si>
+    <t>Jaideep Ahlawat Echoes Manoj Bajpayee’s Pay Disparity In OTT Remark: 'Heroes Can Bring Numbers But...' | Exclusive</t>
+  </si>
+  <si>
+    <t>Navigating the film industry is no cakewalk, especially for outsiders. And Jaideep Ahlawat would agree. After graduating from FTII, he forayed into Bollywood with Priyadarshan’s Khatta Meetha and Aakrosh. But it was Anurag Kashyap’s Gangs Of Wasseypur that gave him some bit of visibility. While he thereafter went on to work in big-ticket films like Rockstar and Vishwaroopam, he again hit a rough patch following Commando: A One Man Army when he had to say no to many films. Speaking exclusively to News18 Showsha, Jaideep says, “It happened after Commando. I started getting offered a lot of weird negative characters. The character I played in that film was a little weird and off. Everybody started coming to me with roles with that kind of weirdness – ki basically aap gaadhe ho. It was very annoying! Once you do something different, every second script that comes to you starts looking exactly the same. Why should I take them up? Once a character is over, it’s done. I don’t want to play it again." Yet another flipside of the film industry that continues to plague many actors is pay disparity – not only does it exist between a male and a female star but also a commercial and middle-of-the-road actor. A while ago, Jaideep’s The Family Man 3 co-actor Manoj Bajpayee had stated that he was underpaid for the series and referred to himself as ‘cheap labour’. He added that big stars command higher pay even in the streaming world. Quiz Jaideep about it and he says, “I agree with Manoj bhai. That very much happens." But he adds that the change also has to happen in the mainstream, theatrical space. “Commercial cinema is like a race. Horse races hota hai na… kisi ghode pe paise lagaaoge, toh woh jeetega hi kyunki aap ko pata hai ki woh jeet ne ke laayak hai. If I’m putting in Rs 100 crores on a film, I’ll look for a face who I know can give me Rs 200 crore. It’s obvious that I’ll place my bet on an actor who can bring in the numbers," he remarks. The Jaane Jaan and Jewel Thief actor continues, “This change has to come from the top – producers and directors. I always say this – ek naayak ki kahaani nahi hoti hai, ek kahaani ka naayak hota hai. If you write a story and then choose your hero, only then a systemic change will happen. But if you choose the hero first and then weave a story around and according to him, it won’t work. It may bring you the money but it won’t turn out to be a good film. But that’s how the system is." But would he say that the industry’s perception of him has changed, especially after being a part of acclaimed shows like Paatal Lok and The Family Man 3? “I would say that I now have some kind of an access to certain filmmakers and production houses [which I didn’t have earlier]. People have accepted me in some ways. That’s why my reach has increased, relatively," Jaideep states.</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/movies/bollywood/jaideep-ahlawat-echoes-manoj-bajpayees-pay-disparity-in-ott-remark-heroes-can-bring-numbers-but-exclusive-9723044.html</t>
+  </si>
+  <si>
+    <t>Shubman Gill Given Injection For Nerve Injury, Likely To Return Next Year: Report</t>
+  </si>
+  <si>
+    <t>India Test and ODI captain Shubman Gill may have to wait a couple of months before returning to action following a neck injury which is said to be worse than it looks. Gill seemed to have aggravated a neck issue while batting on the second day of the first Test between India and South Africa in Kolkata, forcing him to be retired hurt after facing just three deliveries. He was subsequently stretchered off to a local hospital where he was kept under observation for a day before being discharged. Now, multiple reports claim that Gill could miss the remainder of 2025 due to what appears to be a nerve injury for which he has been given an injection to “alleviate his symptoms". The 26-year-old left the Kolkata hospital in a neck brace but did travel to Guwahati with the India Test squad for the ongoing second match that got underway from Saturday morning. However, he wasn’t picked in the playing XI, having been ruled out of action on match eve. Gill flew to Mumbai where he consulted spinal injury specialist Dr Abhay Nene. The medical report has been forwarded to BCCI chief selector Ajit Agarkar. A report in The Times of India claims that Gill has a nerve injury and the team management isn’t looking to rush his comeback given the T20 World Cup in February-March next year. It’s likely that we’ve seen the last of the batting star on the field as far as 2025 is concerned and he could likely return for the New Zealand series that starts from January 11 next year. Before Gill can start his rehab, he will have to undergo a period of rest and it’s unlikely he will be available for the five-match T20I series against South Africa as well. India are also set to host South Africa for three ODIs from November 30 once the Test series concludes. Swipe Left For Next Video In the final leg of the tour, South Africa will play five T20Is from December 9. “Gill has been given an injection to alleviate his symptoms and will need a period of rest before starting rehab, training and skill work. There is every chance he could also be doubtful for the T20I series," news agency PTI quoted a BCCI source as saying.</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/cricket/shubman-gill-given-injection-for-nerve-injury-likely-to-return-next-year-report-ws-bkl-9725871.html</t>
+  </si>
+  <si>
+    <t>News18 Cookie Policy</t>
+  </si>
+  <si>
+    <t>Network18 Media &amp; Investments Limited, having its registered office at First Floor, Empire Complex, 414, Senapati Bapat Marg, Lower Parel, Mumbai – 400013, India (“we”, “us”, “our”, “Network18”, “News18”) is committed to protecting the privacy and security of your personal data, your privacy is important to us. We are committed to being transparent about the technologies we use while making the website (“Website”). This Cookie Policy (“Policy”) applies to the Website that links to this Policy offered by us to all individuals (“you”, “your”, “user”). We use cookies to provide you our services (“Services”) and improve your experience of the Website. This Policy explains how and why we use cookies and the choices you have. This Policy describes the usage of the data captured using cookies which we collect from you when you access or use the Website. Before using our Website or availing any of our products and/or services, you are advised to carefully read the Privacy Policy of our Website. Except otherwise stated in this Policy, the Privacy Policy shall govern the way we collect and process data via cookies. By visiting and/or using our Website, you are consenting to the collection, use and storage of cookies in the manner as set forth in this Policy. A cookie is a small text file that the Website saves on your computer or mobile, tablet or any other devices (“Device”) when you visit the Website, to the extent you agree to the same. It enables the Website to remember your actions and preferences (such as login, language, location, and other display preferences) over a period, so you don’t have to keep re-entering them whenever you re-visit the Website or browse different pages, thereby making your next visit easier and to identify and learn more about your interests. This allows our Website to uniquely identify your device from those of other users of the Website. We do not store data for longer than is necessary to fulfil the purposes covered herein. A number of cookies we use last only for the duration of your web session and expire when you close your browser or exit the Website. Others are used to remember you when you return to the Website and will last depending on the purpose. These cookies are set by the Website and only that Website can read them. They are also called internal cookies. For example, first-party cookies can keep you logged in as you navigate through different pages or remember your language settings. Some of these cookies are necessary for proper functioning of our Website. You can opt-out of these cookies through your browser settings. If you choose to opt-out of these cookies, then we may not be able to provide you an optimum Website experience. Others are used for purposes such as analytics and performance. We identify these cookies before they are used so that you can decide whether you wish to accept them or not through the cookie banner that is provided when you visit the Website (for the first time and when the consent should be renewed) or through the cookie settings page at the bottom of every page of the Website. These cookies are set by third parties when you access or use our Website and have a different domain to that of the Website you are visiting and they enable certain Website functionality, such as perform analytics, deliver personalized content to the users, etc. We identify these cookies before they are used so that you can decide whether you wish to accept them or not through the cookie banner that is provided when you visit the Website (for the first time and when the consent should be renewed) or through the cookie setting page at the bottom of every page of the Website We use the following categories of cookies to provide our services when you access our Website: You can choose to allow or block cookies, delete existing cookies, and set cookie preferences for the Website. We use cookies to personalize your experience when you interact with or use our services. Please note that blocking cookies may restrict us from providing certain website features, and your overall user experience may deteriorate. Furthermore, if your browser setting is already set to block all cookies, then some of the website features may not operate as intended. Please remember that updating browser’s cookie setting will apply to all websites you visit unless you choose to allow/block cookies from a particular Website. If you allow cookies through your browser or device, they will be readable only by their issuer. If you want to remove previously stored cookies, you can manually delete the cookies at any time through your browser’s cookie settings. However, this will not prevent the Website from placing further cookies on your device. You may choose to change your cookie preference at any time by updating your browser’s cookie settings. We recommend that you allow all cookies in order to provide you with a personalized experience on the website. We do not knowingly collect or solicit personal data from minors. Our products and/or services are not designed for any person who is under 18 years of age, and we do not knowingly permit such persons to register for products and/ or services or share data through any of the web forms without verifiable consent from minors’ parents or lawful guardians. Further, we do not undertake tracking or behavioral monitoring of children or targeted advertising directed at children. If we learn that we have collected personal data from a minor without verified parental consent, we will erase such personal data. If you believe that a child under 18 years may have provided us their personal data, please contact us on dpo@nw18.com. If you have questions or comments regarding this Policy or for any other queries of your device data that we have collected and processed, please contact us using the contact details given in our Privacy Policy We reserve the right to change this Policy at our sole discretion at any time. Any material changes to this Policy will be posted on this page. We encourage you to review this Policy regularly for such changes. The updated Cookie Policy will take effect as soon as it has been updated. This Policy was last updated as of 14th November 2024.</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/cookie-policy.html</t>
+  </si>
+  <si>
+    <t>DISCLAIMER &amp; TERMS OF USE</t>
+  </si>
+  <si>
+    <t>By accessing News18.com or any of its associate/group sites, you have read, understood and agree to be legally bound by the terms of the following disclaimer and user agreement: This Site is owned and operated by Web18 Software Services Limited ("the Company/Web18") and contains material which is derived in whole or in part from material supplied by the Company, various new agencies and other sources, and is protected by international copyright and trademark laws. The restrictions on use of the material and content on this Web18 Site by the Subscriber are specified below. Except where specifically authorised, the Subscriber may not modify, copy, reproduce, republish, upload, post, transmit or distribute in any way any material from this site including code and software. Web18 has taken due care and caution in compilation of data for its web site. The views and investment tips expressed if any by investment experts on Web18 are their own, and not that of the website or its management. Web18 advises users to check with certified experts before taking any investment decision. However, Web18 does not guarantee the accuracy, adequacy or completeness of any information and is not responsible for any errors or omissions or for the results obtained from the use of such information. Web18 especially states that it has no financial liability whatsoever to any user on account of the use of information provided on its website. The Stock Market data has been provided on this site through moneycontrol.com for information purposes only. The Company shall have the right at any time to change or modify the terms and conditions applicable to Subscriber's use of the Web18 Site, or any part thereof, or to impose new conditions, including but not limited to, adding fees and charges for use. Such changes, modifications, additions or deletions shall be effective immediately upon notice thereof, which may be given by means including but not limited to, posting on the Web18 Site, or by electronic or conventional mail, or by any other means by which Subscriber obtains notice thereof. Any use of the Web18 Site by Subscriber after such notice shall be deemed to constitute acceptance by Subscriber of such changes, modifications or additions. By visiting our site you are agreeing to be bound by the following terms and conditions. We may change these terms and conditions at any time. Your continued use of News18.com means that you accept any new or modified terms and conditions that we come up with. Please re-visit the `Terms of Use' link at our site from time to time to stay abreast of any changes that we may introduce. The term ` News18.com ' is used through this entire Terms of Use document to refer to the website, its owners and the employees and associates of the owner The term ` News18.com ' is used through this entire Terms of Use document to refer to the website, its owners and the employees and associates of the owner News18 uses the YouTube API Services to showcase video content on it's web and app platforms, and by accepting the above terms you also accept the YouTube Terms of Service (ToS) By registering, you certify that all information you provide, now or in the future, is accurate. Your registration at News18.com is valid for 90 days from the date you first login and is automatically renewed for a period of 90 days every time you login thereafter. If you do not login at News18.com for a continuous period of 90 days your registration could be automatically cancelled. News18.com reserves the right, in its sole discretion, to deny you access to this website or any portion thereof without notice for the following reasons (a) immediately by News18.com for any unauthorized access or use by you (b) immediately by News18.com if you assign or transfer (or attempt the same) any rights granted to you under this Agreement; (c) immediately, if you violate any of the other terms and conditions of this User Agreement News18.com hereby grants you a limited, non-exclusive, non-assignable and non-transferable license to access News18.com provided and expressly conditioned upon your agreement that all such access and use shall be governed by all of the terms and conditions set forth in this USER AGREEMENT. News18.com as well as the design and information contained in this site is the valuable, exclusive property of News18.com, and nothing in this Agreement shall be construed as transferring or assigning any such ownership rights to you or any other person or entity. You may not resell, redistribute, broadcast or transfer information, software and applications or use the information, software and applications provided by News18.com in a searchable, machine-readable database unless separately and specifically authorized in writing by News18.com prior to such use. You may not rent, lease, sublicense, distribute, transfer, copy, reproduce, publicly display, publish, adapt, store or time-share News18.com, any part thereof, or any of the software, application or information received or accessed therefrom to or through any other person or entity unless separately and specifically authorized in writing by News18.com prior to such use. In addition, you may not remove, alter or obscure any copyright, legal or proprietary notices in or on any portions of News18.com without prior written authorization. Except as set forth herein, any other use of the information, software or application contained in this site requires the prior written consent of GBN and may require a separate fee. Neither News18.com (including its and their directors, employees, affiliates, agents, representatives or subcontractors) shall be liable for any loss or liability resulting, directly or indirectly, from delays or interruptions due to electronic or mechanical equipment failures, telephone interconnect problems, defects, weather, strikes, walkouts, fire, acts of God, riots, armed conflicts, acts of war, or other like causes. News18.com shall have no responsibility to provide you access to News18.com while interruption of News18.com is due to any such cause shall continue. YOU EXPRESSLY AGREE THAT USE OF THE WEBSITE IS AT YOUR SOLE RISK. THE CONTENTS, INFORMATION, SOFTWARE, PRODUCTS, FEATURES AND SERVICES PUBLISHED ON THIS WEB SITE MAY INCLUDE INACCURACIES OR TYPOGRAPHICAL ERRORS. CHANGES ARE PERIODICALLY ADDED TO THE CONTENTS HEREIN. News18.COM AND/OR ITS RESPECTIVE SUPPLIERS MAY MAKE IMPROVEMENTS AND/OR CHANGES IN THIS WEB SITE AT ANY TIME. THIS WEB SITE MAY BE TEMPORARILY UNAVAILABLE FROM TIME TO TIME DUE TO REQUIRED MAINTENANCE, TELECOMMUNICATIONS INTERRUPTIONS, OR OTHER DISRUPTIONS. News18.COM (AND ITS OWNERS, SUPPLIERS, CONSULTANTS, ADVERTISERS, AFFILIATES, PARTNERS, EMPLOYEES OR ANY OTHER ASSOCIATED ENTITIES, ALL COLLECTIVELY REFERRED TO AS ASSOCIATED ENTITIES HEREAFTER) SHALL NOT BE LIABLE TO USER OR MEMBER OR ANY THIRD PARTY SHOULD News18.COM EXERCISE ITS RIGHT TO MODIFY OR DISCONTINUE ANY OR ALL OF THE CONTENTS, INFORMATION, SOFTWARE, PRODUCTS, FEATURES AND SERVICES PUBLISHED ON THIS WEBSITE. IN NO EVENT SHALL News18.COM AND/OR ITS ASSOCIATED ENTITIES BE LIABLE FOR ANY DIRECT, INDIRECT, PUNITIVE, INCIDENTAL, SPECIAL OR CONSEQUENTIAL DAMAGES ARISING OUT OF OR IN ANY WAY CONNECTED WITH THE USE OF THIS WEB SITE OR WITH THE DELAY OR INABILITY TO USE THIS WEBSITE, OR FOR ANY CONTENTS, INFORMATION, SOFTWARE, PRODUCTS, FEATURES AND SERVICES OBTAINED THROUGH THIS WEB SITE, OR OTHERWISE ARISING OUT OF THE USE OF THIS WEB SITE, WHETHER BASED ON CONTRACT, TORT, STRICT LIABILITY OR OTHERWISE, EVEN IF News18.COM OR ANY OF ITS ASSOCIATED ENTITIES HAS BEEN ADVISED OF THE POSSIBILITY OF DAMAGES. If this Web site may contain message/bulletin boards, chat rooms, or other message or communication facilities (collectively, "Forums"), you agree to use the Forums only to send and receive messages and material that are proper and related to the particular Forum. By way of example, and not as a limitation, you agree that when using a Forum, you shall not do any of the following: • Defame, abuse, harass, stalk, threaten or otherwise violate the legal rights (such as rights of privacy and publicity) of others. • Publish, post, distribute or disseminate any defamatory, infringing, obscene, indecent or unlawful material or information • Upload files that contain software or other material protected by intellectual property laws (or by rights of privacy of publicity) unless you own or control the rights thereto or have received all necessary consents. • Upload files that contain viruses, corrupted files, or any other similar software or programs that may damage the operation of another’s computer. • Conduct or forward surveys, contests, or chain letters. • Download any file posted by another user of a Forum that you know, or reasonably should know, cannot be legally distributed in such manner. All Forums are public and not private communications. Chats, postings, conferences, and other communications by other users are not endorsed by News18.com, and such communications shall not be considered reviewed, screened, or approved by News18.com. News18.com reserves the right for any reason to remove without notice any contents of the Forums received from users, including without limitation message board postings. You shall provide and maintain all telephone/internet and other equipment necessary to access News18.com, and the costs of any such equipment and/or telephone/internet connections or use, including any applicable taxes, shall be borne solely by you. You are responsible for operating your own equipment used to access News18.com. The links in this site will allow you to leave News18.com. The linked sites are not under the control of News18.com. News18.com has not reviewed, nor approved these sites and is not responsible for the contents or omissions of any linked site or any links contained in a linked site. The inclusion of any linked site does not imply endorsement by News18.com of the site. Third party links to News18.com shall be governed by a separate agreement. YOU SHALL INDEMNIFY, DEFEND AND HOLD HARMLESS News18.COM (INCLUDING ITS AND THEIR OFFICERS, DIRECTORS, EMPLOYEES, AFFILIATES, GROUP COMPANIES, AGENTS, REPRESENTATIVES OR SUBCONTRACTORS) FROM ANY AND ALL CLAIMS AND LOSSES IMPOSED ON, INCURRED BY OR ASSERTED AS A RESULT OF OR RELATED TO: (a) your access and use of News18.COM (b) any non-compliance by user with the terms and conditions hereof; or (c) any third party actions related to users receipt and use of the information, whether authorized or unauthorized. Any clause declared invalid shall be deemed severable and not affect the validity or enforceability of the remainder. These terms may only be amended in a writing signed by News18.com. If there is any conflict between this User Agreement and other documents, this User Agreement shall govern, whether such order or other documents is prior to or subsequent to this User Agreement, or is signed or acknowledged by any director, officer, employee, representative or agent of News18.com. You agree to keep the information received from the News18.com and services CONFIDENTIAL and will NOT Disclose the knowledge gained to other any person or firm for any reason. You hereby consent to the Jurisdiction of the Courts of New Delhi, India with respect to violation of any part of this Agreement. This User Agreement and the license rights granted hereunder shall remain in full force and effect unless terminated or canceled for any of the following reasons: (a) immediately by News18.com for any unauthorized access or use by you (b) immediately by News18.com if you assign or transfer (or attempt the same) any rights granted to you under this Agreement; (c) immediately, if you violate any of the other terms and conditions of this User Agreement. Termination or cancellation of this Agreement shall not effect any right or relief to which News18.com may be entitled, at law or in equity. Upon termination of this User Agreement, all rights granted to you will terminate and revert to News18.com. Except as set forth herein, regardless of the reason for cancellation or termination of this User Agreement, the fee charged if any for access to News18.com is non-refundable for any reason. The terms of this agreement are exclusively based on and subject to Indian law. You hereby consent to the exclusive jurisdiction and venue of courts in New Delhi, India in all disputes arising out of or relating to the use of this website. Use of this website is unauthorized in any jurisdiction that does not give effect to all provisions of these terms and conditions, including without limitation this paragraph.</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/disclaimer/</t>
+  </si>
+  <si>
+    <t>Complaint Redressal</t>
+  </si>
+  <si>
+    <t>Complaints relating to ContentAny complaint relating to content of TV channel of TV18 Broadcast Limited namely: NEWS18, under the Code of Ethics &amp; Broadcasting Standards and News Broadcasting Standards (Disputes Redressal) Regulations of News Broadcasters Association (NBA) shall be made by a person aggrieved within a reasonable time not exceeding 7 (seven) days from the date of first broadcast to the following person appointed by the Company whose details are reproduced below: Group General Counsel TV18 Broadcast Limited Plot No. 15 &amp; 16, Sector 16A Noida, Uttar Pradesh 201301 Phone: + 91 120 4341818 Email: complaint@network18online.com However, before making a complaint viewers are encouraged to go through the Code of Ethics &amp; Broadcasting Standards, News Broadcasting Standards (Disputes Redressal) Regulations and Guide to the Complaints Process. These details are available on the website of NBA www.nbanewdelhi.com</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/complaint/</t>
+  </si>
+  <si>
+    <t>News18 Website and App Privacy Policy</t>
+  </si>
+  <si>
+    <t>Network18 Media and Investments Limited, having its registered office at First Floor, Empire Complex, 414, Senapati Bapat Marg, Lower Parel, Mumbai - 400013, India (“we”, “us”, “our”, “Network18”, “News18”) is committed to protecting the privacy and security of your personal data, your privacy is important to us. This Privacy Policy (“Policy”) applies to all products and/or services offered by us to all individuals (“you”, “your”, “user”). This Policy explains how we collect, receive, store, disclose, share, and use your personal data for the purpose of your participation and consumption of our products and/or services offered by us through our website and/or software application (collectively, “Platform”) or during any interaction with us, and how you can exercise your privacy rights. Before using our Platform or availing any of our products and/or services, you are advised to carefully read this Policy. If you do not agree with the terms of this Policy, please do not access this Platform. By visiting and/or using our Platform, you are consenting to process your personal data in the manner as set forth in this Policy. The scope of this policy is limited to the product and/or services provided by us within the territory of India and applies to users who request for these products and/or services within the Indian territory. When you interact with us, we collect different types of information from you based on the type of interaction. “Personal Data” means any data about an individual who is identifiable by or in relation to such data. “Processing”, “Processed”, “Process” in relation to personal data, means a wholly or partly automated operation or set of operations performed on digital personal data, and includes operations such as collection, recording, organization, structuring, storage, adaptation, retrieval, use, alignment, or combination, indexing, sharing, disclosure by transmission, dissemination or otherwise making available, restriction, erasure, or destruction. We endeavor to collect only such personal data that is reasonably necessary to perform our services for you. When you interact with our Platform or otherwise us, we may collect the following personal data from you directly: 1. General Data – your first name, last name, email, mobile number, address with Pin Code as well as your preferred language; 2. Government Identification Data – data that enables us to identify you, e.g. your Aadhaar card and PAN card; 3. Authentication – data required for authentication, such as username and password; 4. Technical and Network Activity Data – data about your device and your usage of our Platform, including your IP address, device ID, hardware model and version, mobile network information, operating system and other online identifiers, type of browser, browsing history, search history, access time, pages viewed, URLs clicked on, forms submitted, and physical location; 5. Financial Data – your bank details, including account name, account number, cancelled cheque; 6. Employment Details- your employment details, such as company name, designation, education qualification, and resume You can choose not to give us personal data when we ask you for it. If you decide not to give us your personal data, it may restrict our relationship with you. Information you directly provide to us: You may choose to provide us with the data, which is essential for us to deliver the products and/or services you request. Without this data, we may not be able to provide you with all the requested products and/or services; Information you provide to us voluntarily: If you send us personal correspondence, such as emails or letters, or if other users or third parties send us correspondence about your activities or postings on the Platform, we may collect and store such data. We may collect additional data at other times, when you provide feedback(s), modify your content or email preferences, respond to surveys, or communicate with us. This data may include your name, e-mail id, mobile number, etc. Information we collect automatically: We collect data about you, your interactions with us, as well as data regarding your computer or other devices used to access our Platform. This source may include, but is not limited to: Information we collect from other sources: We may collect or receive data about you from third-party sources and process this data in accordance with this policy. The sources may include, but is not limited to: If you connect your social media account to our Platform, you will share certain personal data from your social media account with us. This may include your name, email address, photo, list of social media contacts, and any other data you make accessible to us. We will collect personal data by lawful and fair means and, where appropriate, with the knowledge of the individual concerned. We only collect and process personal data about you where we have a lawful basis. Lawful basis on which we would process data from you includes: We use your personal data for the purposes we have described below in this privacy notice, or for purposes which are reasonably compatible to the ones described. To manage our relationship with you. To manage and improve our processes and our business operations. To achieve other purposes. When you visit our offices, we process your personal data in accordance with this privacy statement and some specific information regarding the use of visitor data and the potential use of CCTV in our offices is provided in the reception area. We implement reasonable technical and organizational measures in relation to the data and personal data that is processed by us. We take reasonable measures to protect all personal data from unauthorized processing or accidental disclosure, alteration, misuse, destruction or loss or unauthorized access and modification that compromises the confidentiality, integrity, and availability of such data. While we endeavor to always protect our Platform, operations and data against unauthorized access, use, modification, and disclosure, due to the inherent nature of the Internet, we cannot guarantee that any data, during transmission or while stored on our systems, will be safe and secure from intrusion by others. We respect your right to access and control your personal data, and we will respond to requests to exercise your rights under applicable laws and, where applicable, will correct, update, or erase your personal data. You have the following rights: For exercising any of your rights, you can contact us using dpo@nw18.com. We will need you to furnish proof of your identity before you can exercise these rights. We may not be able to process any requests made in the event you fail to establish your identity, or if we are unable to authenticate your identity. As far as this is necessary for the purposes set out above, we will share your personal data with the following recipients who either have a need to know and who will process it for us based on our instructions and for no other purpose: External service providers: Occasionally, to provide our products and/or services, it is necessary to collaborate with external service providers. We may use these service providers to assist us with some features or functions of our Platform. These external service providers shall process your personal data on our behalf subject to appropriate safeguards only insofar as it is necessary for them to provide their products and/or services to us. Our prior authorization is required before they are permitted to transfer responsibility for processing personal data to a third party. We provide personal data to our affiliates and other trusted businesses or persons to process it for us, based on our instructions and in compliance with our Privacy Policy and any other appropriate confidentiality and security measures. In the event if we merge with or acquired by another company or in case of re-organization or re-structuring of business, we and our affiliates may share your personal data, wholly or in part, with another business entity. Courts and public authorities: We only share your personal data with recipients that have an adequate level of data protection by implementing appropriate technical and organizational security measures, or we take measures to ensure that all recipients provide an adequate level of data protection as prescribed by applicable law. We do not sell your personal data to anyone. We operate globally and may transfer your personal data to our affiliates or third parties in territories outside India for the purposes described in this Policy in accordance with applicable data protection laws, provided that no such restriction is notified by the Government/ appropriate authority. We will retain your personal data which we have collected for as long as we reasonably consider it necessary for achieving the above mentioned purposes and as is permissible under applicable law. This is determined on a case-to-case basis. We will delete your personal data whenever you request us to do so. However, we may archive and/or retain your personal data for as long as there are statutory retention obligations or potential legal claims are not, yet time barred. We do not knowingly collect or solicit personal data from minors. Our products and/or services are not designed for any person who is under 18 years of age, and we do not knowingly permit such persons to register for products and/ or services or share data through any of the web forms without verifiable consent from minors’ parents or lawful guardians. Further, we do not undertake tracking or behavioral monitoring of children or targeted advertising directed at children. If we learn that we have collected personal data from a minor without verified parental consent, we will erase such personal data. If you believe that a child under 18 years may have provided us their personal data, please contact us on dpo@nw18.com. If you have questions or comments regarding this Policy or want to exercise any of your rights or express your grievances regarding the processing of your personal data, please contact us using the contact details given below: Network18 Media and Investments Limited Data Protection Officer Apurv Narula dpo@nw18.com If you are not satisfied with the resolution provided you may log your complaint with the Data Protection Board of India following the procedure prescribed by them. We reserve the right to change this Policy at our sole discretion at any time. Any material changes to this Policy will be posted on this page. We encourage you to review this Policy regularly for such changes. The updated Privacy Policy will take effect as soon as it has been updated. This Policy was last updated as of 14th November 2024.</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/privacy_policy/</t>
+  </si>
+  <si>
+    <t>‘Not Final, No Alteration’: Centre Clarifies Amid Punjab Row Over Chandigarh Law-Making Proposal</t>
+  </si>
+  <si>
+    <t>Amid the political storm in Punjab, the Ministry of Home Affairs (MHA) on Sunday issued a clarification on the Chandigarh law-making proposal. “The proposal to simplify the process of law-making exclusively by the Central Government for the Union Territory of Chandigarh is currently under consideration at the level of the Central Government. No final decision has been taken on this proposal," the MHA said. According to the MHA, the proposal does not in any way involve altering the governance and administrative arrangements of Chandigarh or the traditional relations of Chandigarh with Punjab or Haryana. “An appropriate decision will be taken only after adequate consultation with all stakeholders, keeping in mind the interests of Chandigarh. There is no need for concern on this matter," the MHA said. The Ministry further clarified that the Central Government has no intention of presenting any bill to this effect in the upcoming Winter Session of Parliament. संघ राज्य क्षेत्र चंडीगढ़ के लिए सिर्फ केंद्र सरकार द्वारा कानून बनाने की प्रक्रिया को सरल बनाने का प्रस्ताव अभी केंद्र सरकार के स्तर पर विचाराधीन है| इस प्रस्ताव पर कोई अंतिम निर्णय नहीं लिया गया है| इस प्रस्ताव में किसी भी तरह से चंडीगढ़ की शासन-प्रशासन की व्यवस्था या चंडीगढ़…— PIB – Ministry of Home Affairs (@PIBHomeAffairs) November 23, 2025 The Centre has proposed to include the UT of Chandigarh under the ambit of Article 240 of the Constitution, which empowers the president to make regulations for the UT and to legislate directly. A Lok Sabha and Rajya Sabha bulletin allegedly stated that the Centre would bring the Constitution (131st Amendment) Bill, 2025, in the upcoming winter session of Parliament, beginning December 1. If the bill is passed in its current form, Chandigarh could have an independent administrator, in line with Union Territories without legislatures, such as Andaman and Nicobar Islands, Lakshadweep, Dadra and Nagar Haveli and Daman and Diu, and Puducherry, during periods when their Assemblies are dissolved or suspended. Chandigarh serves as the joint capital of Punjab and Haryana. This proposed amendment has sparked political outrage in Punjab, with the ruling AAP, Congress, and Shiromani Akali Dal (SAD) criticising the Bharatiya Janata Party-led Centre, accusing the government of attempting to “snatch" Chandigarh from Punjab. ਸੰਸਦ ਦੇ ਆਗਾਮੀ ਸਰਦ ਰੁੱਤ ਸੈਸ਼ਨ ਵਿੱਚ ਕੇਂਦਰ ਸਰਕਾਰ ਵੱਲੋਂ ਲਿਆਂਦੇ ਜਾ ਰਹੇ ਪ੍ਰਸਤਾਵਿਤ ਸੰਵਿਧਾਨ (131ਵੇਂ ਸੋਧ) ਬਿੱਲ ਦਾ ਅਸੀਂ ਸਖ਼ਤ ਸ਼ਬਦਾਂ 'ਚ ਵਿਰੋਧ ਕਰਦੇ ਹਾਂ। ਇਹ ਸੋਧ ਪੰਜਾਬ ਦੇ ਹਿੱਤ ਦੇ ਵਿਰੁੱਧ ਹੈ। ਕੇਂਦਰ ਸਰਕਾਰ ਵੱਲੋਂ ਪੰਜਾਬ ਵਿਰੁੱਧ ਘੜੀ ਜਾ ਰਹੀ ਸਾਜ਼ਿਸ਼ ਅਸੀਂ ਬਿਲਕੁੱਲ ਕਾਮਯਾਬ ਨਹੀਂ ਹੋਣ ਦੇਵਾਂਗੇ। ਸਾਡੇ ਪੰਜਾਬ ਦੇ… pic.twitter.com/06K8e5wZ4w — Bhagwant Mann (@BhagwantMann) November 22, 2025 Currently, the Punjab governor serves as the Administrator of the UT of Chandigarh. It was previously administered independently by a chief secretary since November 1, 1966, when Punjab was reorganised. However, since June 1, 1984, Chandigarh has been administered by the Punjab governor and the chief secretary’s position was converted to an adviser to the UT administrator. In August 2016, the Centre sought to restore the old practice of having an independent administrator by appointing former IAS officer K J Alphons for the top post. However, the move was withdrawn after stiff opposition from the then-Punjab chief minister, Parkash Singh Badal, who was part of the NDA, and other parties, including the Congress and AAP. Punjab, which has staked its claim on Chandigarh, also wants the immediate transfer of Chandigarh to it. The chief minister has reiterated this demand during a recent meeting of the Northern Zonal Council held in Faridabad. Amid the row, Punjab BJP chief Sunil Jakhar on Sunday said Chandigarh is an integral part of Punjab, assuring that the “confusion" regarding the Union territory will be resolved. “Chandigarh is an integral part of Punjab, and the Punjab BJP stands firmly with the interests of the state, whether it is the issue of Chandigarh or the waters of Punjab. Whatever confusion has arisen regarding Chandigarh will be resolved by discussing it with the government. As a Punjabi myself, I assure you that for us, Punjab always comes first," said Jakhar in a post on X. Punjab Chief Minister Bhagwant Mann on Saturday strongly opposed the Centre’s proposed Constitution (131st Amendment) Bill. The chief minister said it goes against Punjab’s interests and could weaken the state’s authority over Chandigarh. He asserted that Punjab would not allow any move that threatens its rights over the Union Territory. Shiromani Akali Dal (SAD) president Sukhbir Singh Badal appealed to the Union government not to introduce the bill in Parliament. Doing so would amount to betraying and discriminating against the brave Punjabis who sacrificed the most for the country, and going back on all commitments made to Punjab to hand over Chandigarh to it, he said. Swipe Left For Next Video Punjab Congress president Amrinder Singh Raja Warring warned against “taking away" Chandigarh from Punjab. With PTI, Agency Inputs</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/india/not-final-no-alteration-centre-clarifies-after-objections-to-chandigarh-law-making-proposal-9726167.html</t>
+  </si>
+  <si>
+    <t>Toxic Mix: Uranium Found In Breastmilk Across 6 Bihar Districts, Study Warns Of Infant Health Risks</t>
+  </si>
+  <si>
+    <t>A recent scientific study has revealed significant levels of uranium contamination in the breastmilk of lactating mothers across six districts of Bihar. The research, which focused on mothers in Bhojpur, Samastipur, Begusarai, Khagaria, Katihar, and Nalanda, indicates a troubling exposure pathway for infants, with the potential to cause serious non-carcinogenic health effects. The study, conducted by the Mahavir Cancer Sansthan in Patna in collaboration with AIIMS, New Delhi, analysed breastmilk samples from 40 mothers. Uranium-238 was detected in all analysed samples, with Katihar recording the single-highest concentration and Khagaria showing the highest average contamination among the districts studied. Crucially, the researchers estimated that nearly 70% of the infant population exposed through breastfeeding had the potential to face non-carcinogenic health risks. This contamination is believed to be linked to the high presence of uranium in the state’s groundwater, which is the primary source of drinking and irrigation water for most of Bihar’s population. Previous studies have already identified elevated uranium levels in groundwater across several Bihar districts, linking this to natural geogenic sources like uranium-rich rocks and compounded by anthropogenic factors such as water table decline and long-term use of chemical fertilisers. The detection of uranium in breastmilk signals that the metal has successfully entered the food chain, reaching the most vulnerable population group—infants. Infants are particularly susceptible to toxic metals because their organs are still developing, and their low body weight amplifies the effects of exposure. Medical experts warn that uranium contamination can lead to kidney damage, neurological impairment, and cognitive delays, alongside increasing the risk of cancer later in life. Swipe Left For Next Video Despite the alarming findings, the research team strongly emphasised that breastfeeding must continue, as it provides irreplaceable benefits for immunity and early development and should only be discontinued on explicit medical advice. The study indicates the need for immediate public health intervention, demanding rigorous biomonitoring, widespread water-quality testing, and a dedicated effort by state and central geological agencies to identify and mitigate the source of this hazardous contamination.</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/india/toxic-mix-uranium-found-in-breastmilk-across-6-bihar-districts-study-warns-of-infant-health-risks-9725793.html</t>
+  </si>
+  <si>
+    <t>Russian Aerobatic Team Pays Tribute To Fallen IAF Wing Commander At Dubai Air Show | Video</t>
+  </si>
+  <si>
+    <t>The Russian Knights aerobatic team paid a heartfelt tribute to Wing Commander Namansh Syal, the Indian Air Force (IAF) pilot who lost his life after a Tejas fighter jet crashed during its display at the Dubai Air Show. The highly skilled Russian formation team dedicated their full routine to the late pilot, calling him a “brother in the skies". A member of the Russian Knights, speaking after their performance, said the minutes following the crash were “impossible to describe". The member further added that the team chose to continue their show in honour of pilots “who do not return from their final flight." ⚡ Russian Aerobatic Team Pays Tribute to Wg Cdr Namansh Syal at Dubai Airshow 2025:The Russian Knights aerobatic team has honoured Wing Commander Namansh Syal, the Indian Air Force pilot who tragically lost his life after the Tejas crashed during its display at the Dubai… pic.twitter.com/62INZRohXD — OSINT Updates (@OsintUpdates) November 23, 2025 The tragedy happened on Friday when the Tejas, India’s indigenous Light Combat Aircraft, went down during a planned demonstration. The jet reportedly lost height while performing a low-level negative-G manoeuvre and plunged into the ground within seconds, erupting into a fireball. Thick black smoke rose over Al Maktoum International Airport at Dubai World Central as stunned onlookers — including families gathered in the grandstand area — watched the accident in shock. Wing Commander Namansh Syal, believed to be in his mid-30s and originally from Himachal Pradesh, was the sole occupant of the aircraft. He had taken off for an eight-minute display slot when the crash occurred at around 2:10 pm local time (3:40 pm IST). Despite immediate emergency response, he could not be saved. Swipe Left For Next Video This was the second accident involving a Tejas aircraft in under two years. The previous incident took place on 12 March 2024, when another Tejas crashed near a residential area in Jaisalmer after returning from the tri-services exercise ‘Bharat Shakti’. That event marked the first crash of the homegrown fighter since its maiden flight in 2001. (With inputs from agencies)</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/world/russian-aerobatic-team-pays-tribute-to-fallen-iaf-wing-commander-at-dubai-air-show-video-ws-l-9726433.html</t>
+  </si>
+  <si>
+    <t>Smriti Mandhana's Father Suffers Heart Attack; Wedding With Palash Muchhal Deferred</t>
+  </si>
+  <si>
+    <t>Indian women’s cricketer Smriti Mandhana’s father, Shrinivas, suffered a heart attack at the Mandhana family’s farmhouse in Samdol, Sangli. Mandhana was supposed to get married to music composer Palash Muchhal at the venue on Sunday, but it has now been indefinitely postponed. According to the family, Mr. Shrinivas’s health deteriorated on Sunday morning, and he was rushed to the hospital in an ambulance. His condition is stable, but the doctors have prescribed that he stay in the hospital for some time. Mandhana’s manager, Tuhin Mishra, confirmed that Mandhana has postponed the wedding ceremony indefinitely till Mr. Shrinivas gets better. “Today morning, when Smriti’s father, Mr. Shrinivas Mandhana, was having his breakfast, his health started to worsen," Mishra told the media on Sunday. “We waited for a while because we thought it might be something normal and he’d get better. But it kept getting worse. We thought we wouldn’t take a risk and called up the ambulance. He has been taken to the hospital and is under observation. Smriti Mandhana, as you know, is very, very close to her father. So she decided that till the time he’s not okay, this marriage, which was supposed to happen today, is postponed indefinitely." “The doctors have said that he’d need to stay in the hospital till the time he gets okay… I mean, we are all also in a bit of shock. We all want him to recover soon. Like I said, Smriti is very clear. She wants her father to be better first before thinking about the wedding," he added. Muchhal got engaged with Mandhana at the DY Patil Cricket Stadium — the venue where Smriti and the Indian women’s team won the 2025 World Cup — recently. Swipe Left For Next Video Mr. Shrinivas is an ex-cricketer. He represented Sangli at the district level and wanted to pursue the sport professionally, but couldn’t due to a lack of support. He gave that support to his son, Shravan, and Smriti, with the latter going on to become one of the most successful cricketers in India.</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/cricket/smriti-mandhanas-father-suffers-heart-attack-wedding-with-palash-muchhal-postponed-9726456.html</t>
+  </si>
+  <si>
+    <t>Jamiat Chief Says 'Govt Ensuring Muslims Never Raise Heads' Amid Delhi Blast Probe, BJP Hits Back</t>
+  </si>
+  <si>
+    <t>The BJP on Sunday strongly criticised Jamiat Ulema-e-Hind president Maulana Arshad Madani for his remarks alleging discrimination against Muslims in India, terming his statements “confusing" and “misleading" at a time when the Delhi blast probe is underway. BJP leader Yaser Jilani said Madani’s comments ignored the inclusive efforts of the Central government and instead sought to create “unnecessary confusion" among the community. “There cannot be a better place for Muslims than India, nor a better big brother than the Hindus," Jilani said, responding to Madani’s claim that the government was ensuring Muslims “never raise their heads." Pointing to contradictions in Madani’s speech, Jilani said, “On one hand, he says the condition of Muslims in the world is not good, and on the other, he talks about Zohran Mamdani becoming Mayor-elect of New York. He also mentioned London Mayor Sadiq Khan and referred to Azam Khan and Al-Falah University." Jilani further asserted that the cases involving Azam Khan and the owner of Al-Falah University were rooted in legal violations. “The owner of Al-Falah University is a perpetrator, and Azam Khan is also involved in various offences. The Central government is taking everyone along. He should not create confusion among the people of the nation," he said. Madani had earlier claimed that Muslims were being targeted in India and cited examples of leaders abroad rising to top positions, adding that those who attain such roles in India end up in jail. “The world thinks that Muslims have become helpless, finished, and barren. I don’t believe so. Today, a Muslim Mamdani can become mayor of New York, a Khan can become mayor of London, whereas in India, no one can even become a university vice-chancellor. And even if someone does, they will be sent to jail, like Azam Khan. Look at what is happening today in Al-Falah. The government is working relentlessly to ensure that Muslims never raise their heads," he had said. His remarks have triggered political reactions, with the BJP accusing him of attempting to stoke fear and division. BJP leader Mohsin Raza alleged that Madani and his family have looted the country’s Muslims and played blame-game politics. “This has been their dual character for a very long time. They kept receiving grants in the name of Muslim minorities for years but did nothing for them." Swipe Left For Next Video Meanwhile, the Congress backed Jamiat Ulema-e-Hind president Maulana Arshad Madani’s sharp remarks on the condition of Muslims in India, with party leader Udit Raj endorsing his concerns and accusing the government of discrimination. “I support his statement. I agree that someone has done terrorist activity in the Al-Falah University, but the university should not be targeted. Why are homes of Muslims being bulldozed? America is great, as there is no discrimination there," he said.</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/india/blame-game-politics-bjp-slams-jamait-chief-on-govt-ensuring-muslims-never-raise-heads-remark-ws-l-9725816.html</t>
+  </si>
+  <si>
+    <t>Delhi Bomber Distanced Himself From Al Qaeda-Aligned Co-Accused: Report</t>
+  </si>
+  <si>
+    <t>A deep ideological divide within the terror module behind the November 10 Delhi car blast has come to light, with the alleged bomber, Umar-un-Nabi, distancing himself from co-conspirators due to conflicting extremist beliefs. According to an NDTV report, Umar, who drove the Hyundai i20 that exploded near the Red Fort, even skipped the wedding of fellow accused Adeel Ahmed Rather over disagreements linked to ideology, operational methods and finances. Investigators say Umar-un-Nabi, a Kashmiri doctor associated with Al-Falah University in Haryana’s Faridabad, subscribed to the ideology of the Islamic State (ISIS). In contrast, the other members of the module were aligned with al-Qaeda-backed groups, including Ansar Ghazwat-ul-Hind. Though both terror outfits trace their origins to Salafism and violent jihad, their worldviews differ sharply, particularly regarding sectarian violence, global vs regional priorities, and the roadmap to establishing a caliphate. This ideological difference reportedly created tension within the group, leading Umar, described as the “most radicalised" among the cell, to skip Adeel’s wedding in Jammu and Kashmir earlier this year. Despite the friction, Umar later travelled to Qazigund in October to repair ties and align the group’s plans for multiple coordinated blasts, as per reports. Beyond ideology, disputes over funding reportedly deepened internal rifts. The module had pooled nearly Rs 26 lakh for explosives and logistics. Umar was allegedly displeased when asked to provide a detailed expenditure account. According to investigators, Umar contributed Rs 2 lakh, Adeel Ahmed Rather contributed Rs 8 lakh, Shaheen Saeed and Muzammil Shakeel provided Rs 5 lakh each. Adeel’s brother, Muzaffar Ahmed Rather, now believed to have fled India, added Rs 6 lakh. These disagreements extended to the method of attack, with Umar insisting on a more dramatic operational approach. The blast on 10 November killed 14 people and injured several others near the Red Fort Metro Station. Umar originally intended to detonate the car bomb inside the Red Fort parking area, a bustling location near popular markets. However, he reportedly panicked after learning that co-accused Shaheen Saeed and Muzammil Shakeel had been arrested earlier that day in connection with the wider “white-collar" terror module. When he arrived at the Red Fort, he found it shut due to Monday closures and noticed the absence of crowds. After waiting inside the parking area for nearly three hours, Umar drove out and triggered the explosion near a traffic signal outside the Metro station. Swipe Left For Next Video Just hours before the blast, Jammu and Kashmir Police announced that it had cracked an interstate and transnational terror module linked to Jaish-e-Mohammed and the al-Qaeda-affiliated Ansar Ghazwat-ul-Hind. Police also seized 2,900 kg of explosive material, including ammonium nitrate, which investigators believe was used in the Delhi blast. With ideological fractures, financing disputes and a failed original plan now emerging, the probe into the Red Fort blast continues to widen.</t>
+  </si>
+  <si>
+    <t>https://www.news18.com/india/delhi-bomber-distanced-himself-from-al-qaeda-aligned-co-accused-report-9726170.html</t>
+  </si>
+  <si>
+    <t>News18Punj_Crawler</t>
+  </si>
+  <si>
+    <t>LATEST PUNJAB NEWS</t>
+  </si>
+  <si>
+    <t>Clarification of the Center on bringing the bill regarding Chandigarh, CM Bhagwant Mann tweeted the reply of the Ministry of Home Affairs regarding the change of Chandigarh's UT status We will not succeed in the nefarious plans of the Center to take away Chandigarh from Punjab - CM Mann will take away Chandigarh from Punjab Center, Preparation of 131st Amendment in the Constitution Sufficient provision for Sangat during the events from 23rd to 25th November: The Constitutional (131st Amendment) Bill should not be presented in the Parliament: To the center of Sukhbir</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/</t>
+  </si>
+  <si>
+    <t>IPL Auction 2025</t>
+  </si>
+  <si>
+    <t>Players Bought:182/577 Slots Available:22/204 The mega auction of IPL 2025 is scheduled to be held on November 24 and 25 in Jeddah, Saudi Arabia. A total of 1574 players were registered in this auction, out of which 574 players have been selected. Of these, 366 are Indian and 208 are foreign players. 10 teams have a total of 204 vacancies. Rishabh Pant, KL Rahul, Shreyas Iyer, Ravi Chandran Ashwin, Mohammad Shami, Yuzvendra Chahal etc. are big names among Indian players. While the foreign players include David Warner, Jos Buttler, etc. Live Update: IPL Auction 2025: Top 10 Players Live Update: IPL Auction 2025: Gujarat Titans Gujarat Titans will participate in the auction with a budget of ₹69 crore and fill 20 vacancies. The team has retained players like Rashid Khan, Shubman Gill, Sai Sudharsan for ₹51 crore. The team has dropped players like Mohammad Shami, David Miller. The team has an RTM option. Live Update: IPL Auction 2025: Chennai Super Kings Chennai Super Kings will participate in the auction with a budget of ₹55 crore and fill 20 vacancies. The team has retained players like Ruturaj Gaikwad, MS Dhoni, Ravinder Jadeja, Shivam Dubey and Mathisa Pathirana for ₹55 crore. Ruturaj Gaekwad received ₹18 crore. The team has dropped players like Ajinkya Rahane, Mitchell Santner. The team has an RTM option. Live Update: IPL Auction 2025: Delhi Capitals Delhi Capitals will participate in the auction with a budget of ₹73 crore and fill 21 vacancies. The team has retained players like Oxar Patel (₹16.5 crore), Kuldeep Yadav, Tristan Stubbs for ₹47 crore. The team has left a captain like Rishabh Pant. Delhi has two RTM options I Live Update: IPL Auction 2025: Kolkata Knight Riders Kolkata will participate in the auction with a budget of ₹51 crore and will fill 19 vacancies. The team has retained players like Rinku Singh (₹13 crore), Varun Chakraborty, Sunil Narine, Andre Russell for ₹69 crore. The team has left out big players like Shreyas Iyer, Mitchell Starc. The team has no RTM option. Live Update: IPL Auction 2025: Punjab Kings Punjab Kings will participate in the auction with a budget of ₹110.5 crore and fill 23 vacancies. Uncapped players like Shashank Singh, Prabhasimran Singh have been retained. The team has left out big players like Arshdeep Singh, Liam Livingston. The team has four RTM options. Live update</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/ipl-auction/</t>
+  </si>
+  <si>
+    <t>Latest news, in your own language</t>
+  </si>
+  <si>
+    <t>The News18 app is part of Network18, India's largest media conglomerate. The digital platform of the country's leading Hindi news channels News18 India, CNN News18, News 18 Lokmat and News 18 Bangla. Here you will find the latest news from the country and the world, which you can read in your own language. I can do it. You can also watch 16 live TV channels in 11 languages. I can do it. News 18 gives you access to every major news of the country and the world. Will send notification. So that you don't miss any big news. News18 is currently available in 11 different languages ​​of the country. In this app of News 18 you can read English, Bangla apart from Hindi. Marathi, Gujarati, Kannada, Tamil, Telugu, Malayalam, Punjabi and Urdu you can read news and watch live TV. Here you can watch your channel live by selecting your language. For this you can also select your favorite news on News18 app you just have to select your preferred category. News 18U offers- Politics, Technology, Business, Gadgets, Sports, Auto, Lifestyle, World, Knowledge, Entertainment and Cricket categories in which you can choose your favorite news. This app of News 18 brings you the latest news, photos and in video format. If you have any news to read again later if you want, you can also save as a bookmark. You can save news, photos and videos in bookmarks. If your internet speed is bad, you can watch the news later. You can also download to read News 18 brings you an app that slows down internet speed will also make work easier. You can also watch live TV and find videos in low internet speed. Also the news can be read at the same time without any interruption. Are you also bothered by ads appearing in between videos? This app of News 18 you will be able to quickly watch your choice without any ads. News 18 gives you access to every major news of the country and the world. Will send notification. So that you don't miss any big news. News18 is currently available in 11 different languages ​​of the country. In this app of News 18 you can read English, Bangla apart from Hindi. Marathi,</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/app-download/</t>
+  </si>
+  <si>
+    <t>Clarification of the Center on bringing the bill regarding Chandigarh, CM Bhagwant Mann tweeted</t>
+  </si>
+  <si>
+    <t>Since Saturday, the politics of Punjab has heated up due to the discussion of bringing a bill related to Chandigarh in the winter session by the central government. Now the clarification of the Union Ministry of Home Affairs has come out in this regard, in which they have said that currently no such bill is being brought in the winter session of the Parliament. Chief Minister Bhagwant Singh Maan has expressed happiness over this decision of the central government. CM Mann tweeted, "I am happy that the Central Government has decided to withdraw the Chandigarh Bill and not bring it in the Parliament. Hope that in the future no decision related to Punjab will be taken without consulting the people of Punjab." I am happy that the Central Government has decided to withdraw the Chandigarh Bill and not bring it in the Parliament.. I hope that in the future no decision related to Punjab will be made without asking the people of Punjab.. Chief Minister Bhagwant Singh Mann has said that the Central Government has decided to withdraw the Chandigarh Bill and not bring it in the Parliament. Along with this, he also hoped that in the future no decision related to Punjab will be made without asking the people of Punjab.</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/news/punjab/center-clarification-on-bringing-bill-regarding-chandigarh-cm-bhagwant-mann-tweeted-skm-912725.html</t>
+  </si>
+  <si>
+    <t>The response of the Ministry of Home Affairs regarding the change of UT status of Chandigarh</t>
+  </si>
+  <si>
+    <t>Amid the turmoil in Punjab politics over Chandigarh, the central government has made its stand clear. The Ministry of Home Affairs on Sunday officially said that the Central Government's proposal to simplify the legal process for Chandigarh is currently under consideration and no final decision has been taken. The ministry also clarified that the government does not intend to introduce any bill in this regard in the upcoming winter session of Parliament. A Home Ministry statement said the proposal does not seek to change Chandigarh's system of governance or affect its traditional ties with Punjab and Haryana. The Ministry appealed to the public that there is no need to worry about the matter, and any decision will be taken only after extensive consultation with all stakeholders, keeping in mind the interests of Chandigarh. What is this bill and why is it creating controversy? In fact, earlier there were reports that the central government had proposed to include Chandigarh under Article 240 of the Constitution. Under Article 240, the President has the power to directly make rules and laws for the Union Territories. The proposal to simplify the process of making laws by the Central Government only for the Union Territory of Chandigarh is currently under consideration at the Central Government level. No final decision has been taken on this proposal It is also alleged that the Lok Sabha and Rajya Sabha bulletins indicate that the government may introduce the Constitution (131st Amendment) Bill, 2025 in the upcoming winter session of Parliament (starting from December 1). It has been said that if the Bill is passed in its current form, it is likely that an independent administrator will be appointed for Chandigarh, as there was an independent chief secretary earlier. The uproar over the proposed bill is because the change will completely change the administrative identity of Chandigarh. Currently, Chandigarh is a Union Territory, governed by Punjab, headed by the Governor of Punjab. Key appointments like SSP and DC are also made from the Punjab and Haryana cadre, with the city serving as the joint capital of the two states. However, the proposed amendment will change the Chandigarh model. Direct it to the President</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/news/punjab/home-ministrys-response-regarding-changing-chandigarhs-ut-status-912657.html</t>
+  </si>
+  <si>
+    <t>Uncut Opinion: Whose performance do voters like?</t>
+  </si>
+  <si>
+    <t>Uncut Opinion: Khadur Sahib's political FIGHT...Whose performance do voters like? Lok Sabha Elections | ... Chota Sidhu was seen shaking on the song of Bade Musewale Sunita Ahuja Files Divorce Against Govinda Disha Patani #shorts | N18S 'FWICE Called Diljit Traitor' Film Sardar G3 Protest | Sardaar Ji 3 | Diljit Dosanjh | N18V Preeti Sapru Podcast : Conversation with 'Billo' of the 80's | Gurdas Mann |Pollywood | Veerendra | N18P</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/videos/punjab/lok-sabha-elections-2024-which-party-in-khadur-sahib-is-the-trend-of-the-public-sk-577265.html</t>
+  </si>
+  <si>
+    <t>We will not let the nefarious plans of the central government succeed to take away Chandigarh from Punjab - CM Hon</t>
+  </si>
+  <si>
+    <t>Chandigarh: Strongly opposing yet another heinous move by the central government against Punjab, Punjab Chief Minister Bhagwant Singh Mann said that the Punjab government is using the BJP-led NDA to take away its capital Chandigarh from the state. The nefarious plans of the government will not be allowed to succeed. Chief Minister Bhagwant Singh Mann said that Chandigarh was, is and will remain an integral part of Punjab. He said that the proposal being brought by the Central Government to amend Article 240 of the Constitution to connect the capital of Punjab with the rest of the Union Territories will not be allowed at all. He said that although every state has full right to its own capital, but by refusing to hand over its capital to Punjab, great injustice is being done to the state. Bhagwant Singh Mann said that it is true that the central government led by BJP has succumbed to open bullying. Chief Minister Bhagwant Singh Mann said that no state is deprived of its capital while Punjab was deprived of its capital. He said that no one can deny the fact that his right is being taken away from Punjab. Bhagwant Singh Maan sadly said that previous governments have also bullied Chandigarh, Punjab by not giving it. Chief Minister Bhagwant Singh Mann said that there is no other example in the country where a state has been deprived of its capital after forming it on the basis of language. He said that Punjab has been a victim of bullying from the Center for a long time and now the Modi government is sprinkling salt on the wounds of Punjabis by taking such arbitrary decisions. Bhagwant Singh Mann said that under the universally accepted law, Chandigarh is an integral part of Punjab and should be returned to the state.</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/news/punjab/we-will-not-allow-the-central-government-nefarious-plans-to-snatch-chandigarh-from-punjab-to-succeed-cm-bhagwant-singh-mann-skm-912478.html</t>
+  </si>
+  <si>
+    <t>Center will take away Chandigarh from Punjab, preparations to make 131st amendment in the constitution, political leaders objected</t>
+  </si>
+  <si>
+    <t>Chandigarh will be taken away from Punjab by the Centre, preparation for 131st amendment in the constitution, political leaders expressed Itraj Pratap Singh Bajwa has expressed his objection, he has shared the post on social media X Chandigarh was created in 1966 as Punjab's capital, with the Punjab Governor serving as its Administrator for decades. Now the Centre's 131st Amendment move to pull Chandigarh under Article 240 is nothing short of snatching the city away from Punjab — an open attack on history,... Pargat Singh has objected and shared a post on social media X BJP's Constitution (131st Amendment) Bill exposes its real agenda — a full-scale attempt to snatch Chandigarh from Punjab. This assault has been years in the making: • Pushing for a separate Haryana Assembly inside Chandigarh• Plotting to convert Panjab University into a… pic.twitter.com/p0fUvrQGUj Which Union Territories in India are headed by Administrators instead of Lieutenant Governors Chandigarh, Dadra and Nagar Haveli and Daman and Diu, and Lakshadweep. These Union Territories do not have legislative assemblies, so the entire administration is in the hands of an administrator appointed by the President.</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/news/punjab/the-center-will-take-away-chandigarh-from-punjab-preparations-to-make-the-131st-amendment-in-the-constitution-political-leaders-have-expressed-objections-skm-912421.html</t>
+  </si>
+  <si>
+    <t>Vigilance arrested SDM Batala red-handed by accepting a bribe of Rs 50,000.</t>
+  </si>
+  <si>
+    <t>Chandigarh – During its ongoing operation against corruption, the Punjab Vigilance Bureau has today caught the Commissioner-cum-SDM Batala Vikramjit Singh Panthe red-handed while accepting a bribe of Rs 50 thousand from the complainant. Another amount of Rs 13,50,000 was also recovered by the Vigilance Bureau during the investigation of the accused, regarding which he could not give correct details. Giving information in this regard, the spokesperson of the Vigilance Bureau said that the complainant is a resident of Batala district Gurdaspur and he had done patch work and repair work of roads at Municipal Corporation Batala, whose two bills were Rs.1,87,483 and Rs.1,85,369, the total amount of which was Rs. In this regard, he met the Commissioner of Municipal Corporation, Batala, who told him that for the said payment of bills, i.e. for clearing these bills, a bribe of Rs.37000 would have to be paid as 10% commission. He further stated that the complainant had also done camera and other related work for a light and sound show in Batala, for which an amount of Rs.1,81,543 was also owed. Thus the total amount due was approximately Rs.5,54,395/-. Regarding the payment of these bills, he met SDO Rohit Uppal who said that he would have to follow the orders of the commissioner and pay 9% commission as bribe to release the due amount to the complainant. But the complainant did not want to get his work done by paying bribe. Acting on the information of the complainant, the Vigilance Bureau recorded the statement of the complainant at the Vigilance Bureau Unit Gurdaspur. After confirming the allegations, the Vigilance Bureau laid a trap and caught Vikramjit Singh Panthe red-handed while accepting a bribe of Rs 50 thousand from the complainant in the presence of two government witnesses. A case has been registered against the accused at the Police Station Vigilance Bureau, Range Amritsar under the relevant sections of the Prevention of Corruption Act. The accused will be produced in the court tomorrow and further investigation is on in this regard.</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/news/punjab/vigilance-bureau-catches-commissioner-municipal-corporation-cum-sdm-batala-red-handed-while-accepting-bribe-of-rs-50-thousand-ak-912310.html</t>
+  </si>
+  <si>
+    <t>Anandpur Sahib, the land of the Ninth Patshah, is ready to welcome the devotees: Harjot Singh Bains</t>
+  </si>
+  <si>
+    <t>Chandigarh: Education and Information and Public Relations Minister Harjot Singh Bains has said that the ancestral land of the ninth Patshah Sri Guru Teg Bahadur Sahib Sri Anandpur Sahib is fully ready to welcome the Sangat. The Punjab government is celebrating 350 years of Guru Sahib's martyrdom with full devotion and respect. Tourism and Cultural Affairs Minister Tarunpreet Singh Saund said that all the arrangements are complete for the gathering during the events to be held from November 23 to 25. No trouble of any kind will be allowed to the Sangat. Both the ministers have appealed to the people of the country and abroad to pay obeisance at the land of Sri Anandpur Sahib. He said that the great life and philosophy of the Ninth Patshah Sri Guru Teg Bahadur Ji, the protector of religious freedom and human rights, the embodiment of mercy and sacrifice and the symbol of sacrifice, is a beacon of light for the entire humanity. We along with our families should be a part of these supernatural events by paying obeisance at the great land Sri Anandpur Sahib. Meanwhile, Nagar Kirtans from Talwandi Sabo and Faridkot were warmly welcomed by Bains, Saund and Lok Sabha member Malwinder Singh Kang on reaching Sri Anandpur Sahib. Details of events to be held at Sri Anandpur Sahib from November 23 to 25, 2025: These special events will begin on November 23 at 10 am with initiation of Sri Akhand Path Sahib. The event will be held at Gurdwara Sahib near Baba Budha Dal Cantonment where Chief Minister Bhagwant Singh Mann will also be present. An exhibition based on the life of Sri Guru Tegh Bahadur Ji will be inaugurated at Virasat-e-Khalsa hall at 11 am. All religions meeting will be held at the main pandal of Baba Budha Dal cantonment from 12 noon. At 3 pm there will be a guided tour of Virasat-e-Khalsa, Bhai Jaita Ji Memorial and Panj Pyare Park. There will be a drone show at Virasat-e-Khalsa at 5 pm and Katha and Kirtan Durbar will be held at the main pandal at 6 pm. On 24th November at 8 am Sis Bhet Nagar Kirtan will go from Kiratpur Sahib to Sri Anandpur Sahib. There will be a heritage walk at Sri Anandpur Sahib at 10 am. From 11 a.m. to 1 p.m., Baba Budha Dal will decorate the main pandal of the cantonment with poetry recitals, dhadi and kavishari darbar based on the life and teachings of Guru Sahib. There will be a special session of Punjab Vidhan Sabha dedicated to Sri Guru Teg Bahadur Ji at Bhai Jaita Ji Memorial from 1 pm. Gatka and other Jangju at Charan Ganga Stadium from 2 p.m</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/news/punjab/sri-anandpur-sahib-the-legacy-of-the-ninth-king-is-ready-to-welcome-the-devotees-harjot-singh-bains-skm-912406.html</t>
+  </si>
+  <si>
+    <t>India's daughter Meht Sandhu won the gold medal, hoisted the flag in Tokyo Olympics</t>
+  </si>
+  <si>
+    <t>New Delhi: India's Meht Sandhu continued her impressive run to win her fourth gold medal in the women's 50m rifle 3 position event at the ongoing Deaf Olympic Games in Tokyo. Meht scored a total of 456.0 points after 45 shots to win his second gold medal at the Deaf Olympic Games. South Korea's Dan Jeong won the silver medal with 453.5 points, while Hungary's Mira Zuzana Biatowski won the bronze medal with 438.6 points. Mahit set a new world record for the Deaf Games during his run to the finals. He scored 585 points in the qualifying round and reached the final. Meht scores 194 in kneeling Meht scored 194 in kneeling, 198 in prone and 193 in standing, breaking his own previous record of 576 scored at the World Deaf Shooting Championships in Hannover last year. India's Natasha Joshi also qualified for the final, finishing seventh with 566 points. She finished fifth in the final with a score of 417.1. Indian shooters have won 14 medals at the Deaf Olympics so far, including five gold, six silver and three bronze medals. Abhinav Deswal and Chetan Hanumant Spakal are competing in the 25m pistol event.</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/news/sports/mahit-sandhu-win-gold-medal-tokyo-olympic-912422.html</t>
+  </si>
+  <si>
+    <t>16 fours, century in 69 balls... Travis Head wreaked havoc, England's bowlers struggled</t>
+  </si>
+  <si>
+    <t>New Delhi: Australia opener Travis Head created a sensation in the first match of the 2025-26 Ashes series against England. Travis Head completed his 69-ball century in the fourth innings of the first Test in Perth. He hit 12 fours and four sixes during his century. It is also the second fastest century off balls in Ashes history. Earlier, in 2006, Adam Gilchrist completed his century in 57 balls. This is Travis Head's 10th century in Test cricket. In the Test match being played in Perth, the bowlers dominated early, but in the fourth innings, Travis Head's explosive batting gave the match a T20 feel. England bowlers were facing the loss of Travis Head. It was Travis Head's aggressive batting that helped Australia turn the match into a one-sided match. Australia set a target of 203 In the first match of the Ashes series, England set Australia a target of 203 in the fourth innings. Batting first, England scored 172 in their first innings. In reply, England were bowled out for just 132, giving England a 40-run lead in the first innings. After this, when England came out to bat in the second innings, the Australian bowlers bowled them out for just 162 runs. England set Australia a target of 203 runs to win.</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/news/sports/16-fours-century-in-69-balls-travis-head-created-havoc-england-bowlers-were-thoroughly-crushed-ak-912290.html</t>
+  </si>
+  <si>
+    <t>A new district will be formed in Punjab!</t>
+  </si>
+  <si>
+    <t>News of forming another district in Punjab is coming out. It should be said that there is a preparation to divide the district Rupnagar/Ropar into two parts. On the 350th martyrdom day of Sri Guru Teg Bahadur ji, the state government can declare Sri Anandpur Sahib as a district. This district will be the 24th district of the state. The state government has directed the concerned departments to identify the areas which can be included in this district. Sources say that if Sri Anandpur Sahib is made a district, then which two Vidhan Sabha constituencies should be included in it, discussions are also going on. Meanwhile, opposition to this decision is also coming to the fore. Congress leader Barinder Singh Dhillon has posted a post on his social media account opposing this decision, he wrote... "I strongly oppose the Punjab government's proposed exercise of making Anandpur Sahib a new district. Rupnagar district has already been divided many times with the formation of Mohali, Fatehgarh Sahib and Nawanshahr. Now reducing it further will not do justice to the development, administrative strength and historical identity of Rupnagar. Anandpur Sahib is a very sacred and historically important land for all of us. Its greatness will not increase by making a new office or by giving a district status. If the government really wants to pay tribute to the 350th martyrdom anniversary of Anandpur Sahib, then it should announce a big development package, heritage preservation and employment projects for Guru Sahib. This proposal is not in the interest of both Rupnagar and Anandpur Sahib The government should be careful: if this wrong decision is carried forward, we will be forced to launch a strong public protest campaign. Rupnagar will not be allowed to weaken further."</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/news/punjab/a-new-district-will-be-formed-in-punjab-912107.html</t>
+  </si>
+  <si>
+    <t>Sri Anandpur Sahib | Mahaguru of all religions on the same stage, listen LIVE | Bhagwant Mann | News18 Punjab</t>
+  </si>
+  <si>
+    <t>Sri Anandpur Sahib | Mahaguru of all religions on the same stage, listen LIVE | Bhagwant Mann | News18 Punjab ... Chhota Sidhu was seen dancing on the song of Bade Musewale Sunita Ahuja Files Divorce Against Govinda Disha Patani #shorts | N18S 'FWICE Called Diljit Traitor' Film Sardar G3 Protest | Sardaar Ji 3 | Diljit Dosanjh | N18V Preeti Sapru Podcast : Conversation with 'Billo' of the 80's | Gurdas Mann |Pollywood | Veerendra | N18P</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/videos/sri-anandpur-sahib-mahaguru-of-all-religions-on-one-stage-listen-live-bhagwant-mann-news18-punjab-912733.html</t>
+  </si>
+  <si>
+    <t>Arshad Madani News | Maulana spews venom, Muslim can become mayor in New York, will go to jail in India</t>
+  </si>
+  <si>
+    <t>Arshad Madani News | Maulana Ne Ugla Jahar, Muslims can become mayor in New York, will be jailed in India... Chota Sidhu was seen shaking on the song of the big moosewale Sunita Ahuja Files Divorce Against Govinda | Disha Patani #shorts | N18S 'FWICE Called Diljit Traitor' Film Sardar G3 Protest | Sardaar Ji 3 | Diljit Dosanjh | N18V Preeti Sapru Podcast : Conversation with 'Billo' of the 80's | Gurdas Mann |Pollywood | Veerendra | N18P</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/videos/arshad-madani-news-maulana-spews-venom-muslim-can-become-mayor-in-new-york-will-go-to-jail-in-india-912726.html</t>
+  </si>
+  <si>
+    <t>The Constitutional (131st Amendment) Bill should not be presented in Parliament: Sukhbir Singh Badal appealed to the Centre</t>
+  </si>
+  <si>
+    <t>Chandigarh: Shiromani Akali Dal President Sardar Sukhbir Singh Badal today appealed to the Central Government not to introduce the 131st Constitutional Amendment Bill in the upcoming winter session of the Parliament and he insisted that doing so would be a betrayal and discrimination against the brave Punjabis who gave the most martyrdoms for the country and it would be a backtracking on all the promises made to give Chandigarh to Punjab. In a statement issued here, Shiromani Akali Dal President said that the purpose of the 131st Amendment Bill of the Constitution is to permanently remove the Union Territory from the administrative and political control of Punjab. He said that the aim was to end Punjab's claim on Chandigarh as its capital city. Describing this proposed bill as an attack on the rights of Punjab, Sardar Sukhbir Singh Badal said that it is against the spirit of federalism and it is discrimination against those Punjabis who gave their martyrdom as the foremost in the freedom struggle and guarded the borders of the country and brought the green revolution to ensure food security of the country. Sardar Badal asserted that with the proposed bill, the promises made by the central government to give Chandigarh to Punjab will also end. He said that in 1970, the central government had agreed to give Chandigarh to Punjab in principle. After this, the date of January 1986 was fixed for handing over Chandigarh to Punjab through the Rajiv-Longowal Agreement. He said that this agreement was also approved by the Parliament but till date it has not been implemented. Sardar Badal said that for the past few decades, the central government has been continuously weakening Punjab's claim on Chandigarh and instead of implementing the 60:40 ratio formula for the deployment of employees in the Union Territory, UT (AGMUT) cadre officers are being posted in Chandigarh and efforts are being made to end Punjab's control over Punjab University. Sardar Badal said that Punjabis are feeling cheated and discriminated against due to these steps. He said that there is anger in the hearts of Punjabis that the central government has ignored the claim of Punjabi on its capital city and now efforts are being made to make such an arrangement that Chandigarh remains a Union Territory permanently, the control of which remains in the hands of the central government.</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/news/punjab/sukhbir-singh-badal-appeals-to-the-centre-not-to-introduce-the-constitutional-131st-amendment-bill-in-parliament-ak-912394.html</t>
+  </si>
+  <si>
+    <t>Minister's PA's wife commits suicide, family alleges harassment...</t>
+  </si>
+  <si>
+    <t>Maharashtra Minister Pankaja Munde's (PA) wife allegedly committed suicide at her home in central Mumbai following a domestic dispute. The police gave this information on Sunday (November 23). Gauri Palve, wife of Anant Garje, personal assistant to state animal husbandry and environment minister Munde, was found hanging at her house in Worli area on Saturday (November 22) evening, an official said. He said that both of them got married in February this year. Palve was a doctor at Govt KEM Hospital. According to the police, Palve's family has alleged that her husband tortured and harassed her, due to which she committed suicide. The family has demanded a full probe into Palve's death. The official said that preliminary information suggests that a domestic dispute was the reason for the suicide. He further said that a report of accidental death has been registered. Further investigation is currently underway. The deceased, Gauri Palve, was a doctor in the dental department at the government-run KEM Hospital. According to police, Palve's family has alleged that her husband tortured and harassed her, which is why she took this step. They have demanded a full investigation into the death. The wife of Maharashtra Minister Pankaja Munde's personal assistant allegedly committed suicide at her home in central Mumbai due to a domestic dispute, police said. Gauri Palve, wife of Anant Garje, personal assistant to the state Animal Husbandry and Environment Minister Munde, was found hanging at her house in Worli area on Saturday evening, an official said. He said that this couple got married in February this year. According to the police, Palve's family has alleged that her husband tortured and harassed her, which is why she took this drastic step. They have demanded a full investigation into the death. This matter has now become a topic of discussion in Maharashtra politics. This incident has shocked the local community. The suicide has drawn political attention, leading to calls for justice and tougher measures to tackle domestic violence. The case has also highlighted concerns about the mental health and safety of women, even women who are involved in mainstream politics.</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/news/national/maharashtra-news-wife-of-minister-pankaja-munde-pa-commits-suicide-family-alleges-harassment-sk-912713.html</t>
+  </si>
+  <si>
+    <t>Excited about TMC making inroads in Bengal to quench its hunger for power, PM said, in the face of politics of appeasement...</t>
+  </si>
+  <si>
+    <t>Kolkata: Prime Minister Narendra Modi on Friday launched a scathing attack on the ruling Trinamool Congress in West Bengal, accusing it of encouraging infiltration to satisfy its "hunger for power". Addressing a rally in Damdum area of ​​North 24 Parganas, Modi said the Bharatiya Janata Party (BJP)-led central government has launched a major campaign against encroachers who are "changing the demographics of West Bengal." He alleged that this country cannot tolerate intruders anymore. We will not allow them to stay in India, that is why our government has launched such a massive campaign against the infiltrators.' In their hunger for power, these parties are encouraging infiltration. The Prime Minister said, 'To ensure that the infiltrators leave Bengal and the country, the Trinamool Congress government will have to go. Only your vote can ensure that these infiltrators are kicked out of the country. Describing the border state of West Bengal as particularly vulnerable, Prime Minister Modi said the infiltrators are "putting pressure on the economy and persecuting our mothers and sisters." The Prime Minister also accused the Trinamool Congress of obstructing development in Bengal and said the BJP has a "solid blueprint" for the development of the state. PM Modi added, "West Bengal is a border state. The way the demographics are changing in the border areas is also creating a social crisis in West Bengal." Especially the farmers are being cheated and their lands are being encroached upon, the tribals are being misled and their land is being grabbed. The country cannot afford it, it has to be stopped. That is why this time from the Red Fort I have announced a special population mission against infiltration."</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/news/national/tmc-is-encouraging-infiltration-into-bengal-to-satisfy-its-hunger-for-power-pm-said-in-the-face-of-politics-of-appeasement-skm-859774.html</t>
+  </si>
+  <si>
+    <t>Schools, colleges and offices will remain closed on November 25, why public holiday? The Chief Minister explained the reason</t>
+  </si>
+  <si>
+    <t>Delhi Chief Minister Rekha Gupta announced to declare November 25, 2025 as a public holiday in commemoration of the 350th martyrdom anniversary of Sri Guru Tegh Bahadur Sahib Ji. The Delhi government says that this day is not just a tribute, but an opportunity to remember his unique courage, humanity, religious freedom and the message of freedom for all religions. As soon as the order was issued, a holiday was imposed in all schools, colleges, government offices and many institutions in Delhi. What did Chief Minister Rekha Gupta say? Chief Minister Rekha Gupta wrote on X, "Delhi Government has decided to declare November 25, 2025 as a public holiday on the auspicious occasion of the 350th Martyrdom Day of Sri Guru Teg Bahadur Sahib. Guru Sahib's message of courage, compassion and religious freedom will always inspire us. Sikhs play an important role in Delhi's politics. Sikhs constitute about 3.4% of Delhi's population. Their influence is wide and positive. The Sikh population in West Delhi, Hari Nagar and Delhi Cantonment is quite large. That is why all the parties try to woo the Sikh community, the Sikh Guru and the symbols Pratikshree Tegh Bahadur Sahib is a symbol of humanity, courage and religious freedom, the likes of which are rarely found in history. He sacrificed his life for the weak, persecuted people and communities facing religious persecution. His martyrdom left the message to the world that the supreme sacrifice for the protection of truth and religion is non-violence, mercy and equality The 350th Martyrdom Day of Guru Tegh Bahadur Sahib is a source of inspiration for every Indian.</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/news/national/in-delhi-cm-rekha-gupta-declares-schools-colleges-and-offices-will-remain-closed-on-november-25-skm-912450.html</t>
+  </si>
+  <si>
+    <t>A neighbor stabbed a 10-year-old girl 21 times over a small matter, she died on the spot.</t>
+  </si>
+  <si>
+    <t>Hyderabad: A 10-year-old girl was stabbed 21 times with a knife! The reason? Just wanting to steal a cricket bat. This shocking incident has come to light from Hyderabad. This girl named Sahasra was a student of the sixth standard. His father was a bike mechanic his mother was a lab technician leading a simple middle class life. It was Monday, her younger brother who is only 6 years old had gone to school and Sahasra was alone at home. At the same time this incident happened. Neighbor boy's horrifying exploit Police investigation revealed that a 14-year-old boy who lives next door to her house sneaked into the house. Knife in hand… and what happened next will shake your soul. He attacked that innocent girl 21 times. According to the police, the boy wanted to steal Sahasra's cricket bat. When the father returned he found out… That afternoon when Sahasra's father returned home, he saw a scene that turned his life upside down. His innocent daughter was lying in a pool of blood. From there, the matter reached the police and sensation spread throughout the area. Cyberabad police formed several teams and after a four-day search, nabbed the neighbor boy. During interrogation, he also confessed that he had killed Sahasra. But the big question for the police remains - if he only wanted to steal the cricket bat, why did the boy bring the knife?</t>
+  </si>
+  <si>
+    <t>https://punjab.news18.com/news/national/in-hyderabad-neighbor-stabs-10-year-old-girl-21-times-over-minor-issue-dies-on-the-spot-skm-859748.html</t>
+  </si>
+  <si>
+    <t>IndiaToday_Crawler</t>
+  </si>
+  <si>
+    <t>Women's World Cup 2025</t>
+  </si>
+  <si>
+    <t>The Women's World Cup-winning Indian team had a special gift for Prime Minister Narendra Modi as they met him at his official residence in New Delhi on Wednesday, November 5. The 2025 Women’s Cricket World Cup will be held from 30 September to 2 November 2025. This edition will be hosted by India, with 8 teams competing in various cities across India and Sri Lanka. Participating Teams (2025 Women’s Cricket World Cup) India (Host), Australia, England, New Zealand, South Africa, Sri Lanka, Pakistan, Bangladesh All teams will play each other in a round-robin format. The top four teams will qualify for the semifinals. Key Matches:_x005F_x000D_
+1. Opening match: 30 September 2025, India vs Sri Lanka, Guwahati_x005F_x000D_
+2. India vs Pakistan: 5 October, Colombo_x005F_x000D_
+3. Semifinals: 29 and 30 October_x005F_x000D_
+4. Final: 2 November Venues:_x005F_x000D_
+1. India: Navi Mumbai, Indore, Guwahati, Visakhapatnam_x005F_x000D_
+2. Sri Lanka: Colombo (all Pakistan matches) Key Highlights:_x005F_x000D_
+1. 2025 Women’s World Cup will be special for Indian audiences as India is the host._x005F_x000D_
+2. Indian women will play a home World Cup match in ODIs for the first time since 2013._x005F_x000D_
+3. Total of 28 league matches and 3 knockout matches (2 semifinals + 1 final)._x005F_x000D_
+4. West Indies did not qualify for this edition.</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/sports/cricket/womens-world-cup</t>
+  </si>
+  <si>
+    <t>Women's world cup 2025 Schedule</t>
+  </si>
+  <si>
+    <t>The 2025 Women’s Cricket World Cup will be held from 30 September to 2 November across India and Sri Lanka. India, Australia, England, New Zealand, South Africa, Sri Lanka, Pakistan, and Bangladesh will play in a round-robin league, with each team playing 7 matches. 1. All league matches will conclude by 26 October 2. Semifinals: 29 and 30 October India will play its first match on 30 September against Sri Lanka in Guwahati, with the high-profile India-Pakistan match on 5 October in Colombo. For the full schedule please check on indiatoday.in.</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/sports/cricket/womens-world-cup/schedule</t>
+  </si>
+  <si>
+    <t>Women's world cup 2025 Points Table</t>
+  </si>
+  <si>
+    <t>Talking about the points table of the Women's World Cup 2025, Australia Women currently leads the standings with 13 points. They have played 7 matches so far, winning 6 and losing 0, with a net run rate of +2.102. In second place are England Women, who have collected 11 points from 7 outings, with 5 wins and 1 defeats. Each team receives two points for a win, one for a no-result or tied game. The top four teams at the end of the group stage qualify for the semi-finals of the Women's World Cup 2025. The points table is updated based on wins, losses, net run rate (NRR), and points. You can view it live on https://www.indiatoday.in/. The updated points table is available on ICC and https://www.indiatoday.in/. 2 points for a win, 1 point for a tie/no result, and 0 points for a loss. NRR determines which team advances if two teams have equal points. There are 8 teams participating this year. The table is updated immediately after every match. The top 4 teams in the points table will qualify for the semifinals. Net Run Rate (NRR) will be used to determine rankings. Both teams will get 1 point each, and the points table will be updated. No, it only shows team standings and points. Player stats are listed separately. The 2025 Women’s Cricket World Cup will be held from 30 September to 2 November 2025, co-hosted by India and Sri Lanka. This is the 13th edition, and India is hosting it for the fourth time. A total of 8 teams will compete in a round-robin format, with the top 4 qualifying for the semifinals. 1. Opening match: India vs Sri Lanka, 30 September 2. India vs Pakistan: 5 October in Colombo 3. Some venue changes: matches originally scheduled in Bangalore will now be in Navi Mumbai and Guwahati, with key matches in Colombo. 4. Semifinals: 29 and 30 October As the ICC Women’s World Cup progresses, the points table will be in constant flux, showcasing the fierce battle between the world’s top cricketing nations. Teams will aim for a place at the top of the standings to secure a favourable path to the knockout stage, while those in the middle will fight hard to keep their campaign alive. A healthy Net Run Rate (NRR) could prove decisive in separating qualification from early elimination, making every run scored and every over bowled vital._x005F_x000D_
+Fans can follow the updated standings after each match to track their favourite team’s journey toward the final, where the world’s best will vie for the coveted World Cup trophy. In the Women’s World Cup 2025 teams will earn two points for a win, while a tie or no result will give one point each. The tournament features all eight teams in a single group. Each side will play the others once, and the top four teams at the end of the group stage will progress to the semifinals. Supporters can follow the Women’s World Cup 2025 points table here for real-time updates on rankings, match results, and net run rate calculations. As the tournament progresses, the race for a place in the final is certain to keep attention firmly fixed on the standings.</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/sports/cricket/womens-world-cup/points-table</t>
+  </si>
+  <si>
+    <t>Check Today's Weather Forecast and AQI in Your City</t>
+  </si>
+  <si>
+    <t>Timings? Look no further! Get the latest updates from the Indian Meteorological Department (IMD) right here on http://indiatoday.in . From Air Quality Index (AQI) reports to humidity levels, we provide detailed and accurate weather news and forecasts to keep you informed. Stay updated with every important weather-related development at your fingertips. The temperature in Delhi today is 24°C, with an air quality index of 520. The temperature in Indore today is 26°C, with an air quality index of 164. The temperature in Assam today is 22°C, with an air quality index of 153. The temperature in Kolkata today is °C, and the air quality is . The temperature in Jaipur today is 24°C, with an air quality index of 169. The temperature in Dehradun today is 21°C, with an air quality index of 145. The temperature in Bangalore today is 27°C, with an air quality index of 52. The temperature in Chennai today is 28°C, with an air quality index of 66.</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/weather</t>
+  </si>
+  <si>
+    <t>Bihar Election Constituencies</t>
+  </si>
+  <si>
+    <t>The Bihar Assembly Election 2025 will be held in two phases on November 6 and 11 and the counting of votes will be done on November 14. A total of 121 seats will go to polls in the first phase of Bihar elections and the remaining 122 will vote in the second phase on November 11. The term of the 243-member Bihar Assembly will end on November 22. If you want the latest updates related to the Bihar election, stay connected with indiatoday.in. To find information about any Bihar assembly constituency, either search via the box below or click on its name from the list. The Bihar Assembly (Vidhan Sabha) has a total of 243 seats. Public representatives are elected directly. Bihar will go to polls in two phases on November 6 and 11. In the first phase, polling will be held for 121 seats, while the remaining 122 constituencies will vote in the second phase. The 2025 Assembly Elections may be conducted in two phases. Counting of votes for Bihar elections will be done on November 14. According to the updated 2025 draft voter list, there are more than 72.4 million (7.24 crore) voters in Bihar. After the Special Intensive Revision (SIR) process, around 6.5 million (65 lakh) names were removed. National Democratic Alliance (NDA): Bharatiya Janata Party (BJP), Janata Dal (United) [JDU], Hindustani Awam Morcha (HAM)(S), Lok Janshakti Party (Ram Vilas), Rashtriya Loktantrik Morcha (RLM), etc. Grand Alliance (Mahagathbandhan): Rashtriya Janata Dal (RJD), Indian National Congress, Vikassheel Insaan Party (VIP), CPI (ML) Liberation, Communist Party of India (CPI), Communist Party of India (Marxist) [CPI(M)], etc. The major issues in the Bihar Assembly elections will include employment, education, women empowerment, farmers’ issues, law and order, inflation, corruption, caste-based dynamics, and promises of development. SIR, or Special Intensive Revision, is a special process by the Election Commission through which names are added, removed, or corrected in the voter list. It is implemented in Bihar to ensure the voter list is completely updated and impartial. On average, around 800 to 1,200 voters are listed per polling station (booth) in Bihar, though this number may vary depending on the location. You can check the name of the winning candidate in your area on the official website of the Election Commission: https://results.eci.gov.in/. You can also check it on India Today website: https://www.indiatoday.in/elections/assembly/bihar</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/elections/assembly/bihar/constituency-list</t>
+  </si>
+  <si>
+    <t>New, clear Tejas jet crash video suggests pilot tried to eject last minute</t>
+  </si>
+  <si>
+    <t>A new video of the crash of the ill-fated Indian Air Force's Tejas fighter jet in Dubai provides a crystal clear view of the final moments of the pilot. As per the clip, posted by WL Tan's Aviation Videos, the pilot, Wing Commander Namansh Syal, likely attempted to eject at the last moment, but he neither had the time nor the elevation as the jet slammed into the ground. The Tejas jet was executing a low-altitude aerobatic manoeuvre when it went down at the Dubai Airshow, erupting into a massive fireball as soon as it thudded to the ground. Several videos on social media showed large plumes of black smoke emanating from the crash site. The IAF pilot, Wing Commander Namansh Syal, who is from Himachal Pradesh, died in the accident. TRACING TEJAS JET'S FINAL MOMENTS The new video gives a clear picture of what transpired in the final seconds. At the 49-52 second timestamp, just as the aircraft erupts into flames, a parachute-like object is visible. It suggests that the pilot tried to eject, but it was too late. It could have been due to the pilot attempting to regain control and save the aircraft, which has a near-spotless safety record. In fact, this was the first fatality linked to the Tejas, India's first home-grown lightweight multi-role fighter jet, in its 10 years of service. A Tejas crashed near Jaisalmer in March last year. However, the pilot had managed to eject safely then. The new video, supposedly captured by a spectator at the air show, shows the Tejas jet performing a manoeuvre known as a barrel roll, in which the jet turns over and then back up again. Just before going down, the jet was executing a negative-G turn. However, at this moment, the jet was flying at a very low altitude.
+Firefighters work at the site of a crash involving an Indian-made HAL Tejas fighter jet The jet went lower and lower before crashing to the ground. Aviation experts said there was no room for a post-loop manoeuvre to stabilise the fighter jet to gain altitude. However, the exact reason behind the crash will be known after an inquiry. The IAF has constituted a court of inquiry to ascertain the cause of the tragedy. Wing Commander Syal, 37, a resident of Kangra in Himachal Pradesh, will be cremated on Sunday. His wife is a retired wing commander. The couple has a seven-year-old daughter.- EndsPublished By: Abhishek DePublished On: Nov 22, 2025Must Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/india/story/tejas-fighter-jet-crash-new-video-last-moments-pilot-ejection-attempt-2824338-2025-11-22</t>
+  </si>
+  <si>
+    <t>Extensive misinformation: French Navy torpedoes Pak media's Rafale losses claim</t>
+  </si>
+  <si>
+    <t>The French Navy on Sunday strongly refuted claims made by Pakistani media that a French commander had confirmed Pakistan’s air superiority over India during the May 2025 conflict and the loss of Rafale jets. The Navy called the reports "extensive misinformation". Pakistan’s Geo TV had published an article claiming that French commander Captain Jaquis Launay had confirmed Pakistan’s dominance in the aerial engagement during Operation Sindoor. It also claimed that the Pakistan Air Force was "better prepared" and that the Rafale fighter was downed not because of the technological superiority of the Chinese J-10C fighters. Refuting the claim, the French Navy termed it “fake news,” saying, “These statements were attributed to Captain Launay who never gave his consent for any form of publication. The article contains extensive misinformation and disinformation”. The development drew sharp criticism online, with many condemning what they described as anti-India propaganda in the Pakistani media. BJP leader Amit Malviya highlighted the incident as evidence of Pakistan’s “desperate misinformation machinery”. “The French Navy has called out Pakistan’s Geo TV and its correspondent Hamid Mir for spreading “misinformation and disinformation.” In his report, Hamid Mir peddled the same old, fabricated claims about Rafales and the so-called May conflict and has now been publicly exposed. When official institutions start debunking their propaganda, you know how desperate Pakistan’s misinformation machinery has become,” he wrote. Several others also criticised the Pakistani media along similar lines, alleging that it has a history of spreading misinformation and making unfounded claims against India. "Pakistan whole existence is based on validation from their Western Masters," an X user, who goes by the name Argha, said. In May, India launched a swift military operation against Pakistan, codenamed Operation Sindoor, in response to the Pahalgam terror attack that claimed 26 innocent lives. The operation dealt a significant blow to the Pakistani army and resulted in casualties, before both sides agreed to a ceasefire at Islamabad’s request.- EndsPublished By: Ajmal Published On: Nov 23, 2025Must Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/world/story/french-navy-refutes-pakistan-air-superiority-claims-may-2025-conflict-2824666-2025-11-23</t>
+  </si>
+  <si>
+    <t>Smriti Mandhana–Palash Muchhal wedding postponed after cricketer's father falls ill</t>
+  </si>
+  <si>
+    <t>The wedding of Indian cricket star Smriti Mandhana and music composer Palash Muchhal has been postponed indefinitely after the cricketer’s father was rushed to a hospital in Sangli due to illness. The ceremony was scheduled to take place in her hometown in Maharashtra on Sunday, November 23. According to Mandhana’s manager, the cricketer made it clear that she did not wish to proceed with the wedding in the midst of a medical emergency involving her family. “Smriti Mandhana’s father was not feeling well since this morning. He was rushed to a hospital in Sangli, and he is currently under observation while various tests are being conducted,” Mandhana’s manager, Tuhin Mishra, told India Today. “Mandhana was very clear that in these circumstances she did not want to get married, which is why the decision has been taken to postpone the wedding indefinitely,” he added. Mandhana and Muchhal were set to tie the knot on Sunday, November 23 in a private ceremony. The celebrations had already been underway for the past couple of days, featuring traditional rituals such as Mehendi, Haldi, and Sangeet, which had built up excitement ahead of the main event. Adding a playful twist, the couple had also organised a friendly Bride Team vs Groom Team cricket match, bringing laughter and cheer to the guests. Several of Smriti’s teammates, including Jemimah Rodrigues, Radha Yadav, Shafali Verma, Arundhati Reddy, Shivali Shinde, and Richa Ghosh, were present to celebrate the occasion. A video of Mandhana dancing joyfully with her teammates during the Haldi ceremony went viral, perfectly capturing the fun and festive spirit of the celebrations. Mandhana had announced her engagement to music composer Palash Muchhal with a lively Instagram reel, dancing with her India teammates to the iconic “Samjho Ho Hi Gaya” track from Lage Raho Munna Bhai (2006). The fun routine, featuring Jemimah, Shreyanka, Radha and Arundhati, doubled as a cheerful reveal of the big news. A day later, Palash shared a touching proposal video from Mumbai’s DY Patil Stadium — the same venue where India lifted the Women’s World Cup. Mandhana, blindfolded and guided to the centre of the pitch, was met with a surprise as Palash went down on one knee. The engagement came on the heels of Mandhana’s stellar World Cup campaign. She amassed 434 runs in nine innings at an average of 54.25 and a strike rate of 99.08, registering a century and two fifties. Her steady 45 off 58 in the final against South Africa provided the perfect platform for India’s championship-winning triumph.- EndsPublished By: Akshay RameshPublished On: Nov 23, 2025</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/sports/cricket/story/smriti-mandhana-wedding-postponed-father-unwell-palash-muchhal-2824709-2025-11-23</t>
+  </si>
+  <si>
+    <t>Home disadvantage? India bowlers toil as South Africa pile on 489 in Guwahati</t>
+  </si>
+  <si>
+    <t>While the cricket fraternity has been busy debating whether India’s batters have forgotten the art of playing spin, it appears the bowlers may have misplaced something too — the willingness to grind and work hard for wickets on pitches that aren’t home dustbowls. India paid the price for being timid and reactive, both with the ball and in their tactics, as South Africa piled on a commanding 489 in the first innings. IND v SA, 2nd Test Day 2 Highlights | Scorecard South Africa made the Indian bowlers toil for 151.1 overs — nearly ten overs longer than the entire first Ashes Test in Perth. All-rounder Senuran Muthusamy, 31, struck his maiden Test hundred, while lower-order batter Marco Jansen smashed a career-best 93. The last four South African wickets added a massive 242 runs, as Muthusamy and Jansen forced India’s bowlers to work relentlessly throughout Day 2. India had the visitors at 247 for 6 at stumps on Day 1, but they squandered the chance to wrap up the innings and allowed the lower order to do far more than just wag its tail. Under pressure after losing the opening Test in Kolkata last week, India are now staring at another uphill climb. Having let South Africa bat for nearly two full days, the hosts are up against a daunting first-innings total on a pitch expected to deteriorate. Time, too, may not be on their side. To push for a result, India must bat with urgency; South Africa, 1–0 up, will happily take a draw to seal the series. Kuldeep Yadav was the pick of India’s bowlers, claiming four wickets with his left-arm wrist-spin. Ravindra Jadeja took two but looked far from threatening on a surface that demanded proactiveness and patience from both bowlers and on-field decision-makers. Washington Sundar, who enjoyed a purple patch on spinner-friendly pitches earlier in the series, looked ordinary in Guwahati. With sixth bowler Nitish Kumar Reddy bowling only six overs and the spinners failing to pose the sort of threat they did in Kolkata, Jasprit Bumrah and Mohammed Siraj were left to shoulder the burden. The pace duo bent their backs through a gruelling 62 overs in the first innings — a workload India would have hoped to avoid.- EndsPublished By: Akshay RameshPublished On: Nov 23, 2025Tune InMust Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/sports/cricket/story/india-vs-south-africa-2nd-test-day-2-score-senuran-jansen-bowlers-2824711-2025-11-23</t>
+  </si>
+  <si>
+    <t>Polls were rigged, but have no proof: Prashant Kishor opens up on Bihar rout</t>
+  </si>
+  <si>
+    <t>Jan Suraaj founder and former poll strategist Prashant Kishor on Sunday broke his silence after his newly formed political party drew a blank in the Bihar Assembly elections, claiming that the polls were 'rigged', though he admitted he has no proof to back the charge at this stage. Kishor, whose party contested statewide for the first time, said the defeat was 'crushing' but insisted his campaign had traction on the ground. He claimed the voting trends did not match the feedback his team gathered during the months-long Jan Suraaj yatra, adding that he believed "something went wrong". "There were some invisible powers at play. Parties that people barely knew ended up with lakhs of votes. Some people are asking me to raise my voice and say the EVMs were manipulated. This is something people allege after losing. I have no proof. But many things don't add up. Prima facie, it appears something went wrong, but we don't know what," Kishor said while speaking to India Today TV's Managing Editor Preeti Choudhry. #Exclusive | Jan Suraaj Party chief @PrashantKishor hints at EVM manipulation, says "...wo dikh raha hai kuch toh hua hai. Kya hua hain wo hume pata nahi hai, lekin ye add nahi ho raha." #PrashantKishor #BiharElections2025 @PreetiChoudhry pic.twitter.com/656AuWTGTx— IndiaToday (@IndiaToday) November 23, 2025 Furthermore, the Jan Suraaj founder also accused the National Democratic Alliance (NDA) of distributing money to thousands of women voters in Bihar to manipulate the election outcome. "From the day the election was announced till voting day, women were handed ten thousand rupees. Even that amount wasn't enough for what they were being promised. They were told they would receive two lakh rupees in total, and this ten thousand was just the first instalment. If they went and voted for the NDA, for Nitish Kumar, they would get the rest. In Bihar, or anywhere in the country, I don't recall a government ever handing out money like this to 50,000 women," Kishor said. #Exclusive | @PrashantKishor opens up on Jan Suraaj’s loss, pointing to three major reasons behind the setback in Bihar Elections.#BiharPolls #PrashantKishor @PreetiChoudhry pic.twitter.com/XftlVh8DIN— IndiaToday (@IndiaToday) November 23, 2025 Another factor that worked heavily against Jan Suraaj was the fear of the return of Lalu's Jungle Raj. "By the final phase of the campaign, many voters assumed Jan Suraaj wasn't in a position to win. Their worry was simple: if they voted for us and we didn't make it, it might somehow pave the way for Lalu's jungle raj to return. That fear definitely drove some people away," he said. He also dismissed commentary that his political career was over. When asked about critics writing his obituary, Kishor shot back: "These are the same people who applauded when I was winning. If they're writing my obituary, it's not about them. It's about what I do next. If I succeed, they will clap again. They are doing their job and I am doing mine. The ones criticising me are the most curious about me. That only shows I am not dead yet. Abhi kahani baki hai [the story is far from over]". "I am not dead yet, the story is still left" - @PrashantKishor on his political critics.#BiharPolls #PrashantKishor @PreetiChoudhry pic.twitter.com/0w1oZedfAF— IndiaToday (@IndiaToday) November 23, 2025 The Jan Suraaj Party, which threw its weight behind 238 of 243 seats in Bihar elections, scored a zilch. It did not win a single constituency and, by its own early estimates, managed only about 2 to 3 per cent of the vote. Most of its candidates lost their deposits.- EndsPublished By: Sahil SinhaPublished On: Nov 23, 2025Tune InMust Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/india/story/prashant-kishor-bihar-election-defeat-jan-suraaj-evm-manipulation-nda-nitish-kumar-2824599-2025-11-23</t>
+  </si>
+  <si>
+    <t>How Tata Projects is tapping AI to build, deliver projects faster</t>
+  </si>
+  <si>
+    <t>Tata Projects Ltd (TPL), an engineering, procurement and construction company, is using artificial intelligence (AI), robotics and automation not as pilots but productivity tools across projects to execute work faster, safer and more predictably, says Vinayak Pai, managing director and CEO, Tata Projects. One such use is AI-enabled planning and scheduling. The Integrated Construction Management Platform is used for project controls, quality, safety and tracking of progress. It also generates optimised work sequences that cut planning time and significantly reduce schedule deviations. IoT (Internet of Things) and sensor-based systems are deployed across sites for asset and equipment monitoring. They enable real-time tracking of concrete strength, equipment health, fuel usage and manpower productivity, leading to data-backed decision-making on site. AI-enabled surveillance cameras are also used to monitor compliance across projects, track safety issues to identify training needs, and support equipment tracking to improve productivity. LiDAR (light detection and ranging) technology is used to measure distances and create detailed 3D maps of the project environment. This helps conduct quality checks during construction and create as-built models post-construction. LiDAR-based drones are also used for topographic surveys and bi-weekly site monitoring to accelerate work while improving safety. Tools like construction twins and 4D/5D BIM (Building Information Modelling) help visualise the project in a virtual environment, detect clashes early, and streamline procurement and execution. This, Pai says, leads to a significant reduction in rework due to early detection of design and execution issues. “This robust digital ecosystem integrates field execution, workflows and analytics, giving us visibility across all project stages,” says Pai. These technologies have helped achieve a 10-15 per cent reduction in execution timelines through digital planning and clash-free engineering. “We have also seen a 20-25 per cent improvement in productivity in activities where AI and automation are deployed,” he says. There are also cost savings of 5-8 per cent through better material control and predictive maintenance. Currently, the company is exploring the use of generative AI for design automation and faster engineering turnaround, and AR/VR (Augmented Reality/Virtual Reality) solutions for remote inspections, immersive training and real-time design-field alignment. To build these new capabilities, TPL has set up a Digital Capability Academy that is upskilling engineers, planners, supervisors and site managers in areas such as BIM, data analytics, drone operations, Industrial Internet of Things (IioT) and AI-based tools. It also runs the Skill Shakti, Nirman Nayak and Kaushal Nayak programmes in partnership with the Construction Industry Development Council (CIDC) and Kalinga University to train and upskill frontline workers. Subscribe to India Today Magazine</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/india-today-insight/story/how-tata-projects-is-tapping-ai-to-build-deliver-projects-faster-2821851-2025-11-20</t>
+  </si>
+  <si>
+    <t>Smriti Irani on bagging Kyunki: Ekta saw me at office reception, cast me as Tulsi</t>
+  </si>
+  <si>
+    <t>Actor-politician Smriti Irani took a stroll down memory lane and recalled the time when she bagged the role of Tulsi Virani in ‘Kyunki Saas Bhi Kabhi Bahu Thi.’ During her session ‘Kyunki Smriti Lekhak Bhi Hai’ at Sahitya Aajtak 2025 in New Delhi, the actor shared how fate, struggle, and persistence led her to one of Indian television’s most iconic roles. She revealed that she had gotten the role of an actor’s sister initially in the show, but when Ektaa Kapoor saw her, she tore her contract and offered her ‘Kyunki’. “Before I got Kyunki, I had actually gone to play another actor’s sister. I had borrowed money from my father, and the deal was that if I couldn’t return it, I would have to marry wherever he decided. So I was already stressed and fighting my own battles.” Smriti added, “While I was at the office with my contract, Ektaa Kapoor saw me at the reception and said, ‘Oh, you’re Tulsi,’ and then tore up my contract. At that moment, I wondered how someone could just take away my job like that.” The next day was tougher. “When I went to the office, the guard didn’t even let me in. I told him I was an actor, and he said, ‘You don’t look like one.’ Somehow, I managed to get in, but when they made me audition again, I failed. Still, Ektaa was adamant that she wanted me as Tulsi.” “Ektaa told me that this role is not a glamorous one. She explained that when Tulsi cries, her whole face will distort. She’ll endure everything in her relationships with sincerity. That’s the kind of woman she is.” Listening to the character sketch, Smriti agreed, “When she narrated the character, it was exactly what I had said. That’s when I agreed.” 'Kyuki Saas Bhi Kabhi Bahu Thi reboot' premiered earlier in August on Star Plus and has already made a strong impact on the ratings chart. Within just one week of its debut, the show clocked a TRP of 2.3, with its opening episode peaking at 2.5. In doing so, it outperformed several long-standing favourites, including 'Taarak Mehta Ka Ooltah Chashmah' and 'Anupamaa'. The original show, which first aired in 2000, was a cultural phenomenon, and the decision to revive it with key cast members and the same production team has clearly resonated with audiences. As viewership numbers suggest, the legacy of Tulsi and Mihir continues to hold strong, even 25 years later.- EndsPublished By: Prachi aryaPublished On: Nov 23, 2025ALSO READ  |  25 years later, Smriti Irani and Amar Upadhyay relive their iconic Kyunki sceneMust Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/entertainment/television/story/ektaa-kapoor-saw-me-at-office-reception-cast-me-as-tulsi-smriti-irani-bagging-kyunki-saas-bhi-kabhi-bahu-thi-2824654-2025-11-23</t>
+  </si>
+  <si>
+    <t>Mazak bana rakha hai? Rishabh Pant loses cool on Kuldeep Yadav in Guwahati Test</t>
+  </si>
+  <si>
+    <t>Stand-in India captain Rishabh Pant cut a frustrated figure on the morning of Day 2 of the second Test against South Africa in Guwahati, losing his cool at teammate Kuldeep Yadav after the side was issued a second warning for delaying the start of an over. Pant, already carrying a first warning from Day 1, was pulled up again by umpire Richard Kettleborough during the 88th over for breaching the 60-second rule. With the clock running down and the umpire’s patience wearing thin, Pant turned his frustration towards Kuldeep and urged the left-arm spinner to pick up the pace between overs. A few Indian players were seen jogging casually in the background, adding to the captain’s irritation. IND v SA, 2nd Test Day 2 Updates | Scorecard "Yaar, 30 seconds ka timer hai. Ghar pe khel rahe ho kya? Ek ball daal jaldi. (The timer is on. Are you playing at your home? Just bowl the ball quickly," Pant was heard as saying on the stump mic. "Yaar Kuldeep, dono baar warning le li (Kuldeep, we got the second warning).Pura ek over thodi na chahiye. Mazak bana rakha hai Test cricket ko (Do you guys need an entire over (to move)? You guys have made Test cricket a joke)," he added. The outburst brought back memories of Rohit Sharma’s time as captain. The recently retired 38-year-old was known for keeping his players alert and disciplined through every passage of play, regardless of format. What's going to be a good score for #TeamIndia to chase in the 1st innings? #CheteshwarPujara backs the batters to score big in Guwahati! #INDvSA 2nd Test, Day 2 LIVE NOW  https://t.co/J8u4bmcZud pic.twitter.com/vGjwWPopSm— Star Sports (@StarSportsIndia) November 23, 2025 Earlier this year, the ICC introduced a stop-clock rule for Tests, requiring the fielding side to begin the next over within one minute of the previous one finishing. Teams are given two warnings; from the third offence onwards, the batting side receives five penalty runs for every breach. The count resets after every 80 overs. The regulation has already been in use in ODIs and T20Is since June 2024.SA IN CONTROL OF 2ND TEST While India were preoccupied with overrate pressure, South Africa continued to dictate terms. Senuran Muthusamy and Marco Jansen put together the highest partnership of the series, an unbeaten 94 off just 16.3 overs. Jansen set the tone with a no-look six, and Muthusamy matched him with intent, eventually raising his maiden Test hundred. By lunch on Day 2, South Africa had moved to an imposing 428/7, with Muthusamy on 107* and Jansen on 51*. Earlier, the visitors lost only one wicket in the opening session, Kyle Verreynne, stumped for 45, but India’s bowling attack struggled to maintain intensity. The overnight pair had started cautiously, punishing only the loose deliveries and steadily extending the lead. India remains in the contest, but the path to a comeback is narrowing. They need the remaining wickets quickly to keep South Africa from inching towards a rare Test series win on Indian soil.- EndsPublished By: Saurabh KumarPublished On: Nov 23, 2025Read More |  Passive? Rishabh Pant's captaincy questioned after wicketless session in Guwahati TestMust Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/sports/cricket/story/rishabh-pant-frustration-kuldeep-warning-india-vs-south-africa-2nd-test-2824657-2025-11-23</t>
+  </si>
+  <si>
+    <t>Lost in translation: Indian techie terrified after Uber driver's message misreads as threat</t>
+  </si>
+  <si>
+    <t>An Indian techie’s ordinary morning ride turned into an adrenaline rush he never saw coming when a mistranslated Uber driver's message convinced him that his driver was facing a “threat of murder.” X user Arnav Gupta began his post by explaining how he had booked a cab and asked the driver to wait for a couple of minutes as he stepped out of his house. “Today I made my Uber driver wait for 2 minutes as I was getting out of my house,” he wrote. But what followed left him frozen. According to him, he suddenly received an eerie notification from the Uber app that read: “I am facing the threat of murder.” He described the moment in detail, writing, “A chill ran down my spine. It is Delhi after all. Anything can happen.” In that split second, dozens of alarming possibilities rushed through his head. Was the driver threatening him because he made him wait? Was the man in danger from someone nearby on the road? Was he indirectly warning him? The techie wrote that he was “sweating, with trembling fingers,” when he rushed to open the app to check for more context. But to his surprise, the chat contained nothing more, but just the earlier message where the driver had politely replied “OK” when asked to wait. “Exactly 2 minutes later when the requested period was over, he dropped this message,” he said, still processing the sequence of events. And then came the twist. While staring at the message in confusion and fear, the techie noticed something important: the sentence had been auto-translated by Google. Curious and terrified at once, he clicked “See original.” That’s when the real truth came out. The original message from the driver had simply said that he was “in front of Mother Dairy," which was a completely harmless update about his location. The accompanying screenshot showed the driver's original message, reading, "Murder deri ke saamne hu." Gupta described the relief he felt in dramatic detail: “I heaved the biggest sigh of relief in a long, long time." Check out the translated message Gupta received here: Check out the original message here: The internet was left in fits of laughter and confusion over the story, which prompted a wave of memes about auto-translated chaos and the wild unpredictability of Delhi daily life. Several users commented that they would have fainted on the spot, while others joked that translation apps could cause faster heart attacks than horror movies.- EndsPublished By: Yashna TalwarPublished On: Nov 22, 2025</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/trending-news/story/lost-in-translation-indian-techie-terrified-after-uber-drivers-message-misreads-as-threat-2824315-2025-11-22</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy S25 gets Rs 11,000 discount: Should you buy it?</t>
+  </si>
+  <si>
+    <t>If you’ve been eyeing Samsung’s latest flagship but couldn’t quite justify the price tag, this might be your moment. The Samsung Galaxy S25 has just received a significant price cut on Flipkart, making one of 2025’s most powerful Android phones far more tempting. Launched earlier this year at Rs 80,999, the phone can now be yours for as low as Rs 69,999, thanks to a mix of bank discounts, exchange offers, and combo deals. For those who’ve been waiting to upgrade, this could be the best deal Samsung has offered so far, and with the kind of performance the S25 packs, it’s one worth paying attention to.Samsung Galaxy S25 price drop The Galaxy S25 is currently available on Flipkart with a Rs 10,000 instant discount for HDFC Bank credit card users, effectively dropping the price to Rs 70,999. That alone is a solid deal for a phone that’s only been on the market for a few months. But the real fun starts when you add in the exchange offer. If you’re trading in an older smartphone, Samsung is offering an extra Rs 11,000 off on top of your device’s exchange value. While the previous bank discount doesn’t stack with this deal, you can still add a Rs 2,095 discount with the Flipkart Axis Credit Card.Here’s how the math works out. If you exchange, say, an iPhone 13, you’d qualify for the Rs 11,000 exchange bonus, your old phone’s trade-in value, and that Rs 2,095 card discount, bringing the price down significantly.There’s also another ongoing Flipkart promotion called “Buy more, save more.” Under this, if your combined cart value exceeds Rs 15,000, you can save an additional Rs 6,000. Combine all these offers, and you could potentially take home the Galaxy S25 for as little as Rs 39,794. Yes, you read that right, a flagship Samsung phone for under 40,000, provided you stack the right offers.Samsung Galaxy S25: Should you buy? Here’s how the math works out. If you exchange, say, an iPhone 13, you’d qualify for the Rs 11,000 exchange bonus, your old phone’s trade-in value, and that Rs 2,095 card discount, bringing the price down significantly. There’s also another ongoing Flipkart promotion called “Buy more, save more.” Under this, if your combined cart value exceeds Rs 15,000, you can save an additional Rs 6,000. Combine all these offers, and you could potentially take home the Galaxy S25 for as little as Rs 39,794. Yes, you read that right, a flagship Samsung phone for under 40,000, provided you stack the right offers.Samsung Galaxy S25: Should you buy? In short: yes, and here’s why. The Galaxy S25 is powered by the latest Snapdragon 8 Elite processor, offering a noticeable boost in speed and efficiency compared with last year’s model. The performance difference is especially clear when compared to the Exynos 2400 chip inside the Galaxy S24. The new chip, combined with a 15 per cent larger vapour chamber cooling system, means the S25 runs cooler, faster, and smoother, whether you’re gaming, multitasking, or shooting 4K videos. Samsung has also made 12GB RAM the new standard across the entire S25 lineup, a big jump from the 8GB found in the S24. That extra memory makes multitasking feel effortless. You can juggle apps, games, and heavy editing tasks without reloads or stutters. It even improves camera processing and system stability, ensuring your phone stays snappy for years. Speaking of cameras, while the hardware may look familiar, the new image signal processor (ISP) takes photo quality up a notch. Images are sharper, with more natural skin tones and better colour balance. Samsung has refined the camera experience further with smoother lens switching in video mode and a redesigned zoom slider. Pro users will love the upgrades to Expert RAW, which now adds tools like exposure monitoring, ND filter strength adjustment, and virtual aperture control for dynamic background blur. You can see the photo sample in our review. Design-wise, Samsung hasn’t reinvented the wheel, but it’s certainly refined it. The Galaxy S25 is thinner at 7.2mm (down from 7.6mm on the S24) and comes in fresh colours like Navy and Icy Blue, both sporting sleek black camera rings. It feels more ergonomic and premium in hand, while the reduced bezels make the display even more immersive. The only mild disappointment is the 4,000mAh battery, unchanged from the S24. However, the improved efficiency of the Snapdragon 8 Elite helps squeeze out better endurance. You can comfortably get a full day of use on a single charge, even with heavy tasks. Still, if you crave multi-day battery life, you might want to consider one of the larger S25 models. With its upgraded processor, extra RAM, refined cameras, and sleeker design, the Samsung Galaxy S25 already stands out as one of the most complete Android phones this year. But now, with Flipkart’s discount avalanche, it’s also one of the best deals around. If you’ve been waiting for the right moment to upgrade, this is it.- EndsPublished By: Unnati GusainPublished On: Nov 23, 2025Must Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/technology/news/story/samsung-galaxy-s25-gets-rs-11000-discount-should-you-buy-it-2824632-2025-11-23?utm_source=hp_lead&amp;utm_medium=it_web</t>
+  </si>
+  <si>
+    <t>Who is Senuran Muthusamy? Indian-origin star hits maiden Test hundred in Guwahati</t>
+  </si>
+  <si>
+    <t>Senuran Muthusamy produced the finest knock of his Test career, raising a gritty maiden hundred to put South Africa in firm control and leave India searching for answers on Day 2 of the second Test in Guwahati. Playing just his eighth Test, Muthusamy brought up the landmark in 192 balls. His previous best was an unbeaten 89 against Pakistan earlier this year. Resuming with patience and discipline, the overnight pair of Muthusamy and Kyle Verreynne adopted a cautious, Bavuma-like approach through the morning session, refusing to flirt with anything outside their scoring zones and cashing in only on the loose deliveries. Muthusamy brought up his half-century off 121 balls before shifting gears with calculated aggression, anchoring the innings with remarkable composure. Though India finally broke through after Tea when Verreynne was stumped for a hard-earned 45 off 122 balls, the dismissal did little to slow South Africa's charge. IND v SA, 2nd Test Day 2 Updates | Scorecard Muthusamy found an ideal partner in Marco Jansen, and together the pair continued to frustrate the hosts, stitching a crucial stand and driving the visitors past the 400-run mark. By the end of the second session, South Africa had seized full control of the contest, thanks largely to Muthusamy's milestone knock and his unflappable temperament under pressure.WHO IS SENURAN MUTHUSAMY?Senuran Muthusamy was born on 22 February 1994 in Durban, Natal Province, South Africa, to parents of Indian origin. He maintains a strong connection to his Tamil heritage, with members of his extended family still residing in Nagapattinam, Tamil Nadu.Educated at Clifton College, Muthusamy later pursued a bachelor's degree in social science from the University of KwaZulu-Natal, specialising in media and marketing. His cricketing journey began early in Durban, where he quickly stood out in school matches and local tournaments. Senuran Muthusamy was born on 22 February 1994 in Durban, Natal Province, South Africa, to parents of Indian origin. He maintains a strong connection to his Tamil heritage, with members of his extended family still residing in Nagapattinam, Tamil Nadu. Educated at Clifton College, Muthusamy later pursued a bachelor's degree in social science from the University of KwaZulu-Natal, specialising in media and marketing. His cricketing journey began early in Durban, where he quickly stood out in school matches and local tournaments. He represented KwaZulu-Natal from Under-11 through Under-19 level, though he initially hesitated to believe he could turn professional. His steady improvement eventually earned him a place in South Africa's Under-19 setup. In the 2015-16 season, he was signed by the Dolphins as a top-order batter. Despite smashing a career-best 181 against the Knights in January 2017, that role didn't last long. "His batting just dropped off a bit but his bowling went to another level," his former teammate Imraan Khan told ESPNcricinfo in 2019. That shift led Muthusamy to reinvent himself as a genuine all-rounder. His impressive returns with the ball earned him a maiden Test call-up for South Africa's 2019 tour of India, where he made his debut in Visakhapatnam. In that match, he claimed his first Test wicket by dismissing none other than Indian captain Virat Kohli, caught and bowled-a moment that hinted at his big-stage composure. Yet cementing a permanent place in the national side has been challenging, given South Africa's depth in spin bowling and the continued excellence of Keshav Maharaj. Still, Muthusamy has remained a persistent, quietly impactful presence in the setup.- EndsPublished By: Saurabh KumarPublished On: Nov 23, 2025Read More |  Passive? Rishabh Pant's captaincy questioned after wicketless session in Guwahati TestMust Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/sports/cricket/story/who-is-senuran-muthusamy-maiden-test-century-south-africa-control-india-2824643-2025-11-23?utm_source=hp_lead&amp;utm_medium=it_web</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/entertainment/television/story/ektaa-kapoor-saw-me-at-office-reception-cast-me-as-tulsi-smriti-irani-bagging-kyunki-saas-bhi-kabhi-bahu-thi-2824654-2025-11-23?utm_source=hp_lead&amp;utm_medium=it_web</t>
+  </si>
+  <si>
+    <t>India vs South Africa 2nd Test Day 2 Highlights: India see off tricky phase after South Africa post 489</t>
+  </si>
+  <si>
+    <t>Hello and welcome to the live coverage of Day 2 of the second Test between India and South Africa from Guwahati. Well the day is not over if you're an Indian cricket team fan. The selection meeting is taking place for the upcoming ODI and T20I series against the Proteas. With Shubman Gill and Shreyas Iyer out injured, it will be interesting to see who will take over the captaincy role for the team. Follow all the updates on the selection live blog RIGHT HERE! After a lot of complaining from the Indian bowlers and one delivery in the 7th over, umpires have had enough and ask the players to head back to the pavilion. India end the day with both their openers at the crease but with a mountain to climb to remain in the series. South Africa are in the driver's seat and they will be hoping for early wickets on Day 3 of the match. IND vs SA 2nd Test Day 2 Live Score: India (9/0 in 6.1 ov), trail by 480 runs. Jaiswal (7*), Rahul (2*) The floodlights are fully functional and at the moment, India are ready to recover and go at it on Day 3. Rahul has been defending well and the same with Jaiswal. The umpires are constantly checking the light at the end of each over, so we could see the end of play coming soon. IND vs SA 2nd Test Day 2 Live Score: India (9/0 in 5 ov), trail by 480 runs. Jaiswal (7*), Rahul (2*) While Jaiswal has looked to be positive with his intent, Rahul seems to be a bit nervy. He leaves a delivery from Jansen that almost takes the off-stump for a walk. The Indian opener needs to see off this period but has to be positive, possibly attack on Day 3. IND vs SA 2nd Test Day 2 Live Score: India (9/0 in 4 ov), trail by 480 runs. Jaiswal (7*), Rahul (2*) A positive start from Yashasvi Jaiswal in Guwahati. He starts with a double and then follows it up with a boundary off Jansen as India get off to a quick start in their first innings. The light meter is out as well as it has gotten darker in Guwahati. IND vs SA 2nd Test Day 2 Live Score: India (7/0 in 1 ov), trail by 482 runs. Jaiswal (7*), Rahul (0*) Marco Jansen misses out on a century by seven runs as he looks to attack Kuldeep Yadav and sees the stumps rattled. But that ends an entertaining knock from the all-rounder as he hit 7 sixes during this time and put on a strong stand with Muthusamy earlier in the day. South Africa are all out for 489 as Kuldeep takes four. But it was a hard day at the office for the Indian team as everyone was made to toil. They have half an hour left before stumps on Day 2 to get some runs on the board. We will have Jaiswal and Rahul at the crease shortly. Another bowling change comes in as Kuldeep Yadav comes into bowl with Marco Jansen closing in on his hundred. But Maharaj takes him on hits a boundary, much to the shock of everyone in the stadium. Pant keeps egging Kuldeep on but the crowd seems to be grim at the moment. 500 seems to be right around the corner and a couple of hits away for the Proteas. IND vs SA 2nd Test Day 2 Live Score: South Africa (488/9 in 150. ov). Jansen (93*), Maharaj (12*) Never thought this moment would come, but here is Nitish Kumar Reddy back into the bowling. Jansen gets into the 90s for the first time in his career but Nitish almost forces him to cut the ball onto the stumps. This seems to be the last roll of the dice from Pant as he can't trust the spinners against Jansen. IND vs SA 2nd Test Day 2 Live Score: South Africa (482/9 in 149 ov). Jansen (90*), Maharaj (8*) Mohammed Siraj is left fuming as Yashasvi Jaiswal doesn't get reach there to stop the ball from going to the boundary and Jansen goes past previous best of 86, which was also against India. South Africa will be hoping that the all-rounder will stay and they can get to the 500-run mark. IND vs SA 2nd Test Day 2 Live Score: South Africa (477/9 in 147 ov). Jansen (88*), Maharaj (5*) Fun stat: India have now bowled a total of 145 overs, which was more than the entire first Ashes Test, which came to an end in Perth on Saturday. While Australia and England enjoy a two-week break the Indian players are toiling it out in Guwahati as they hope to get some batting done. IND vs SA 2nd Test Day 2 Live Score: South Africa (468/9 in 145 ov). Jansen (82*), Maharaj (2*) When you need a wicket, better call Bumrah! The star pacer delivers an absolute peach to clean up Simon Harmer, who sees his stumps uprooted. This one squared up the spinner and knocked over his off stump. Keshav Maharaj is the final man in. IND vs SA 2nd Test Day 2 Live Score: South Africa (462/9 in 143.1 ov). Jansen (76*), Maharaj (0*) Jasprit Bumrah has been brought back into the attack and it must be due to Marco Jansen effect. Bumrah gets to bowl at Harmer and he has been targeting the stumps consistently. Harmer gets a lucky edge off the last ball for a double as India will aim to end the innings quickly. IND vs SA 2nd Test Day 2 Live Score: South Africa (458/8 in 142 ov). Jansen (76*), Harmer (3*) Marco Jansen is targeting Mohammed Siraj and is constantly looking for the big hits. He gets into the 70s with a big shot that goes to the boundary. He follows it up with another six as the crowd is silenced once again. That's his 7th six of the innings. IND vs SA 2nd Test Day 2 Live Score: South Africa (456/8 in 141 ov). Jansen (76*), Harmer (1*) Marco Jansen was in destructive mode before lunch and now with Muthusamy gone, he has decided to go into overdrive. He launches Jadeja for a couple of big hits as South Africa inch closer to 450. There isn't a lot of batting left and the all-rounder will be targeting to get his side close to 500. 13 comes off the Jadeja over. IND vs SA 2nd Test Day 2 Live Score: South Africa (444/8 in 140 ov). Jansen (65*), Harmer (0*) Finally, India got the big wicket of Senuran Muthusamy to end his stay at the crease. The first false shot from the southpaw in a long time as he holes out to Yashasvi Jaiswal. Muthusamy falls for 109 off 206 balls. IND vs SA 2nd Test Day 2 Live Score: South Africa (431/8 in 138.1 ov). Jansen (52*), Harmer (0*) The players walk out to the middle with India gathering quickly in a tight huddle, Rishabh Pant at the centre, animatedly driving home his message before they take their positions. As play resumes, the big question looms: how many more runs will South Africa add before contemplating a declaration? With 35 overs still left in the day, the visitors have ample time to push their advantage, while India will be desperate for early breakthroughs to keep the target within reach. At this point in time, India have their backs against the wall. Each day will only see 80 overs being bowled and South Africa still batting as we head into the final session. Steyn feels that India doesn't have an answer at the moment to get a wicket and that could become dangerous. "They have knocked the wind out of India's sails and they're looking for that killer punch. I don't know where it will come from. Who knows? Maybe Marco Jansen goes on to get 100. Muthusamy goes on to get 150, and that first innings lead is one that's too far where India can breach and get a first innings total lead when they bat." "South Africa can just take this game out of reach for India, where it leads into a draw or who knows, even skittle India for something trying to get that score and even record a second win, but right now the way that they're playing, it just looks like India don't have an answer in terms of trying to get another wicket and bowl South Africa out," said Steyn. What went wrong for India here? We keep asking this question as the plans seemed to be defensive from the start. Anil Kumble has slammed the strategy, saying the hosts panicked during the session and kept going back to being defensive. "These are good batting conditions. It's just that I thought in terms of their approach to having a strategy, having a plan in place, especially. The field sets and what you want to achieve on a wicket like this, I don't think India had that. India sort of panicked, and when they were desperate, that's when they looked to attack. Suddenly bring in fielders for a couple of overs and then again go back to their old self of saying, OK, let's push the fielders back. I think the plan of how to get a batter out when they first walk into the crease wasn't there. It was just saying, OK, we'll just continue to do the routine things. It's going to happen. It's going to happen. That didn't happen on the surface like this," said Kumble. 112 RUNS AND JUST ONE WICKET! South Africa are batting India out of the game at the moment as they head into lunch in full command. Muthusamy's hundred and Jansen's fifty deflated India's momentum after the Kyle Verreynne wicket. The partnership is 94 off 99 balls at the moment and the Indian team need to think hard and fast about their plans. IND vs SA 2nd Test Day 2 Live Score: South Africa (428/7 in 137 ov). Muthusamy (107*), Jansen (51*) A bowling change comes in the form of Washington Sundar and Jansen strolls to his fifty. This partnership has now made South Africa dream of getting to 500 as batting has become easier as the day has worn on. IND vs SA 2nd Test Day 2 Live Score: South Africa (423/7 in 135.3 ov). Muthusamy (105*), Jansen (50*)</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/sports/cricket/story/india-vs-south-africa-2nd-test-live-score-day-2-guwahati-updates-2824534-2025-11-23?utm_source=hp_lead&amp;utm_medium=it_web</t>
+  </si>
+  <si>
+    <t>Weekly horoscope from November 23 to November 29: Your luck for this week; see which signs have lady luck smiling for them</t>
+  </si>
+  <si>
+    <t>Aries (Mar 21 – Apr 19) A time for learning lessons from the past. Some patterns may begin to repeat themselves with a clear reason for you to learn from past mistakes. Look back on the times you were too hasty, or too trusting of others. Resolve to never let it happen again. In relationships you may no longer settle with “all talk and no action” from a special someone. Heart to heart conversations will help strengthen the bonds and make the other person aware of how their behaviour affects you. Stay in control of your emotions if you want to make headway in your personal relationships. Property matters may cause a little concern as you discover things are working out to be more expensive than you imagined. Be mindful of your dental health and be regular with your check ups. Taurus Apr 20- May 20) Too much analysis leads to paralysis. Overthinking may be causing you to miss opportunities or take a few necessary risks. Time to build your skill set if you haven’t already. Your work is valuable to the team, now work on being irreplaceable. You may be on the crossroads about making a few key decisions about your personal life. Trust your gut about someone or something and remember to go with that feeling. Some people may need you to be more compassionate and forgiving of them. If people owe you money, this a good week to follow up and remind them. A new source of income may come through networking or an old contact that could prove very lucrative in the long run.Gemini (May21- June 20)Money and work matters take the lead. Financial discussions, negotiations, bills, documents and contracts come into the fore. You may find yourself multi-tasking and handling 3 different projects at one go. And if you haven’t already, you may start dialogues with your bosses about a possible promotion or pay raise. Self employed Geminis may stretch themselves to get new business or promote their work. Your love life may be quiet but it doesn’t mean nothing is happening. Wait a bit till you truly feel like socialising. Quiet time spent in meditation and introspection brings answers. A good phase to restructure your budget and plan for your next big purchase. Gemini (May21- June 20) Money and work matters take the lead. Financial discussions, negotiations, bills, documents and contracts come into the fore. You may find yourself multi-tasking and handling 3 different projects at one go. And if you haven’t already, you may start dialogues with your bosses about a possible promotion or pay raise. Self employed Geminis may stretch themselves to get new business or promote their work. Your love life may be quiet but it doesn’t mean nothing is happening. Wait a bit till you truly feel like socialising. Quiet time spent in meditation and introspection brings answers. A good phase to restructure your budget and plan for your next big purchase. Cancer (June 21 – July 22) Your mind is sharp and people will listen to what you're saying. A good phase for promotions, presentations and anything to do with public speaking, the cards foretell success especially for students. Content creators, writers and even Cancerians in research and development have the potential to shine and achieve success in the coming few months. Personal relationships are a different challenge. You may have realised that you can no longer expect anything from a few souls who are truly on their own trip. Let go of the need to be heard by them and do your own thing for now. Acts of charity bring good karma your way. You may get a pleasant surprise in money matters. Leo (July 23- Aug 22) Stay positive even if you have to force yourself. Don't allow the obstacles and challenges to dishearten you. Someone may be acting difficult at the workplace. Or you could discover the true face of someone you thought was an ally. Just keep going and don’t dwell on their negativity. Family and home bring a sense of refuge as you retreat for some much needed peace. There may be family discussions and even a decision to be made about a family elder. Joy and solace comes from old childhood friends, and if single, you may decide to stop looking actively and allow whoever is meant to be, to come looking for you. Businesses and financial matters slowly pick up pace and you may consider outsourcing or hiring new people. Health matters reveal a need to be more mindful about your diet. Virgo (Aug 23- Sept 22) Learn to let go. Your mind may be making things worse than they really are. Whatever you are worried about isn't as bad as you fear. A nagging sense of anxiety needs to be released. Surround yourself with positive influences. Don't expect your loved ones to read your mind or mood, and extra effort would need to be made to be patient with them. Children can get annoying but you will need to stay extra calm with them in this period. Money that was owed to you will be returned, and negotiations will proceed smoothly. But you will need to find ways to consciously de-stress and relax your mind. Talking with a trusted friend will help but taking charge of your wellbeing will help you even more. Libra (Sept 23- Oct 22) What happened, happened. Time to leave the past behind and start a new chapter in your life. Those who hurt you will face their karma, you do not need to do anything about it. Relook your life and your daily habits and see what needs changing. You are being given an opportunity by the Universe to recreate your life. Even at home, you may feel like the need for change. Declutter, reorganise and redecorate if you need to. Start connecting with a new set of people. Elders in the family may come for a visit or choose to stay with married couples. Health matters show a strong need to detox and let go of the old. In terms of finances, you begin to restructure your portfolio or embark on a new saving plan. Scorpio (Oct 23- Nov21) You’ve earned your stripes. And your reputation ensures doors open for you. Scorpions in business can look forward to a phase of expansion and alliances. You may partner with an ex colleague. And there may be work related travel ahead. Family and home may take a back seat as you focus on your ambitions. A part of you is keen to build wealth and your childrens’ future. An old friend may reach out for a favour. Documents and valuables that went missing will be found. Just watch out for seasonal allergies and make sure you get enough sleep to keep your battery running during the busy phase. Saggitarius (Nov 22- Dec) Your creativity shines, so give it all you’ve got. Your audience and influence grows. And there may be some interesting job offers coming your way. You may have accepted an important new position or, if you’re self-employed, agreed to launch a new venture for your current business. Be a little more budget conscious in the weeks ahead, keep track of your expenses and be extra careful during online transactions. In matters of the heart, you may decide to help a close friend who is going through a hard time. Conversations with old friends bring solace and peace. Plans may be finalised for a family holiday or a get together. Just watch out for sleepless binges, and consider doing some breathwork for the overactive mind. Capricorn (Dec 22-Jan19) Stay firm even in the face of obstacles. Someone may be pressuring you to accept an offer or sign a contract and if you don’t feel comfortable with it, ask for time. Important dialogues with seniors will help lay the ground for your future growth and success. If single, step back a little and don’t be the one who always initiates things. Allow the other person to reach out. Even in personal relationships, you may decide to stop giving so much to the taker and choose to keep a polite distance. A good phase to channel your energies towards health and fitness. Sign up for classes. Join a gym. Go outdoors more. Money matters show a sense of security but also some large expenses coming up. Aquarius (Jan 20- Feb 18) Teamwork will benefit you. The more you share, the better you feel and the higher the chances of success for all of you. You may take on the role of a mentor, leading young recruits. Or organise a workshop that will benefit everyone. Aquarians in the field of education and research can expect growth in the coming few months. Your love life may feel boring or too quiet for your liking. How about throwing a party? Or going on a group trip somewhere. A part of you is craving company and excitement but if you don’t do anything about it, nothings going to happen. Money matters sees you contributing to a cause you believe in or a needy person, which will bring blessings your way. Health matters look good, use the bursts of energy to get things done. Pisces (Feb 19-Mar 20) As you become more self aware, your confidence begins to grow. Pay attention to any patterns in your life that may be repeating. Learning a new skill or subject may feel difficult at first but once you get the hang of things you will wish you’d started earlier. You're capable of so much more than you realize, so don't hold yourself back. Learn what you're truly capable of. Relationships improve as you open up more and share your time and energy with like minded souls. Friends made in this phase can be with you for the long term. Listen to the advice of your mother, deep down you know she’s right. Health matters look better as you begin to get more mindful of what you eat and drink. Just be a little more careful with your budgets.- EndsPublished By: Ayush BishtPublished On: Nov 22, 2025</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/horoscopes/story/weekly-horoscope-november-23-to-november-29-your-luck-for-this-week-which-signs-have-lady-luck-smiling-2824288-2025-11-22?utm_source=hp_lead&amp;utm_medium=it_web</t>
+  </si>
+  <si>
+    <t>Mother, kids killed in sleep at Jharkhand home; father found dead in field</t>
+  </si>
+  <si>
+    <t>In a chilling incident, four members of a family were found murdered in Jharkhand's Dumka early on Sunday morning. The bodies of a couple and their two young children were discovered in and around their home, triggering panic across the area and a massive police response. According to initial findings, 24-year-old Aarti Kumari and her two children, four-year-old Rohi and two-year-old Viraj, were attacked with a sharp weapon while they were asleep inside their house. Her husband, 30-year-old Birendra Manjhi, was found dead nearly 500 metres away in a field, raising suspicion that he may have been chased or dragged out before being killed. Early in the morning, villagers heading out for daily chores spotted the bodies and raised an alarm, plunging the entire area into fear and confusion. Soon after, Hansdiha police reached the village and cordoned off the crime scene. Given the brutality of the killings and the lack of immediate clues, police have roped in a dog squad and a forensic team to scan the home, the field and the route between the two spots. Officers say every angle, from personal enmity to property dispute or external assault, is being examined. The family’s elderly father, Manoj Manjhi, who lives nearby, has been assisting police with information. Birendra and Aarti had been married for six years. Dumka Superintendent of Police Pitambar Singh Kherwar said the recovery of four bodies from a single family has “shocked the entire district,” adding that a comprehensive investigation is underway and teams have been deployed to gather evidence and speak to villagers.- EndsPublished By: Sonali VermaPublished On: Nov 23, 2025</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/india/story/mother-kids-killed-in-sleep-at-jharkhand-home-father-found-dead-in-field-2824707-2025-11-23</t>
+  </si>
+  <si>
+    <t>IndiaToday_Chandigarh_Crawler</t>
+  </si>
+  <si>
+    <t>Centre cancels notification to dissolve Panjab University Senate amid protests</t>
+  </si>
+  <si>
+    <t>After a week-long protest and hunger strike by the students at Panjab University, the central government on Wednesday revoked its decision to dissolve the 59-year-old Senate, the university's highest decision-making body. A week ago, the government decided to restructure the top decision-making body from an elected body to a fully-nominated body through the amended Panjab University Act, 1947 (East Punjab Act 7 of 1947). The new amendments were made to abolish the Graduate Constituency, reduce the Senate’s strength from 90 to 31 members, and significantly alter its composition — with 18 elected, six nominated, and seven ex officio members. It also marked the inclusion of the Chandigarh MP, UT Chief Secretary, and Education Secretary as ex officio members, alongside senior Punjab officials, for the first time since its inception. The Ordinary Fellows category was redefined with a maximum of 24 members, including professors, associate professors, college principals, Punjab MLAs, and distinguished personalities nominated by the Chancellor. Overall, the syndicate was restructured into a high-powered body led by the Vice-Chancellor and senior representatives from the Centre, Punjab, and Chandigarh. It was given the power to delegate executive functions to the VC or subcommittees. As the government has now revoked the decision, it suggests that the authoritative body will not be restructured and will operate in the way it has been operating since its inception. The decision triggered widespread outrage across the university. The student bodies started protesting as soon as the decision was announced, and Abhishek Dagar, the general secretary of Panjab University Student Council (PUCSC), started a hunger strike to protest against the decision and has not called it off even after a week. Earlier this week, the representatives of PUCSC met with Vice Chancellor Renu Vig, and the minutes of the meeting suggested that the University authority would withdraw its affidavit from the Punjab and Haryana High Court. The student body also agreed to call off its protests. However, the student leaders later accused the university authorities of altering the document and removing references to “immediate” and “unconditional” withdrawal. This led to further protests. On Monday, grounds for negotiations regarding the withdrawal of the affidavit were also made. However, it remained inconclusive.POLITICAL REACTIONS FROM CONGRESS The centre’s decision has sparked a major political reaction in the state. Several political leaders from the Congress Party from both Punjab and Haryana have met with the students and expressed their dissatisfaction over the centre’s decision. The former Chief Minister and the Congress leader Charanjeet Singh Channi is one of them, who on Monday visited the protest site, met Dagar, and called the decision an attack on democracy. He further added that the decision is an attempt by the BJP and RSS to take control of the university.” Channi further demanded that the Punjab government convene a special Assembly session and approach the court against the decision. Congress MPs Deepender Hooda and Manish Tewari had also met Dagar on Monday, assuring that they would raise the Panjab University Senate issue in the upcoming winter session of Parliament.- EndsPublished By: Akash ChatterjeePublished On: Nov 4, 2025Tune InMust Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/cities/chandigarh/cities/chandigarh/story/centre-may-reconsider-dissolving-panjab-university-senate-as-student-protests-intensifies-2813453-2025-11-04</t>
+  </si>
+  <si>
+    <t>Speeding Thar runs over two sisters in Chandigarh, one killed, other critical</t>
+  </si>
+  <si>
+    <t>A speeding Thar vehicle on Wednesday ran over two sisters, leaving one dead and the other one critically injured. The two sisters - Josef and Isha - were returning from college and waiting for an auto-rickshaw on the roadside, when the speeding black colour Thar hit them. The driver fled from the spot after the accident. Locals took the two sisters to a nearby hospital, where doctors declared Josef, the elder sister, dead. The younger sister, who received serious injuries, is currently undergoing treatment at the hospital. The family lives in the Burail area of the city. The police traced the address of the accused driver with the help of the registration number of the car, however, they discovered upon reaching the place that he had vacated the place long ago. The police are now looking for him with the help of the CCTV footage. The city has witnessed several hit-and-run cases over the past few months. An Ambala Cantonment resident lost his life a month ago after his bike was hit by an unidentified speeding vehicle. Similar to the Wednesday accident, the driver fled from the spot, and the police registered a case under sections 281, 125(A), and 106 of the Bharatiya Nyaya Sanhita (BNS).- EndsPublished By: Akash ChatterjeePublished On: Oct 16, 2025Must Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/cities/chandigarh/cities/chandigarh/story/speeding-thar-kills-one-in-chandigarh-driver-flees-police-investigate-2803721-2025-10-16</t>
+  </si>
+  <si>
+    <t>One dead, 3 injured in violence at Panjab University after Masoom Sharma concert</t>
+  </si>
+  <si>
+    <t>A 22-year-old student was stabbed by unidentified assailants during a concert at Panjab University’s student fest, which turned violent after a quarrel between student groups. The second-year Computer Science student succumbed to his injuries during treatment, while three others were injured. The violence took place backstage while Haryanvi singer Masoom Sharma was performing at the university's Scitron Fest. The victim has been identified as Aditya Thakur, a native of Himachal Pradesh. Among the injured, two students have been identified as Aman and Aryan. One sustained a stab wound near the shoulder, while the other suffered severe injuries to his right thigh above the knee. The identity of the third injured student remains unknown. A large crowd of students gathered for the event at the University Institute of Engineering and Technology (UIET), which was organised by a group of students, including one who had been expelled from the Akhil Bharatiya Vidyarthi Parishad (ABVP). As the fest was nearing its end and students began dispersing, tensions erupted between two groups on the campus. The altercation quickly escalated into violence, with both sides pelting stones before resorting to stabbing. The confrontation created widespread panic and chaos, prompting terrified students to flee in all directions. Due to the loud volume of the concert's speakers, the commotion went unnoticed until a critically injured student, Aditya Thakur, collapsed on the ground. Thakur, a native of Nalagarh in Himachal Pradesh and a second-year Computer Science student at Panjab University, succumbed to his injuries. Despite the presence of police at the scene, the attackers exploited the confusion and managed to escape before any arrests could be made. The injured students were immediately rushed to a nearby hospital, though the police and university administration have yet to disclose their identities. DSP Chandigarh North, Udaypal Singh, told India Today that while the audience numbered between 9,000 and 10,000, no prior inspection was conducted, and security arrangements were inadequate.STUDENT LEADERS' FACTIONALISM SUSPECTED While university officials, along with the police, continue their investigation into the matter, the police have not ruled out the possibility that the attackers acted in retaliation for previous student-related tensions. According to University Security Chief Vikram Singh, four students were injured in the clash -- three from Panjab University and one from Chandigarh University, Gharuan. "The situation is under control, and the injured students are receiving treatment at the nearby Government Multi-Specialty Hospital (GMSH) in Sector 16," Vikram Singh said. Authorities are investigating the cause of the violence and have pointed to possible factionalism among student groups as a contributing factor. Tensions had been building following the cancellation of two major events -- Arjan Dhillon's concert and Gurdas Maan’s program -- organised by other student organisations. In contrast, the fest went off without a hitch, leading some to believe that the altercation might be linked to rivalries between student factions.ABVP BEGINS PROTEST The ABVP has launched a protest demanding justice for Aditya Thakur, who died in the incident. Blaming the administration, the group demanded answers for the inaction and negligence. "The brutal murder of Aditya Thakur during Scitron Fest is a direct consequence of the gross negligence of the Dean of Students Welfare (DSW) and Panjab University administration," the ABVP said. ABVP state joint secretary Pratham Singla told India Today that the incident occurred around 9.30 pm and the clash was over securing a spot in the front row of the show. "As the injured said, the attackers were outsiders. We had already warned the university and staff about the possibility of violence at the event, but no security arrangements were made. Our concerns were ignored, and the same happened," Singla said. "Aditya fought for his life for 30 minutes on campus, but no one helped. We demand the resignation of Security Head Vikramjit Chaudhary and the Dean of Student Welfare," he said, questioning the lack of management and security on campus. The organiser of the event, Jaswinder Rana, has been expelled from ABVP, Pratham Singla added. An investigation into the matter is underway, with police scrutinising CCTV footage and other sources. The assailants are suspected to be residents of a nearby slum, and people living in the area are also being screened.- EndsPublished By: Harshita DasPublished On: Mar 29, 2025</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/cities/chandigarh/cities/chandigarh/story/punjab-university-scitron-fest-violence-masoom-sharma-concert-one-dead-three-injured-2701104-2025-03-29</t>
+  </si>
+  <si>
+    <t>Chandigarh crash: 1 killed, scooter split in two after being dragged by Porsche</t>
+  </si>
+  <si>
+    <t>A man was killed and two women were injured after their scooters were allegedly hit by a "rashly-driven" Porsche near a petrol pump in Chandigarh, officials said on Tuesday. The horrific accident took place near Sector 4 on Monday night when the luxury car coming from the opposite direction at an "excessive speed" hit two young women on an Activa scooter before colliding with another Activa rider ahead. According to eyewitnesses, the Activa got lodged into the front engine of the luxury car and was dragged for a significant distance before the Porsche lost control. The car first smashed into an electric pole, then a traffic signboard, before finally crashing into a tree with immense force. The Activa that was caught in the car’s engine was split into two pieces due to the force of the collision. The Activa driver, identified as Ankit, a resident of Nayagaon, succumbed to his injuries on the spot. The two young women, identified as Soni and Gurleen, sustained severe leg injuries and were rushed to PGI Hospital for treatment. Police reached the accident site and arrested the Porsche driver, seizing the vehicle. A case has been registered under sections related to reckless driving, negligence, and road safety violations. Preliminary investigations revealed that the Porsche is registered in the name of Sanjeev, a resident of Sector 21, Chandigarh. Authorities are now probing the circumstances leading to the accident, including the possibility of overspeeding and reckless driving.- EndsPublished By: Sahil SinhaPublished On: Mar 11, 2025Must Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/cities/chandigarh/cities/chandigarh/story/chandigarh-porsche-accident-speeding-car-collides-with-two-scooters-1-killed-2691917-2025-03-11</t>
+  </si>
+  <si>
+    <t>So sorry, Nek Chand: Citizens after Chandigarh's Rock Garden outer wall demolished</t>
+  </si>
+  <si>
+    <t>A section of the outer wall of Nek Chand’s Rock Garden has been demolished to make way for a road and parking space, triggering objections from residents on social media. Some have raised concerns with the Chandigarh Administration, questioning the impact on the city’s heritage and environment. The demolition follows a directive from the Punjab and Haryana High Court, which had ordered the broadening and straightening of the road several months ago. In response, the Chandigarh Administration notified the land as deforested with the Governor’s consent before proceeding with the demolition. While the affected section was at the outer part of the Rock Garden, some longtime residents see the move as damaging to the city's historical and emotional landscape. Manmohan Sarin, a senior citizen and activist, voiced his disapproval on X, writing, “So sorry, Nek Chand Saini, your precious creation is being demolished in part to make way for a road and parking of polluting vehicles. We, the people of Chandigarh and the Administration, have let you down, that too in your birth centenary year. I have tears in my eyes.” So sorry, Nek Chand Saini , your precious creattion is being demolished in part to make way for a road and parking of polluting vehicles. We, the people of Chandigarh and the Administration have let you down, that too in your birth centenary year. I have tears in my eyes. pic.twitter.com/ClnUaGSrLR
+— MANMOHAN SARIN Save Chandigarh (@macsarin) February 22, 2025 Sarin further expressed concern over the loss of trees, writing, “Many great, old trees have also been cut, without thinking how much damage that will do to our environment. The world is converting concrete city centres into green areas to have a cleaner environment, we are doing the opposite. Nek Chandji, your Rock Garden gave Corbusier’s Capitol Complex a fantastic competition in popularity. Even our worthy Prime Minister, Narendra Modiji, preferred to meet President Hollande of France first in the Rock Garden, Chandigarh, before proceeding to the Capitol Complex.” The Rock Garden is one of Chandigarh’s recognised heritage sites, marked by UNESCO. Some citizens argue that while the court had asked for road expansion, it had not directed the demolition of any part of the structure.- EndsPublished By: Akhilesh NagariPublished On: Feb 24, 2025Must Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/cities/chandigarh/cities/chandigarh/story/citizens-reacts-after-chandigarhs-rock-garden-outer-wall-demolished-video-2684407-2025-02-24</t>
+  </si>
+  <si>
+    <t>Nayab Saini, ML Khattar's convoy forced to wait for 15 minutes in Chandigarh</t>
+  </si>
+  <si>
+    <t>A convoy of Union Minister Manohar Lal Khattar and Haryana Chief Minister Nayab Singh Saini was forced to wait on the road for around 15 minutes in an alleged security breach incident in Chadigarh on Wednesday (February 19) night. According to officials, the convoy of the two senior BJP leaders was unexpectedly stalled due to a locked gate on the designated route. The incident occurred on the road leading from the Chief Ministers’ residences of Haryana and Punjab towards the High Court and Secretariat. A gate linking the main road to Haryana Niwas and Punjab Bhavan was found locked, preventing the convoy from proceeding further. Meanwhile, sources told India Today TV that the key to the gate was in the possession of a security guard stationed at Punjab Bhavan. As a result, the convoy had to halt until the key was retrieved and the gate was unlocked. Nayab Singh Saini and Manohar Lal Khattar were returning from a wedding ceremony in Chandigarh when the incident took place, sources added. During the return journey, Saini and Khattar were in the same vehicle, with the Haryana Chief Minister planning to drop the Union Minister at Haryana Niwas.Despite the seriousness of the situation, no official statements have been made by any authorities.The Haryana Police has expressed concerns about the alleged breach, emphasising that the area is under Chandigarh's jurisdiction, with the pilot vehicle belonging to the Chandigarh Police.Both Haryana and Chandigarh Police are currently investigating the matter to prevent any such security lapses in the future.- EndsPublished By: Sahil SinhaPublished On: Feb 21, 2025Must Watch Despite the seriousness of the situation, no official statements have been made by any authorities. The Haryana Police has expressed concerns about the alleged breach, emphasising that the area is under Chandigarh's jurisdiction, with the pilot vehicle belonging to the Chandigarh Police. Both Haryana and Chandigarh Police are currently investigating the matter to prevent any such security lapses in the future.- EndsPublished By: Sahil SinhaPublished On: Feb 21, 2025Must Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/cities/chandigarh/cities/chandigarh/story/security-breach-nayab-saini-manohar-lal-khattar-convoy-forced-to-wait-chandigarh-2683556-2025-02-21</t>
+  </si>
+  <si>
+    <t>Chandigarh club owner arrested after complaint of extortion by partner</t>
+  </si>
+  <si>
+    <t>The Chandigarh Police on Thursday arrested Arjun Thakur, a partner of the De'Orra club, on charges of extortion. This comes two days after a crude bomb exploded at a club in a city which is 30 meters away from the bar-cum-lounge owned by rapper Badshah. The arrest followed a complaint filed by Nikhil Chaudhary, another partner of the club, alleging that Thakur was demanding Rs 50,000 monthly and threatening harm if the demand was not met. A case has been registered under relevant sections of Bharatiya Nyaya Sanhita (BNS) and police have disclosed that Thakur has a criminal record and is being questioned about the blast outside the lounges. Thakur, a resident of Sector 49, holds a 25 per cent stake in the club. Recently, a 10 per cent share was sold to another individual, Tekchand Singal, a resident of Patiala. This reportedly caused a rift between Thakur, Chaudhary, and other partners. Police believe the extortion demand may be connected to this dispute. Thakur has several cases registered against him and served jail time in the past. He first gained notoriety in 2018 after a shooting incident at a birthday party for Sahdev Salaria, an associate of former Chandigarh MP Kirron Kher. Authorities suspect he has links to criminal gangs. During the investigation, police uncovered a phone call reportedly made by Kali, a gangster associated with the Lawrence Bishnoi gang, to another club partner a week before the blast. The call’s significance is being probed. CCTV footage of the blast showed an unidentified suspect throwing a bomb at the lounge, which led to a small explosion. Two suspects were seen arriving on a motorcycle and fleeing shortly after. The explosion caused damage to De’Orra’s glass windows, but no injuries were reported.- EndsPublished By: Sahil SinhaPublished On: Nov 28, 2024Must Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/cities/chandigarh/cities/chandigarh/story/chandigarh-club-blast-case-police-arrest-deorra-club-partner-extortion-charges-blast-outside-rapper-badshahs-bar-2641799-2024-11-28</t>
+  </si>
+  <si>
+    <t>Chandigarh Mayor questions BJP's compliance over hoardings for PM Modi's visit</t>
+  </si>
+  <si>
+    <t>The Mayor of Chandigarh Municipal Corporation has sought details from the Commissioner regarding whether the necessary permission was granted to the BJP for putting up hoardings to welcome Prime Minister Narendra Modi and the chief ministers for the oath ceremony of Haryana Chief Minister Nayab Saini. Mayor Kuldeep Kumar, who belongs to the Aam Aadmi Party (AAP), wrote to Municipal Corporation Commissioner Amit Kumar, raising concerns about the hoardings. He enquired whether the BJP had obtained the necessary permission for these displays. In his letter, the Mayor urged the commissioner to issue a notice to the party's state president and collect the required fee along with a fine, if permission was not granted. "Did the BJP obtain the required permission from the Municipal Corporation, Chandigarh, for the installation of these hoardings and banners? If so, please provide the permission letter and disclose the fees collected from the BJP. If permission was not obtained, please issue a notice to the BJP President to pay the necessary fee with a penalty as per the rules," the Mayor said in his letter. He requested the Commissioner to furnish the following information within three days. Speaking to India Today, Kumar said, "Rules are the same for everyone. In 2019, a fine of over Rs 60 lakh was imposed for the Valmiki Shobha Yatra, and now the BJP has violated the norms. According to my information, no permission was obtained prior to the event for placing hoardings throughout the city".- EndsPublished By: Ajmal Published On: Oct 19, 2024Must Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/cities/chandigarh/cities/chandigarh/story/chandigarh-mayor-kuldeep-kumar-bjp-hoardings-pm-modi-visit-nayab-singh-saini-swearing-in-ceremony-2619532-2024-10-19</t>
+  </si>
+  <si>
+    <t>Madrasa teacher arrested for sexually assaulting 13-year-old boy in Chandigarh</t>
+  </si>
+  <si>
+    <t>A 24-year-old teacher at a madrasa in Chandigarh was arrested for allegedly sexually assaulting a 13-year-old student. The incident was reported after the victim informed his family, who subsequently approached the police. The teacher, Mohammad Salik from Uttar Pradesh's Meerut, had called the boy to his room, asking him to massage his legs before touching him inappropriately. The incident was reported on Friday. The boy has undergone a medical examination, and his statement has been recorded. The police are investigating whether Salik has been involved in similar incidents before and have collected statements from madrasa staff. He has been charged under the Protection of Children from Sexual Offences (Pocso) Act. - EndsPublished By: Manisha PandeyPublished On: Sep 28, 2024Also Read |  Madrasas fail to provide suitable education, child rights panel tells courtMust Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/cities/chandigarh/cities/chandigarh/story/madrasa-teacher-sexual-assault-minor-student-chandigarh-pocso-act-2607887-2024-09-28</t>
+  </si>
+  <si>
+    <t>Punjab man dies by suicide after killing mother, daughter and pet dog</t>
+  </si>
+  <si>
+    <t>A man shot dead his mother, daughter and pet dog before ending his life with his revolver in Punjab's Barnala district, police said on Sunday. The incident happened at his residence in Ram Rajya colony on Saturday evening, they said. Kulbir Mann Singh first shot dead his 21-year-old daughter Nimrat Kaur, then killed his mother Balwant Kaur (85) and pet dog, a police official said. Later, he killed himself with a licensed revolver, they added. Preliminary investigations revealed that Mann had been suffering from depression for a long time, the official said. According to police, Mann's daughter had recently returned from Canada. Further investigation is underway, they said.- EndsPublished By: Soumya Published On: Jun 23, 2024ALSO READ  |  Mystery surrounds woman's death in Pune after body found inside water tankerALSO READ  |  Kerala teen influencer bullied online after breakup, dies by suicideTrending Reel</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/cities/chandigarh/cities/chandigarh/story/man-kills-mother-daughter-pet-dog-and-himself-in-punjabs-barnala-district-2556871-2024-06-23</t>
+  </si>
+  <si>
+    <t>'Don't believe in casteism': Kirron Kher on AAP's mic sanitisation charge</t>
+  </si>
+  <si>
+    <t>Senior BJP MP and Bollywood actor Kirron Kher on Thursday refuted discrimination charges levelled against her by Chandigarh Mayor and Aam Aadmi Party (AAP) leader Kuldeep Kumar. Kuldeep Kumar has claimed that Kirron Kher asked for the mike to be sanitised after the speech of the Chandigarh Mayor during a programme held at the Raj Bhavan on Tuesday. "Because of my health issues, my immunity is weak. I avoid going close to people having coughs. I always take precautions. The allegation made by Chandigarh Mayor is not true. I sanitised the microphone as a precautionary measure and do not believe in casteism," Kirron Kher told India Today. The Chandigarh unit of the AAP strongly criticised Kirron Kher over her gesture, saying the BJP MP not only insulted the Chandigarh Mayor, but also the Dalit community. Kuldeep Kumar belongs to the Dalit community. While speaking to reporters after the event, Kuldeep Kumar said, "Madam MP first sat on the chair where my nameplate was mentioned. I did not say anything, as she is senior to us. During all this, another incident took place. I had to speak before Madam MP's address. The moment I finished speaking, she got the mic sanitised. Would you get the mic sanitised if a poor child gives a speech? Why am I being treated like an untouchable?" Kumar also said that he would boycott all future events attended by both Kirron Kher and the administrator of Chandigarh. Reacting to the controversy, Banwarilal Purohit stated that Kirron Kher was a cancer patient and doctors had asked her to take precautions. "MP Kirron Kher is a cancer patient. The doctor has asked him to be careful. She wears a mask all the time. If she cleaned the mic so that there was no infection and sat next to me as she wanted to talk about something, then what crime did she commit?" the Governor stated.- EndsPublished By: Abhishek DePublished On: Mar 14, 2024ALSO READ |  2 Chandigarh councillors who crossed over to BJP now back in AAP foldALSO READ |  BJP clinches deputy, senior deputy mayor seats in ChandigarhMust Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/cities/chandigarh/cities/chandigarh/story/chandigarh-mayor-kirron-kher-stanitised-mic-before-her-speech-insulted-dalits-bjp-mp-responds-2514832-2024-03-14</t>
+  </si>
+  <si>
+    <t>BJP hopeful of fresh Chandigarh mayoral polls after winning Deputy Mayor posts</t>
+  </si>
+  <si>
+    <t>Former Chandigarh Mayor and BJP leader Manoj Sonkar on Monday hinted at the possibility of a fresh mayoral election in the city, saying that 'anything can happen'. Sonkar's reaction came after BJP's Kuljeet Singh Sandhu and Rajinder Sharma won the posts of Senior Deputy Mayor and Deputy Mayor in the repolls to the Chandigarh Municipal Corporation. "We are happy that we have won the polls for Senior Deputy Mayor and Deputy Mayor. Anything can happen. When the time comes, there may be another mayoral poll," Manoj Sonkar told India Today TV. Other BJP supporters also echoed similar sentiments, emphasising that "picture abhi baaki hai" (the story is far from over). The Supreme Court, on February 20, nullified the results of the Chandigarh mayoral poll held on January 30. Despite the initial victory of the BJP's Manoj Sonkar, the top court declared the AAP-Congress alliance candidate, Kuldeep Kumar, as the new Mayor of the city. Sonar resigned from the post of Chandigarh Mayor a day before the Supreme Court's verdict. As Mayor is the presiding officer for the elections to the posts of Senior Deputy Mayor and Deputy Mayor, elections were held again earlier in the day. In today's polls, Sandhu won the post of senior deputy mayor by securing 19 votes, while Sharma became the Deputy Mayor of the city. Reacting to the development, BJP MP Kirron Kher expressed her belief that the current Mayor would remain in office, saying, "I don't think so; I feel the Mayor will remain". Kirron Kher, who is a BJP member, also has voting rights in Chandigarh Municipal Corporation elections as an ex-officio member of the corporation. Kher, however, took a jibe at Congress and AAP, pointing out that one vote was invalidated, suggesting dissent within the alliance. She asserted, "Everyone is in favour of BJP. Big leaders have switched to BJP. Look at Himachal - Abhishek Manu Singhvi lost. So, it is no surprise that everyone wants to join such a party". Meanwhile, Chandigarh Mayor Kuldeep Kumar Tita rejected the BJP's claim, stating, "We have conducted free and fair polls; we would have won all three elections on the date of polling because we had the numbers". Tita also accused the BJP of luring 3-4 of their councillors. "If they (BJP) are thinking about a repolling, I want to tell them that I am here to serve the people of Chandigarh. BJP will also face a defeat in the upcoming Lok Sabha polls," he added. In the 35-member Chandigarh municipal House, the BJP has 17 councillors. The number of BJP's strength increased from 14 to 17 after three AAP councillors switched over to it on February 19. The AAP has 10 members while the Congress has seven. The Shiromani Akali Dal has one councillor.- EndsPublished By: Rishabh SharmaPublished On: Mar 4, 2024ALSO READ |  'Will upset BJP's equation': AAP, Congress seal seat deal in Chandigarh, 4 statesMust Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/cities/chandigarh/cities/chandigarh/story/chandigarh-mayor-elections-bjp-wins-deputy-mayor-posts-2510408-2024-03-04</t>
+  </si>
+  <si>
+    <t>BJP clinches deputy, senior deputy mayor seats in Chandigarh</t>
+  </si>
+  <si>
+    <t>The Bharatiya Janata Party (BJP) won the deputy mayor, senior deputy mayor seats in the Chandigarh Municipal Corporation on Monday. Kuljeet Sandhu clinched the senior deputy mayor seat, while Rajendra Sharma won the deputy mayor post. The BJP secured 19 votes, while the AAP-Congress alliance got 16 votes, and 1 vote was declared invalid in the senior deputy mayor election. In the deputy mayor poll, the BJP received 19 votes, while the India Bloc alliance won 17 votes. The election for the senior deputy mayor and deputy mayor of the Chandigarh Municipal Corporation started at 10 am today. There was chaos before the counting began as the mayor called a councilor from the Aam Aadmi Party to him, leading to objections from the BJP councilors. In the 35-member Chandigarh Municipal Corporation House, a party needs 19 votes to win the poll. The BJP has 14 councilors, three have crossed over to the party from AAP, there is one ex-officio vote of BJP MP Kirron Kher, and they have the support of the sole Akali Dal councilor. AAP, on the other hand, has 10 councilors, and the Congress has seven votes. After the orders of the High Court, the election is being conducted under the chairmanship of mayor Kuldeep Kumar. Earlier, these elections were supposed to be held on February 27, but due to the non-arrival of Presiding Officer Mayor Kuldeep Kumar and the hearing of a petition filed by Congress councillors in the High Court, the elections were postponed. AAP councillor Kuldeep Kumar last week assumed the charge as mayor of the Chandigarh Municipal Corporation, a week after the Supreme Court declared him the civic body chief. On February 20, the Supreme Court declared Kumar as the new mayor of Chandigarh after it overturned the result of the mayoral poll in which the BJP candidate had emerged the winner.- EndsPublished By: Vivek MishraPublished On: Mar 4, 2024</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/cities/chandigarh/story/chandigarh-deputy-senior-deputy-mayor-bjp-aap-congress-2510192-2024-03-04</t>
+  </si>
+  <si>
+    <t>AajTak_Crawler</t>
+  </si>
+  <si>
+    <t>Uttar Pradesh</t>
+  </si>
+  <si>
+    <t>In Hapur district of Uttar Pradesh, a farmer who had been roaming around the tehsil for two and a half years to get the inherited land in his name, died of a heart attack. After the death of the farmer, angry family members and villagers protested by keeping the dead body outside the SDM office. A heart-wrenching incident has come to light in Mohanlalganj, Lucknow in UP. Here a madman reached his girlfriend's house and killed her by slitting her throat. After the incident the accused fled from the spot. As soon as the information was received, the police and forensic team reached the spot and started investigating the case. Bareilly administration took bulldozer action on Mohammad Arif's market for the second consecutive day i.e. on Sunday. In the morning, three bulldozers reached the market and started the demolition process. Bareilly Development Authority has continuously taken bulldozer action against illegal constructions against close relatives of Maulana Tauqeer Raza in Bareilly, Uttar Pradesh. Mohammad Arif's two-storey illegal market was demolished, which included more than two dozen shops. Security arrangements have been tightened by imposing prohibitory orders in the entire area so that there is no chaos and crowd. A new debate has erupted in politics regarding SIR i.e. Special Intensive Revision. Samajwadi Party President Akhilesh Yadav has alleged that BJP and Election Commission together are planning to reduce more than fifty thousand votes on the seats won by BJP and SP in 2024. He said that this vote reduction is happening especially on the seats won by Samajwadi Party. Two policemen found guilty in a corruption case in Jarwa police station area of ​​Balrampur have been dismissed from service. Both the constables were accused of illegal extortion from local people and a case was registered under the Prevention of Corruption Act in 2023. After the conviction by the Special Judge in 2025, both were removed from service by taking departmental action. The SP clearly said that strict action against corruption will continue. Chief Minister Yogi Adityanath has also become strict against Bangladeshis and Rohingyas. He has ordered officials and DMs of the districts to build detention centers in every district. Taking major action against negligence in voter list revision (SIR), Gautam Buddha Nagar district administration, on the instructions of District Magistrate Medha Rupam, has lodged an FIR against a total of 60 BLOs and 7 supervisors under Section 32 of the Representation of the People Act 1950. Greater Noe</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/uttar-pradesh</t>
+  </si>
+  <si>
+    <t>Madhya Pradesh</t>
+  </si>
+  <si>
+    <t>After a dispute over a minor vehicle collision in a covered campus located in Rohit Nagar, Bhopal, 20 miscreants attacked four youth with sticks at midnight. The accused entered the colony, threw the victims on the road, beat them and fled. The video of the incident has surfaced. On the complaint, Shahpura police station has registered an FIR and the search for the accused is going on based on the car number. Four months after resigning from the post, Jagdeep Dhankhar appeared on the public platform for the first time and openly praised the ideological stream of RSS. He said that India with its civilizational strength of 6000 years can guide the world in today's global turmoil. The matter came to light when first year batch students of the college lodged a complaint on the anti-ragging helpline of the University Grants Commission (UGC). Dean of the college, Dr. Arvind Ghoshghoria said that after investigation, the Anti-Ragging Committee found the complaint to be true. In the blast case near the Red Fort, the investigating agencies have detained two doctors of Al-Falah Medical College, Junaid Yusuf and Nasir Rashid. Even before this, information about the involvement of many doctors and students of this college in terrorist activities has come to light. Agencies are busy locating other people associated with the network. A case of blackmailing a married woman by creating a fake ID on Instagram has come to light in Gwalior. The accused youth first befriended the woman, then created a new fake profile by taking the woman's photo and posted the photo with an obscene caption. On the complaint of the victim, the police have registered a case and started searching for the accused. Former Vice President of the country Jagdeep Dhankhar had arrived in Bhopal, the capital of Madhya Pradesh, on Friday to attend a program related to Rashtriya Swayamsevak Sangh (RSS). Digvijay Singh claims that during this period no BJP leader came to welcome the former Vice President. Jawad Siddiqui Mhow Property: The demolition process of the Mhow house of Al-Falah University Chairman Jawad Ahmed Siddiqui, related to the Delhi blast case, has been stopped for the time being. Madhya Pradesh High Court has given this relief. MP News: Police have arrested two youths named Mohammad Zaid and Aman Baba, accused of this incident which took place in July. Police have made 9 accused in this case. EOW Raid in Bhopal: Against Madhya Pradesh businessman Dilip Gupta and his companies for fraudulently charging Rs 35.75 crore from investors.</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/madhya-pradesh</t>
+  </si>
+  <si>
+    <t>Bihar News</t>
+  </si>
+  <si>
+    <t>In Motihari, Bihar, the body of the accused younger brother, who was absconding after the murder of his elder brother, has been found hanging from a litchi tree. There was a sensation in Shripur village of Nawada Panchayat of Pakdidayal police station area on Saturday morning when the body of youth Sakal Sah, who was absconding for three days, was found hanging from a litchi tree. A big revelation of ISI terror module has been made in Arrah, Bihar. Ludhiana Police arrested a youth from Bihiya police station area, who is accused of being an expert in throwing hand grenades and taking missions in Rajasthan, Punjab and Bihar under the direction of foreign handlers. The youth had earlier been involved in arms supply, absconding from juvenile home and criminal gangs. Why has Nitish Kumar kept the Home Department with himself despite being the Chief Minister for twenty years? This question comes in everyone's mind because the Home Department is considered to be the most powerful department which is related to the politics and security of the state. The Chief Minister has the right to assign which responsibility to which minister and which department he handles. A new study published in the journal Nature has revealed that extremely high levels of uranium have been found in the breast milk of 40 lactating women of Bihar. In this research conducted by a joint team of Mahavir Cancer Institute, AIIMS Delhi and other institutions, U-238 was found in the samples of women from Bhojpur, Samastipur, Begusarai, Khagaria, Katihar and Nalanda, in which the levels were highest in Khagaria and Katihar. A dreadful crime of an eccentric and suspicious husband has come to light from Narayanpur village of Abadpur police station area of ​​Katihar district of Bihar. Here the wife was murdered because the younger son was not as dark as the elder son and due to illicit suspicion. At present, the police have arrested the accused husband in the case and have started further action. Jansuraj Party has suffered a crushing defeat in Bihar Assembly elections. Prashant Kishore has broken his silence for the first time after the results. He raised serious questions on the election process. However, it was also clearly said that they do not have any concrete evidence at present. Prashant Kishore argued that due to fear of Jungle Raj, the mood of the voters changed and they could not come with us. A husband killed his wife in Katihar district of Bihar. The accused did this because he suspected his wife of having an illicit relationship with someone. Besides, he was not considering the younger son as his own. Because the younger son was not as dark as the elder son. Bihar</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/bihar</t>
+  </si>
+  <si>
+    <t>west bengal</t>
+  </si>
+  <si>
+    <t>Preparations for next year's assembly elections have gained momentum in West Bengal and political activities have intensified. Meanwhile, TMC MLA Humayun Kabir has created a new controversy by announcing the construction of Babri Masjid. He told that he had made this announcement a year ago and the construction of the mosque would be completed within three years. Voters are under a lot of pressure due to the political controversy regarding Bengal elections. It took two years for the 2021 elections but now with the elections coming again, efforts are being made to politically influence the Election Commission. In the context of Amit Shah's statement, concern is being expressed over the election process of Bengal. It took time to establish power after the elections of 2001, and now efforts are being made to politically influence the Election Commission regarding the upcoming elections. Due to this, there is huge tension among the voters, and many people are taking steps like suicide due to the pressure. BLO Rinku Tarafdar in Nadia district of West Bengal committed suicide due to alleged administrative pressure. According to family members, Rinku wrote in the suicide note that she was not able to bear the pressure of the difficult and online work of BLO. Earthquake tremors have been felt in Kolkata. The epicenter of the earthquake was in Bangladesh but its effects were felt till Kolkata. This incident created concern among the people because such a shock was felt suddenly. Initial information about the intensity and epicenter of the earthquake suggests that its impact may extend to neighboring states as well. ED has conducted extensive raids against the coal mafia in West Bengal and Jharkhand. Hundreds of locations have been raided on charges of illegal mining and transportation in many districts including Durgapur, Purulia, Howrah, Kolkata. In this ongoing investigation at more than 40 places, a large amount of cash and gold jewelery has also been recovered. The Supreme Court on Thursday gave its verdict regarding the time limit on the bills passed by the state assemblies. The Governor of Bengal has given his first reaction on this. He has praised this decision. Political tension has increased in West Bengal regarding the voter list revision campaign. Mamata Banerjee has written a letter to the Election Commission highlighting the flaws in the sensitive process. He said that getting the work done without better planning and training is putting unbearable pressure on the employees, due to which even BLOs are committing suicide. Mild earthquake felt around Kolkata</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/west-bengal</t>
+  </si>
+  <si>
+    <t>Himachal Pradesh</t>
+  </si>
+  <si>
+    <t>Tejas fighter jet crashed during Dubai Air Show practice. In which Indian Air Force pilot Wing Commander Namansh Syal died. On Sunday, his mortal remains were brought to Sulur Air Base in Coimbatore. A tragic accident occurred on the last day of Dubai Air Show 2025. India's indigenous fighter aircraft Tejas crashed in which pilot Wing Commander Namansh Syal was martyred. Tejas fighter aircraft crashed during practice in the 19th Air Show in Dubai. In which 34-year-old Wing Commander Namansh Syal of the Indian Air Force was martyred. He was originally a resident of Kangra district of Himachal Pradesh. Mandi acid attack victim Mamta was cremated under police protection at Hanuman Ghat in the city on Friday. He died on Wednesday night after treatment for six days at PGI, Chandigarh. The dispute regarding the mosque has been going on for days in Sanjauli area of ​​Shimla, the capital of Himachal Pradesh. Hindu organizations expressed strong protest and also demonstrated against the illegal construction. Due to their opposition, the administration accepted their demands and took the initiative to calm the dispute. Namaz was not held in Sanjauli Masjid of Shimla today due to dispute and tension. There is presence of security forces outside the mosque. Given the situation, only a few people reached the mosque to offer namaz. The environment outside Sanjauli Masjid is calm and under security cover. The situation is said to be stable at present, although there is a shadow of tension in the atmosphere. Mandi acid attack victim Mamta was cremated under police protection at Hanuman Ghat. He died during treatment in PGI, Chandigarh. Before dying, Mamta had given a written demand for strict punishment to her husband Nandlal. On November 15, her husband threw acid and pushed her from the terrace. Candle march will be taken out this evening. Controversy regarding Sanjauli Mosque is increasing in Shimla city of Himachal Pradesh. The entire structure of the mosque has been declared illegal by the civic body and the court, which has spread discontent among local Hindu organizations. These organizations have planned to hold a strong demonstration against the mosque prayers. This dispute may increase religious and social tension in the city. In view of the sensitivity of the matter, both sides are being appealed to exercise peace and restraint. The controversy regarding namaz in the mosque in Sanjauli, Shimla has intensified. Protesting against the registration of FIR against the members of Devbhoomi Sangharsh Samiti for two days.</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/india/himachal-pradesh</t>
+  </si>
+  <si>
+    <t>Jammu and Kashmir</t>
+  </si>
+  <si>
+    <t>Controversy has increased after the selection of 42 Muslim students in the first MBBS list in Vaishno Devi Medical College of Jammu and Kashmir. BJP and many Hindu organizations have objected to this and said that Hindu students should get priority in the institute run by the Shrine Board. BJP has demanded review of the rules from LG Manoj Sinha. Making a big revelation in the investigation of Jaish-e-Mohammed's inter-state terror module and Red Fort blast case, SIA and SOG Srinagar have detained electrician Tufail Ahmed from the Industrial Estate of Pulwama. Tufail is a resident of Batmaloo, Srinagar. He is suspected to have provided AK-47 rifle to terrorist Dr. Umar during his posting in GMC Srinagar, which was later recovered from Dr. Adeel's locker in GMC Anantnag. Investigating agencies have detained another suspect in Delhi's Red Fort blast case. SIA and SOG of Jammu and Kashmir have picked up electrician Tufail Ahmed, resident of Pulwama, from an industrial area. In Pulwama, the police has given a strong message by seizing the property of Mubashir Ahmed, who spread terrorism from Pakistan occupied Kashmir. He used this land and house located in Syedabad Pastuna area of ​​Tral to support terrorist activities. Indian Army doctors have given the gift of new light to thousands of people living amidst bullets on the borders of Jammu and Kashmir. A major medical mission was conducted in the Command Hospital of Udhampur and eye surgeries of more than 2000 people were performed, due to which thousands of civilians regained their sight. This Army mission is not just a treatment, but has emerged as a new hope, a new vision and the deepest expression of humanity. BJP spokesperson Altaf Thakur criticized Mehbooba and her daughter Iltija Mufti. He made serious allegations against Mufti and demanded that he and his family's possible links with terrorism should be investigated. In this operation, security forces have foiled a possible terrorist plot by recovering a huge amount of arms and ammunition. These weapons could have been used for any terrorist act in the near future, but the joint operation completely foiled this plan. In a major action, security forces have exposed the narco-terror network in Handwara, Jammu and Kashmir. Father son duo arrested in operation conducted by joint team of police and CRPF 162 battalion</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/india/jammu-kashmir</t>
+  </si>
+  <si>
+    <t>South Cinema</t>
+  </si>
+  <si>
+    <t>South Cinema is one of the four major film industries in India. In South Indian cinema, feature films are made in the four major languages ​​of the country - Telugu, Tamil, Kannada and Malayalam. They are often colloquially called Tollywood, Kollywood, Sandalwood and Mollywood. South Indian films, whether Kannada, Malayalam, Telugu, or Tamil, are largely tailored to the culture, dialect, politics, social structure, and lifestyle of the people of their respective regions (South Cinema Culture). South cinema has always produced its films effectively. It has produced many of the most expensive films in Indian cinema, including KGF 2.0, Enthiran, Baahubali, Pushpa and RRR. These films have been superhit. One song from the film RRR has received the Oscar Award for Original Song (Oscars for South Cinema). The first South Indian film to gross Rs 200 crore worldwide was the 2008 Tamil film 'Dasavathaaram', in which Kamal Haasan, one of India's most successful actors, played ten different roles. Additionally, the first South Indian film to gross over Rs 100 crore worldwide was the 2007 Tamil film 'Sivaji', starring Rajinikanth in the lead role (South Cinema Gross over Rs 200cr Worldwide). Artists of South Cinema are popular all over the world, these include actors Vijay, Prabhas, Ajit Kumar, Ramcharan, Ju. NTR, Dhanush, Kamal Haasan and Rajinikanth are included. South Indians worship actor Rajinikanth like a god. If we talk about the most successful actresses of South Cinema, they include Nayanthara, Samantha Ruth Prabhu, Pooja Hegde, Anushka Shetty, Tamannaah Bhatia, Rashmika Mandanna and Sai Pallavi (South Cinema Most Famous Actors and Actresses). In 2021, South Cinema's combined domestic box-office total was Rs 2,400 crore, significantly higher than the Hindi film markets (South Cinema Box Office Collection 2021). The Telugu film industry has emerged as India's largest film industry in terms of box office revenue. On one hand, AI is making people's work much easier, while on the other hand, this technology is also being misused a lot. Every day some celebs are reacting to this. Meanwhile, the reaction of South actress Keerthy Suresh has also come. Actor Ram Charan's wife</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/topic/south-cinema</t>
+  </si>
+  <si>
+    <t>bhojpuri cinema</t>
+  </si>
+  <si>
+    <t>Bhojpuri Cinema- Bhojpuri Cinema is an Indian film industry, where Bhojpuri language films are made. It has developed in Western Bihar and Eastern Uttar Pradesh, whose main production centers are in Lucknow and Patna. Bhojpuri cinema is a major part of Bihari cinema. The first Bhojpuri talking film 'Ganga Maiya Tohe Piyari Chadhaibo' was released in 1963 - First Bhojpuri Film. In the 1980s, many hit and run-of-the-mill Bhojpuri films like Bitiya Bhail Sayan, Chandwa Ke Taake Chakor, Hamar Bhauji, Ganga Kinare Mora Gaon and Sampoorna Teerth Yatra were released - Hit Bhojpuri Movies. Bhojpuri cinema has developed in recent years. Bhojpuri film industry has now become an industry worth Rs 2000 crore. Bhojpuri cinema has connected the Bhojpuri speaking Indian diaspora all over the world with its existence. Bhojpuri cinema attracts second and third generation NRIs in Guyana, Trinidad and Tobago, Suriname, Fiji, Mauritius and South Africa, who still speak the language – Bhojpuri Cinema NRI. Pawan Singh has released a new wedding song 'Le Jayenge Tere Sajna', in which Bigg Boss OTT fame Sana Sultan is his heroine. The song is becoming increasingly viral on social media and fans are appealing to make it number 1. Independent candidate Jyoti Singh had to face defeat in Bihar Assembly elections. He has alleged irregularities in the election process and voting machines malfunctioning. In Bihar Assembly elections, Khesari Lal Yadav had decided to contest from Chapra on RJD seat. The decision of whether the people of Chhapra will give him victory or defeat will be taken in a few hours. Before the election results, exit polls declared Khesari Lal's defeat. When he was asked about this, he gave a blunt answer. How important is Chirag Paswan's role going to be in the politics of Bihar. This will be known by the time the voting results come on 14th November i.e. this afternoon. Bollywood's hero Dharmendra played the role of Pawan Singh's father in the Bhojpuri film 'Des Pardes'.  This film gave new heights to Bhojpuri industry and won the hearts of the audience. Amidst Bihar elections, once again the series of statements started among Bhojpuri stars. This time Pawan Singh got angry at Khesari Lal Yadav and called the actor mad. The marriage of Bhojpuri star Pawan Singh and his wife Jyoti Singh is once again in the headlines. Amidst the news of breakup of relationship, Jyoti said</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/topic/bhojpuri-cinema</t>
+  </si>
+  <si>
+    <t>movie review</t>
+  </si>
+  <si>
+    <t>Netflix's iconic show 'Delhi Crime' has reached its third season. This time the story of the show is based on the real case of Baby Falak, which had shocked the people of Delhi. But is it as strong as the last two seasons? Will 'Maddam Sir' and his team be able to give you a thrilling experience again this time? Ajay Devgan and Rakul Preet Singh's 'De De Pyar De' (2019) was a big hit. This film is based on a love story that breaks the age limit. _x005F_x000D_ Now the sequel of the funny comedy has arrived. R Madhavan and Meezaan Jaffrey have come as new entries this time. Is 'De De Pyaar De 2' as fun as the previous film? There is a character written 200 years ago in English literature, who is called the Godfather of Monsters. This character, which has appeared on screen more than a thousand times, has now been recreated in the film 'Frankenstein' released on Netflix. This time it has not just appeared on the screen, but has also come alive. Read the detailed review of the film... 'Baramulla' is a new film on Netflix. Aditya Dhar, who made 'Uri- The Surgical Strike' and 'Article 370', is its producer. The atmosphere of this horror story taking place in Kashmir was visible in the trailer itself. Know how the film is in this review. There are many such moments in Emraan Hashmi and Yami Gautam starrer film 'Haq', which force you to think. About women's rights, about their lives and about their identity. Know how this film is in our review. Actor Harshvardhan Rane's most awaited film 'Ek Deewane Ki Deewaniyat' has been released in theaters today on 21st October. There is a strong buzz regarding this. Actress Sonam Bajwa is also seen with Harshvardhan Rane in this film. Know how this film is in our review. The first half of Ayushmann Khurrana and Rashmika Mandanna starrer 'Thamaa' is quite strong. The first specialty of the film is that it is creating a new world in this horror universe. The love story shown in the film will keep you engaged. Varun Dhawan and Jhanvi Kapoor's film 'Sunny Sanskari Ki Tulsi Kumari' has been released. In this you will see Sunny and Tulsi trying to win back their love. If you are planning to watch the picture, then read our review first. Rishabh Shetty's film 'Kantara Chapter 1' has been released today. It starts with the promise he made to the public outside the theatre. In 2022, his film ‘Kantara’ based on the legend</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/entertainment/film-review</t>
+  </si>
+  <si>
+    <t>tarot horoscope</t>
+  </si>
+  <si>
+    <t>Today's Pisces (Pisces) Tarot Card Horoscope, 23 November 2025: The money stuck from somewhere is getting back. This can give peace of mind. You can use your money to buy a personal property. Today's Kumbh (Aquarius) Tarot Card Horoscope, 23 November 2025: Be it the stock market or any scheme, avoid investing money in any such place. Try to stay away from investments for now. Today's Capricorn (Capricorn) Tarot Card Horoscope, 23 November 2025: You can consider your financial aspects. Some are trying to find sources of earning small money. Don't let any relationship dominate you so much. Today's Sagittarius (Sagittarius) Tarot Card Horoscope, 23 November 2025: Do not ignore small health problems. If any problem persists for a long time then definitely get it treated at the right time. Today's Vrishchik (Scorpio) Tarot Card Horoscope, 23 November 2025: Your relationship with your beloved may seem to be getting better than before. Some work which was not being completed for a long time. Now he will also be seen moving forward at a slow pace. Today's Libra (Libra) Tarot Card Horoscope, 23 November 2025: Bitter experiences given to you by some people in the past can make you think of leaving everything and surrendering yourself to God. At this time you are surrounded by a lot of dilemma. Today's Virgo (Virgo) Tarot Card Horoscope, 23 November 2025: You may feel a lot of trouble due to sore throat and blocked nose due to cold. Today's Leo (Leo) Tarot Card Horoscope, 23 November 2025: Some of your colleagues at work are jealous of your progress due to which they are making a plan to defame you. Today's Kark (Cancer) Tarot Card Horoscope, 23 November 2025: You are planning to spend some time alone with your spouse. For a long time, due to excessive work, both of you have not been able to spend any time together. Today's Mithun (Gemini) Tarot Card Horoscope, 23 November 2025: You start new tasks keeping in mind the old mistakes and failures. So it is possible that you may not be able to achieve relative success. Today's Vrishabh (Taurus) Tarot Card Horoscope, 23 November 2025: At this time, efforts can be made to resolve the misunderstandings in your married life. It is possible that you may have to face some adversities.</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/religion/rashiphal/tarot</t>
+  </si>
+  <si>
+    <t>financial horoscope</t>
+  </si>
+  <si>
+    <t>Aaj ka Arthik Rashifal 23 November 2025 (Economic Horoscope): Performance in the plans will remain expected, that is, you will have to stick to your pre-planned strategies. You will avoid risks. Aaj ka Arthik Rashifal 22 November 2025 (Economic Horoscope): You will move forward with wisdom. Commercial matters will be in your favor. Focus will remain on the goal. Profit will remain increased. Credit and respect will increase. Will happen. Today's Economic Horoscope 21 November 2025 (Economic Horoscope): It will be important to respect professional relationships. It is necessary to maintain clarity in financial matters. Opposition may show activism today. Today's Arthik Rashifal 20 November 2025 (Economic Horoscope): Sagittarius people need to keep distance from white-collared thugs. Increase investment efforts, but avoid ostentation. Meetings and communication will be strengthened. Today's Economic Horoscope 19 November 2025: It is possible for people to receive valuable gifts. Will be effective in financial discussions. Will avoid lending. There will be focus on economic matters. There will be an increase in profits. Today's Economic Horoscope 18 November 2025: Busyness in financial matters will increase. Will maintain patience. Work by planning. Stay away from strangers. Judicial matters may arise. Will follow the rules. Today's Economic Horoscope 17 November 2025: It is mandatory to maintain complete clarity in contracts and agreements. You should avoid showing any kind of haste or haste in transaction matters, Aaj ka Arthik Rashifal 16 November 2025 (Economic Horoscope): You should emphasize on commercial activities. There is a possibility of you getting good news with the help of close ones. Your plans will take shape today, Aaj ka Arthik Rashifal 15 November 2025 (Economic Horoscope): Action plans will gain momentum. Will increase harmony. Will be interested in business work. Will move forward on the path of progress. The strategy of financial action plans will remain better. Today's Arthik Rashifal 14 November 2025 (Economic Horoscope): Increase caution in career and business. Increase focus on professionalism. Maintain smartness in work. Avoid taking risks. Keep focus on the goal. Will improve professional relationships. Today's Economic Horoscope 13 November 2025 (Economic Horoscope): Teamwork will be maintained. Will take initiative in financial and commercial efforts. Savings will increase. The financial aspect will remain in check. Will take interest in ground matters. Like</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/religion/rashiphal/arthik</t>
+  </si>
+  <si>
+    <t>career horoscope</t>
+  </si>
+  <si>
+    <t>Today's Career Horoscope 23 November 2025 (Career Horoscope): Various professional endeavors will remain routine. Profit percentage will be mixed. Various matters will be pursued with caution so that losses can be avoided. Today's Career Horoscope 22 November 2025 (Career Horoscope): Personal performance will improve today, due to which you will be able to capitalize on opportunities well. You should focus on improving your system today. Today's Career Horoscope 21 November 2025 (Career Horoscope): Do not get confused and misled. They will carry forward their plans on the strength of their hard work and training. They will be better in service work today. Today's Career Rashifal 20 November 2025 (Career Horoscope): People with Libra zodiac sign will maintain influence in their career. There will be auspicious signs in professional matters. Acquaintances will support you. Will show energy and confidence in business. There will be success in transactions. Will keep pace with traditional business. Today's Career Rashifal 19 November 2025 (Career Horoscope): Performance in career business will be good. Credit and respect will increase. Financial efforts will be in favor. Will give impetus to action plans. Today's Career Horoscope 18 November 2025 (Career Horoscope): Will be associated with artistic subjects. There will be influence in career. Will achieve the goals. Will carry forward the pending works. Will make a place with courage and bravery. Commercial matters will improve. Today's Career Rashifal 17 November 2025 (Career Horoscope): Capricorn people will perform remarkably all around, because their business will be better. They will have a spirit of cooperation and will focus on bold efforts and management. Today's Career Horoscope 16 November 2025 (Career Horoscope): Acting with courage is the key to your success. Maintain interest in cooperative efforts. Emphasize progress in work and business with everyone's cooperation. Today's Career Horoscope 15 November 2025 (Career Horoscope): There will be auspiciousness in professional work. Do not be negligent in various tasks. The profit percentage will be normal. There will be speed in court cases. Bring clarity in tasks. Today's Career Rashifal 14 November 2025 (Career Horoscope): One should avoid the company of crooks in industry and business. Maintain caution in transactions. Work will be accomplished with courage and wisdom. Will perform better with the help of colleagues. Today's Career Horoscope 13 November 2025 (Career Horoscope): Do not show haste. There will be an increase in topics related to distant countries. strength of individual efforts</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/religion/rashiphal/career</t>
+  </si>
+  <si>
+    <t>Numerology Radix</t>
+  </si>
+  <si>
+    <t>Numerology Number 9 Prediction, Today's Date 9 23 November 2025: There will be mixed results. Will increase activity in economic matters. You will get the company of elders. Don't try to take risks. Maintain the rules. Be cautious in business transactions. Numerology Number 8 Prediction, Today's Date 8 23 November 2025: You will get suitable offers. Will accelerate professional efforts. Will make a place by performing competently. Post, prestige and influence will increase. Senior people will be happy. Will move ahead with ease. Will be enthusiastic about career and business. Will think big. Will remain reticent. Numerology Number 7 Prediction, Today's Number 7 23 November 2025: Creativity and positivity will increase. Various efforts will be intensified. Profits and expansion will be easy. Desired proposals will be received. Employed people will keep their place. Business influence will increase. Devote time to work. Numerology Number 6 Prediction, Today's Date 6 23 November 2025: Will maintain profits. Colleagues will be cooperative. Will show patience in immediate matters. Increase focus on the words of the experienced. Will emphasize on management. Make arrangements with elders. Numerology Number 5 Prediction, Today's Date 5 23 November 2025: The percentage of success will be high. Will take everyone along. Achievementable results can be achieved. Peers will remain cooperative. Will maintain emphasis on professionalism. Profit percentage will remain on the rise. Will not be tempted by greed. Numerology Number 4 Prediction, Today's Date 4 23 November 2025: Success percentage will improve. Will keep emphasis on position and prestige. Will take decisions according to the circumstances. Will be comfortable in work. There will be emphasis on professionalism and management. Career will be in favor of business. Numerology Number 3 Prediction, Today's Date 3 23 November 2025: Business understanding will increase. Will show activeness. Plans will remain in the right direction. Will be active in the meeting. There will be emphasis on harmony. Numerology Number 2 Prediction, Aaj ka Mulank 2 23 November 2025: Will keep learning and advice from experiences. Will remain ahead in professional activities. Will be involved in commercial matters. Will be effective in art skills. Will keep focus. Will move ahead with ease. Numerology Number 1 Prediction, Today's Date 1 23 November 2025: The effect will remain. You will get better results from commercial positivity. Will take advantage of the opportunity. The goal will remain in focus. Will increase connection with officials. Numerology Number 9 Prediction, Today's Date 9 22</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/religion/rashiphal/numerology</t>
+  </si>
+  <si>
+    <t>Vaastu Shastra</t>
+  </si>
+  <si>
+    <t>Vastu Shastra is an ancient and rich tradition of Indian civilization, which is considered to be a scientific system based on directions and energy balance for houses, buildings, temples and other constructions. This word is made up of two parts, "Vastu" (site or place) and "Shastra" (science). That is, Vastu Shastra means "scientific method of construction". The main objective of Vaastu Shastra is to create a place by making balanced use of natural elements – earth, water, fire, air and sky which can provide happiness, prosperity, health and mental peace to the residents. It is considered to be based on the principles of positive and negative energy. Vastu Shastra remains important even in today's fast pace and urban lifestyle. The principles of Vastu are being kept in mind in building construction, flat design, office setup and interior design. It is believed that this will help people in health, morale and business progress. Tulsi Vastu Tips: Tulsi is considered very sacred in Sanatan Dharma and it is said to be the abode of Goddess Lakshmi. Astrologers say that a remedy done with a small Tulsi leaf on Ekadashi or any special festival can remove the poverty of a person from seven births. Mirror Vastu Tips: Some special rules for keeping mirrors in the house have been mentioned in Vastu Shastra. A mirror placed in the wrong direction can cause bad luck, stress and financial loss. Whereas keeping a mirror in the right direction increases positive energy and wealth. Vastu Tips: In our everyday life we ​​often borrow or give things when needed. Initially this seems normal, but according to Vastu Shastra, there are some special items whose transaction can be inauspicious. Vastu Tips: Aarti is not just a part of worship, but it is considered to be related to the universe. At the same time, whenever Aarti is performed, it goes clockwise i.e. clockwise. So let us know the reason behind it. Lakshmi Upay: According to Vastu, if Goddess Lakshmi gets angry then the financial condition of the person starts weakening. Expenses always increase and income starts decreasing. In such a situation, shortage of money can be overcome by adopting some special measures. Happiness and prosperity can be brought to the house. Vastu Tips: According to Vastu Shastra, the west direction is considered the source of energy for business success and profits. If this direction becomes faulty then</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/topic/vastu-shastra</t>
+  </si>
+  <si>
+    <t>festivals</t>
+  </si>
+  <si>
+    <t>Why don't people get married on Vivah Panchami 2025? Know the reasons for Ram-Sita marriage, religious beliefs and bad omens related to marriage. Vivah Panchami date 2025: The festival of Vivah Panchami marks the wedding anniversary of Lord Ram and Goddess Sita, which is celebrated every year on the fifth day of Shukla Paksha in the month of Margashirsha. On this day devotees worship Lord Ram and Goddess Sita. It is believed that by observing fast on this day, devotees get their desired groom. Kaal Bhairav ​​Jayanti 2025 will be celebrated on Wednesday, 12 November this year. Worship of Kaal Bhairav, the fierce form of Lord Shiva, removes fear, diseases and negative powers. Know the worship method, auspicious time and religious significance of this day. Donating a lamp on the full moon day of Kartik month has special religious significance, which provides peace to ancestors, freedom from debt, relief from diseases and freedom from negative energy. By donating a lamp on the river bank or pond, one gets the blessings of Goddess Lakshmi and Lord Vishnu, which brings happiness and prosperity in life. Guru Nanak Jayanti 2025 will be celebrated on 5 November this year. Know the date of 'Guruparab', the birthday of Guru Nanak Dev Ji, the first Guru of Sikhism, its religious significance, history and traditions related to it like Akhand Path, Nagar Kirtan and importance of Langar. Shaligram worship is very important in Sanatan Dharma, which is considered to be the idol form of Lord Vishnu. The Gandaki River, which originates in Nepal, is the source of the Shaligram stones and its sanctity is described in many Puranas and devotional poetry. In the Sanatan tradition, the worship of Lord Shaligram has special significance, which is considered to be the idol form of Lord Vishnu. Shaligrams are black colored smooth stones, worshiping which brings happiness and prosperity in the house and provides relief from troubles. Akshaya Navami is the ninth date of Shukla Paksha of Kartik month, which is important from both religious and Ayurvedic point of view. Amla, which is worshiped on this day, is considered the best medicinal fruit in Ayurveda. This fruit provides cooling effect and is the basis of medicines like Triphala. November Vrat Tyohar List 2025: Many big and major festivals are going to come in the month of November including Dev Deepawali and Tulsi Vivah, due to which this month will be very wonderful. So let us know which big festivals are coming in this month of November. Devotthan Ekadashi of Kartik month is considered the festival of awakening of Lord Vishnu. Special puja on this day</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/religion/festivals</t>
+  </si>
+  <si>
+    <t>Visual Stories</t>
+  </si>
+  <si>
+    <t>African batsman rained sixes in Guwahati test, equaled Afridi's record Flipkart sale started, bumper offer on phone-TV, air purifier, this company of Gautam Adani, deal for 231Cr, know the business Groom Palash sang a song for Smriti, tears shed after seeing sister's emotional performance Smriti's millionaire sister-in-law was seen in mehendi, white Showed royal style in lehenga, see photos Actress became a mother at the age of 44, changed her life, said - Nowadays my life is... Actress will become the bride of a millionaire businessman, hid the identity of her fiance, said - waiting for marriage... Sonam Kapoor will become a mother for the second time at the age of 40, flaunted her baby bump in a suit, her style is royal, bones will remain strong till old age! Include these 5 healthy foods in your diet. This director is single at the age of 53, father of 2 children but did not get married, said - No... 'Love is not needed by abuses and fights', said Govinda's wife, expressed displeasure with Bigg Boss. Actress will become a mother after one and a half year of marriage, flaunted baby bump in bikini, flaunted on the beach, romanced with Ranbir Kapoor, actress will get work, broken hopes, Suffered depression 'Are you playing at home...', captain Rishabh Pant got angry on Kuldeep Yadav, Palash danced with cricketer Smriti Mandhana in his arms, romantic in music, Video 75 thousand phone available for 40 thousand, offer on Flipkart These green leaves are very beneficial for health, Ayurveda expert told its 5 amazing benefits Nita Ambani danced with Akash-Shloka's daughter Veda, Grandma-granddaughter's cute VIDEO will win hearts Smriti Mandhana in Palash's arms, Mehendi in Piya's name applied on her hands, VIDEO R Madhavan seen in Mumbai local train! When the video went viral, the truth came out. Tanushree Dutta will marry at the age of 41, will become the mother of a son? She said - the saint told that Sonam Kapoor will become a mother again at the age of 40, flaunted her baby bump in a stylish style, Jaya Kishori looked beautiful in a pink suit, her simple look went viral! PHOTOS 'UP's boy' Mridul, away from dating life, longs for love, says - Meri Babu... Copyright © 2025 Living Media India Limited. For reprint rights: Syndications Today</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/visualstories</t>
+  </si>
+  <si>
+    <t>real estate</t>
+  </si>
+  <si>
+    <t>In many big cities of the country, even breathing has become difficult due to pollution, but property prices in these cities are skyrocketing. In such a situation, people are asking why we are buying such expensive houses to live in bad air. Wealth advisor Abhishek believes that in a city like Mumbai, middle class people are buying themselves a financial punishment of 40 years by buying houses worth crores. Where there is not even clean air to live. As India strengthens its position as an emerging destination for stable, long-term real estate investments in the Asia-Pacific region, foreign capital will continue to be an important driver. Sunder Nagar, one of the most expensive and high-profile areas of Delhi, is once again in the headlines. The recent bungalow deal worth crores here is attracting people's attention. After all, why do billionaires stand in line to make this area their permanent home? These days, Sonipat seems to be the new choice for real estate investors. The changes in connectivity and development have suddenly brought this city into the limelight. Know, what happened in Sonipat that the eyes of property buyers got fixed here? Now AI is being used extensively in home decoration. With just a photo it suggests a new look for your space. Why are people liking it and how is it changing the whole designing? Fast growing Ranchi is now becoming the new choice of real estate investors. Due to better connectivity and increasing housing demand, property prices have increased rapidly in many areas. Where in Ranchi can one get good returns on investment? Know here... Demand for ultra luxury homes has increased rapidly in Gurugram in the last few years. Big builders of the country are building luxurious houses of premium segment here. Whose price is above Rs 100 crore. Not only have house prices and rents increased rapidly in NCR, office rents and commercial space rates are also increasing and their prices are expected to increase further in the coming time. There is relief news for the people who have bought houses in two projects of Amrapali. NBCC has sold the rights of the flat to AU Real Estate for ₹1,069 crore to complete the stalled project. While buying a new house, the biggest question is whether to buy ground floor or not. Despite appearing to be an easier option, it also has its own benefits and some significant risks. know the ground</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/business/real-estate</t>
+  </si>
+  <si>
+    <t>The hottest stocks of today, this week, month and year</t>
+  </si>
+  <si>
+    <t>Which stocks of Nifty 500 rose the most today? Were these 10 stocks also included in the top 10 stocks of this week and month?     Was any stock one of the biggest gainers during the week, month and year?     We will give you all this information every day. Soon. To know about short and long term winners in stock markets, let's meet every evening at 4 pm. Gillette India. gained 11.4% today, the most among NSE 500 stocks. It suffered a loss of -6.2% in the last week. The second biggest gainer of the day was NLC India (NLCINDIA), up 9.0%. Godfrey Phillips India gained 22.6% in the last 1 week. There was also an increase of 56.1% in the last month. The second-biggest gainer of the week was Glaxosmithkline Pharmaceuticals (GLAXO), up 18.5%. If your selected stocks have given returns of 20%+ in 30 days then you are lucky or very knowledgeable. Fast Moving Consumer Goods company Godfrey Phillips India grew 56.1% in a month. The top 5 stocks included in the top 10 have given returns of more than 10 percent in a month. GILLETTE, which was the day's top gainer, is not among the monthly winners. Godfrey Phillips India has performed top. He has given 159.4% return in one year. Before you consider investing, be sure to compare its performance with other Fast Moving Consumer Goods stocks. Four out of the top 10 stocks in this list doubled investors' money in the last one year. If you are not a day trader, you are looking for a consistent performer on these lists. To help you in choosing such shares, we have made a list of common shares in the four lists given above. Godfrey Phillips India Limited appears the most in these four lists. It appears in 3 out of the four top lists. The real diamond will probably be the one that appears in all four lists and in the top-five. These lists include only Nifty 500 stocks. Nifty 500 comprises the top 500 companies listed on the NSE. This free float represents approximately 96% of the market capitalization and approximately 96.5% of the total turnover on the National Stock Exchange.         There are many days when the closing value of some shares is not updated till 4 pm. Those shares will not be included in these lists at 4 pm. this list</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/hottest-stocks-of-today-this-week-month-and-year</t>
+  </si>
+  <si>
+    <t>Bitcoin</t>
+  </si>
+  <si>
+    <t>Bitcoin is the world's first decentralized cryptocurrency or digital coin. It is called decentralized cryptocurrency because no financial regulatory authority in the world controls it. It works on peer-2-peer software and cryptography. Almost a decade has passed since the creation of Bitcoin. In these 10 years, it has become the world's most popular cryptocurrency. Bitcoin blockchain is used for transactions in this popular cryptocurrency. Each Bitcoin is made up of 10,00,00,000 Satoshis, this is the smallest unit of Bitcoin. You can understand it like this that there are 100 paise in 1 rupee. These units enable one Bitcoin to be divided into 8 decimal places. That's why people are able to buy one bitcoin in many pieces. It is worth keeping in mind that there is no actual coin or note like Bitcoin. It is kept only as a balance record in a public account. A huge amount of computing power is used to register all transactions related to Bitcoin. This process is called ‘mining’. As mentioned earlier, Bitcoin is not issued by the government of any country in the world or any financial institution, bank etc. In fact, in many countries of the world it is not even considered a legal tender. But one thing is that since Bitcoin became popular, many more cryptocurrencies were launched in the world.</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/interactive/cryptocurrency-price-in-india-bitcoin-ethereum-dogecoin-ripple-litecoin/bitcoin-price-in-india-today</t>
+  </si>
+  <si>
+    <t>Gold price today in Delhi (Delhi Gold Price Today)</t>
+  </si>
+  <si>
+    <t>Indian oil companies release prices every morning at 6 am. Amidst the ongoing fluctuations in crude oil prices in the global market, oil prices in the national market are stable even today, 23 November 2025. You can check the prices of petrol and diesel sitting at home through RSP code through an SMS from your phone. The price of 24 carat gold in Delhi reached Rs 1,23,540 per 10 grams on 01 November 2025. On 23 November 2025, the rate of 24 carat gold in Delhi city became Rs 1,26,120 per 10 grams. The maximum price of 24 carat gold in November 2025 was Rs 1,28,910 per 10 grams. The minimum price of 24 carat gold in November 2025 was Rs 1,13,790 per 10 grams. 23 November By 2025, the price of 24 carat gold has increased by Rs 2580. The price of 24 carat gold in Delhi reached Rs 1,17,600 per 10 grams on 01 October 2025. On 31 October 2025, the rate of 24 carat gold in Delhi city had become Rs 1,21,740 per 10 grams. The maximum price of 24 carat gold in October 2025 was Rs 1,32,953 per 10 grams. The minimum price of 24 carat gold in October 2025 was Rs 1,17,600 per 10 grams. 31 October By 2025, the price of 24 carat gold had increased by Rs 4140. The price of 24 carat gold in Delhi had reached Rs 1,05,113 per 10 grams on 01 September 2025. On 30 September 2025, the rate of 24 carat gold in Delhi city had become Rs 1,16,583 per 10 grams. The maximum price of 24 carat gold in September 2025 was Rs 1,17,040 per 10 grams. The minimum price of 24 carat gold in September 2025 was Rs 1,05,113 per 10 grams. 30 September 2025 The price of 24 carat gold had increased by Rs 11470. The price of 24 carat gold in Delhi reached Rs 1,00,193 per 10 grams on 01 August 2025. On 31 August 2025, the rate of 24 carat gold in Delhi city had become Rs 1,05,123 per 10 grams. The maximum price of 24 carat gold in August 2025 was Rs 1,05,123 per 10 grams. The minimum price of 24 carat gold in August 2025 was Rs 99,983 per 10 grams. 31 August 2025 The price of 24 carat gold had increased by Rs 4930. The price of 24 carat gold in Delhi reached Rs 97,423 per 10 grams on July 01, 2025. On July 31, 2025, the rate of 24 carat gold in Delhi city had become Rs 1,00,663 per 10 grams. 24 carat gold in July 2025</t>
+  </si>
+  <si>
+    <t>https://www.aajtak.in/commodity/gold-rate-in-delhi-today</t>
+  </si>
+  <si>
+    <t>IndiaTv_Crawler</t>
+  </si>
+  <si>
+    <t>At IBSA meet, PM Modi pushes for UNSC reforms, says 'it is not an option, but a necessity'</t>
+  </si>
+  <si>
+    <t>Speed News: RSS Chief Mohan Bhagwat says 'Without Hindus, the World Will Cease To Exist' PM Modi to Attend G20 Summit in South Africa: What's on His Agenda? Speed News: PM Modi Embarks For G20 Summit, Says India's Perspective Will Be Vision-Driven Miss Universe 2025: Who Is Fatima Bosch, Called a 'Dumbhead' and Later Won the Crown! Speed News: PM Modi's 'Gamcha' wave lifts Bihar, Nitish Kumar thanks crowd at Patna Rally</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/</t>
+  </si>
+  <si>
+    <t>Web Stories</t>
+  </si>
+  <si>
+    <t>Active players with most runs in Ashes No Shubman Gill, Shreyas Iyer? Predicting India's likely squad for ODI series against South Africa Fastest to 19 centuries in ODI cricket 7 high-profile spinners most likely to be on teams' radar at IPL 2026 auction Jacqueline Fernandez to Janhvi Kapoor, Indian celebs who attended Wimbledon 2025 Kiara Advani to Patralekha, Bollywood celebs who are expecting The Odyssey to The Devil Wears Prada 2, a look at Anne Hathaway's Hollywood lineup Dhurandhar to Kill Dill, times when Ranveer Singh did action on screen How to book a vacant seat after chart preparation in Indian Railways? 7 countries with no mosques: Check details Is there any full form of Army? Which country has zero Muslim population? Infinix Note 40 5G gets Rs 6,500 discount: Find out where to buy Which SIM is used the most in India? How many years can a SIM card last? How to create Nano Banana image within minutes? Steps 7 best fruits that help reduce bloating 5 best coffee + food pairings that will surprise your taste buds 5 reasons why olives should be a part of your diet 7 reasons why rosemary is beneficial for your hair 7 bad habits your kidneys hate 5 surprising health benefits of kombucha you need to know 1 in 2 diabetics don’t know they have it; signs you should test 7 shocking health risks of diet soda From HCL to TCS to BPL, do you know the exact full forms of these companies? Belrise Industries Vs Borana Weaves IPO: From GMP to price band, here's everything you need to know From Ashok Leyland to LTIMindtree: These stocks to trade ex-dividend this week LIC Mutual Fund re-introduces these five flagship equity schemes - Full details here Horoscope Today, March 17: Big benefits for Geminis in government work, know about other zodiac signs Horoscope Today, March 3: Libra to get benefit in ancestral property, know about other zodiac signs Horoscope Today, February 20: Lucky day for Taurus students, know about other zodiac signs Horoscope Today, February 9: Financial problems to solve for Libra, know about other zodiac signs</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/web-stories</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>The Family Man 3 Series Review: Manoj Bajpayee's Srikant Tiwari races against time to save the country and family 120 Bahadur Movie Review: Farhan Akhtar turns misfit in compelling war-drama De De Pyaar De 2 Movie Review: R Madhavan, Meezaan outshine; Ajay Devgn-Rakul deliver above-average comedy Delhi Crime Season 3 Series Review: Shefali Shah, Huma Qureshi lead morally charged and complex case Jassi Weds Jassi Movie Review: Ranvir Shorey starrer is a love letter to the 90s</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/entertainment</t>
+  </si>
+  <si>
+    <t>Smriti Mandhana's wedding with Palash Muchhal postponed as her father falls ill India women create history, win inaugural blind T20 World Cup after beating Nepal 'It's amateurish': Michael Vaughan lambasts England, advises them to ready themselves ahead of second Test Matt Henry continues his smashing form across formats, becomes leading wicket-taker in ODIs in 2025 Ravichandran Ashwin blasts England's batting unit for 'reckless' batting in Ashes opener in Perth Geoffrey Boycott launches scathing attack on England after Perth Test loss against Australia Sanju Samson named captain as Kerala announces squad for Syed Mushtaq Ali Trophy 'Not reading Kuldeep': R Ashwin questions South Africa's game plan against spin ahead of day 2 Cricket Australia headed towards hefty financial loss after Ashes opener ends in two days 'Dedicate it to Shane Warne': Ravindra Jadeja remembers late Aussie legend on his return to Rajasthan Royals 'Shellshocked': Ben Stokes opens up after England lose Ashes opener in Perth Sports Wrap: New Zealand End Series on a High, England Walk Away With a 2-1 Win Sports Wrap: Australia Take Control of Gabba Test but Rain Continues to Have a Say Sports Wrap: South Africa inch closer to WTC final; ICC Reprimands Head &amp; Siraj Sports Wrap: India bat first against Australia in pink-ball Test in Adelaide India women create history, win inaugural blind T20 World Cup after beating Nepal Smriti Mandhana's wedding with Palash Muchhal postponed as her father falls ill IND vs SA 2nd Test Live Cricket Score: South Africa boss second day as India trail by 480 'It's amateurish': Michael Vaughan lambasts England, advises them to ready themselves Geoffrey Boycott launches scathing attack on England after Perth Test loss against Australia Sanju Samson named captain as Kerala announces squad for Syed Mushtaq Ali Trophy Sanju Samson IPL record against CSK 4 Indian players set to feature in Abu Dhabi T10 League 2025 Players with most wickets in current WTC cycle Travis Head played a jaw-dropping knock in the 205-run chase against England in the first Ashes Test in Perth. With Australia struggling for openers in the Test format and Head having experience of opening, many Australian supporters would want to see him open the innings in the longest format. Mohammed Shami is among the 17 players named in Bengal's squad for the Syed Mushtaq Ali Trophy. Meanwhile, Delhi have also named their squad with Nitish Rana named captain for the domestic premier T20 competition. Shubman Gill suffered a neck injury during the first Test against South Africa and missed out on playing in the second match. Meanwhile, Gill is set to miss the ODI series against South Africa as two players are in the race for the captaincy. Australia made light work of England in the Perth Test after a batting masterclass from Travis Head, who scored a blistering 83-ball 123. Australia have created a few world records en route to their win over England in the Ashes Test in Perth. Travis Head shattered a 123-year-old world record with his blistering hundred in the 205-run chase against England in the Perth Test. Australia have gone 1-0 up in the series after their big win at the Optus Stadium. India pegged South Africa back with four wickets in the third session to keep their noses ahead at the end of the first day of the second Test in Guwahati. The Proteas ended the day on 247/6 and would be disappointed for their batters missing out on scoring big. Australia created a major world record as they mauled England in the fourth innings of the Ashes opener in Perth. Travis Head produced a knock for the ages as the Aussies chased down 205 in 28.2 overs. New Zealand swept the West Indies 3-0 in the ODI series in Hamilton on Saturday. After two closely fought matches, the Windies could muster just 162 runs in the finale and even though the Black Caps stuttered a bit, Mark Chapman kept their innings in control. Australia thrashed England in the first Ashes Test as they chased down 205 in just 28.5 overs with Travis Head scoring a jaw-dropping century. Australia have maintained their unbeaten record intact in the ongoing WTC cycle. © 2009-2025 Independent News Service.  All rights reserved.</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/sports/cricket</t>
+  </si>
+  <si>
+    <t>All India Pin Code</t>
+  </si>
+  <si>
+    <t>India has 29 states with at least 720 districts comprising of approximately 6 lakh villages, and over 8200 cities and towns. Indian postal department has allotted a unique postal code of pin code to each district/village/town/city to ensure quick delivery of postal services. A Postal Index Number or PIN or PIN code is a code in the post office numbering or post code system used by India Post, the Indian postal administration. The code is six digits long. The first three digits of the PIN represent a specific geographical region called a sorting district that is headquartered at the main post office of the largest city and is known as the sorting office. A state may have one or more sorting districts depending on the volumes of mail handled. The fourth digit represents the route on which a delivery office is located in the sorting district. The last two digits represent the delivery office within the sorting district starting from 01 which would be the GPO or HO. Disclaimer: The information provided here is latest and updated as available from India Post, but the users are advised to verify information with the respective Postal Office before using the information provided. The website or author is not for the topicality, correctness, completeness or quality of the information provided. Any liability claims regarding damage caused by the use of the information provided will therefore be rejected.</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/india-pin-codes</t>
+  </si>
+  <si>
+    <t>Delhi HC seeks Bansuri Swaraj's reply on Somnath Bharti's plea challenging her victory in elections</t>
+  </si>
+  <si>
+    <t>Digvijaya Singh moves Madhya Pradesh High Court over EVM after Lok Sabha poll defeat from Rajgarh Somnath Bharti challenges Bansuri Swaraj's Lok Sabha victory in Delhi High Court, hearing on Monday Why BJP lost Lok Sabha polls in Uttar Pradesh? State party chief submits 15-page report to PM Modi FACT CHECK: Did Pushkar Singh Dhami distribute money during Lok Sabha elections? Here’s the truth Nobel laureate Amartya Sen says 'idea of turning India into Hindu Rashtra is inappropriate' Adhir Ranjan Chowdhury clears air about his resignation as West Bengal state Congress president Election Commission receives applications for EVM verification on 8 Lok Sabha seats in six states PM Modi visits ruins of Nalanda University in Bihar's Rajgir | VIDEO RESULT DATE: 4 JUNE,2024 Kahani Kursi Ki: Maharashtra elections...who will bet? Coffee Par Kurukshetra:  Will Yogi continue to lead Uttar Pradesh? Priyanka Gandhi Political Debut: I am Priyanka Gandhi...I can fight! Haqiqat Kya Hai: Both Rahul and Priyanka will become MPs...what will they say now? Coffee Par Kurukshetra: Who will give 'command' to BJP cadre? Special report: UP's X-ray report... the truth behind 36 Coffee Par Kurukshetra: The target was 80..I did not get 60!...Does Yogi know who is the culprit? Modi 3.0 NDA Cabinet:  Narendra Modi To Take Oath as Prime Minister for the Third Time at 6 pm on June 9 Lok Sabha Elections 2024: How BJP, Congress and other political parties fared from 2014 to 2024 Aaj Ki Baat: PM Modi thanks countrymen after Lok Sabha election results PM's first reaction on results: 'People placed faith in NDA for third consecutive time, historical' UP Lok Sabha Election 2024: Chandrasekhar Azad wins Nagina by margin of 1.5 lakh votes MP Lok Sabha Election Results 2024: BJP to make clean sweep, shows trend, leads in Chhindwara Madhya Pradesh Lok Sabha Election Results: List of constituency-wise winning candidates, parties Rajasthan Lok Sabha Election Results 2024: List of constituency-wise leading candidates and parties Rajasthan Election Results 2024 Live: BJP clinches Jaipur, Ajmer, Bikaner seats 'Not going anywhere, have some strategy in mind': Devendra Fadnavis rubbishes resignation rumours Maharashtra Lok Sabha Election Results 2024: MVA takes lead, BJP-led alliance trails Bihar businessman accuses newly-elected MP Pappu Yadav of demanding Rs 1 crore extortion Bihar Lok Sabha Election Results 2024: List of constituency-wise winning candidates and parties Karnataka Lok Sabha Election Results 2024: BJP-JDS alliance ends tally at 19 seats, Congress wins 9 Shimoga Lok Sabha Election Results 2024: BJP's BY Raghavendra defeats Cong's Geetha Shivarajkumar India TV-CNX exit poll predicts third term for NDA | A look at state-wise survey Sixth phase of polling concludes with historic voter turnout in Anantnag, Delhi at 54.48% Delhi all set to vote in sixth phase today. Check last-minute arrangements A sneak peak into PM Modi's biggest election interview with Rajat Sharma | Photos 'INDIA bloc will rewrite Constitution': PM Modi holds 3 rallies | Key takeaways PM Modi takes sharp digs at opposition in Bihar rally: Key quotes PM Modi campaigns for Kangana Ranaut in Mandi, actress greets him with a rose | IN PICS Don't run my govt for good editorial or headline: Top quotes from PM Modi's interview with India TV PM Modi offers prayers at Jagannath temple, holds roadshow in Odisha | In pics PM Modi's rallies in West Bengal: Six key takeaways Amit Shah, Smriti Irani ignite Amethi with vibrant roadshow ahead of fifth phase polling Mumbai welcomes Modi with 'high josh', PM says 'Mumbai lives its dreams' PM Modi's electrifying rallies sweep through UP's Lalganj, Jaunpur, Bhadohi, and Pratapgarh PM Modi performs seva, makes roti at Patna Sahib Gurudwara | In pics Kejriwal leads massive roadshow in Delhi with Bhagwant Mann day after release from jail © 2009-2025 Independent News Service, All Rights Reserved.</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/elections</t>
+  </si>
+  <si>
+    <t>Nitish Kumar allocates portfolios in Bihar, Deputy CM Samrat Choudhary gets Home | Who gets what?</t>
+  </si>
+  <si>
+    <t>Hope new Bihar govt lives up to expectations of people: Tejashwi Yadav Prashant Kishor observes ‘maun upvas’ at Mahatma Gandhi's Ashram in Bihar | Video Video: PM Modi's 'Gamcha' wave cheers Bihar, CM Nitish Kumar thanks people at Patna's Gandhi Maidan Nitish Kumar Cabinet 10.0: Complete list of MLAs who took oath as Bihar ministers Nitish Kumar takes oath as chief minister of Bihar for record 10th time in Patna Nitish Kumar ahead of taking oath as CM: 'Bihar will embark on new journey of development' Nitish Kumar to become CM for record 10th time: List of Chief Ministers with multiple terms Result Date : 14 NOV 2025 Breaking News: 9th installment of Women Employment Scheme will be released, CM Nitish will release the installment to women. Bihar Assembly Election: Will Rahul Gandhi remain at zero? PM Modi–Nitish Kumar Join Hands After Oath Ceremony: Is West Bengal the Next Big Political Battle? Nitish Kumar Takes Oath as Bihar CM for Record 10th Time; 19 Ministers Sworn In at Gandhi Maidan Siwan Assembly Election 2025: BJP's Mangal Pandey aims to win back the seat from RJD's Awadh Bihari Katihar Assembly Election 2025: BJP's Tarakishore Prasad in three-way contest with VIP, Jan Suraaj Jhajha Election: JDU's Damodar Rawat eyes another win in three-way battle against RJD and Jan Suraaj Bettiah Election 2025: BJP's Renu Devi faces tough triangular battle despite strong winning record Tarapur Assembly Election 2025: Will BJP's Samrat Choudhary be able to continue his father's legacy? Lakhisarai Assembly Election 2025: Can Deputy CM Vijay Kumar Sinha continue his winning streak? Raghopur Assembly Election 2025: Can BJP challenge Tejashwi at his traditional Yadav bastion? Chapra Assembly Election 2025: Can RJD's Khesari Lal Yadav break BJP's two-term winning streak? © 2009-2025 Independent News Service. All rights reserved.</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/elections/assembly-elections/bihar</t>
+  </si>
+  <si>
+    <t>Prime Minister Narendra Modi on Sunday asserted that reforms in the United Nations Security Council (UNSC) is not an option anymore, but an imperative. Participating in the India-Brazil-South Africa (IBSA) Leaders' Meeting in South Africa's Johannesburg, he also said there is a need for close coordination on counter-terrorism, asserting that there is no room for double standards while fighting terrorism.
+Advertisement The prime minister also proposed setting the 'IBSA Digital Innovation Alliance' for sharing of Digital Public Infrastructure like UPI, health platforms like CoWIN. He emphasised that IBSA is not just a group of three countries but an important platform connecting "three continents, three major democratic nations, and three major economies".  
+Advertisement According to the Ministry of External Affairs (MEA), PM Modi stressed that global governance institutions are far removed from 21st century realities. He also emphasised that IBSA's "potential to contribute to the development of safe, trustworthy and human-centric AI norms". "Prime Minister stated that IBSA can complement each other's development and become an example for sustainable growth," the MEA said in a release. "He highlighted cooperation opportunities in areas such as millets, natural farming, disaster resilience, green energy, traditional medicines and health security." "Appreciating the IBSA Fund's work in supporting projects across forty countries in sectors like education, health, women empowerment and solar energy, Prime Minister proposed IBSA Fund for Climate Resilient Agriculture to further advance South-South cooperation," the MEA said. PM Modi had arrived in Johannesburg on Friday to participate in the G20 Summit. Upon his arrival, he had thanked South African President Cyril Ramaphosa for the warm welcome and for organising this important Summit. This is PM Modi's fourth official visit to South Africa, following his bilateral visit in 2016 and later for the two BRICS summits in 2018 and 2023. South Africa is hosting the first G20 Summit being held in Africa. The African Union became a member of the G20 during India's presidency in 2023.</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/news/world/pm-modi-pushes-for-unsc-reforms-at-ibsa-meet-says-it-is-not-an-option-but-a-necessity-2025-11-23-1018738</t>
+  </si>
+  <si>
+    <t>Smriti Mandhana's wedding with Palash Muchhal postponed as her father falls ill</t>
+  </si>
+  <si>
+    <t>Smriti Mandhana's wedding with Palash Muchhal has been postponed as the cricketer's father has fallen ill, Mandhana's manager Tuhin Mishra confirmed. Mandhana's marriage was scheduled to take place on November 23 in Sangli, Maharashtra.
+Advertisement Mandhana's manager confirmed the development to the media. "Today in the morning, when Smriti's father was having breakfast, his health deteriorated. We waited for a bit, thinking he would get fine. But when it deteriorated further, we called for an ambulance and took him to the hospital, and he is under observation," her manager, Tuhin Mishra, said.  
+Advertisement "Smriti is very close to her father. She has decided that the marriage will be indefinitely postponed until he gets well. Her father is under observation and the doctor has told that he will have to stay in hospital until he recovers. Smriti is clear, she wants to see her father well and then get married," he said. Mandhana and Muchhal recently hosted the mehndi ceremony, as only close ones attended the event, including Mandhana's cricket teammates. The Indian women's cricketers kept the fans updated with the ceremony pictures on their social media. The wedding would be an intimate one, as informed by Palash. "Yes, it’s an afternoon wedding. We haven’t invited too many people, just our close ones. There are about 70 guests from my side and 70 from hers. It’s an intimate wedding with no reception. We’ll just have a small get-together with a few people from the political and cricketing world. It is going to be a close-knit celebration," Palash had said. Prime Minister Narendra Modi had sent his wishes to the couple. "Walking hand in hand through every season of life, may the couple find strength in each other's presence and their hearts, minds, and souls be in harmony. May their dreams intertwine and grow together, guiding them toward a future filled with joy and deep understanding," Modi wrote for the couple. "May Smriti and Palaash build a shared life rooted in trust, standing by each other always, embracing responsibilities with love and growing together through each other's strengths and imperfections. "As they start a new, beautiful life together, the grace of Smriti's cover drive meets the lilting musical symphony of Palaash in a wonderful partnership," he added. Recently, the women cricketers shot a video revealing Mandhana and Palash's marriage. With the background song of 'Samjho ho hi gaya' from the popular movie 'Lage Raho Munna Bhai', Mandhana and her teammates danced to the song. Jemimah Rodrigues, Radha Yadav, Shreyanka Patil and Arundhati Reddy danced with Mandhana.</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/sports/cricket/smriti-mandhanas-wedding-with-palaash-muchhal-postponed-as-her-father-falls-ill-2025-11-23-1018745</t>
+  </si>
+  <si>
+    <t>'Election Commission must take action': Row over Ajit Pawar's 'funds' remark; Fadnavis backs his deputy</t>
+  </si>
+  <si>
+    <t>Maharashtra Chief Minister Devendra Fadnavis came to the rescue of his deputy Ajit Pawar following a row over his 'you have votes and I have funds' remark, affirming that his government is dedicated to ensuring development across every region of the state. The 55-year-old was speaking to reporters on sidelines of an event in Nagpur.
+Advertisement "Many times lot of things are said in a speech (during election), but it does not mean the same," news agency PTI quoted Fadnavis as saying. "Even if our ally or someone had said like that, it was not their intention and they would never do such discrimination. And certainly, the people will elect Mahayuti in the coming elections, though we may fight separately in some places."  
+Advertisement While campaigning for the Malegaon Nagar Panchayat elections in Baramati tehsil of Pune district on Friday, Pawar had told voters that if they help the Nationalist Congress Party (NCP) candidates win, he will ensure that there is no shortage of funds. However, he warned that he will 'reject' them if the people 'reject' his party. It should be noted that Pawar, whose party is in alliance with the Bharatiya Janata Party (BJP) and Eknath Shinde's Shiv Sena, holds the finance portfolio in the Mahayuti government in Maharashtra. "I will ensure there is no shortage of funds if you elect all 18 NCP candidates. If you elect all 18 candidates, I am committed to give whatever I have promised. But if you reject, I will also reject. You have votes, I have funds," he said, as reported by news agency PTI. The opposition took this opportunity to attack the Maharashtra government, asking the Election Commission of India (ECI) to take action against the deputy chief minister. "How is this happening in a democratic country? We must ask the Election Commission," Supriya Sule, NCP-SP MP and Pawar's sister, told PTI. Congress national spokesperson Atul Londhe also attacked Pawar, calling his remarks a 'direct threat' to the voters. "No work has been done in 11 years, so now they are giving such bribes, but this is Maharashtra, and Ajit ji must have forgotten that here, dignity works, not bribes," Londhe said.</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/maharashtra/election-commission-must-take-action-row-over-ajit-pawar-s-funds-remark-maharashtra-cm-devendra-fadnavis-backs-his-deputy-2025-11-23-1018742</t>
+  </si>
+  <si>
+    <t>Uranium found in breastmilk of lactating mothers in Bihar, newborns at potential health risk</t>
+  </si>
+  <si>
+    <t>A recent study has uncovered alarming levels of uranium (U-238) in the breastmilk of lactating mothers across several districts in Bihar, raising serious concerns about potential health risks to infants. Researchers from multiple institutions warn that uranium exposure through breastfeeding could lead to significant non-carcinogenic health effects in young children.
+Advertisement The study was conducted by Mahavir Cancer Sansthan, Patna, under the leadership of Dr Arun Kumar and Prof. Ashok Ghosh, in collaboration with AIIMS, New Delhi, led by Dr Ashok Sharma from the Department of Biochemistry.  
+Advertisement Researchers analysed breastmilk samples from 40 lactating mothers across multiple districts in Bihar and detected uranium (U-238) in every sample, with concentrations ranging from 0 to 5.25 g/L. The highest levels were recorded in Katihar district. The health risk assessment revealed that infants are especially vulnerable, as their bodies have a limited capacity to eliminate uranium. The study estimates that nearly 70 per cent of the infants exposed could face non-carcinogenic health impacts. Uranium is a naturally occurring radioactive element found in granite and other rocks. It can enter groundwater through natural leaching as well as human activities such as mining, coal combustion, emissions from nuclear industries, and the use of phosphate-based fertilisers. Dr Ashok Sharma of AIIMS Delhi, who is a co-author of the study, said, "The study analysed breast milk from 40 lactating mothers and found uranium (U-238) in all samples. Although 70% of infants showed potential non-carcinogenic health risk, the overall uranium levels were below permissible limits and are expected to have minimal actual health impact on both mothers and infants. The highest average contamination occurred in Khagaria district, and the highest individual value in Katihar district. While uranium exposure may pose risks such as impaired neurological development and reduced IQ, breastfeeding should not be discontinued and remains the most beneficial source of infant nutrition unless clinically indicated." "The study showed that: 70% of the infants had HQ &gt; 1, indicating possible non-carcinogenic health risks from uranium exposure through breast milk. Uranium exposure in infants may affect: Kidney development, Neurological development, Cognitive and mental health outcomes (including low IQ and neurodevelopmental delay) if long-term exposure continues." "However, based on the observed uranium concentrations in breast milk samples (0-5.25 ug/L), the study still concludes that the actual impact on infant health is likely low, and most uranium absorbed by mothers is excreted primarily through urine, not concentrated in breast milk. Therefore, breastfeeding remains recommended, unless a clinical indication suggests otherwise," he said. Dr Ashok also said that such studies will be conducted in other states to know about the presence of heavy metals. "We are under the process of examining the heavy metals in other states and their impact on human health which is a need of the hour." On further studies to identify the presence of pesticides, environmental pollutants in breastmilk Dr Ashok said, "the article does address future directions, and pesticides are included in their plans. From the study's discussion and conclusion sections, this investigation focused on uranium (U-238) in breast milk; our previous work had already identified arsenic, lead, and mercury in breast milk. We further highlight the need for continued biomonitoring of toxic contaminants, including environmental pollutants such as pesticides in breast milk, to better understand infant exposure risk." The World Health Organisation (WHO) sets a provisional limit of 30 micrograms per litre (ug/L) for uranium in drinking water, while some countries, such as Germany, have adopted stricter limits of 10 ug/L. In India, uranium contamination has been reported in an estimated 151 districts across 18 states, with 1.7 per cent of groundwater sources affected in Bihar. Globally, elevated uranium levels have been observed in countries including Canada, the United States, Finland, Sweden, Switzerland, the United Kingdom, Bangladesh, China, Korea, Mongolia, Pakistan, and the lower Mekong Delta region. Though prior global studies have shown high uranium concentrations in groundwater, clear clinical symptoms among exposed populations have not been consistently observed. However, the current research underscores the urgent need to monitor U238 in Bihar to assess and mitigate potential health risks to mothers and their infants. Also Read: Centre clarifies no bill on Chandigarh administration in Parliament's Winter Session Also Read: 'Punjab always comes first': State BJP chief amid uproar over Centre's Chandigarh move</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/news/india/uranium-found-in-breastmilk-of-lactating-mothers-in-bihar-infants-at-potential-health-risk-latest-updates-2025-11-23-1018727</t>
+  </si>
+  <si>
+    <t>Live
+                                    IND vs SA 2nd Test Live Cricket Score: South Africa boss second day as India trail by 480</t>
+  </si>
+  <si>
+    <t>India vs South Africa 2nd Test, Day 1 Live Updates: India and South Africa are all set to lock horns once more as they take on each other in the second Test of the ongoing multi-format series. The two sides face off at the Barsapara Stadium in Guwahati from November 22, and India will be without the services of Shubman Gill in the clash, as Rishabh Pant will be leading the hosts against the Proteas.
+Advertisement And that will be it for the day. Light will not allow any further action and it is almost time too. Stumps on Day 2 and South Africa are in the driver's seat. India 9/0 after 6.1 and trail by 480 more. The umpires are frequently checking the light meters here. It is looking a bit of dark at the moment. The Indian openers are out in the middle here. KL Rahul and Yashasvi Jaiswal are in the middle and look for a strong start. Ohh what a soft dismissal to end the innings. Marco Jansen has played it on and is dismissed on 93. Kuldeep Yadav strikes for the fourth time and first on the day. South Africa have been bowled out for 489. This is an absolute belter to bat on today and South Africa have made the most of it. They are closing in on their 500 now. What a massive task it will be for India now. Marco Jansen stands tall against the Indian team. After 144.3 overs, the score reads 467-9. Jansen on a score of 82 runs in 76 deliveries. Bumrah strikes! Simon Harmer departs on a score of five runs. South Africa now 462-9. South Africa show no signs of slowing down here. Marco Jansen is on the attack as the visitors hit the 450 mark. The score reads 450-8 after 140.4 overs. Jansen now into the 70s. Muthusamy departs after an exceptional knock. Having scored 109 runs, the star player departs. South Africa now 431-8, Siraj gets the breakthrough. The two sides are back after lunch, and South Africa is completely in command of the game. The score reads 428-7, and Jadeja has the ball in his hand. South Africa is in a commanding position at lunch. India is in a load of trouble. The score reads 428/7, with Jansen past his 50, and Muthusamy cruising after his ton. Muthusamy has completed his century! What a knock, completes his ton in 192 deliveries. South Africa now 418-7. South Africa have breached the 400 mark here. After 131.2 overs, the score reads 400-7. Jansen approaching his half century, with Muthusamy on his way to a ton. Marco Jansen goes big on the last ball of the over, what a huge six down the ground. After 128 overs, the score for South Africa reads 379-7. Jansen moves into the 30s. Marco Jansen has already scored 11 runs in 16 deliveries since coming on after Verreyne's wicket. South Africa now 346-7 after 123.3 overs. Ravindra Jadeja breaks the deadlock! Verreynne departs on a score of 45 runs in 122 deliveries. India takes their seventh wicket, with South Africa on a score of 334. Muthusamy and Verreynne have built quite the partnership here. After 118.2 overs, the score reads 330-6. Muthusamy on 65 and Verreyne on 43. Jasprit Bumrah has the ball in hand as the game continues after tea. Muthusamy takes the strike, South Africa on a score of 316/6. Team India is still in the search of their first wicket of the day. At tea time, the score reads 316/6. Muthusamy crosses 50 runs here in Guwahati. A brilliant performance in the middle order for him. The score read 306-6 after 106.2 overs The Proteas are on a score of 303 runs with the loss of six wickets. Muthusamy on a score of 48 runs is approaching his half century. After 97 overs, the score for South Africa reads 282/6. Muthusamy and Verreyne look to hold the fort for the Proteas here. Muthusamy has been putting in quite the show against India on day 2. After 95.1 overs, the score reads 279-6, with Muthusamy on a score of 39 runs in 86 deliveries. The batter is approaching his half century here in Guwahati. South Africa are on a score of 266/6 after 92 overs. Muthusamy and Verreynne are building a good partnership here. Siraj comes in to bowl the 93rd over. The star of day 1, Kuldeep Yadav has come into the attack here. He could be key for India today, as they look to break the Proteas' tailend. Jasprit Bumrah is constantly attacking the stumps in the early stages of the day 2. However, Verreynne and Muthusamy keep their defenses strong. After 86.4 overs, the score reads 253-6. The Proteas kick off day 2 of the clash with Muthusamy and Verreynne on the strike. Muthusamy on a score of 26 and Verreynne on 1. Proteas will hope to hold up and post a big total on the board. We continue the live coverage of the second Test between India and South Africa. The two sides are all set to kick off day 2 of the Test. The score reads 247/6 for the Proteas. Stay tuned for live updates throughout the day! India will be glad with a comeback of sorts in the final session, taking as many as four wickets, including the two set batters, Temba Bavuma and Tristan Stubbs. South Africa won't be too disappointed with their effort, but Tony de Zorzi losing his wicket in dying minutes will surely be gutted. Wiaan Mulder has thrown it away. He didn't come to the pitch of the ball and has ended up hitting straight to the fielder. South Africa are five down now! Wiaan Mulder and Tony de Zorzi are slowly doing the rebuilding which South Africa required after losing two set batters in quick succession. South Africa are 200 up and surely be targeting something in excess of 300. South Africa is four down, they lost Tristan Stubbs as well on a score of 49 runs. The score reads 188-4 after 63.3 overs. Temba Bavuma wanted to get it over the mid-off fielder but chipped it straight to Yashasvi Jaiswal, who took a good low catch as Ravindra Jadeja broke the 84-run partnership for the third wicket. South Africa are three down. Bavuma and Stubbs are back out in the middle. Souh Africa on a score of 156/2, as the two batters look to pose further problems for team India. With Tristan Stubbs and Temba Bavuma well set on the crease, the two will hope to take their partnership forward. On the other hand, team India will look to find ways to break the partnership after lunch. South Africa are cruising in Guwahati. The score reads 152-2 after 53.1 overs. Bavuma and Stubbs still on the crease as India continue their search for wickets. Tristan Stubbs and Temba Bavuma are still set on the crease. Stubbs has scored 22 and Bavuma has scored 32. Proteas now on a score of 142/2. Temba Bavuma and Tristan Stubbs are approaching 50 runs in their partnership, a very crucial one for the Proteas here. The score read 131-2 after 43 overs. South Africa are on a score of 113-2 after 37 overs, Bavuma and Stubbs are looking set on the crease, and they will hope to post a big total on the board here. South Africa have crossed 100 runs at the loss of two wickets. Bavuma and Stubbs are on the crease as India look for their third wicket here. Kuldeep Yadav strikes! Ryan Rickelton is the victim, and a brilliant catch by Rishabh Pant sees the second Proteas' batter fall. The score reads 82-2 after 27.2 overs. First wicket down for South Africa! Aiden Markram departs for 38, Jasprit Bumrah draws first blood. Proteas now 82-1. The duo of Aiden Markram and Ryan Rickelton are looking quite dangerous here in Guwahati. Both on 30+ scores now, India will look to break this partnership as soon as possible. Kuldeep Yadav has the ball in hand. After 18 overs, the score reads 59-0. India in search for a breakthrough here. India have used four bowlers so far, with Washington Sundar coming in now with the aim to get the breakthrough. Aiden Markram and Ryan Rickelton have been pretty solid so far and the pitch definitely looks a lot better, compared to the first one. India's search for a wicket continues as the hosts have let go of a chance, with Aiden Markram being dropped at the third slip by KL Rahul. Rahul planted his hands ahead of Sai Sudharsan, who was standing in the second slip and fluffed it. The chance goes begging and Jasprit Bumrah looks in agony. South Africa have scored 10 runs in three overs. Aiden Markram is yet to get off the mark, as India hope to pile on the pressure here in Guwahati. Ryan Rickelton and Aiden Markram are out in the middle! South Africa hopes for a good start with the bat. Jasprit Bumrah has the new ball in his hand. South Africa (Playing XI): Aiden Markram, Ryan Rickelton, Wiaan Mulder, Temba Bavuma(c), Tony de Zorzi, Tristan Stubbs, Kyle Verreynne(w), Marco Jansen, Senuran Muthusamy, Simon Harmer, Keshav Maharaj India (Playing XI): KL Rahul, Yashasvi Jaiswal, Sai Sudharsan, Dhruv Jurel, Rishabh Pant(w/c), Ravindra Jadeja, Nitish Kumar Reddy, Washington Sundar, Kuldeep Yadav, Jasprit Bumrah, Mohammed Siraj South Africa has won the toss and has opted to bat first in Guwahati. Temba Bavuma will hope for a similar performance in the second clash as the Proteas look to clinch the series. It is worth noting that this clash is the first-ever Test match being held in Guwahati. A historic moment for the city, as the toss is right around the corner at the Barsapara Stadium. It is worth noting that team India will take the field in the second Test without the services of Shubman Gill. The skipper misses out due to a neck injury, and the hosts will be led by Rishabh Pant in Guwahati. Welcome to the live coverage of the second Test of the ongoing series between India and South Africa! The two sides are all set to take on each other at the Barsapara Stadium in Guwahati, and with the toss rapidly approaching, stay tuned for live updates from throughout day 1 of the clash!</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/sports/cricket/ind-vs-sa-2nd-test-live-cricket-score-india-vs-south-africa-live-updates-rishabh-pant-temba-bavuma-barsapara-stadium-guwahati-1018577</t>
+  </si>
+  <si>
+    <t>Shah Rukh Khan pays tribute to 26/11, Pahalgam and Delhi blast victims: 'If we have peace...'</t>
+  </si>
+  <si>
+    <t>Bollywood superstar Shah Rukh Khan recently attended the Global Peace Honours 2025, held at the Gateway of India in Mumbai. During his speech, the Jawan actor paid tribute to the victims of the 26/11 attack, Pahalgam incident and the recent Delhi blast. 
+Advertisement He also shared heartfelt lines for the brave soldiers and jawans (soldiers) of the country. For the unversed, the Global Peace Honours 2025 event was organised by the Divyaj Foundation to mark the upcoming 17th anniversary of the 26/11 attacks. The event was led by Amruta Fadnavis, wife of Chief Minister Devendra Fadnavis.  
+Advertisement While delivering the powerful speech, Shah Rukh Khan said, "My humble tribute to the innocent people who lost their lives in the 26/11 terrorist attack, the Pahalgam terrorist attack, and the recent Delhi blasts and my respectful salute to our brave security personnel who were martyred in these attacks." He also shared a few lines for the courageous soldiers, saying, "Today, I have been asked to recite these four beautiful lines for the brave soldiers and jawans of the country...When someone asks you what you do, say with pride that I protect the country. If someone asks you how much you earn, smile slightly and say, I earn the blessings of 1.4 billion people. And if they turn around and ask you again, Aren't you ever afraid? Look them in the eye and say, those who attack us feel it...Let us all take steps towards peace together. Let us forget the caste, creed, and discrimination around us and walk the path of humanity so that the martyrdom of our heroes for the peace of our country is not in vain..." Shah Rukh Khan concluded his speech by saying, "If we have peace amongst us, nothing can shake India, nothing can defeat India and nothing can break the spirit of us Indians." Besides Shah Rukh Khan, the Global Peace Honours 2025 event was attended by several celebrities and notable personalities such as Nita Ambani, CM Devendra Fadnavis, Amruta Fadnavis, Tiger Shroff, Akanksha Malhotra, Kripashankar Singh, Manisha Koirala, Vikrant Massey, Archana Kochhar and others. Also Read: Palash Muchhal, Smriti Mandhana dance to 'Tenu Le Ke Main Jawanga' at their sangeet | Watch</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/entertainment/news/shah-rukh-khan-pays-tribute-to-26-11-pahalgam-and-delhi-blast-victims-if-we-have-peace-2025-11-23-1018717</t>
+  </si>
+  <si>
+    <t>French Navy debunks Pakistani media's Rafale losses claim, calls it 'extensive misinformation'</t>
+  </si>
+  <si>
+    <t>In yet another instance of anti-India propaganda, Pakistani media outlets have been caught circulating false claims regarding the May 2025 conflict between India and Pakistan. Reports published by Pakistan’s Geo TV alleged that a French naval commander had confirmed Pakistan’s “air superiority” over India and the supposed loss of Indian Rafale jets. However, the French Navy on Sunday strongly refuted the claims, labelling the reports as “extensive misinformation.”
+Advertisement “These statements were attributed to Captain Launay who never gave his consent for any form of publication. The article contains extensive misinformation and disinformation,” the French Navy said in its official clarification.  
+Advertisement The controversy began after Geo TV published an article claiming that French commander Captain Jaquis Launay had validated Pakistan’s dominance in the aerial engagements during Operation Sindoor, launched by India in May 2025. The report further alleged that the Pakistan Air Force (PAF) was “better prepared” than the Indian Air Force (IAF) and that a Rafale fighter jet had been downed not due to technical issues, but due to the “technological superiority” of China-supplied J-10C fighters. In May, India initiated Operation Sindoor in retaliation to the Pahalgam terror attack, which claimed 26 lives. The military engagement lasted several days before a ceasefire was reached at Pakistan’s request. Despite the sensitive nature of the conflict, Pakistani media outlets have repeatedly attempted to project fabricated victories. Pakistan’s false narrative did not go unnoticed. Social media users quickly called out the misleading report, while senior BJP leader Amit Malviya sharply criticised Pakistan’s propaganda machinery. “The French Navy has called out Pakistan’s Geo TV and its correspondent Hamid Mir for spreading ‘misinformation and disinformation.’ In his report, Hamid Mir peddled the same old, fabricated claims about Rafales and the so-called May conflict and has now been publicly exposed. When official institutions start debunking their propaganda, you know how desperate Pakistan’s misinformation machinery has become,” Malviya wrote.</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/news/world/french-navy-debunks-pakistani-media-s-rafale-losses-claim-calls-it-extensive-misinformation-2025-11-23-1018744</t>
+  </si>
+  <si>
+    <t>Huge twist in F1 title race as leader Lando Norris, Oscar Piastri disqualified from Las Vegas GP</t>
+  </si>
+  <si>
+    <t>In what is a big blow to Formula 1 title leader Lando Norris, both he and his partner and title rival Oscar Piastri have have been disqualified from the Las Vegas GP after failing the post-race inspection. This turns out to be great news for the third title contender, Max Verstappen, who is now just 24 points behind the leader Norris and equal on points with Piastri at 366.
+Advertisement "McLaren drivers Lando Norris and Oscar Piastri have been disqualified from the Las Vegas Grand Prix after both their cars were found not to comply with technical regulations," the Formula 1 website confirmed in a release.  
+Advertisement "As a result, race winner Max Verstappen has made a significant gain with regards to the 2025 Drivers' Championship, as the Red Bull man now sits level on points with Oscar Piastri on 366. Lando Norris is 24 points ahead on 390 at the top of the standings with just two rounds of the season to go," the body added. The two McLarens failed the post-race inspection. On inspection by the technical delegates, the rearmost skid wear on both McLaren MCL39 machines was below the minimum 9mm. As per the document from the stewards, the skid blocks on both cars were "measured and found to be below the minimum thickness of 9mm specified under Article 3.5.9 of the Technical Regulations. "The relevant measurements were RHS Front 8.88mm, RHS Rear 8.93mm. The measuring device was a Mitutoyo Micrometre purchased in May 2025, and according to the manufacturer’s specifications, accurate to within 0.001mm. "The rear skids were re-measured in the presence of the Stewards and the three McLaren representatives, and those measurements confirmed that the skids did not comply with the regulations. The relevant measurements were even lower than those measured originally by the Technical Delegate." The F1 title race now gets much more interesting as Norris' lead of 30 points over Piastri and of 42 over Verstappen has now been cut down to 24 points from the two racers. Two races and a Sprint remain with 58 points on offer.</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/sports/formula-1/huge-blow-to-f1-title-leader-lando-norris-as-mclarens-disqualified-from-las-vegas-gp-2025-11-23-1018739</t>
+  </si>
+  <si>
+    <t>Centre clarifies no bill on Chandigarh administration in Parliament's Winter Session</t>
+  </si>
+  <si>
+    <t>The Ministry of Home Affairs (MHA) clarified that the proposal to simplify the Central Government’s law-making process for Chandigarh is still under consideration, and no final decision has been taken. The government emphasized that the plan does not seek to alter Chandigarh’s governance or administrative structure, nor does it aim to change the traditional arrangements between Chandigarh and the states of Punjab or Haryana.
+Advertisement The MHA further stated that any decision regarding the Union Territory will be made only after adequate consultations with all stakeholders, keeping Chandigarh’s interests in mind. The Central Government reassured that there is no need for concern and confirmed that it has no intention of introducing any bill on this matter in the upcoming Winter Session of Parliament.  
+Advertisement Earlier, a Parliament bulletin had listed the Constitution (131st Amendment) Bill 2025, which proposed bringing Chandigarh under Article 240 of the Constitution, giving the President direct powers to make regulations for the Union Territory. The move faced strong opposition from Punjab politicians, prompting the Centre to clarify that the Bill would not be tabled in the upcoming Winter Session. Article 240 of the Indian Constitution empowers the President of India to frame administrative regulations for the peace and good governance of Union Territories, including the Andaman and Nicobar Islands, Lakshadweep, Dadra and Nagar Haveli, Daman and Diu, and Puducherry. Had Chandigarh been brought under Article 240, the President would have the authority to appoint a Lieutenant Governor to administer the Union Territory, whereas currently, the Punjab Governor holds the additional charge as Chandigarh's administrative head. The Home Ministry stressed that the proposal does not involve altering Chandigarh's governance or its traditional relations with Punjab or Haryana. “An appropriate decision will be taken only after adequate consultation with all stakeholders, keeping Chandigarh's interests in mind. There is no need for concern on this matter,” the MHA said. Punjab leaders across parties expressed concerns over the proposed Bill. AAP Chief Minister Bhagwant Mann called it a conspiracy to "snatch Punjab’s capital," while Punjab Congress chief Amarinder Singh Raja Warring described it as "totally uncalled for." Akali Dal chief Sukhbir Singh Badal termed the move an “anti-Punjab Bill” and a “blatant attack on federal structure.” Punjab BJP chief Sunil Jakhar reaffirmed that Chandigarh is an “integral part of Punjab” and assured that the state’s interests would remain a priority. The MHA reiterated that no final decision has been taken and that any action will involve consultation with all stakeholders. The clarification aims to address concerns and prevent misunderstandings about the status and administration of Chandigarh ahead of the Winter Session.</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/news/india/centre-clarifies-no-bill-on-chandigarh-administration-in-parliament-s-winter-session-2025-11-23-1018725</t>
+  </si>
+  <si>
+    <t>IAF Wing Commander Namansh Syal's mortal remains reach Himachal, last rites in Kangra today</t>
+  </si>
+  <si>
+    <t>The mortal remains of Indian Air Force (IAF) pilot Wing Commander Namansh Syal, who tragically lost his life in the LCA Tejas crash in Dubai, were brought to Himachal Pradesh’s Kangra airport on Sunday. From there, they were taken to his native village, Patiyalkar, in Kangra district for the last rites. The single-engine light combat aircraft crashed around 3:40 pm IST during a demonstration flight in Dubai, which had been scheduled to last eight minutes.
+Advertisement Before reaching Himachal Pradesh, Wing Commander Syal’s body was flown to Sulur Air Force Station near Coimbatore, Tamil Nadu. Coimbatore District Collector Pavankumar G. Giriyappanavar paid tribute by laying a wreath at the base, while IAF personnel and local officials honoured the fallen pilot for his service and bravery.  
+Advertisement Syal, in his mid-30s, is survived by his father, mother, his wife—who also serves in the Air Force—and their six-year-old daughter. The couple had met during their first posting in Pathankot and married in 2014. Villagers from Patiyalkar described him as a dedicated officer and an outstanding athlete, who exemplified courage even in his final moments by diverting the aircraft to avoid casualties at the airshow. (Image Source : PTI) Mortal remains of Wing Commander Namansh Syal, Emotional scenes were witnessed at Syal’s family home in Nagrota Bagwan, with relatives and villagers mourning the loss. Pankaj Chadha, a former schoolmate from Sainik School Sujanpur Tira, said, “We have lost one of our gems. He was the pride of our school.” Rajiv Jamwal from Palampur added, “He was the best performer in the Air Force too. We have come to pay respect to our very own pilot Namansh.” According to Jogindernath Syal, Namansh's uncle, the mortal remains arrived at Sulur Air Force Station on Saturday morning and were flown to Gaggal airport in Kangra on Sunday. “We have made all arrangements for the cremation,” he said, as the village prepares to bid a final farewell to its brave son. (Image Source : PTI)Mortal remains of Wing Commander Namansh Syal, who lost his life in the LCA Tejas crash during the Dubai Air Show on Friday, brought to the Sulur Air Base for last rites, in Coimbatore. On Sunday, the mortal remains Syal were brought to Sulur Air Force Station near Coimbatore, Tamil Nadu, and received with full military honours. The Indian Air Force (IAF) carried out a solemn repatriation of the pilot, who sustained fatal injuries during the aerial display at the Dubai Air Show 2025. An IAF C-130 aircraft transported his body to the Southern Air Command, where Coimbatore District Collector Pavankumar G. Giriyappanavar laid a wreath to pay tribute to the fallen officer. (Image Source : PTI)Officials lay a wreath on the mortal remains of Wing Commander Namansh Syal, who lost his life in the LCA Tejas crash during the Dubai Air Show on Friday, at the Sulur Air Base, in Coimbatore. Following the ceremony at Sulur, the mortal remains were flown to Wing Commander Syal’s ancestral home in Kangra, Himachal Pradesh, for the last rites, once again accompanied by full military honours. The IAF stated that all personnel of the Southern Air Command stand in solidarity with the bereaved family during this moment of profound loss, ensuring a dignified farewell to the officer who laid down his life in the line of duty.</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/news/india/iaf-wing-commander-namansh-syal-last-rites-patiyalkar-kangra-wife-afshan-lca-tejas-crash-dubai-latest-updates-2025-11-23-1018733</t>
+  </si>
+  <si>
+    <t>Russia launches largest attack of the year on Ukraine; 33 killed as Zelenskyy urges stronger air defence</t>
+  </si>
+  <si>
+    <t>Russia carried out its biggest assault of 2025 on Ukraine on Saturday, launching more than 1,050 attack drones and 1,000 glide bombs across multiple cities, even as former US President Donald Trump pushed a new peace proposal. At least 33 people, including six children, were killed, while dozens were injured. Six people remain trapped under debris, according to Ukrainian authorities.
+Advertisement Ukrainian President Volodymyr Zelenskyy posted videos of the destruction on X (formerly Twitter) on Sunday, confirming that rescue operations in Ternopil had concluded after four days of continuous work.  
+Advertisement “Thirty-three people, including six children, have been killed as a result of this Russian crime. My deepest condolences to the bereaved families,” Zelensky wrote. He added that six more individuals remain missing and thanked all rescue workers for their relentless efforts. Zelenskyy said emergency operations are still underway in Dnipro, where a Russian drone struck near a residential building, injuring 14 people, including a child. In Nikopol, an FPV drone attack injured two children and one woman. Zelensky noted that residential areas, civilian infrastructure, and energy facilities across various regions were targeted throughout the week, reflecting a sustained escalation in Russian strikes. Detailing the scale of the assault, Zelensky stated that Russia deployed over 1,050 attack drones, nearly 1,000 glide bombs, and more than 60 missiles of different types. He added that Ukrainian advisers would hold discussions in Switzerland with representatives from the United States, Germany, France, and the United Kingdom to strengthen Ukraine’s defence strategy. The Ukrainian president stressed the urgent need to speed up international commitments on air defence systems and missiles, saying it is crucial to counter such massive Russian attacks. “We must do everything possible to strengthen our defence against these malignant Russian strikes,” Zelensky said, thanking all nations and volunteers working to save lives and support peace efforts. The latest attack underscores the severe escalation on the battlefield, even as diplomatic talks continue internationally.</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/news/world/russia-launches-largest-attack-of-the-year-on-ukraine-33-killed-as-zelenskyy-urges-stronger-air-defence-2025-11-23-1018741</t>
+  </si>
+  <si>
+    <t>Gujarat: Bhavnagar Municipal Corporation clears illegal encroachments near Madarsa under police security</t>
+  </si>
+  <si>
+    <t>In Bhavnagar district’s Akwada locality, a significant demolition drive is underway to complete the 24-meter-wide TP Road. The authorities in Gujarat have removed illegal encroachments covering 1,500 square meters in and around the Darul Ulum Madarsa to facilitate this infrastructure project. The demolition work is progressing peacefully under tight security maintained by the Bhavnagar district police and municipal corporation teams.
+Advertisement The operation began early in the morning, involving heavy machinery including four JCBs and three Hitachi excavators. The municipal corporation bulldozed six illegally constructed flats and one hostel room adjacent to the madrasa, clearing substantial space for the road expansion. Approximately 150 police personnel, along with specialised units like LCB and SOG, have been deployed to prevent any disturbances and ensure smooth execution of the demolition work.  
+Advertisement DSP Nitesh Pandey said, "One block of a madrassa was blocking the work of road development and it is being demolished after a due legal process. We have deployed 150 police officials for the security here... The police are patrolling in different regions of the city to maintain law and order." Residents living in the flats and hostel vacated the premises with their belongings before demolition began. Authorities clarified that only illegal constructions obstructing the TP Road were targeted- not the madarsa's core structure. The municipal corporation has previously issued notices to the encroachers as the demolitions followed due legal process. This clearance campaign is part of a larger municipal effort to remove encroachments obstructing public infrastructure development. The Bhavnagar clearance operation reflects broader state efforts to reclaim public land for the intended communal and infrastructural benefits. The authorities are committed to enforcing law and order during these operations, deploying adequate police forces to maintain peace and order. Similar demolition drives are ongoing across Gujarat, including in Gir Somnath district where over 1,300 square meters of encroached land was freed. The state government, reaffirming its zero-tolerance stand, continues to target illegal religious, commercial, and residential structures on government land to open spaces for parks, playgrounds, community centers, and other public facilities.</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/gujarat/gujarat-demolition-drive-bhavnagar-municipal-corporation-clears-illegal-encroachments-near-darul-ulum-madarsa-under-police-security-video-2025-11-23-1018718</t>
+  </si>
+  <si>
+    <t>Bangladesh protests: People take to streets, opposition demands extradition of Sheikh Hasina</t>
+  </si>
+  <si>
+    <t>The streets of Dhaka, Bangladesh’s capital, were once again filled with protesters on Saturday, with demonstrations spreading to several other cities. Thousands of people took to the streets demanding that former Prime Minister Sheikh Hasina be brought to the country and executed following a court ruling. On November 17, Hasina was sentenced to death by the International Crimes Tribunal (ICT) for alleged killings during the 2024 student protests. Former Home Minister Asaduzzaman Khan Kamal also received a similar sentence for crimes against humanity. Hasina was not present in court when the verdict was announced.
+Advertisement Following the court’s ruling, tensions escalated sharply in Bangladesh. On Sunday, a joint rally was held by the main opposition Bangladesh Nationalist Party (BNP) and the Islamic organisation Jamaat-e-Islami. Protesters marched from the Dhaka University campus to Shahbagh Chowrangi, raising slogans such as “Give Hasina the death penalty,” “Extradite from India,” and “Ensure justice.” Student organisations, families of victims, and political activists participated. Dhaka University student R. Rafi stated, “Hasina ordered the killing of our brothers and sisters. Death is the only justice.”  
+Advertisement During the rally, BNP General Secretary Mirza Fakhrul Islam Alamgir described the verdict as “the end of dictatorship” and urged India to hand over the “fugitive.” Jamaat-e-Islami General Secretary Mia Golam Parwar called it the “aspiration of 18 million people” and stressed the need for a fair process compared to previous trials. The 2024 student movement in July-August had protested against the reinstatement of a 30% quota in government jobs, during which Hasina’s government was accused of using excessive force. According to UN reports, over 1,400 people were killed and 14,000 were injured. Interim government head Muhammad Yunus has promised elections in February 2026, but tensions have risen due to the ban on the Awami League. Hasina’s supporters called for a “lockdown” between November 13 and 17, disrupting traffic in Dhaka and leading to buses being set on fire. During Sunday’s rally, Jamaat and seven other parties also demanded election reforms while controversially labelling the Ahmadiyya community as “kafir.” Police resorted to baton charges and tear gas, leaving dozens injured. The “Moulik Bangla” group staged a symbolic hanging of Hasina in Shahbagh. Former IGP Chowdhury Abdullah Al-Mamun testified against Hasina but received a light sentence. Amnesty International criticised the trial as “unfair,” while the United Nations called for justice but opposed the death penalty. Sheikh Hasina described the sentence as “political revenge.” Experts warn that the ruling could increase instability ahead of elections, especially amid the Awami League boycott. Families of victims argued that “justice remains incomplete without the death penalty.” While BNP and Jamaat displayed unity in the protests, concerns over Islamic extremism have added further complexity. Meanwhile, the Hindu minority in Bangladesh continues to face escalating challenges, with the Dhaka-based HRCBM (Human Rights Congress for Bangladeshi Minorities) reporting over 2,200 cases between January and December 2024, including attacks on Hindus, temple vandalism, blasphemy allegations, abduction of 94 girls (half of whom remain missing), 50 cases of forced religious conversions, and 1,190 instances of rape or harassment; most cases were registered as FIRs but saw little action, prompting the NGO to file court cases to pressurise authorities, while its General Secretary Rudra highlighted the worsening conditions and urgent need for protection for the Hindu community.</t>
+  </si>
+  <si>
+    <t>https://www.indiatvnews.com/news/world/bangladesh-protests-people-take-to-streets-opposition-demands-extradition-of-sheikh-hasina-2025-11-23-1018720</t>
+  </si>
+  <si>
+    <t>HindustanTime_Crawler</t>
+  </si>
+  <si>
+    <t>Guest Column | Digital duniya, AI and human beings</t>
+  </si>
+  <si>
+    <t>I joined an online book club sometime back. One day, one of the quite active and contributing members shared that during olden days scarcity of things lent a charm to the few that one had or could procure. A parallel was drawn with the world of books that getting to hold a desired title was a luxury back then. But now, with scores of e-books and online reading material available, hardcopies lose their value and/or charm. Though there’s another dimension to all this - about the smell of new (and old) books, about the delight when a recommended book was spotted at the shelf of the local bookstore, I would just stick to the point already made by picking the words of that dear member and adding my two cents to it – Endless access to something makes us take it for granted and the value of the thing is then lost upon us. Examples galore – back in childhood we used to get cassettes recorded with our favourite songs, but with YouTube and ease of MP3 files, the music we listen to is not exactly curated/ that intentionally selected. For example, ordering things on Amazon/Flipkart /any other platform reduces the entire previous fun of visiting shop after shop (sometimes to return to the first shop itself) for getting the best deal, to scrolling and further scrolling till the cheapest yet (seemingly) best quality product comes into the vision. Don’t get me wrong for I don’t intend to harp on ‘old times vs present times’. Change, anyhow, as they say, is the only permanent thing in life. And I am a big advocate of accepting this and changing cum evolving, if need be, but sometimes purposeful initiatives are needed in present times, to add value and meaning to our days. For instance, while we have the option and convenience of ordering groceries for our home from apps like Blinkit, my father takes my just-turned-teenager son every Sunday to fruit, vegetable and grocery shops for reaping multiple benefits - like engaging youngsters of the home in household activities, for a mini ‘boys outing’, for teaching my son ‘offline shopping’ and to meet fellow customers and different shopkeepers and hold light conversations, etc. On another yet similar note, questions have started coming up at various societal levels about artificial intelligence replacing humans. Computers, digital world and artificial intelligence – everything is meant to enhance and ease our experiences as human beings. Ultimately, I firmly believe it’s in our hands how much power we lend to them. They will assist us, if we choose so. Yes, they can surpass us; but only if we let them. So, if we can deliberately take measures to curtail the disadvantages and harness maximum benefits out of these, the battle can be won, at least for the time being. And before offering some pointers in that direction, I’d lay the foundation stone by mentioning that this battle (if I may already use the word), is not between AI and humans, but it is a kind of a conflict within the human psyche. Limit your screen time Whatever we give our time and efforts most to, will fruition – goes for both constructive and destructive pursuits. We urgently need to assess the hours that we are spending glued to our screens, and monitor the same. While the internet and gadgets are an unavoidable part of life now, we are still homo sapiens, with certain still-primitive wirings of the brain. We still seek immediate gratification of our various desires. But while WiFi and Google might satisfy in the short-run, they won’t sustain a lifetime of companionship and bonds. Learn more real-life skills Computer literacy is highly needed, but so are real-life skills like decision-making, confidence and genuine empathy (the list can be endless). ChatGPT cannot replace actual therapy, neither can Zomato/Swiggy replace our kitchens with recipes-handed-down generation after generation – unless we are willing to play a slow havoc with our mind and body. Find joy in simple things There’s so much contentment in watching one’s favourite people laugh – can the same intensity of joy and satisfaction be achieved via emojis? Isn’t feeling the texture of a to-be-purchased cloth also quite a livening-up act? Let us not forget the small and home-based businesses. Let us begin to smell the jasmine instead of just clicking it for Instagram. Last but not the least, life is best done ‘in reality’, virtual life might smoothen and add-on to that; but, let’s resolve not to let it overtake the essence. (The writer is an assistant professor of psychology at Rajiv Gandhi Government College, Saha)</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/guest-column-digital-duniya-ai-and-human-beings-101763846925085.html</t>
+  </si>
+  <si>
+    <t>India still sees through 1971 prism but Bangladesh has moved on: Deep Halder</t>
+  </si>
+  <si>
+    <t>While India may still view Bangladesh through the prism of the 1971 Liberation War which freed it from Pakistan, the neighbouring country has undergone a fundamental shift in its identity, experts at a panel discussion at the 13th Edition of CLF Literati 2025, being organised by the Chandigarh Literary Society(CLS), which kicked off at the Lake Club on Saturday. Titled ‘Bangladesh: The story of an unfinished revolution’, the discussion featured journalist and author Deep Halder besides author and researcher Rami Desai, and was moderated by senior journalist Kartikeya Sharma. Halder’s book, ‘Inshallah Bangladesh’, which looks at the events leading up to the downfall of the Sheikh Hasina government in 2024, was launched during the event. Explaining why the newer generation in Bangladesh may not identify with India’s portrayal of it, Halder said, “If you do the math, somebody who was in their early 20s during the 1971 war, that gentleman or lady may be in the later stages of their lives now. So, while India tends to look at Bangladesh through the prism of 1971, the new generation may not look at it like that anymore.” He added that the “anti-India” sentiment was rampant in the country even during Hasina’s regime. “In the interiors of Bangladesh, citizens increasingly view India as a ‘Big Brother’ that interferes in its domestic politics by running the country through rigged elections and dummy prime ministers,” Halder said. Desai echoed similar views, “We look at the 1971 war as though it brought a loyalty towards India... but the fact of the matter is that there was always a simmering group, which wanted to be a part of Pakistan even then.” There is a level of radicalisation in the country, which, Desai says, leaves a lot of scope for manipulation (by anti-India forces) and it is something that India will have to deal with.</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/india-still-sees-through-1971-prism-but-bangladesh-has-moved-on-101763846620840.html</t>
+  </si>
+  <si>
+    <t>It’s story that makes an ad powerful, not the product: Prahlad Kakkar</t>
+  </si>
+  <si>
+    <t>The Chandigarh LitFest being organised at the Lake Club, on Saturday, hosted a deep dive into the craft of advertising with acclaimed ad film director Prahlad Kakkar, who headlined the session ‘The Power of Story: Advertising Insights.’ In a neutral yet evocative tone, Kakkar asserted that “Advertisement is an art of story-telling. It is the story that adds value, the story that makes it powerful, not the product.” Kakkar captivated the audience by delving into the world of ideas and creativity, sweeping them with a wave of nostalgia by showcasing his most iconic ad films from the 90s, including the memorable Pepsi advertisements featuring cricketing legend Sachin Tendulkar and actor Shah Rukh Khan. He recalled that his imagination was consistently fuelled by listening to stories narrated by his grandparents during his childhood. Showcasing the highly popular 90’s ad with the tagline ‘Yeh Dil Maange More’, which featured children wearing Tendulkar’s masks, Prahlad described how the film was conceptualised around the joy of the icon surprising his young fans. The core idea was that the children were playing cricket wearing Sachin masks, and Tendulkar would unmask to reveal himself as a surprise. The power of authenticity Kakkar detailed the authentic approach taken during the filming of the surprise moment. He emphasised that the children, who were from economically weaker sections, had no clue that Sachin Tendulkar would actually be present. “I wanted to capture their actual expressions on seeing Sachin in person as the cricketer removed his mask,” he stated, adding, “I told the cameraman he only has one shot and there will be no retake.” He recounted the deeply touching moment of the surprise: “I remember one of the kids pinched Sachin’s shirt to believe it was actually true.” Reflecting on his personal journey, Kakkar revealed that the oral tradition of storytelling grew with him. He shared that he was dyslexic as a child and was not interested in studies. “To escape the drudgery of school, I used to create stories,” he confessed, concluding, “A product becomes relevant with the story and the great ads are the one which touches one’s heart.” He also offered a life lesson, saying he learned very early in life to laugh at himself. “If you develop the confidence and the panache to carry this off, to not pay heed to criticism, then one is able to carve his own niche,” he advised. ‘Reading builds imagination’ Prahlad concluded the session by expressing his sorrow that children these days have stopped reading. He contrasted visual media with books, arguing, “A story that you see on television is like packaged food, there is no imagination.” He stressed the link between reading and creativity: “When you read a book, like for example Harry Potter, you imagine him, that sparks creativity and thrill. Only when you read can you imagine.”</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/its-story-that-makes-an-ad-powerful-not-the-product-prahlad-kakkar-101763846857310.html</t>
+  </si>
+  <si>
+    <t>Guest Column | Beyond the barricades: Of voice, space &amp; power</t>
+  </si>
+  <si>
+    <t>When the red-brick corridors of Panjab University (PU) echo with chants instead of lectures, it feels like more than a campus disturbance. The university, that grand old institution straddling history and aspiration, has once again become a mirror reflecting how India’s public universities are wrestling with a contemporary question: who gets to decide what autonomy really means. From senate seats to street chants For over two weeks, PU has lived in protest mode. What began as opposition to an October notification by the ministry of education, which proposed a downsized and partly nominated senate and syndicate, has grown into a wider debate on institutional democracy. The Centre’s notification, which sought to trim the senate from 91 to 31 members, was paused on November 7 after objections from faculty, students, and alumni. But the pause did little to calm tempers. The demand now is clear: hold the long-pending senate elections, overdue since 2020. The Panjab University Bachao Morcha, a collective of teachers and students, argues that without elections, representation withers into tokenism. The administration maintains that delays are procedural rather than political. It insists academic life cannot stop every time governance turns turbulent. Both camps are protecting the same ideal of autonomy, only through different definitions of it. Why the senate still matters The Panjab University senate is not a ceremonial relic. Created under the 1947 Panjab University Act, it brings together teachers, graduates, and government nominees from Punjab, Haryana, Himachal and Chandigarh, making it a rare federal model in a time of increasing centralisation. Historically, this senate was never just a bureaucratic body. It was the conscience of the university. Its debates once shaped academic priorities, regional policies, and even the city’s cultural life. Reducing its size may appear efficient on paper, but in practice it risks thinning the voices that give the institution its democratic character. Across India, similar tensions have surfaced in recent years, from Delhi University’s disputes over appointments to Visva-Bharati’s governance controversies. The University Grants Commission’s 2023 note calling for “streamlined structures” may have been well-intentioned, but it raised an old question: can efficiency and democracy truly coexist in the same classroom? That this debate unfolds in Chandigarh adds irony. Le Corbusier’s city was designed on a grid of perfect order, the promise that geometry could civilise chaos. Yet institutions, like cities, need a measure of disorder to stay alive. For decades, PU has embodied that balance. Its open lawns and low-slung corridors welcomed first-generation learners, poets in waiting, and future administrators alike. The affidavit circulated earlier this year, asking students to pledge not to protest without permission, struck a jarring note. It seemed to turn civic space into controlled space. But this is not a simple story of youth versus authority. Administrators face real constraints such as limited funding, politicised unions and the challenge of maintaining continuity. The protests are not rebellion for its own sake; they are a plea for conversation. What is unfolding at PU is less a standoff and more a stress test of India’s democratic design. Governance structures need reform, but process matters as much as intent. Universities, after all, are rehearsal spaces for democracy, where dissent teaches as much as discussion. If nominated bodies replace elected ones, decisions may become faster but trust slower to build. And legitimacy, unlike order, cannot be enforced; it must be earned. As evening falls and students linger around the Arts Block steps, the chants soften into conversation. It is a reminder that democracy does not disappear when it is loud. It disappears when it falls silent. Much like Chandigarh itself, the challenge before Panjab University is one of proportion: to find a design that allows both structure and voice to coexist without one overpowering the other. aashna.gakhar@gmail.com (The writer is a Chandigarh-based architect &amp; interior designer)</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/guest-column-beyond-the-barricades-of-voice-space-power-101763846738765.html</t>
+  </si>
+  <si>
+    <t>Chandigarh set for another turbulent day as farmers, PU groups brace for major protests on Nov 26</t>
+  </si>
+  <si>
+    <t>Chandigarh is bracing for a day of severe disruptions on November 26, with two major mobilisations—the fifth anniversary march of the Samyukta Kisan Morcha (SKM) and a complete shutdown called by the Panjab University Bachao Morcha—expected to converge into a high-pressure law and order challenge for the city. Residents across the tricity may face gridlocks, movement restrictions and possible border closures as police prepare crowd-control measures. The largest mobilisation is likely to come from the SKM, which will mark the fifth anniversary of the farmers’ agitation against the now-repealed three farm laws. While SKM and central trade unions have called for nationwide demonstrations, farmers from Punjab are preparing to march towards Chandigarh in significant numbers. Farmer leader Joginder Singh Ugrahan, who heads the BKU (Ekta-Ugrahan) said their demand for a protest site is currently under consideration. “We have sought the Sector 34 ground as the location for our protest site and more than 5,000 farmers are expected to join the protest in Chandigarh. The administration is going to give us a location during a meeting on November 24,” he said. Last year in September, thousands of farmers converged onto Chandigarh for a state-level dharna and stayed for over five days. They came with lodgings set up in trucks and ration supplies stocked in huge containers. The five-day demonstration drew thousands of farmers under the banner of the Bharti Kisan Union (Ugrahan), officially ended after assurances from Punjab chief minister Bhagwant Mann. Adding to the city’s security concerns, the PU Bachao Morcha has announced a complete shutdown of Panjab University (PU) on November 26. The group has also threatened to gherao BJP offices in Chandigarh and Punjab if the long-pending senate election schedule is not announced by November 25. The call for a shutdown comes just days after the November 10 protest, which threw the tricity into disarray. With PU borders sealed, commuters were stranded for hours and multiple arterial roads were choked. The campus witnessed open lawlessness as protesters—primarily from Punjab—stormed the university by breaking open locked gates. Police later registered a criminal case over the violent incidents. Leaders of the PU Bachao Morcha say that while the scale of the November 26 mobilisation is expected to be smaller than the previous one—around 1,000–1,500 people—the gathering could still draw sizeable participation. Students from nearby villages, PU students, members of major kisan unions, and civil society groups who have been supporting the agitation over the senate election delay are expected to join. Though the call this time is not as broad as the November 10 action, the overlapping of the PU shutdown with the SKM’s farmers’ march is likely to create pressure points across key entry roads, university-adjacent sectors, and central junctions. The Chandigarh police is expected to issue traffic and security advisories closer to the date, with possible barricading and diversions. “We have not decided to seal the borders yet, but a heavy police force will be deployed to ensure the mobilisation does not turn unruly. We are monitoring the situation closely and have been in talks with farmers’ unions to finalise a designated protest site,” said a senior police official.</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/chandigarh-set-for-another-turbulent-day-as-farmers-pu-groups-brace-for-major-protests-on-nov-26-101763846317113.html</t>
+  </si>
+  <si>
+    <t>Amid protests, Vice-President CP Radhakrishnan postpones maiden visit to PU</t>
+  </si>
+  <si>
+    <t>Vice-President of India CP Radhakrishnan, who is the Chancellor of Panjab University, has cancelled his maiden visit to the varsity amid the ongoing senate election protest. The V-P, who is yet to visit Chandigarh after assuming office in September this year, had specially directed PU to schedule its convocation for December. But the V-P’s office has now confirmed that he won’t be attending the PU convocation scheduled for December 13. While the official reason given for the cancellation is a busy schedule, PU sources have confirmed that this move has been taken in view of the protest for the senate elections, which has now gone on for over a month now. PU vice-chancellor Renu Vig also confirmed that the V-P won’t visit, but the cited the Chancellor’s busy schedule as the reason. As per officials, it is not just students protests that are a cause of worry -- outsider influx is also security issue. Even during last year’s convocation, a protest for the senate elections was witnessed during which effigies were also burnt by students on campus. With the Chancellor’s cancellation, PU may look at rescheduling the convocation to early 2026. PU officials added that the impact of the protests can also be seen on other events planned in the varsity. The venue for the India International Science Festival, which is to kick off on December 6, has been shifted from PU to Panchkula. Higher officials of the Union Ministry of Earth Sciences are expected to attend it. As per officials, they had also looked at cancelling the entire event or just holding the inaugural event in Panchkula while having the main academic events on campus but now they have decided to shift the venue to Dusshera Ground, Panchkula. The Panjab University Bachao Morcha on Saturday reiterated that no examinations scheduled for November 26 will be allowed to take place, asserting that the PU bandh will go ahead as planned. Morcha leaders said that holding exams on the day of the shutdown would “defeat the very purpose” of their protest, which demands the immediate announcement of the long pending senate electionschedule. Tensions escalated earlier in the day after an all-party meeting called by the dean students welfare (DSW) failed to materialise. The meeting was intended to bring together all student organisations to discuss the November 26 bandh and the possible postponement of exams. It was essentially called to inform them that the Student Council, in a meeting held on Friday, had unanimously suggested that the postponement should not take place but Morcha leaders refused to participate upon learning that Akhil Bharatiya Vidyarthi Parishad (ABVP) members werepresent. The Morcha has been adamant that it would not sit for discussions alongside Akhil Bharatiya Vidyarthi Parishad (ABVP) representatives. The standoff comes a day after the PU Student Council-dominated by ABVP-formally opposed the bandh call, arguing that academic processes should not be disrupted. Morcha leaders, however, maintained their stance. “What’s the point of a shutdown if exams still take place?” said Raman, one of the Morcha representatives. He added that the group has also urged all shopkeepers on campus to keep their establishments closed on November 26, aiming for a complete halt of normal activity to press their demands.</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/amid-protests-vice-president-cp-radhakrishnan-postpones-maiden-visit-to-pu-101763846137364.html</t>
+  </si>
+  <si>
+    <t>Edu dept on PSPCL defaulters’ list: Ludhiana govt schools rack up over ₹2cr in unpaid electricity bills</t>
+  </si>
+  <si>
+    <t>Government schools in the district have accumulated a staggering ₹2.37 crore in unpaid electricity bills, placing the school education department on the defaulters’ list of the Punjab State Power Corporation Limited (PSPCL), officials aware of the matter said. Despite repeated reminders and notices from the PSPCL, the dues continue to mount. According to PSPCL data, the unpaid bills are spread across multiple zones in the district: ₹33.15 lakh from the East Circle, ₹52.54 lakh from the West Circle, ₹108.70 lakh from the Suburban Circle, and ₹43.19 lakh from the Khanna Circle. School officials said the bills have piled up due to delayed and insufficient fund release by the department. Sukhdhir Singh Sekhon, head teacher of Government Primary School, Moti Nagar, said, “The dues have crossed lakhs of rupees, but the department hasn’t released the necessary funds. Even when funds arrive, they are far too little to clear the electricity bills.” Schools have installed solar panels to reduce electricity usage, but many are either dysfunctional or inefficient, leading to continued high consumption and mounting bills. Another teacher, speaking on condition of anonymity, said, “Schools with higher enrolment naturally consume more electricity for lighting, fans and equipment. When bills aren’t cleared on time, repeated notices become embarrassing to justify, even though usage is beyond our control.” Officials from the electricity department confirmed that notices are sent after a month of non-payment and schools are expected to clear bills like any other consumer. Deputy district education officer (Elementary) Manoj Kumar assured that schools will not face punitive action. “The bills will be cleared by the department. Power supply will not be discontinued nor the schools will be penalised by the power corporation,” he said.</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/edu-dept-on-pspcl-defaulters-list-ludhiana-govt-schools-rack-up-over-2cr-in-unpaid-electricity-bills-101763840557725.html</t>
+  </si>
+  <si>
+    <t>2018 Maqsudan police station grenade attack: NIA court rejects bail pleas of three accused</t>
+  </si>
+  <si>
+    <t>The Special NIA Court has rejected the bail applications of three accused involved in the 2018 grenade attack on the Maqsudan police station in Jalandhar, holding that the seriousness of the terror charges and the evidence presented by the prosecution do not justify their release. The court dismissed the bail pleas of Aamir Nazir, Shahid Qayoom and Fazil Bashir Pinchoo, all residents of Pulwama in Jammu and Kashmir, who have been in custody for their alleged roles in the attack. According to the prosecution, the case stems from the incident of September 14, 2018, when four grenades were hurled at the Maqsudan police station building, injuring a police personnel and triggering panic across the area. The prosecution stated that the attack was executed to target law enforcement and create widespread fear. The prosecution highlighted that Shahid and Fazil were then students at a private engineering college and were allegedly recruited to support Ansar Ghazwat-ul-Hind’soperational modules. The accused are charged under Indian Penal Code (IPC) Sections 307 (attempt to murder) and 120-B (criminal conspiracy), along with stringent provisions of the Unlawful Activities (Prevention) Act, including Sections 10, 13, 15, 16, 18, 20 and 23. After examining the arguments from both sides, the court held that the allegations involve serious terrorism-related offences and that bail cannot be considered in such circumstances. The court observed that the nature of the attack, the intention behind it, and the claimed links of the accused with AGH module make their release legally untenable. All three accused will continue in judicial custody.</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/2018-maqsudan-police-station-grenade-attack-nia-court-rejects-bail-pleas-of-three-accused-101763840555613.html</t>
+  </si>
+  <si>
+    <t>Punjab BJP Mahila Morcha hold protest over ‘unkept’ ₹1,000 poll promise, AAP hits back</t>
+  </si>
+  <si>
+    <t>Punjab BJP’s Mahila Morcha on Saturday held a protest against the Aam Aadmi Party (AAP) government for failing to fulfil its poll promise of giving ₹1,000 monthly to women. Protesters led by Mahila Morcha state president Jai Inder Kaur tried to force their way through police barricades to gherao the Punjab chief minister’s camp office but were detained. The protesters were released later. The protesters alleged that it has been nearly 45 months since November 22, 2021, when AAP supremo Arvind Kejriwal made the promise during a rally in Moga. “We are demanding ₹45,000 due from the Punjab AAP government, as per their poll promise, should be released. Today, 45 months have passed, yet not a single rupee has reached the hands of the women who trusted the AAP,” Jai Inder Kaur said. Kaur said both Kejriwal and CM Bhagwant Mann have betrayed the trust of Punjab’s women, turning their so-called ‘guarantees’ into nothing but political fraud. Slamming the Bhagwant Mann government over the law and order in the state, Kaur also alleged that with snatching incidents happening every day, women were not feeling safe. “Every day, cases of snatching, assault, and crime surface across the state, exposing the grim reality of Punjab’s deteriorating security situation,” she said. AAP chief spokesperson and MLA Kuldeep Singh Dhaliwal hit back at Kaur and asked her to instead protest against former CM Amarinder Singh, who is also her father. “She should ask her father what happened to promises made to the people of Punjab when they formed the government in 2017,” he said. Dhaliwal reminded Kaur that Amarinder had taken a sacred oath on the holy “Gutka Sahib”, promising to end the drug menace within four weeks, provide one job per household, and give unemployment allowance to the youth. “But after coming to power, he did not fulfil even a single promise,” Dhaliwal said. The AAP government has so far provided government jobs to 58,000 youth, he said and challenged Kaur to give an account of just 10 jobs given during her father’s tenure. In a statement, Dhaliwal said CM Mann has already announced that from March onwards, women will start receiving ₹1,000. Our government is committed to fulfilling every promise, said the former minister.</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/punjab-bjp-mahila-morcha-hold-protest-over-unkept-1-000-poll-promise-aap-hits-back-101763840436008.html</t>
+  </si>
+  <si>
+    <t>Ludhiana: 8 teams to battle for title at Jagtar Singh Memorial Hockey tourney from Dec 16</t>
+  </si>
+  <si>
+    <t>The city is gearing up for a grand display of hockey talent as the eighth edition of the All India Jagtar Singh Memorial Hockey Tournament (Under-21) is set to begin on December 16 at the Pritpal Singh Hockey Stadium, Punjab Agricultural University (PAU). A total of eight teams will compete in this year’s championship, which will conclude on December 20, featuring some of the most reputed hockey academies and institutions in the region. Teams from Surjeet Hockey Academy, Jalandhar; Namdhari XI; RoundGlass Hockey Academy; SAI Sonepat; SAI Bhopal; SAI Lucknow; and Ludhiana XI are among the top contenders expected to draw strong crowds. The much-awaited event is likely to bring together some of the finest young players from across the Asian subcontinent, promising fast-paced matches and fierce competition. According to the organising committee, the tournament will be played in a league-cum-knockout format. Gurinderpreet Singh, general secretary of the society, said that the event holds deep emotional significance for the hockey fraternity. The tournament is organised in memory of Jagtar Singh, a distinguished hockey player who also served as an advocate. He was the founding force behind the District Hockey Association, where he worked tirelessly for two decades. Widely admired for his leadership, he was elected thrice as president of the District Bar Association, leaving behind a legacy of sportsmanship and service.</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/ludhiana-8-teams-to-battle-for-title-at-jagtar-singh-memorial-hockey-tourney-from-dec-16-101763840375518.html</t>
+  </si>
+  <si>
+    <t>Parliament winter session: Political row as Centre lists Bill to allow Prez to frame regulations for Chandigarh</t>
+  </si>
+  <si>
+    <t>The Union government is preparing to introduce the Constitution (131st Amendment) Bill, 2025, in the upcoming winter session of Parliament — a move that could alter Chandigarh’s administrative structure and have vast consequences for Punjab’s claim and association with Chandigarh, the state capital. The development has triggered a political storm in Punjab, with the ruling Aam Aadmi Party (AAP) and the Opposition Congress and Shiromani Akali Dal (SAD) alleging that it is an attempt to “snatch Chandigarh from Punjab”. According to the Bill listed in the Rajya Sabha bulletin, the proposal seeks to bring the Union territory of Chandigarh under Article 240 of the Constitution, placing it in the same category as Union territories without legislatures — including the Andaman and Nicobar Islands, Lakshadweep, Dadra and Nagar Haveli and Daman and Diu, and Puducherry (when its assembly is dissolved or suspended). Also Read | 3 key bills propose norms to remove PM, CMs, ministers over criminal charges Could pave way for LG to administer Chandigarh If enacted, the amendment would empower the President to frame regulations for Chandigarh, and is widely seen as paving the way for the appointment of a lieutenant governor to administer the city. This would mark a significant shift from the current arrangement, under which the Punjab governor serves as Chandigarh’s administrator. Administrative changes Before the present system, Chandigarh had a chief commissioner who reported directly to the Union home ministry. The post was abolished in 1984 at the peak of militancy in Punjab and replaced with an adviser to the Punjab governor, who was given the charge of the UT administrator. In August 2016, the Centre had sought to restore the old practice of having an independent administrator by appointing former IAS officer KJ Alphons for the top post. However, the move was withdrawn after stiff opposition from the then chief minister Parkash Singh Badal. A retired bureaucrat said the proposed shift “has political and administrative implications, particularly for Punjab, which has long claimed Chandigarh as its capital”, though he added that the Centre already has the power to enact laws for Chandigarh. At present, the Punjab governor holds a largely symbolic role as administrator. “What the Centre ultimately intends will become clear once the full Bill is tabled,” he said. AAP, Cong, SAD mount sharp attack Chief minister Bhagwant Mann strongly opposed the proposal, accusing the BJP-led NDA government of conspiring to “snatch Chandigarh” from Punjab. “Chandigarh was, is and will always remain an integral part of the state,” he said, asserting that Punjab has the sole right over its capital. Mann termed the amendment a “grave injustice” and a continuation of the Centre’s alleged attempts to undermine Punjab. Punjab Congress president Amarinder Singh Raja Warring and Leader of Opposition Partap Singh Bajwa also denounced the move, calling it an assault on Punjab’s rights. Warring warned that removing Chandigarh from Punjab’s purview “will have serious repercussions” and vowed that the Congress would oppose the legislation in Parliament. Bajwa accused the Union government of systematically eroding Punjab’s rights — “whether on Chandigarh, river waters, or Panjab University.” Shiromani Akali Dal (SAD) president Sukhbir Singh Badal appealed to the Centre not to introduce the Bill, saying it would “betray brave Punjabis who have sacrificed the most for the nation”. He said the proposal would permanently remove Chandigarh from Punjab’s administrative control and violate past commitments — including the Centre’s 1970 decision to transfer Chandigarh to Punjab and the Rajiv-Longowal Accord, which set January 1986 as the deadline for the transfer. ‘Amendment won’t change UT status’ A former Punjab-cadre IAS officer, however, argued that bringing Chandigarh under Article 240 rather than Article 239 would not alter its administrative status. “It will remain a Union territory,” he said, adding that the amendment does not mandate the appointment of a separate administrator. He noted that even now there is no constitutional guarantee that the Punjab governor must be the ex-officio administrator of Chandigarh — it has merely been the practice since Punjab’s reorganisation in 1966. The Centre, if it wished, could change this arrangement without passing a special law, though such a move would be unwise given political sensitivities. The officer said Article 240 simply empowers the President to make regulations for UTs without legislatures, giving such regulations the force of law. “The intent appears to be smoother administrative functioning backed by legal clarity rather than modifying Chandigarh’s status,” he said, calling the political rhetoric “misplaced.” He added that Chandigarh’s association with Punjab as its original capital “was settled long ago and reaffirmed repeatedly,” saying that Punjab retains a natural and historical right over the city that no constitutional amendment can alter.</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/parliament-winter-session-political-row-as-centre-lists-bill-to-allow-prez-to-frame-regulations-for-chandigarh-101763840255626.html</t>
+  </si>
+  <si>
+    <t>State school games: Host Ludhiana clinch state softball title with 8-0 win over Patiala</t>
+  </si>
+  <si>
+    <t>Host district Ludhiana delivered a spectacular performance to clinch the 69th Punjab State Inter-District School Games Under-19 Boys Softball Championship title, defeating Patiala 8-0 in a one-sided final on Saturday. In the bronze medal match, Amritsar outplayed Fazilka 12-0 to secure third place. The three-day championship was held at the grounds of Government Senior Secondary School PAU and concluded with high enthusiasm and competitive spirit. Organised under the guidance of district education officer (secondary education) Dimple Madan and deputy district education officer (secondary education) Amandeep Singh, the tournament commenced on November 20 and showcased sporting talent from district teams across Punjab. District sports coordinator Kulvir Singh and game convener Ravi Dutt supervised the event. Ludhiana’s title victory was driven by disciplined teamwork and outstanding individual performances. Manish Kumar, Sukhwinder Singh and Akash Kumar emerged as the star players of the tournament, displaying remarkable skill, precision, and game sense that kept spectators on their feet. Following the final match, a prize distribution ceremony was held to honour the winners. Rajesh Khanna, principal of Government Senior Secondary School Kasabad, and state awardee Ajit Pal, lecturer of physical education at School of Eminence Jawahar Nagar Camp, presented trophies and medals to the champion and runner-up teams. Ludhiana crush Patiala 8-0 to lift Under-19 State Softball Championship Ludhiana crowned champions in Under-19 boys softball; Amritsar secure bronze Hosts Ludhiana outclass Patiala 8-0 in state softball final</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/state-school-games-host-ludhiana-clinch-state-softball-title-with-8-0-win-over-patiala-101763840201691.html</t>
+  </si>
+  <si>
+    <t>Ludhiana: Mother of murder-accused sons duped of ₹70k, fraudster booked</t>
+  </si>
+  <si>
+    <t>Samrala police have booked a Sahnewal resident for allegedly duping a woman of ₹70,000 by promising to secure a clean chit for her two sons accused in an attempt-to-murder case.The accused claimed that he has direct links with the senior police officials and he can manage the reports, police said. The accused has been identified as Khushpreet Singh of Sahnewal. The complainant, Paramjit Kaur of Himmat Nagar, Samrala, told police that her sons, Sunil Kumar alias Bachi and Rohit, were booked by Samrala police on April 11 in connection with an attempt-to-murder case involving the owner of a cafe and food joint in Samrala’s main market, following an altercation over a food bill. Paramjit Kaur said she initially came in contact with Rohit’s friend Armandeep of Bondal Road, Samrala, who introduced her to Khushpreet Singh. Khushpreet allegedly claimed that he had direct links with senior police officials and could ensure that her sons received a clean chit. Acting on his assurances, the woman gave him ₹70,000 in cash. When the police did not provide any relief, Kaur contacted Khushpreet again, but he kept making excuses and eventually stopped answering her calls. Realising she had been duped, she filed a complaint with Samrala police. ASI Avtar Chand, who is investigating the case, said that an FIR has been registered under Sections 308(2), 329(4), 324(4), 351(2), and 190 of the Bharatiya Nyaya Sanhita (BNS) against Khushpreet Singh and a hunt is on to arrest him.</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/ludhiana-mother-of-murder-accused-sons-duped-of-70k-fraudster-booked-101763840015520.html</t>
+  </si>
+  <si>
+    <t>Ludhiana: Truck driver charred to death as CNG cylinder explodes after collision on Ferozepur Road</t>
+  </si>
+  <si>
+    <t>A truck driver was burnt alive after the CNG cylinder of his vehicle exploded following a collision on a flyover near Nanaksar Gurdwara Sahib on Friday night. According to eyewitnesses, the explosion triggered a massive fire that engulfed the entire truck, leaving the driver trapped inside with no chance of escape. The deceased, identified as Bhushan, was employed with Malwa Transport and had loaded parcels from Transport Nagar earlier that evening. He was en route to deliver goods to various shops when the accident occurred around 11pm, police said. Eyewitness Bal Singh, standing outside his store, recalled hearing a loud explosion moments before seeing the truck in flames. “The driver was crying and waving for help from inside the cabin, but the fire was so intense that no one could go near him,” Singh said, adding that the truck rammed into a pillar on the flyover, sparking the blaze that quickly engulfed the vehicle. Fire officer Rajinder Kumar said they received the alert at 11.30 pm and two to three fire tenders were dispatched to the spot. “The truck was loaded with parcels containing medicines. These materials intensified the fire, and due to thick smoke, the team could not reach the driver immediately,” he said. Bhushan remained trapped inside the vehicle for nearly half an hour before succumbing to the flames. ASI Mewa Singh, who is investigating the case, said that preliminary findings suggest the CNG cylinder was damaged following the impact of the collision, leading to the explosion. “The exact cause will be determined after a detailed investigation,” he added.</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/ludhiana-truck-driver-charred-to-death-as-cng-cylinder-explodes-after-collision-on-ferozepur-road-101763839835319.html</t>
+  </si>
+  <si>
+    <t>Karnal youth Cong chief, among 2 held for defacing PM, CM’s photo</t>
+  </si>
+  <si>
+    <t>The Karnal police on Saturday said that they have arrested Haryana Youth Congress’ district president Rajat Lather and his associate Ashok Kumar for allegedly spraying black paint on the poster of Prime Minister Narendra Modi and chief minister Nayab Singh Saini. However, both were granted bail by a local court. The issue came to light when their video went viral on social media and was also posted on the official X account of the party unit on Friday. Following this, BJP leaders informed the Karnal superintendent of police and filed a complaint. However, they were arrested following the complaint by Karnal roadways general manager Kuldeep Singh. On his complaint, a case under sections 352 of BNS, Section 3A of The Haryana Prevention of Defacement of Property Act and Section 3 of Prevention of Damage to Public Property was registered and the accused were arrested, the police said. Singh had alleged that the duo defaced a poster appealing the farmers not to burn stubble, installed at a new bus stand. Lather’s counsel Vikrant Rathore argued that the arrests were “illegal” and termed it “politically motivated”. “CIA was involved in the probe for the case, which was totally uncalled for as the case does not fall in the category of heinous crimes and no notice was served u/s 41 of CrPC at the time of the arrest of Rajat Lather and Ashok Kumar,” Rathore told HT. After the court proceedings, the duo was granted bail by the court. Order was not uploaded till writing of this report. The incident had drawn sharp criticism from the ruling BJP and a mixed response from the Congress. BJP MLA from Karnal Jagmohan Anand said that such behaviour reflects frustration of the opposition, but was not a democratic dissent and defacing the poster ahead of the PM’s visit to Kurukshetra was unacceptable. Congress leaders, including district presidents Parag Gaba (Urban) and Rajesh Vaid (Rural) condemned the act, calling it uncalled for. Gaba said that though the party has been protesting on “vote chori”, but this form of protest was not right and was also not part of the official party programme. However, the Youth Congress has justified the move by its district president. Thanking the legal team on their bail, the party unit wrote on X, “...Our struggle does not end here. This has further strengthened our fight against the vote thieves and this will continue.”</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/karnal-youth-cong-chief-among-2-held-for-defacing-pm-cm-s-photo-101763839175307.html</t>
+  </si>
+  <si>
+    <t>RSS activist’s murder: Ludhiana woman held for sheltering accused</t>
+  </si>
+  <si>
+    <t>Police on Saturday arrested a Ludhiana-based woman for allegedly harbouring the prime accused after the cold-blooded murder of Rashtriya Swayamsevak Sangh (RSS) worker Naveen Arora in Ferozepur on November 15. The development comes amid indications of a foreign handler’s involvement, prompting Punjab Police to examine whether the killing was part of a larger targeted plot intended to disturb peace in the state. According to police, the accused, identified as Nachhatar Singh of Tihang in Jalandhar, fled Ferozepur moments after the murder of Arora near Sadhu Chand Chowk while the latter was returning home from his shop. Investigators soon learned that he was given refuge in Ludhiana by a woman identified as Bhawna. “She was arrested after police received specific intelligence about her role, and a case under section 349 of the Bharatiya Nyaya Sanhita (BNS) has been registered. She is being questioned to help trace the absconding accused and unravel the wider network behind the crime,” a police officer, privy to development, said. So far, the police have arrested four accused, including Harsh, Kanav, and Gursimran aka Kali, and the woman, while Badal and Nachatar Singh, besides a foreign-based handler of Kali, are yet at large. Senior officers steering the probe confirmed that the murder was carried out with precision and pre-planned coordination. “The involvement of a foreign handler and the methodical execution of the attack clearly suggest a targeted killing aimed at spreading fear,” a senior Punjab Police official said, requesting anonymity. On Thursday, Gursimran Singh, alias Jatin Kali, identified as the key conspirator, was arrested at around 1.30 am after a brief encounter. Kali, riding a motorcycle, attempted to flee and, during the chase, allegedly fired at the police with a .32-bore pistol, shattering a patrol vehicle’s windscreen and narrowly missing the driver. Police returned fire, injuring him in the leg before overpowering him. He was taken to the civil hospital for treatment. Police are probing whether the pistol used by Kali is the same weapon deployed in Arora’s killing. Investigators have found that Kali was radicalised through social media and had been receiving directions from a foreign handler who transferred ₹60,000 via UPI and instructed him to pick up a weapon from Patna. Police teams are now following the money trail. Earlier, the police had arrested Harsh and Kanav, who conducted reconnaissance and provided backup to the shooters. According to SSP Bhupinder Singh, the conspiracy was finalised on November 13 during Kanav’s birthday celebration, where Kali offered ₹1 lakh to Kanav, Harsh, Badal and another associate to execute the hit. All accused were booked under Sections 103 and 3(5) of the Bharatiya Nyaya Sanhita (BNS) and Sections 25, 27, 54 and 59 of the Arms Act. Police said further arrests are imminent and more key disclosures are expected as the investigation deepens.</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/rss-activist-s-murder-ludhiana-woman-held-for-sheltering-accused-101763839115245.html</t>
+  </si>
+  <si>
+    <t>Ludhiana: Extortion bid at bizman’s house foiled, 2 arrested</t>
+  </si>
+  <si>
+    <t>Two miscreants were arrested on charges of attempting to extort money from a city businessman at his residence on Friday night, police said on Saturday. According to police, the accused have been identified as Lakhbir Singh and Anmol Verma, who are part of a larger extortion gang. Lakhbir is already facing trial in multiple criminal cases, highlighting his history of involvement in serious offences, police said. The businessman, Namneet Aggarwal, a resident of Queen Garden, South City, has alleged that the accused had extorted nearly ₹15 lakh from him over the past six months by threatening him and his family. According to police, the gang also includes a woman, Karanjeet Kaur, who made the extortion calls to Aggarwal, and aides Jagdeep Singh, Manpreet Singh, Deepak Kumar, and Robin, residents of Satguru Nagar, Lohara. Aggarwal said that the accused barged into his house on Friday night after threatening the security guard. Watching the miscreants on CCTV, the businessman immediately bolted the doors from inside and alerted the police, while the intruders tried to break in by kicking the doors. Amrik Singh, assistant sub-inspector of police who is investigating the case, said that the police reached the spot quickly and arrested the two accused. A hunt is on for the remaining members of the gang. An FIR has been lodged at PAU Police Station under Sections 308(2) (extortion), 329(4) (criminal trespass), 324(4) (mischief), 351(2) (criminal intimidation), and 190 (unlawful assembly) of the Bharatiya Nyaya Sanhita. The accused were produced before the court on Saturday and remanded to police custody for two days, the police said.</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/ludhiana-extortion-bid-at-bizman-s-house-foiled-2-arrested-101763839114947.html</t>
+  </si>
+  <si>
+    <t>Cotton ginning sector in crisis as acreage declines</t>
+  </si>
+  <si>
+    <t>The cotton ginning industry, which was once a flourishing agri-business of Punjab, is now struggling to survive due to a sharp decline in cotton cultivation. Ginners separate lint (white fibre) and seed from raw cotton. Factory operator says for every quintal (100 kg) of unginned cotton, the recovery of lint is 33-36 kg and 63-66 kg of seed. The seed, in turn, is crushed to produce oil and de-oiled cake. Cottonseed oil is used in cooking, while the protein-rich cake is used as an animal feed. According to industry sources, in 2008, there were 422 cotton ginning factories across the state; however, this number has decreased by 93% to only 32 units that are operational during the current kharif marketing season. Entrepreneurs say nearly 10 more units may shut down next season as the ginning sector lacks support from the government. The southwest area of Punjab under cotton has been steadily decreasing due to repeated crop failures since 2021. The decline in cultivation is also attributed to various other reasons, including pest attacks, lack of irrigation support and inclement weather. In 2024, the area under the crop was 96,000 hectares, the lowest ever and this year the acreage improved marginally to 1.29 lakh hectares, and more than 20,000 hectares were damaged due to unseasonal rains. Factory owners say they are facing financial losses as the units are working less than 25% of their capacity. A Bathinda-based ginner, Kaliash Garg, said he has to wind up his unit this season after working for 47 years. Garg, who is also the treasurer of the Punjab Cotton Mills and Ginning Association, attributes the decline to the shortage of raw cotton, pink bollworm attack in the major cotton-growing districts of Bathinda and Mansa and pockets of Barnala, Sangrur and Muktsar. “Cotton used to be a traditional summer crop for the semi-arid districts. As the hybrid cotton is susceptible to pest attacks, farmers are shying away from growing cotton due to economic reasons. Industrialists are setting up spinning mills with high investment, where from ginning to thread making works are done under a single roof, and the ginning operators are unable to compete with them due to low availability of cotton,” he said. Garg said that the authorities should focus on introducing the next generation of Bt cotton to boost the traditional crop. A prominent cotton ginner from Malout in Muktsar, Bhagwan Bansal, said against the average minimum requirement of 200 bales or 340 quintals per day, units are struggling to get cotton for processing. “A cotton ginning unit operator has to pay about ₹10 lakh fixed electricity charges for the nine-month season from September 1 onwards. As the pest attack has severely hit crop production since 2022, we are unable to run factories. We have to pay fixed charges even when electricity is not used,” he said. “The Punjab government is quick to grant compensation to affected cotton growers, but the interests of ginners have been overlooked by the respective state governments. The government is biased towards investors,” said Bansal. A second-generation ginning operator from Fazilka, Munish Bansal, said that until 2021, his unit was processing 25,000 bales or 42,500 quintals of cotton, but this season, he has got only 2,500 bales. “There is a huge scarcity of cotton, and we are unable to run the factories. After the irrigation system was strengthened over the last decade, farmers of the semi-arid region of Malwa switched from the traditional cotton to a less labour-intensive crop of non-basmati rice,” he added.</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/cotton-ginning-sector-in-crisis-as-acreage-declines-101763838935519.html</t>
+  </si>
+  <si>
+    <t>Ludhiana: Food dept seeks caste details of wheat beneficiaries in district</t>
+  </si>
+  <si>
+    <t>Amid the ongoing wheat distribution cycle, the district food and civil supplies department has asked ration depot holders in Ludhiana to collect caste details of families receiving free and subsidised ration, a move that officials say may be linked to the central government’s caste census efforts. The sudden directive has triggered confusion on the ground, with depot holders and beneficiaries unsure why such information is being sought at this stage. According to officials, the department has circulated a detailed proforma asking area inspectors to prepare a caste-wise list of beneficiaries registered under the National Food Security Act (NFSA) in their jurisdiction. The form specifically seeks the number of Scheduled Caste (SC) and Scheduled Tribe (ST) families receiving free or subsidised ration, demanding a precise caste breakup beyond the usual data checks carried out during distribution. A senior food inspector, speaking on condition of anonymity, said this is not the first time that such data has been requested. “The head office in Chandigarh had previously asked for similar caste breakup details, but this time the department has issued a far more extensive and granular format, demanding precise information for each beneficiary,” he said. Ration depot holders have raised concerns over the directive, stating that no written guidelines have been provided. Amarjeet Singh, a depot holder in Haibowal, said, “We were verbally instructed to record the caste of each beneficiary but have not received any written instructions. People are already anxious about receiving wheat on time during the ongoing eKYC drive. Asking about caste at this stage raises concerns that the rules might change or they could be removed from the list.” Acknowledging the development, Manoj Kumar, a senior food inspector in the department, said, “We have instructed depot holders to collect caste details based on directives from the head office. This exercise is part of our ongoing efforts to strengthen and update the department’s internal database.” “This is a routine process intended to ensure accurate record keeping. Collecting caste information will help maintain comprehensive and precise beneficiary data, which is important for implementing welfare schemes effectively,” he added.</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/ludhiana-food-dept-seeks-caste-details-of-wheat-beneficiaries-in-district-101763838875855.html</t>
+  </si>
+  <si>
+    <t>Three held in Barnala honeytrap case</t>
+  </si>
+  <si>
+    <t>Three persons have been arrested in connection with a honeytrap case, Barnala deputy superintendent of police (DSP) Satvir Singh said on Saturday. The police said that a first information report (FIR) was lodged on Friday under sections 127(2), 308(2), and 61(2) of the Bharatiya Nyaya Sanhita, based on the statement of the victim’s son, a resident of Mansa. “Harsimranpreet Singh alias Harry from Barnala, Rajveer Kaur from Sangrur, Bhola Singh alias Kala from Sangrur have been arrested while Sukhwinder Kaur from Barnala remains at large, police added. Barnala City 2 station house officer Charanjit Singh said that according to the complainant, the victim, Gurjant Singh, was lured by the accused, who held him captive at a rented house on Khudi Road and began demanding ₹1.5 lakh from his family and threatening to release an obscene video of the victim on social media. The victim’s family contacted the police, and a trap was laid. Harsimranpreet Singh and Rajveer Kaur were arrested when they came to collect ₹50,000 near Garcha Road in Barnala. Following these arrests, police raided the location on Khudi Road, a rented property, where they rescued the victim and arrested Bhola Singh. DSP Singh stated that Sukhwinder Kaur had a prior relationship with the victim. He said that police have recovered ₹50,000 cash, one motorcycle, and a mobile phone used in the crime. DSP Singh also stated that the gang is suspected of having targeted other victims. Further investigations are underway, he added.</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/cities/chandigarh-news/three-held-in-barnala-honeytrap-case-101763838815412.html</t>
+  </si>
+  <si>
+    <t>BhaskarChandigarh_Crawler</t>
+  </si>
+  <si>
+    <t>Extension of Director Health Services in Chandigarh is in controversy: Social worker sent complaint to the Governor, said rules were ignored, many investigations are pending.</t>
+  </si>
+  <si>
+    <t>The one year additional tenure given to Dr. Suman Singh, Director Health Services, Government Multi Specialty Hospital (GMSH-16) in Chandigarh, is mired in controversy. A social worker has sent a complaint to the Governor regarding this. In which it is alleged that this extension has been given against the rules, DOPT guidelines and restrictions of the Vigilance Department. According to the information, about 2 days ago, Director Health Services Dr. Suman Singh has been given an extension of one year. Now know in sequence what allegations were made in the complaint.. These demands were raised in the complaint</t>
+  </si>
+  <si>
+    <t>https://www.bhaskar.com/local/chandigarh/news/director-health-services-suman-singh-tenure-extension-controversy-inquiry-chandigarh-136492206.html</t>
+  </si>
+  <si>
+    <t>Centre's U-turn on changing the status of Chandigarh: Said- not bringing it in this Parliament session; The bill will not affect relations with Punjab and Haryana.</t>
+  </si>
+  <si>
+    <t>At present the Central Government has refused to change the status of Chandigarh. The Home Ministry has said that neither any final decision has been taken on this proposal yet nor is there any plan to bring any bill related to it in the winter session. The bill was brought only after adequate discussion. Earlier it had come to light that the Central Government can bring such a bill in the winter session from 1st to 19th December, by which Chandigarh will be included in Article 240 instead of Article 239 of the Constitution. With this, Chandigarh can become a completely union territory, due to which administrative powers will go to the President and the Centre. Due to this, the leaders of Punjab feared that this would lead to the loss of their traditional control over Chandigarh. Punjab government, Congress and Akali Dal had expressed strong opposition to this. What did the central government say.. SAD called a core committee meeting, preparations for the movement Shiromani Akali Dal has called a core committee meeting regarding the dispute of Chandigarh status. Giving this information, Daljit Singh Cheema said that this meeting has been called on 24 November 2025 at the party headquarters. In this, along with preparing the outline of the next conflict, discussions are also being held with legal experts. We will launch a big movement against this. 2 big things about Chandigarh... 70 years long dispute, which five commissions could not resolve. The dispute over rights over Chandigarh is almost 70 years old. It started in 1966 with the creation of Haryana state by dividing the vast East Punjab. From 1966 to 1986, six commissions were formed regarding the rights of Chandigarh, but no solution could be found. No initiative has been taken on this since 1986. Now, with the introduction of an amendment bill by the Bharatiya Janata Party at the Centre, this issue has flared up once again. Know when which commission did what.. What the opposition leaders said.. Kejriwal Chandigarh was, is and will remain Punjab's. On the Chandigarh issue, Kejriwal said that the BJP government at the Center wants to end Punjab's rights over Chandigarh by amending the Constitution, which is a direct attack on Punjab's identity and constitutional rights. They allege that the rights of Punjabis are being snatched away by breaking the federal structure, whereas Punjab has always made sacrifices for the country's security, food grains, water and humanity. He called this not an administrative decision but an attack on the soul of Punjab. Said- Punjab has never bowed its head before dictatorship, nor will it bow now. Chandigarh belonged to Punjab, is and will remain so. BJP President Jakhar</t>
+  </si>
+  <si>
+    <t>https://www.bhaskar.com/local/chandigarh/news/chandigarh-lg-appointment-row-heats-up-136489511.html</t>
+  </si>
+  <si>
+    <t>Centenary celebrations begin in Sri Anandpur Sahib: Sarvadharma conference begins, Sri Sri Ravi Shankar arrives, drone show and Kirtan Darbar in the evening</t>
+  </si>
+  <si>
+    <t>The 350th martyrdom centenary celebrations of Sri Guru Tegh Bahadur have begun at Sri Anandpur Sahib. The morning recitation of Shri Akhand Path Sahib has started. In this, everyone including Punjab Governor Gulab Chand Kataria, CM Bhagwant Mann, Aam Aadmi Party (AAP) supremo Arvind Kejriwal were present, now the Sarva Dharma Sammelan has started. Sant Sammelan Dera Beas chief Gurinder Singh Dhillon at the centenary celebrations of Sri Guru Tegh Bahadur. Everyone's views are being expressed. Also the sacrifice of Guru Teg Bahadur Ji is being remembered. In the evening, a drone show and Kirtan Darbar will be organized on the life of Guru. For the first time, the Assembly session will be held outside Chandigarh, the Punjab government has made complete arrangements to ensure that the gathering attending the function does not face any kind of problem. All the ministers including Punjab CM Bhagwant Mann are themselves holding a stand in Anandpur Sahib. At the same time, for the first time there will be a special session of the Assembly on 24th November. For this, a special assembly has been arranged there. Complete security arrangements have been made. CM has already announced in the session, big decisions will be taken. Preparations have been made for this. Every information with one click on mobile. Rupnagar administration has made special digital arrangements for the convenience of lakhs of devotees coming for the 350th centenary celebrations of Guru Tegh Bahadur Ji at Sri Anandpur Sahib. In view of the concern, Rupnagar administration has started a website named “anandpursahib350.com”. The website and app are in both Punjabi and English languages. On which real-time information about shuttle bus routes, tent city, trolley city, traffic diversion and all major events will be given. Due to this, the objective has been kept that the devotees should not face any problem in going anywhere, staying or reaching the congregation. Entire Anandpur Sahib divided into 25 sectors For crowd and security management, the administration has divided Anandpur Sahib city into 25 sectors. Policemen have been deployed, helpdesks and medical teams have been deployed in every sector. Punjab Police has used modern technology to make the event safe. The entire area is being continuously monitored with the help of drone surveillance, facial recognition system, ANPR cameras and real-time control room. The health department has also set up temporary mohalla clinics, ambulances and first-aid points. The administration says that the free service of shuttle buses will control the crowd the most, why</t>
+  </si>
+  <si>
+    <t>https://www.bhaskar.com/local/chandigarh/news/sri-anandur-sahib-sri-guru-tegh-bahadur-shabtadi-celebrations-begin-update-all-religion-conference-sri-sri-ravi-shankar-136490340.html</t>
+  </si>
+  <si>
+    <t>Former DIG Bhullar reached the High Court in protest against the arrest: Question raised on the jurisdiction of CBI, four arguments have been given in the petition</t>
+  </si>
+  <si>
+    <t>Punjab Police DIG Harcharan Singh Bhullar reached Punjab and Haryana High Court against his arrest. He has challenged the arrest. In the petition he has raised questions on the jurisdiction of CBI. In the argument given by him, it has been said that since he was working in Punjab, CBI should have taken permission from the Punjab Government under Section 6 of the Delhi Special Police Establishment (DSPE) Act, 1946. Bhullar further argued that before the CBI, the Punjab Vigilance Bureau had already registered an FIR for the same crime. There is a difference of half an hour between the two. Now let's go into the four points of the petition: 1. In the first petition, Bhullar has raised questions on the jurisdiction of CBI. He says that he is posted in Punjab. In such a situation, it is necessary to take permission from the Punjab Government to register the case. 2. Second, he says that the FIR against him could not have been registered by CBI Chandigarh because the alleged crime took place in Punjab. He could not even be arrested without the permission of the Punjab Government. Whereas the case related to 2023 in which he has been arrested, is related to Sirhind police station of Punjab. 3. The goods which were recovered in Chandigarh were not recovered from them. 4.Questions have also been raised regarding the second FIR. He said that two FIRs cannot be registered for the same crime. Before CBI, Punjab Vigilance had registered FIR. Harcharan Singh Bhullar was arrested in the bribery case. On October 16, 2025, CBI arrested him for demanding a bribe of Rs 8 lakh. After which cash, gold and documents worth crores of rupees were recovered in raids at their locations. On October 19, the Punjab government suspended him. After this, on October 29, 2025, CBI registered a second FIR on charges of possessing disproportionate assets. Earlier, Vigilance Bureau Punjab had also registered a case against him. In November 2025, the court sent him to CBI custody and the case is under further investigation.</t>
+  </si>
+  <si>
+    <t>https://www.bhaskar.com/local/chandigarh/news/dig-harcharan-bhullar-punjab-and-haryana-high-court-petition-arrest-issue-update-136490179.html</t>
+  </si>
+  <si>
+    <t>Chandigarh Railway Station facilities in private hands: Applications for tender for food court, parking, advertising, clock room, cleaning till December 8</t>
+  </si>
+  <si>
+    <t>The world-class Chandigarh Railway Station, which is being built after 5 years, will start with modern facilities, but almost all the services here will be handed over to private companies. Under the ISFM model, Railways has implemented the Integrated Station Facility Management (ISFM) model as a major change. For this, Railway Land Development Authority (RLDA) has issued a tender. Under this model, a private agency will take over the entire responsibility of cleaning, operation and maintenance (O&amp;M) and commercial activities of the station. All will be handled by a single private agency, so that better quality and professional services can be provided. Companies can apply for this tender till 3 pm on 8th December. Hi-tech facilities will be available at the station: Many modern and hi-tech facilities will be added to make Chandigarh Railway Station world-class. These include high-tech CCTV systems, sensor doors, state-of-the-art escalators and lifts, solar panels, auto-management system (BMS), large food courts, commercial spaces, paid lounges, kiosks, spacious parking and large advertising spaces. All these facilities will be completely operated by a private company, leaving almost the entire passenger service of the station under private management.</t>
+  </si>
+  <si>
+    <t>https://www.bhaskar.com/local/chandigarh/news/chandigarh-railway-station-facilities-private-companies-136489641.html</t>
+  </si>
+  <si>
+    <t>Now nights will be cold in Punjab-Chandigarh: Temperature will drop by 3 degrees in 4 days, it will be cloudy at some places, Bathinda recorded 27.9 degrees Celsius</t>
+  </si>
+  <si>
+    <t>Now nights will be cold in Punjab and Chandigarh. In the coming four days, the minimum temperature will gradually drop by 2 to three degrees. According to the Meteorological Department, there is a possibility of light fog at some places. At the same time, there is a possibility of no rain or dry weather for the next 07 days. A drop of 1.1 degrees has been recorded in the average maximum temperature of the state in 24 hours. It has come close to normal. The highest temperature of 27.9 has been recorded in Bathinda. This type of weather will prevail in the coming week. According to the Meteorological Department, there is no possibility of rain on 27th November. The maximum temperature is likely to remain between 22–24°C over northern and eastern districts and 24–26°C over the rest of the state. This week the day temperature in the state will mostly be normal or slightly lower. During this period, the night temperature in the north-western districts of the state i.e. Gurdaspur, Pathankot, Amritsar, Tarn Taran, Ferozepur and Fazilka will be 4 to 6°C. In the remaining districts it will be 6 to 8°C. The temperature will be below normal in most places. Whereas in some central and eastern areas the temperature will be almost normal. The sky will be clear over Delhi-Ambala and Ambala-Amritsar highways. Punjab-Chandigarh's air polluted, AQI increased. The effect of stubble burning in Punjab is also visible in Chandigarh. AQI was recorded at 174 in Sector-22 of Chandigarh, 163 in Sector-25 and 157 in Sector-53 at 7 am. While Amritsar recorded AQI 190, Jalandhar AQI 126, Khanna AQI 124, Ludhiana AQI 147, Mandigobindgarh AQI 186, Patiala AQI 162. Whereas the department did not provide the records of Bathinda and Rupnagar.</t>
+  </si>
+  <si>
+    <t>https://www.bhaskar.com/local/chandigarh/news/punjab-chandigarh-weather-temperature-and-fog-weather-forecast-alert-update-no-rain-chances-136489560.html</t>
+  </si>
+  <si>
+    <t>BJP again surrounded in Punjab: Chandigarh issue raised after agricultural law, Senate-Syndicate, protest of 26 will take new direction</t>
+  </si>
+  <si>
+    <t>The Central Government is going to bring a bill in the winter session of Parliament to bring Chandigarh under Section 240. Due to this, it may become difficult for the Bharatiya Janata Party to establish its foot on the political ground in Punjab. Senate-Syndic in front of BJP engaged in compensation for the first three agricultural laws. If Senate elections are not announced by 25th November, it has already been announced that the University will be closed on 26th. A program is being made to surround the state and district offices of BJP. Not only this, farmers are also coming to Chandigarh on 26th to celebrate the date of protest against agricultural laws. Before that, the information about changing the status of UT is going to be a problem for BJP. CM Mann expressed objection, while Punjab CM Bhagwant Mann has also expressed objection on this. CM wrote on his social media account, we strongly oppose the proposed Constitution (131st Amendment) Bill being brought by the Central Government in the upcoming winter session of Parliament. This amendment is against the interests of Punjab. We will not allow the conspiracy being hatched by the Central Government against Punjab to succeed. Only Punjab has the right on Chandigarh, which was built by destroying the villages of our Punjab. We will not let our rights go just like that. We will take whatever steps need to be taken for this. Alliance broken, already facing problems in voting Due to agricultural laws, Bharatiya Janata Party's alliance with its regional party Shiromani Akali Dal has broken. With whom BJP has remained in power. But even after withdrawing the agricultural law, he is still trying to save his political ground in Punjab. Till now, he has alone contested one Assembly, one Lok Sabha and two by-elections, but the only success he has achieved is that he has been able to set up his own booths in the villages. As soon as the schedule of the winter session of the Lok Sabha was released and it came to light that a bill would be brought to change the status of Chandigarh UTS, the entire opposition has come together against the BJP. Statements have been issued by Aam Aadmi Party, Congress, Shiromani Akali Dal and they have also started making programs internally to corner the Central Government. BJP already has only two MLAs in the assembly. At present, in the 217-seat assembly, BJP has only two MLAs, Ashwani Sharma from Pathankot and Jangi Lal Mahajan from Mukerian. Whereas at one time BJP had won 23 seats in the elections fought in alliance with Akali Dal. Now when BJP is rampant in the entire country</t>
+  </si>
+  <si>
+    <t>https://www.bhaskar.com/local/chandigarh/news/chandigarh-section-240-bill-political-setback-for-bjp-in-punjab-136486280.html</t>
+  </si>
+  <si>
+    <t>Warrant to the complainant in the Rs 1 crore robbery case in Chandigarh: Despite repeated summons, he is not appearing in the court, orders to appear on December 8</t>
+  </si>
+  <si>
+    <t>The district court has issued a bailable warrant against Bathinda complainant Sanjay Goyal in the famous Rs 1 crore robbery case of sacked sub-inspector Naveen Phogat of Chandigarh. The court said that despite repeated summons, the complainant did not appear in the court. Third degree torture was done in the police post. In this case, the accused Phogat had alleged that when he surrendered in the court two years ago, DSP Virk, investigating officer and other policemen beat him badly at Palsora police post. There were serious injuries at many places on his body. Meanwhile, to prove the presence of DSP Virk, he had asked for his mobile location and call details. Earlier, the lower court had also rejected his application. After this Phogat appealed in the Sessions Court, but here too he did not get relief. There was a robbery of Rs 1 crore in Chandigarh. The case is of around 4th August 2023. Bathinda businessman Sanjay Goyal had told in his complaint to the police that he had come to Aero City in Mohali to exchange Rs 1 crore kept in Rs 500-500 notes. His acquaintance had assured him that this amount would be exchanged with Rs 2000 notes and he would get 5% commission in return. According to the complainant, after meeting some people in Mohali, he came with them to Sector-40, Chandigarh. After some time they left from there, but then three other people reached there. One of these persons was in police uniform. These people threatened him and picked up a bag full of Rs 1 crore notes kept in his car, put it in their car and fled from the spot. When the complaint was made, the names of the police personnel came to light. The complainant told that when he reached the police station the next day of the incident to lodge the complaint, he came to know that the role of many policemen posted in the same police station in this robbery came to light. The names of these people came to light in the robbery. Among the people said to be involved in the incident, the names of the then Additional SHO Inspector Naveen Phogat, Constable Shiv Kumar, Constable Varinder Singh and a private person Vajinder Singh Gill came to light.</t>
+  </si>
+  <si>
+    <t>https://www.bhaskar.com/local/chandigarh/news/chandigarh-complainants-absence-bailable-warrant-issued-136489581.html</t>
+  </si>
+  <si>
+    <t>Murder of a friend at a birthday party in Chandigarh: A brawl broke out after drinking alcohol, stabbed him with a knife, had gone to a common friend's birthday.</t>
+  </si>
+  <si>
+    <t>A young man killed his friend at a birthday party in Chandigarh. In a minor dispute, he was stabbed several times with a knife. The young man was admitted to a hospital in Sector-16 in a critical condition, where he died. Both had gone to a common friend's birthday party. After drinking alcohol, a fight started between the two. After some time, accused Shubham picked up a knife and stabbed his friend several times. After this the accused fled from the spot. The police team tracked the location and caught the accused near the IT Park. From where the police also recovered the knife. Read sequentially how the young man was murdered... Police reached the accused from the location. After the murder, the accused Shubham kept changing his location again and again. The police tracked his location by putting his mobile on surveillance. Inspector Ramdayal said that the team of outpost incharge Kuldeep Kumar, constables Neeraj, Ravi and Sandeep surrounded the accused near the IT Park. From there, on the behest of Shubham, the knife used in the murder was also recovered.</t>
+  </si>
+  <si>
+    <t>https://www.bhaskar.com/local/chandigarh/news/chandigarh-birthday-party-youth-murdered-136492122.html</t>
+  </si>
+  <si>
+    <t>Preparation to change the status of Chandigarh, bill will come in Parliament: With this, the Center will appoint an independent administrator; Uproar in Punjab, said - Haryana's advantage</t>
+  </si>
+  <si>
+    <t>There has been a political uproar in Punjab regarding the amendment bill regarding Chandigarh being presented in the Parliament. From the ruling Aam Aadmi Party (AAP) to Congress and Akali Dal have expressed strong opposition to it. This bill is being brought in the winter session of Parliament to be held from 1 to 19 December. Which has been described as 131st Amendment Bill-2025. Under this, the Central Government is going to include Chandigarh in Article 240 of the Constitution. This amendment will bring it into the category of union territories which do not have an assembly. Punjab leaders say that this will end Punjab's administrative and political control over Chandigarh. Through this, a path is being made to hand over Chandigarh to Haryana. First of all, know what will happen from Section 240. Section 240 of the Indian Constitution gives the President the right to make rules and laws for the Union Territories i.e. UTs by the Central Government. This section is for those UTs which do not have their own assembly. After this the Center will have direct power to make laws. The President can directly make rules on Chandigarh's administration, police, land, education, municipal corporation institutions etc. Presently Chandigarh is the capital of Punjab and Haryana. Here SSP is appointed from Punjab and DC is appointed from Haryana cadre. After the bill, their appointment will be done directly by the Centre. What did the leaders of Punjab say on this issue... Congress President Vading said - There is concern in the entire Punjab, Center should give clarification. Punjab Congress President Raja Vading said - I hope that the news in the media is wrong, in which it is being said that the proposed 131st amendment to the Indian Constitution is being amended to separate Chandigarh from Punjab. I urge the Government of India to provide clarification on this matter, as it has caused concerns throughout Punjab. If this is true, it would be an unwise move with serious consequences. Chandigarh is part of Punjab. Sukhbir Badal said- Punjab's control will end. Shiromani Akali Dal President Sukhbir Singh Badal has also expressed his opposition to this. He wrote- Shiromani Akali Dal strongly opposes the proposed Constitution (131st Amendment) Bill being brought by the Central Government in the upcoming winter session of Parliament. This amendment is against the interests of Punjab and amounts to reneging on all the promises made by the Government of India regarding transfer of Chandigarh to Punjab. Delhi's previous Congress government</t>
+  </si>
+  <si>
+    <t>https://www.bhaskar.com/local/chandigarh/news/then-the-big-issue-of-rights-over-chandigarh-136485697.html</t>
+  </si>
+  <si>
+    <t>The couple got married for the second time to grab dowry: Lawan was taken in a mass marriage ceremony in Firozpur; Sarpanch's son recognized him</t>
+  </si>
+  <si>
+    <t>A husband and wife got married again in a mass wedding ceremony in Firozpur, Punjab. Sofas, cupboards and clothes were being given to those getting married at the ceremony. Out of greed for this, both of them also took lava at the function. But even before the goods were found, members of the organization that organized the village Sarpanch function told that after suspicion, both were investigated. After this he was thrown out of the program. Both of them had applied for mass marriage by giving false information. Read sequentially what is the whole matter... Manager said - Wrong information given in registration. The Chief Manager of the program said that sofa, bed, wardrobe and clothes are also given to the couples by the organization in the program. Many times some people give wrong information while registering. Although couples are selected for marriage only after investigation, but in this case the couple tried to misuse the system by lying. Getting married for the second time is completely against the rules.</t>
+  </si>
+  <si>
+    <t>https://www.bhaskar.com/local/chandigarh/news/ferozepur-couple-caught-second-marriage-for-dowry-goods-136485405.html</t>
+  </si>
+  <si>
+    <t>पंजाब पुलिस पर गाड़ी चढ़ाने का प्रयास:मुठभेड़ के बाद पुलिस के हाथ लगा ड्रग तस्कर, 50 किलो हेरोइन बरामद</t>
+  </si>
+  <si>
+    <t>The Anti Narcotics Task Force (ANTF) of Punjab Police has arrested a drug smuggler and recovered 50 kg of heroin from him. When the police chased him to arrest him, the accused tried to run over the police personnel. After chasing the smuggler for some distance, the police caught him and recovered heroin from him. Sandeep Singh alias Sipa, resident of Shanna Sher Singh Wala village of Kapurthala, came out of jail in the beginning of November 2025. The police were keeping an eye on his activities. ADGP and ANTF Chief Neelabh Kishore said that based on technical intelligence, ANTF teams were monitoring the movements of the accused since he came out of jail earlier this month. He said that intelligence information revealed that the suspect had collected a huge quantity of contraband in the border village of Bagge in Jalalabad. ADGP said that ANTF teams immediately took action and saw the suspect moving towards Firozpur. When signaled to stop, the suspect tried to evade arrest, following which the police team chased him. The police had also set up a blockade at one place in Firozpur and tried to run over the personnel standing there. He said the suspect was finally caught after an encounter in Rauke village, where he tried to ram his vehicle into a police party. He said that investigation is going on to identify the possible origin of this consignment. In this regard, an FIR has been registered under Section 21 of the NDPS Act at Police Station ANTF in SAS Nagar. DGP Gaurav Yadav said that preliminary investigation has revealed that this cross-border consignment of 50 kg heroin was sent by Pakistan-based ISI-backed smugglers. He said that the arrested accused Sandeep alias Seepa is a history-sheeter and has eight criminal cases registered against him, including five under the NDPS Act.</t>
+  </si>
+  <si>
+    <t>https://www.bhaskar.com/local/chandigarh/news/punjab-police-antf-seizes-50-kg-heroin-trafficker-arrested-after-chase-136484938.html</t>
+  </si>
+  <si>
+    <t>TribuneChandigarh_Crawler</t>
+  </si>
+  <si>
+    <t>Centre retracts, says no intention to pilot Bill to bracket Chandigarh with other UTs in Parliament</t>
+  </si>
+  <si>
+    <t>As the uproar over a proposed legislation to bracket Chandigarh with other UTs grew, the Centre on Sunday said it had no plans to pilot the related draft law in the upcoming winter session of Parliament. Retracting from previous plans (the Centre had listed in Parliament bulletin the Constitution 131st Amendment Bill) to bring Chandigarh on par with other UTs like Andaman and Nicobar Islands, Lakshadweep, Dadra and Nagar Haveli, Daman and Diu and Puducherry, the Home Ministry said the Bill would not be tabled in the winter session starting December 1. “The proposal to simplify the process of law-making exclusively by the Central Government for the Union Territory of Chandigarh is currently under consideration at the level of the Central Government. No final decision has been taken on this proposal," the MHA said on X. The proposal only to simplify the Central Government’s law-making process for the Union Territory of Chandigarh is still under consideration with the Central Government. No final decision has been taken on this proposal. The proposal in no way seeks to alter Chandigarh’s… — PIB - Ministry of Home Affairs (@PIBHomeAffairs) November 23, 2025 The ministry said the proposal does not in any way involve altering the governance and administrative arrangements of Chandigarh or the traditional relations of Chandigarh with Punjab or Haryana. "An appropriate decision will be taken only after adequate consultation with all stakeholders, keeping in mind the interests of Chandigarh. There is no need for concern on this matter. The Central Government has no intention of presenting any bill to this effect in the upcoming Winter Session of Parliament," the Centre clarified after the Punjab BJP also said it would demand the retraction of the proposed bill which hurts the sentiments of Punjab. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/centre-retracts-says-no-intention-to-pilot-bill-to-bracket-chandigarh-with-other-uts-in-parliament/</t>
+  </si>
+  <si>
+    <t>Punjab BJP to meet Amit Shah, will seek withdrawal of controversial Chandigarh Bill</t>
+  </si>
+  <si>
+    <t>Amid the ongoing anxiety over a proposed bill to bracket Chandigarh with other union territories, Punjab BJP president Sunil Jakhar on Sunday said he would meet Union Home Minister Amit Shah and request him for reconsideration and withdrawal of the Bill. Speaking to The Tribune exclusively, Jakhar said the sentiments of Punjab cannot be ignored to facilitate administrative requirements of Chandigarh. "For Punjab, Chandigarh is not a piece of geography. Our emotions are tied to the capital city. Any such attempt should be reconsidered and withdrawn. We have sought time with the Centre and will press for the Bill to be reconsidered and withdrawn in line with the sentiments of Punjab," Jakhar told The Tribune. Earlier, the BJP Punjab core committee met on Sunday and agreed to resolve the issue with the Centre. After the meeting, Jakhar said the Punjab BJP stood with Chandigarh and its interests. "Chandigarh is an integral part of Punjab, and the Punjab BJP stands firmly with the interests of the state, whether it is the issue of Chandigarh or the waters of Punjab. Whatever confusion has arisen regarding Chandigarh will be resolved by discussing it with the Centre. As a Punjabi myself, I assure you that for us, Punjab always comes first," he said. ਚੰਡੀਗੜ੍ਹ ਪੰਜਾਬ ਦਾ ਅਭਿੰਨ ਹਿੱਸਾ ਹੈ ਅਤੇ ਪੰਜਾਬ ਭਾਜਪਾ ਪੰਜਾਬ ਦੇ ਹਿੱਤਾਂ ਨਾਲ ਦ੍ਰਿੜਤਾ ਨਾਲ ਖੜੀ ਹੈ, ਤੇ ਉਹ ਚਾਹੇ ਚੰਡੀਗੜ੍ਹ ਦਾ ਮੁੱਦਾ ਹੋਵੇ ਅਤੇ ਚਾਹੇ ਪੰਜਾਬ ਦੇ ਪਾਣੀਆਂ ਦਾ। ਚੰਡੀਗੜ੍ਹ ਸਬੰਧੀ ਜੋ ਵੀ ਭਰਮ ਦੀ ਸਥਿਤੀ ਪੈਦਾ ਹੋਈ ਹੈ, ਇਸ ਬਾਰੇ ਸਰਕਾਰ ਨਾਲ ਗੱਲ ਕਰਕੇ ਇਹ ਭਰਮ ਵੀ ਦੂਰ ਕੀਤਾ ਜਾਵੇਗਾ। ਮੈ ਖੁਦ ਇਕ ਪੰਜਾਬੀ ਹੋਣ ਦੇ… — Sunil Jakhar (@sunilkjakhar) November 23, 2025 The Punjab BJP core committee held an early-morning virtual meeting with leaders in the central BJP to discuss the impact of the proposed bill on the psyche of the people in Punjab. The Tribune has learnt that the core committee largely agreed that the timing of the bill was problematic and it could give rise to avoidable distrust among the people of Punjab. The meeting was attended among others by Jakhar, BJP organisational in-charge of the state Mantri Srinivasulu and the entire BJP state top brass, including working president Ashwani Sharma. From the central BJP national general secretary Tarun Chugh attended the meeting. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/punjab-bjp-to-meet-amit-shah-will-seek-withdrawal-of-controversial-chandigarh-bill/</t>
+  </si>
+  <si>
+    <t>Uproar in Punjab as Centre lists Bill in Parl session to club Chandigarh with other UTs</t>
+  </si>
+  <si>
+    <t>The Constitution (131 Amendment) Bill-2025 listed for introduction, consideration and passing in the parliamentary bulletin proposes "to include the UT of Chandigarh in Article 240 of the Constitution of India, in alignment with other UTs without legislatures — namely Andaman &amp; Nicobar Islands, Lakshadweep, Dadra &amp; Nagar Haveli and Daman &amp; Diu, and Puducherry (when its Legislative Assembly is dissolved or suspended)." Article 240 deals with the power of the President to make regulations for the UTs covered under the provision and empowers the President to legislate directly and to frame regulations regarding governance of the said UTs. The winter session of Parliament is scheduled from December 1 to 19. Although the government has so far only listed the Bill along nine other new legislations for the upcoming session and its actual intent is yet to be revealed, the legislative move has spawned fears for its intent to grant the President powers over the Chandigarh Administration. These fears stand accentuated by the fact that all UTs with which the Centre wants to bracket Chandigarh are currently governed by L-Gs. Appointment of an independent L-G for administering Chandigarh would amount to the reversal of a 41-year-old system under which Punjab Governor was named the Administrator. The practice began in 1984, when terrorism hit Punjab. Punjab’s political leaders have now united in outrage over the proposed Bill, saying the move threatens the state’s historic claim and autonomy over its joint capital. While the opposition parties have vowed fierce resistance, the BJP has remained silent. Punjab Chief Minister Bhagwant Mann said, “Punjab strongly and unequivocally opposes the proposed Bill. This move is blatantly against Punjab’s interests. We will not allow any conspiracy against our state to succeed.” Opposing the amendment, SAD president Sukhbir Singh Badal said it was a direct assault on Punjab’s rights and a violation of federal principles. "We will never accept this,” he said. PCC president Amrinder Singh Warring said the Bill, if enacted, would have serious consequences for the state. "This is an ill-advised misadventure with far-reaching repercussions. Chandigarh belongs to Punjab, and any attempt to alter its status will face unprecedented resistance.” Chandigarh Congress MP Manish Tewari said, “I would like to read the Bill before commenting on it.” Reacting to the proposed Bill, Rajya Sabha MP from Punjab Vikramjit Singh Sahney urged all MPs from the state to rise above party lines and call on Home Minister Amit Shah to prevent the Bill that might dilute Punjab's claim over the capital city, which Haryana also claims. Though the Centre is yet to clarify intentions behind the Bill to bring Chandigarh under Article 240, Sahney said with the new Bill, Chandigarh is likely to be administered by an independent Administrator and would have similar administration rules such as Lakshadweep and others. The listing of the new Bill follows a meeting of the Northern Zonal Council, where CM Mann made a strong case for the transfer of Chandigarh to Punjab. The capital of Punjab was officially shifted from Lahore to Shimla in 1947 and subsequently to the newly planned city of Chandigarh on September 21, 1953. Section 4 of the Punjab Reorganisation Act, 1966, designated Chandigarh as a UT effective November 1, 1966, following the state's trifurcation. The proposed amendment also evokes memories of the Centre’s dramatic 2016 experiment, when the BJP-led NDA government appointed former IAS officer and ex-MLA KJ Alphons Kannanthanam as Chandigarh’s first independent Administrator, overturning a 32-year arrangement. That decision sparked an immediate political storm in Punjab, with the then NDA ally and CM Parkash Singh Badal of SAD strongly objecting to it. Within 24 hours, the Centre reversed course, restoring the Administrator’s role to the Punjab Governor. The development comes days after the government withdrew a controversial notification that sought to change the governance structure of Panjab University, triggering massive protests. The notification that altered PU's Senate strength was seen as the Centre's attempt to restructure the university's governance and an interference with Punjab's rights over the varsity. With Punjab Assembly elections due in early 2027, the move to bring a Constitution Amendment Bill is poised to snowball into a major electoral flashpoint, giving opposition parties a fresh rallying point. Leaders across parties argue that once Chandigarh is placed under Article 240, Punjab’s demand for the city’s transfer will be pushed permanently into rhetorical irrelevance. The Centre, however, is yet to issue any statement clarifying the long-term administrative vision behind the amendment. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/uproar-in-punjab-as-centre-lists-bill-in-parl-session-to-club-chandigarh-with-other-uts/</t>
+  </si>
+  <si>
+    <t>Zirakpur-Panchkula bypass stuck in red tape</t>
+  </si>
+  <si>
+    <t>Seven months after getting the Prime Minister-chaired Cabinet Committee on Economic Affairs’ approval, the Rs 1,878-crore Zirakpur–Panchkula Bypass remains knotted in red tape, with the National Highways Authority of India (NHAI) and the Forest Department locked in a blame game over why the crucial Stage-2 forest clearance is still pending. The delay has pushed the project back once again, forcing repeated extensions of the bidding deadline and leaving the Tricity’s biggest decongestion intervention stuck on paper. As per the latest amendment issued by NHAI’s Punjab Division, the last date for online submission of bids has now been pushed to 11 am on December 20, while the technical bids will be opened on December 22. The bypass, meant to pull heavy, inter-state and local traffic out of the chronically choked NH-5 and NH-7 stretch through Zirakpur and Panchkula, had secured Stage-1 forest approval from the Centre on July 31. However, the mandatory final Stage-2 approval — without which NHAI cannot open bids, award work or begin construction — remains elusive, despite the project forming a key component of the PM Gati Shakti National Master Plan. The Forest Department has contended that the delay stems from pending compliance requirements that NHAI has yet to fulfil. A senior official told The Tribune that forest clearances are issued in two stages and the Union government granted in-principle (Stage-1) approval on July 31, 2025. “After this, the user agency, in this case NHAI, must complete all compliance conditions and upload the report on the Centre’s portal. While compensatory levies have been deposited, certain other formalities such as NoCs, undertakings and the submission of ACA plantation details are still ongoing. the NHAI has to liaise with the concerned DFO to complete these. As soon as they do so, the case will be forwarded to the Government of India for grant of final approval,” the official said. The NHAI has strongly disputed this version, asserting that it has completed every requirement long ago and that the file is stuck with the Forest Department. A senior authority official said: “We have completed all formalities and met all conditions mandated in the Stage-1 approval long ago, but Stage-2 approval is still pending with the Forest Department for reasons best known to them, despite our repeated reminders. We are constrained to extend the bidding deadline again and again solely because Stage-2 is the only clearance that allows us to open bids, award the project and start work.” The impasse has again pushed back timelines for the bypass, which was conceived over a decade ago and for which land acquisition was completed as far back as 2020. Stretching 19.2 km from the Zirakpur-Patiala junction on NH-7 to the Zirakpur-Parwanoo junction on NH-5, the six-lane road includes a 6.195-km elevated section, five flyovers, one vehicular underpass, nine light vehicular underpasses, a major and a minor bridge, and a railway overbridge. It is designed to take through traffic away from the saturated Zirakpur lights, the Airport Road entry, and the Panchkula gateway while linking seamlessly with Sectors 24 and 25 and improving onward connectivity to Himachal Pradesh. Despite its strategic importance and repeated assurances from the Centre, the project continues to slip, with officials now expecting the work to be awarded only by early 2026 and construction unlikely to begin before March-April 2026 — provided the forest clearance arrives without further delay. As the file moves back and forth, the Tricity continues to grapple with daily gridlocks, rising pollution and stalled mobility improvements, even as one of its most crucial infrastructure projects remains entangled in bureaucratic loops. Cost: Rs 1,878.31 crore Length: 19.2 km (6.195 km elevated) Land acquisition: Completed 2020 Mode: Hybrid Annuity Mode Forest land diverted: 17.57 hectares Stage-1 approval: July 31, 2025 Stage-2 clearance: Pending Bid deadline: Extended five times since July 2025 Likely work award: Early 2026 Likely construction start: March-April 2026 Expected completion: 2028 Aimed at decongestiing worst choked NH-5/NH-7 overlap at Zirakpur. Key link in the Tricity’s proposed ring road. Reduces travel time, pollution and accident risk. Facilitates smoother movement to HP, Ambala, Airport and Panchkula. Stuck for over 10 years due to procedural clearances and inter-departmental delays. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/zirakpur-pkula-bypass-stuck-in-red-tape/</t>
+  </si>
+  <si>
+    <t>Centre unmoved, PU students continue stir</t>
+  </si>
+  <si>
+    <t>With just three days left for its November 25 ultimatum, the Panjab University (PU) Bachao Morcha’s indefinite dharna entered its 22nd day on Saturday, as students — backed by farmers, religious groups, civil-society outfits, social organisations, political leaders and Nihang factions — geared up for a “historic campus shutdown” on November 26. The bandh is expected to mirror the unprecedented November 10 protest, when the PU witnessed its largest youth mobilisation in recent memory. The Tribune had broken the PU overhaul story on November 1, triggering a political firestorm in Punjab and Chandigarh that forced the Centre to withdraw the restructuring within a week, issuing four notifications between October 30 and November 7. But despite the rollback, the Centre is yet to blink on the core demand: formal notification of the Senate election schedule as per the pre-October 30 structure. Two weeks after PU Vice-Chancellor Prof Renu Vig sent the recommendation to Vice-President and Chancellor CP Radhakrishnan on November 9, the file remains pending. Morcha leaders reiterated that unless the Senate poll notification is issued before November 25, PU will observe a complete bandh the next day with no academic, administrative or transport activity allowed. Fresh political support arrived today with former Punjab Finance Minister Parminder Singh Dhindsa visiting the protest site. “I joined the Panjab University Bachao Morcha today. The Central Government must stop delaying and immediately announce the Senate election date. The PU is not just an institution — it carries the emotions and legacy of Punjab. The Prime Minister should respect this sentiment and take timely action,” Dhindsa said. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/centre-unmoved-pu-students-continue-stir/</t>
+  </si>
+  <si>
+    <t>HC raps Chandigarh Admn for 10-year delay in deciding appeal</t>
+  </si>
+  <si>
+    <t>Acting on the direction of Punjab and Haryana High Court, the UT Administration has issued guidelines for timely disposal of appeals and revisions by statutory appellate/revisional authorities. The direction was issued after the matter came to notice of Justice Deepak Sibbal and Justice Lapita Banerjee. An appeal had been filed against levying of the property tax and fire cess, but had remained pending before the Appellate Authority for more than 10 years The High Court issued the order while hearing a petition filed by CSI Infrastructure Private Limited. The company told the court that it was the owner of Elante shopping mall and commercial complex located in Industrial Area Phase 1. On April 1, 2014, the Municipal Corporation (MC) demanded Rs 53,39,119 from the petitioner as property tax and fire cess, On May 19, 2014, the entire amount was deposited. In May 2015, an appeal under Section 146/147 of the Punjab Mural Corporation Act, 1976, as extended to the UT was filed for a refund, but had remained pending since. The court directed the UT Chief Secretary to file an affidavit explaining therein the reasons for the inordinate delay. The official told the court that the petitioner’s appeal has been finally heard by the appellate authority and order has been reserved for pronouncement. However, the court observed, “the petitioner’s statutory appeal… was finally heard in July 2025 i.e. after an inordinate delay of over 10 years. Least to say, such delay is not appreciated. To prevent a situation, the Chief Secretary is directed to issue and circulate appropriate guidelines to all statutory appellate revisional authorities in Chandigarh to ensure that in future such inordinate delays do not occur in disposal of statutory appeals revisions. The needful be done within two months from the date of rescue of a copy of this order.” Acting on the direction, the UT issued the guidelines, reading: “In case, the statute is silent about the period in which the appeal/ revision is to be decided then the statutory appellate/ revision authority shall put in earnest efforts to dispose of the same within a period of 180 days extendable up to 365 days of the filing of appeal revision. Interim applications be disposed of within a period of 60 days from the date of appearance of both the parties,” it added. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/hc-raps-chandigarh-admn-for-10-year-delay-in-deciding-appeal/</t>
+  </si>
+  <si>
+    <t>Winged visitor count down 67% at Sukhna Lake</t>
+  </si>
+  <si>
+    <t>The arrival of migratory birds to Sukhna Lake and its surrounding areas has dropped substantially, with nearly 67 per cent fewer avian guests being spotted so far this year. During a recent survey, the Chandigarh Bird Club identified 26 species of migratory birds and spotted 232 birds. However, the club had identified 31species and sighted 705 birds during the same period in November last year. Of these migratory birds, the most common species was the ruddy shelduck with 32 sightings, followed by 28 sightings of gadwall, 26 of Indian spot-billed duck, 23 of black-crowned night heron, 11 of great cormorant. The Club conducts annual surveys at Sukhna Lake to commemorate the Birdman of India, Dr Salim Ali, on his birth anniversary, which happens to coincide with the arrival of migrating waterfowl. Rima Dhillon, club president, said, “There were hardly any birds to be seen on the water.” “Birds migrate when it gets too cold in their breeding grounds in the Tundra regions depleting food sources. If food can still be found in plenty, then the birds delay their migratory journey. However, if the areas they have been frequenting traditionally are degraded, they will be forced to divert to other places,” she added. Over the course of the survey, only eight Eurasian moorhen, seven red-wattled lapwing, Indian pond-heron and grey heron each, six northern shoveller and little cormorant each, four white-throated kingfisher and white wagtail each, three grey-headed swamphen, purple heron and oriental darter each, two green sandpiper and little egret each were spotted. Besides, a solitary great egret, a grey wagtail, a woolly-necked stork, a common kingfisher and a stork-billed kingfisher were also found at Sukhna. Dhillon said the elusive stork-billed kingfisher was a single bird resident at the location and has been reported since 2017. She added that while it was too early, the club members hoped to see the arrival of more birds of each species as the temperatures drop further. Another birder attributed the drop in numbers to global warming and possible degradation of habitat. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/winged-visitor-count-down-67-at-sukhna-lake/</t>
+  </si>
+  <si>
+    <t>Nagar Kirtan departs for Sri Anandpur Sahib</t>
+  </si>
+  <si>
+    <t>The Nagar Kirtan, dedicated to the 350th martyrdom anniversary of Sri Guru Tegh Bahadur Sahib and his revered disciples — Bhai Mati Das, Bhai Sati Das and Bhai Dyala Ji — began from Talwandi Sabo. After a night halt in Mohali, the Nagar Kirtan resumed its onward journey to Sri Anandpur Sahib this morning following an Ardas. The Nagar Kirtan took the route via the Kharar flyover to proceed towards Sri Anandpur Sahib, where devotees gathered at Gurdwara Sri Kartarsar Sahib, Padiala, and paid obeisance by offering a Rumala Sahib. After the night halt on Friday at Gurdwara Singh Shaheedan, Sohana, and Gurdwara Sri Amb Sahib, the sangat gathered early in the morning. Under the blessed guidance of the Panj Pyare and Nishanchi Singhs, the Nagar Kirtan proceeded towards the next destination with the holy presence of Sri Guru Granth Sahib Ji. Sri Guru Granth Sahib Ji was ceremoniously carried from the Sukh Aasan location to the Palki Sahib with complete devotion and adherence to the Sikh maryada. A large number of devotees participated in the ceremony. Member of Parliament Malvinder Singh Kang, Punjab Water Supply and Sewerage Board Chairman Dr Sunny Singh Ahluwalia, councillor Sarabjit Singh Samana and Deputy Commissioner Komal Mittal, along with other officials, attended the ceremony. The district police welcomed the Palki Sahib with a Guard of Honour. As the Nagar Kirtan set off towards Sri Anandpur Sahib amidst the resounding chants of “Bole So Nihal… Sat Sri Akal!”, a unique sense of spiritual fervour and joy was witnessed among the devotees. Kang said, “The government feels deeply blessed to commemorate the 350th martyrdom year of Sri Guru Tegh Bahadur Sahib with such devotion.” He urged the sangat to participate in large numbers in the state-level events being organised at Sri Anandpur Sahib from November 23 to 25. “For the first time in the history of the Punjab Vidhan Sabha, a special session will be held on November 24 at Sri Anandpur Sahib, dedicated to honouring the supreme sacrifice of Guru Tegh Bahadur Sahib for the protection of human rights and religious freedom,” he said. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/nagar-kirtan-departs-for-sri-anandpur-sahib/</t>
+  </si>
+  <si>
+    <t>3 held with 16 snatched mobile phones, 3 bikes</t>
+  </si>
+  <si>
+    <t>The police have arrested three youths and recovered 16 snatched mobile phones and three stolen bikes from their possession. Arrested accused have been identified as Desumajra residents Satnam Kumar, Sunny, Arsh Ali, alias Manna, and Karan, alias Bhola, a resident of Sunny Enclave. A case under Sections 304 and 3 (5) of the BNS was registered against the accused at the Phase-1 police station. Prithvi Singh Chahal, DSP (City-1), said, “The accused were arrested near the ESI Hospital, Industrial Area, Phase 7, at a naka.” The accused were produced in a court which sent them to police remand, he said. Their questioning led to solving of snatching and theft cases and subsequent recovery of mobile phones and two-wheelers, he said. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/3-held-with-16-snatched-mobile-phones-3-bikes/</t>
+  </si>
+  <si>
+    <t>Campus notes</t>
+  </si>
+  <si>
+    <t>PU institute gets Rs 42.58L for research Chandigarh: Dr SSB University Institute of Chemical Engineering and Technology (Dr SSBUICET), Panjab University (PU), has received the approval of Rs 42.58 lakh funding for its major CSR-funded research initiative on “Sustainable agri-waste polymeric composites (SAW-POLYCOM)” from Petronet LNG Limited. The project will be led by Prof Anupama Sharma, Chairperson, Dr SSBUICET, and Director, Energy Research Centre. She will be supported by project co-coordinators Dr Gaurav Rattan, Dr Surinder Singh Bhinder and Dr Nidhi Singhal. The tie-up aims to turn agri-waste into useful composite materials, cut stubble burning and open new income routes for farmers. The team will develop durable and high-performance composite panels using rice straw, rice husk and phragmites. ---------------------- Conference on women leadership Chandigarh: The 55th Annual Conference of the Indian Pharmacological Science (IPC–IPSCON 2025) at Panjab University today discussed women leadership, healthcare innovation and youth empowerment during the second day of its three-day international conference on pharmacology. A large number of students, national regulators, global experts and senior industry voices participated in the conference. ------------------------------------- Cyber Crime Awareness Camp Mohali: Sri Sukhmani Group of Institutions, Dera Bassi, organised a Cyber Crime Awareness Camp aimed at educating students and staff about the growing dangers in today’s digital landscape. Officials from the Punjab State Cyber Crime Cell, Mohali — Inspector Manisha Verma and Inspector Manjinder Singh — addressed the audience with insightful presentations focused on modern cyber threats and safety practices. They discussed the sharp rise in cyber fraud cases, particularly among youth, due to the expanding use of smartphones, social media, and digital payment platforms. They shared real-life incidents to help participants understand how cybercriminals operate across different online spaces. -------------------------------------- National-level innovation challenge Mohali: Plaksha University, in collaboration with the Mphasis F1 Foundation, hosted the TrackShift Innovation Challenge at the Plaksha University Campus. The two-day national-level innovation challenge brought together over 150 students from 50 teams across India to co-create open-source, industry-ready solutions inspired by motorsport’s precision, data-led problem solving and engineering excellence. The initiative, inspired by Mphasis, official digital partner of the MoneyGram Haas F1 Team, was aimed at students from STEM backgrounds to apply emerging technologies such as artificial intelligence, data science and simulation to solve real-world challenges across mobility, infrastructure and manufacturing. -------------------------------------------------- Capacity building workshop starts Chandigarh: A two-day capacity building workshop on innovation, design and entrepreneurship (IDE) commenced today at Desh Bhagat University (DBU). The programme is being jointly organised by the Department of School Education and Literacy, the All India Council for Technical Education (AICTE), and the Ministry of Education Innovation Cell (MIC), with support from the Wadhwani Foundation. The programme aims to equip District Education Officers and DIET members with skills in innovation, creativity, design thinking and entrepreneurship, in alignment with the NEP 2020. -------------------------------------- Annual function at Dev Samaj School Chandigarh: IS Dev Samaj Senior Secondary School, Sector 21, organised the annual function “Guldasta” for the pre-primary wing as a heartfelt tribute to the Nirmal Singh Dhillon. Dhillon was a social reformer and the secretary, Dev Samaj Society. The celebration spread over two days aimed at showcasing the talent of young learners, while spreading meaningful and healthy messages through a range of thoughtfully curated performances. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/campus-notes-77/</t>
+  </si>
+  <si>
+    <t>Illegal mining: Panchkula Police conduct raid, seize JCB, tipper truck in Raipur Rani</t>
+  </si>
+  <si>
+    <t>The Panchkula Police continues to take stringent action against illegal mining, maintaining round-the-clock vigilance and carrying out regular checks across all mining zones in the district. In a recent high-level meeting chaired by Panchkula Police Commissioner Shivas Kabiraj, clear directives were issued to adopt a zero-tolerance approach and take immediate and strict action against illegal mining. In line with these instructions, the Anti-Illegal Mining Team-2 of the Panchkula Police, led by Inspector Hitendra Singh, carried out a major operation in the Raipur Rani area today. The team received information that illegal mining was being carried out near Shahjahanpur village using a JCB machine and tipper trucks. Acting swiftly, the team reached the spot and stopped illegal mining. Following the action, Raipur Rani SHO Pritam Singh and the Dial-112 team were called to the site. The police seized one tipper truck and one JCB machine and sent these to the Raipur Rani police station. The Mining Department was also formally notified for further legal proceedings in this connection. The Police Commissioner said illegal mining would not be tolerated under any circumstances. He said strictest legal action would continue against those involved in such activities. The police have made it clear that the joint crackdown on illegal mining would continue, and immediate action would be taken wherever such activities were detected in the district. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/illegal-mining-panchkula-police-conduct-raid-seize-jcb-tipper-truck-in-raipur-rani/</t>
+  </si>
+  <si>
+    <t>4 of family injured as power pole collapses on car in Zirakpur</t>
+  </si>
+  <si>
+    <t>Four members of a family, including a child, sustained serious injuries when an electricity pole and wires fell on a car parked on roadside near Nabha Sahib Gurdwara in Zirakpur today morning. Locals said electricity wires got entangled in an HP registered truck passing through the road. Victim Kush Jindal, 66, son, daughter-in-law, and grandson were inside the car, parked on the roadside, waiting for another vehicle when the pole fell on their four-wheeler suddenly. The victims sustained serious injuries and were rushed to a nearby private hospital. The car was badly damaged in the incident. The electricity cable network was snapped as the impact brought down a nearby power pole on the vehicle. The truck driver reportedly fled the spot, leaving behind his vehicle. Locals said the driver was reversing his truck on the road heading from Patiala Chowk to Nabha Sahib when the wires got entangled in the vehicle. Power supply in the Lohgarh, VIP Road, Green Lotus and the Dyalpura area was snapped and remained affected till afternoon. Punjab State Power Corporation Limited (PSPCL) and police officials reached the spot and began the repair work. On the complaint of PSPCL officials, a case of negligent driving was registered against the absconding driver at the Zirakpur police station. Officials claimed that the damages would be recovered from the truck driver. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/4-of-family-injured-as-power-pole-collapse-on-car-in-zirakpur/</t>
+  </si>
+  <si>
+    <t>Book launches, talks and cultural performances light up Lit Fest Day 1</t>
+  </si>
+  <si>
+    <t>The 13th edition of CLF Literati 2025, organised by the Chandigarh Literary Society (CLS), commenced on Saturday with an array of literary sessions, book launches, and cultural performances that set the tone for two days of intellectual and creative exchange. The festival opened with a welcome address by Dr Sumita Misra, Festival Director and Chairperson, CLS, followed by an inaugural speech from Madhav Kaushik, President, Rashtriya Sahitya Akademi. While highlighting the journey of Literati, Dr Misra, said, “From modest beginnings, Literati has blossomed into one of the most anticipated literary events in the region and India.” She said the theme for this year, “World Within Words”, reflects the universe contained within every word — a doorway to new ideas, emotions, and histories. The day’s sessions offered a rich mix of discourse and book launches. In “The Power of a Story: Advertising Insights”, advertising guru Prahlad Kakkar interacted with writer Aradhika Sharma. Political discourse featured prominently in “Indian Democracy: Evolving Polity and Public Discourse”, with former MP Shahid Siddiqui, Rasheed Kidwai, and journalist Neerja Chowdhury in conversation with another journalist Ramesh Vinayak. Other highlights included Deep Halder launching his book “Inshallah Bangladesh” during a session on the country’s unfinished revolution, while Mehak Grover (The Silent Brave) and Manju Jaidka (The Legend of Sanjhi-Giri) also unveiled their new works in “Book Buzz”. Regional stories take centre stage Sessions on Hindi literature, poetry, and regional stories featured names like Madhav Kaushik, Chandra Trikha, Bubbu Tir, and Dr Sumita Misra, who spoke candidly about balancing administrative responsibilities with her passion for poetry. The festival also included Bharatanatyam performance “Swarit Mudrayen” by disciples of Dr Sucheta Bhide-Chapekar at Bhartiya Vidya Bhawan, Sector 27, here. Saturday set a high bar for Sunday, which promises sessions like “Bihar Diaries and Ground Zero: Real Heroes, Real Stories” featuring IPS officer Amit Lodha, and the CLF Literati Awards 2025, expected to draw significant attention from literature enthusiasts and cultural aficionados alike. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/book-launches-talks-and-cultural-performances-light-up-lit-fest-day-1/</t>
+  </si>
+  <si>
+    <t>Nagar Kirtan accorded warm welcome at Mandi Gobindgarh</t>
+  </si>
+  <si>
+    <t>Government sponsored Nagar Kirtan dedicated to the 350th martyrdom anniversary of Guru Tegh Bahadur Sahib, which commenced from Faridkot, was accorded a warm welcome on its arrival at Mandi Gobindgarh in Fatehgarh Sahib district. Cabinet Minister Tarunpreet Singh Sond, Deputy Commissioner Dr Sona Thind and a large number of devotees were present on the occasion. The district police presented a guard of honour for the Nagar Kirtan. Speaking on the occasion, Saud said, “Sri Guru Tegh Bahadur Ji sacrificed his life for the protection of human rights and religious freedom. Such an example is not found anywhere else in the world. The Punjab Government has planned a wide-ranging programme to pay homage to the martyrdom of guru sahib. Various religious programmes will be held at Sri Anandpur Sahib from November 23 to 25. The aim of these programmes is to convey the eternal message of guru sahib’s teachings, life, martyrdom and the good of humanity to every person living in every corner of the world.” On the occasion the district administration made elaborate arrangements for the convenience of the devotees. The roads were renovated and all defunct street lights were repaired. The streets and drains were cleaned and a complete facelift was given to the city. After night stay at Gurdwara Fatehgarh Sahib, the Nagar Kirtan proceeded towards Sri Anandpur Sahib early in the morning. Sant Baba Lakha Singh, Amloh MLA Gurinder Singh Gary Baring, Fatehgarh Sahib MLA Lakhbir Singh Rai, ADC Arvind Gupta, SDM Chetan Bangar and Chief Minister’s Field Officer Shankar Sharma participated in the Nagar Kirtan. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/nagar-kirtan-accorded-warm-welcome-at-mandi-gobindgarh/</t>
+  </si>
+  <si>
+    <t>Sunny Enclave residents stage dharna over erratic water supply Tribune News Service</t>
+  </si>
+  <si>
+    <t>Residents of several housing societies in Sunny Enclave staged a protest demonstration for an hour on Airport Road, near Gopal Sweets point, after water supply remained disrupted in Sector 123, 124 and 125 for the last three days. Residents complained of erratic water supply after power was disconnected from around 22 tubewells in Sector 123, 124 and 125. Officials said some of the tubewells had already been taken over from the Kharar Municipal Council. Five of these tubewells get supply from Punjab State Power Corporation Limited, Mohali circle, while 11 were under the Kharar circle, they said. Officials said the tubewells were being powered by illegal kundi connections after power was disconnected due to non-payment of bills amounting to Rs 12 lakh. Later in the evening, the water supply was restored in majority of the areas with the help of generator sets. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/sunny-enclave-residents-stage-dharna-over-erratic-water-supply-tribune-news-service/</t>
+  </si>
+  <si>
+    <t>Jeweller held for buying stolen ornaments</t>
+  </si>
+  <si>
+    <t>The Crime Branch, Sector 19, has arrested a jeweller who purchased stolen jewellery at low prices from accused. On January 2 this year, a local resident had lodged a theft complaint with the Sector-10 police post here. According to the complainant, the family had been away for some work. Upon returning home, they found the cupboard locks broken and jewellery and cash missing. A case was registered and an investigation began. During the investigation, a Crime Branch team arrested two accused — Sandeep Kumar, alias Sanju, and Jagjit Singh, alias Jagga — on November 3. Both are residents of Ambala. During questioning, they confessed to the crime and handed over Rs 20,000 in cash stolen from the house. They further disclosed that they had sold the stolen gold jewellery to Vinay Verma, son of Trilokinath, a resident of Ambala district. Following this revelation, the police arrested Vinay Verma on November 17. He was produced in the court and remanded in two-day police custody. During interrogation, the accused led the police to his home in Ambala, from where the stolen jewellery was recovered. The recovered items included one gold necklace, two gold earrings, one gold pendant and four gold rings, weighing a total of 61 grams and valued at approximately Rs 8 lakh. The DCP (Crime), Manpreet Singh Sudan, has issued a public advisory urging citizens to always verify the receipt, original bill, authenticity certificates, seller’s identity and related documents when purchasing any second-hand items. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/jeweller-held-for-buying-stolen-ornaments/</t>
+  </si>
+  <si>
+    <t>2 more arrested in suicide case</t>
+  </si>
+  <si>
+    <t>The Raipur Rani police have arrested two more accused in the Sagar Singla suicide case. They have been identified as Johnny and Parvinder, both residents of Raipur Rani, Panchkula. Earlier, the police had arrested Shiv Kumar, alias Kaku, a resident of Raipur Rani, on November 13. The incident occurred on November 4. Singla had levelled allegations of severe assault and mental harassment against certain individuals in a video recorded before taking his own life. Panchkula DCP Srishti Gupta stated that the two accused were produced before the court today, which remanded them in judicial custody. She added that efforts were underway to trace one more remaining accused in the case, and he would be arrested soon. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/2-more-arrested-in-suicide-case/</t>
+  </si>
+  <si>
+    <t>National Unity Day celebrated with grand march at Sec 17</t>
+  </si>
+  <si>
+    <t>The National Unity Day &amp; Sardar@150 Unity March was held with patriotic fervour today at Tiranga Park, Sector 17, here, commemorating the birth anniversary of Sardar Vallabhbhai Patel, the architect of India’s integration. The event witnessed enthusiastic participation from thousands of citizens, including youth, women, students, various social groups and representatives from 28 states and 8 UTs, symbolising India’s rich diversity and collective identity. Punjab Governor and UT Administrator Gulab Chand Kataria flagged off the march. Addressing the gathering, he said Chandigarh stood as a living example of unity in diversity, where people from all regions, cultures and languages lived together with mutual respect and national pride. He highlighted Punjab’s historic contribution and sacrifices in the nation’s freedom struggle, defence services, sports and academics, and also paid homage to Guru Tegh Bahadur for his supreme sacrifice to protect Kashmiri Hindus. He described Gurdwara Sis Ganj Sahib, Delhi, as a living symbol of that courage and devotion. The Governor remembered Sardar Patel’s monumental role in uniting 562 princely states and shaping a strong and integrated India, honouring him as the Iron Man of India. He emphasised that the spirit of Bardoli Satyagraha and Patel’s principles of justice, courage, discipline and national integrity continued to inspire the nation and form the foundation of Prime Minister Narendra Modi’s “Ek Bharat Shreshtha Bharat” initiative. The Governor stressed that national unity was the key to achieving the vision of Viksit Bharat @ 2047, built upon four pillars — cultural unity, linguistic harmony, inclusive development through poverty elimination and equal opportunity, and connectivity and emotional integration. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/national-unity-day-celebrated-with-grand-march-at-sec-17/</t>
+  </si>
+  <si>
+    <t>Prisha bags skating gold</t>
+  </si>
+  <si>
+    <t>Prisha of The Gurukul School won gold medal in the girls’ U-11 1,000m event at the CBSE All India National Skating Championship, in Gurugram. Kaayna Bhardwaj from the same school, meanwhile, emerged victorious in the 500m girls’ U-11 inline event. Another student from the Gurukul Global School, Gauresh Pawa, also won bronze medal in the boys’ quads 12–15 category. Meanwhile, the skaters of the Rolling Tigers Academy bagged five medals, including two gold, a silver, and two bronze medals. Vihaan Khullar of the Hansraj School, Panchkula, won a silver and a bronze medal in the boys’ U-9 inline event. —TNS Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/prisha-bags-skating-gold/</t>
+  </si>
+  <si>
+    <t>35 challans issued for encroachments in Chandigarh's Sector 22</t>
+  </si>
+  <si>
+    <t>The Municipal Corporation (MC) today carried out an intensive anti-encroachment drive across key locations of Sector 22, including Shastri Market, Kiran Cinema area, the vendor zone and the surrounding stretches in the sector. During the drive, 35 challans were issued to violators found flouting civic norms and occupying public spaces illegally. Encroachments near the Sector-22 dispensary were also effectively removed as part of the coordinated action. The anti-encroachment drive was conducted under the direct supervision of Municipal Joint Commissioner Himanshu Gupta, who was accompanied by the civic body’s enforcement inspectors and field staff. The team undertook a thorough inspection of the market areas, footpaths and vending zones, removing unauthorised structures and items obstructing public movement. Goods displayed beyond permissible limits, illegal extensions and unauthorized setups were cleared to ensure smooth pedestrian movement and restore public convenience. The Joint Commissioner emphasised that such drives will continue regularly to maintain discipline and uphold the city’s cleanliness and accessibility standards. He further reiterated the civic body’s commitment to reclaiming public spaces from illegal occupation and ensuring that market areas remain organised. Take your experience further with Premium access.Thought-provoking Opinions, Expert Analysis, In-depth Insights and other Member Only Benefits Already a Member? Sign In Now</t>
+  </si>
+  <si>
+    <t>https://www.tribuneindia.com/news/chandigarh/35-challans-issued-for-encroachments-in-chandigarhs-sector-22/</t>
   </si>
 </sst>
 </file>
@@ -2329,7 +3970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F260"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2389,7 +4030,7 @@
         <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2397,19 +4038,19 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2417,19 +4058,19 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2437,19 +4078,19 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" t="s">
         <v>29</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2457,19 +4098,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" t="s">
         <v>34</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2477,19 +4118,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
         <v>37</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" t="s">
         <v>39</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2497,19 +4138,19 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
         <v>42</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" t="s">
         <v>44</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2517,19 +4158,19 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" t="s">
         <v>49</v>
       </c>
-      <c r="E10" t="s">
-        <v>50</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2537,19 +4178,19 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="E11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2557,19 +4198,19 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="E12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2577,19 +4218,19 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="E13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2597,19 +4238,19 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E14" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="E14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2617,19 +4258,19 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="E15" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2637,19 +4278,19 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="E16" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2657,19 +4298,19 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" t="s">
         <v>81</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" t="s">
         <v>83</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2677,19 +4318,19 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" t="s">
         <v>86</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" t="s">
         <v>88</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2697,19 +4338,19 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" t="s">
         <v>91</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" t="s">
         <v>93</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2717,19 +4358,19 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" t="s">
         <v>96</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" t="s">
         <v>98</v>
       </c>
-      <c r="E20" t="s">
-        <v>99</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>100</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2737,19 +4378,19 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="E21" t="s">
-        <v>104</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2757,19 +4398,19 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
         <v>107</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="E22" t="s">
-        <v>109</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2777,19 +4418,19 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C23" t="s">
+      <c r="E23" t="s">
         <v>112</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="E23" t="s">
-        <v>114</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2797,19 +4438,19 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C24" t="s">
+      <c r="E24" t="s">
         <v>117</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="E24" t="s">
-        <v>119</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2817,19 +4458,19 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25" t="s">
         <v>122</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="E25" t="s">
-        <v>124</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2837,19 +4478,19 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C26" t="s">
+      <c r="E26" t="s">
         <v>127</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="E26" t="s">
-        <v>129</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2857,19 +4498,19 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C27" t="s">
+      <c r="E27" t="s">
         <v>132</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="E27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2877,19 +4518,19 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" t="s">
         <v>135</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" t="s">
         <v>137</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2909,7 +4550,7 @@
         <v>142</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2917,19 +4558,19 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C30" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2937,19 +4578,19 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C31" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E31" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2957,19 +4598,19 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C32" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E32" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2977,19 +4618,19 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2997,19 +4638,19 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C34" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E34" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -3017,19 +4658,19 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C35" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E35" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -3037,19 +4678,19 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C36" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E36" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -3057,19 +4698,19 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C37" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E37" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -3077,19 +4718,19 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E38" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -3097,19 +4738,19 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C39" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E39" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -3117,19 +4758,19 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C40" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E40" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>120</v>
+        <v>198</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -3137,19 +4778,19 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C41" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E41" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>120</v>
+        <v>203</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -3157,19 +4798,19 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C42" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E42" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>120</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -3177,19 +4818,19 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C43" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E43" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>120</v>
+        <v>213</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -3197,19 +4838,19 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C44" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E44" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -3217,19 +4858,19 @@
         <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C45" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E45" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>120</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -3237,19 +4878,19 @@
         <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C46" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E46" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -3257,19 +4898,19 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C47" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E47" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>120</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -3277,19 +4918,19 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C48" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E48" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>120</v>
+        <v>237</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -3297,19 +4938,19 @@
         <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C49" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E49" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>120</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -3317,19 +4958,19 @@
         <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C50" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E50" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>120</v>
+        <v>247</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -3337,919 +4978,3209 @@
         <v>6</v>
       </c>
       <c r="B51" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="C51" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="E51" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>120</v>
+        <v>252</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B52" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="C52" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="E52" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B53" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="C53" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="E53" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B54" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C54" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="E54" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B55" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="E55" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B56" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="C56" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="E56" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B57" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="C57" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E57" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B58" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="C58" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="E58" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B59" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="C59" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="E59" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B60" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="C60" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="E60" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B61" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="C61" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="E61" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B62" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="C62" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="E62" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B63" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="C63" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="E63" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B64" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="C64" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="E64" t="s">
-        <v>306</v>
+        <v>267</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B65" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="C65" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="E65" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B66" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="C66" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="E66" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B67" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="C67" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="E67" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B68" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C68" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="E68" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B69" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C69" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="E69" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B70" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C70" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="E70" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B71" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="C71" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="E71" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B72" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="C72" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="E72" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B73" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="C73" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="E73" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B74" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="C74" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="E74" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B75" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C75" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="E75" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B76" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="C76" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="E76" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B77" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="C77" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="E77" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B78" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="C78" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="E78" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B79" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="C79" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="E79" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B80" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="C80" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="E80" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B81" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="C81" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="E81" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B82" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="C82" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="E82" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B83" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="C83" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="E83" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B84" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C84" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="E84" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B85" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="C85" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="E85" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B86" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="C86" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="E86" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B87" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="C87" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="E87" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B88" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="C88" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="E88" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B89" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="C89" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="E89" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B90" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="C90" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="E90" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B91" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="C91" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="E91" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B92" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="C92" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="E92" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B93" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="C93" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="E93" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B94" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="C94" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="E94" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B95" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="C95" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="E95" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>242</v>
+        <v>473</v>
       </c>
       <c r="B96" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="C96" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="E96" t="s">
-        <v>466</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>467</v>
+        <v>476</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
+        <v>473</v>
+      </c>
+      <c r="B97" t="s">
+        <v>477</v>
+      </c>
+      <c r="C97" t="s">
+        <v>478</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
+        <v>473</v>
+      </c>
+      <c r="B98" t="s">
+        <v>480</v>
+      </c>
+      <c r="C98" t="s">
+        <v>481</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
+        <v>473</v>
+      </c>
+      <c r="B99" t="s">
+        <v>483</v>
+      </c>
+      <c r="C99" t="s">
+        <v>484</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
+        <v>473</v>
+      </c>
+      <c r="B100" t="s">
+        <v>486</v>
+      </c>
+      <c r="C100" t="s">
+        <v>487</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
+        <v>473</v>
+      </c>
+      <c r="B101" t="s">
+        <v>489</v>
+      </c>
+      <c r="C101" t="s">
+        <v>490</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" t="s">
+        <v>473</v>
+      </c>
+      <c r="B102" t="s">
+        <v>492</v>
+      </c>
+      <c r="C102" t="s">
+        <v>493</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" t="s">
+        <v>473</v>
+      </c>
+      <c r="B103" t="s">
+        <v>495</v>
+      </c>
+      <c r="C103" t="s">
+        <v>496</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" t="s">
+        <v>473</v>
+      </c>
+      <c r="B104" t="s">
+        <v>498</v>
+      </c>
+      <c r="C104" t="s">
+        <v>499</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" t="s">
+        <v>473</v>
+      </c>
+      <c r="B105" t="s">
+        <v>501</v>
+      </c>
+      <c r="C105" t="s">
+        <v>502</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" t="s">
+        <v>473</v>
+      </c>
+      <c r="B106" t="s">
+        <v>504</v>
+      </c>
+      <c r="C106" t="s">
+        <v>505</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" t="s">
+        <v>473</v>
+      </c>
+      <c r="B107" t="s">
+        <v>507</v>
+      </c>
+      <c r="C107" t="s">
+        <v>508</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" t="s">
+        <v>473</v>
+      </c>
+      <c r="B108" t="s">
+        <v>510</v>
+      </c>
+      <c r="C108" t="s">
+        <v>511</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" t="s">
+        <v>473</v>
+      </c>
+      <c r="B109" t="s">
+        <v>513</v>
+      </c>
+      <c r="C109" t="s">
+        <v>514</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
+        <v>473</v>
+      </c>
+      <c r="B110" t="s">
+        <v>516</v>
+      </c>
+      <c r="C110" t="s">
+        <v>517</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" t="s">
+        <v>473</v>
+      </c>
+      <c r="B111" t="s">
+        <v>519</v>
+      </c>
+      <c r="C111" t="s">
+        <v>520</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" t="s">
+        <v>473</v>
+      </c>
+      <c r="B112" t="s">
+        <v>522</v>
+      </c>
+      <c r="C112" t="s">
+        <v>523</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" t="s">
+        <v>473</v>
+      </c>
+      <c r="B113" t="s">
+        <v>525</v>
+      </c>
+      <c r="C113" t="s">
+        <v>526</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" t="s">
+        <v>473</v>
+      </c>
+      <c r="B114" t="s">
+        <v>528</v>
+      </c>
+      <c r="C114" t="s">
+        <v>529</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" t="s">
+        <v>473</v>
+      </c>
+      <c r="B115" t="s">
+        <v>531</v>
+      </c>
+      <c r="C115" t="s">
+        <v>532</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" t="s">
+        <v>534</v>
+      </c>
+      <c r="B116" t="s">
+        <v>535</v>
+      </c>
+      <c r="C116" t="s">
+        <v>536</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" t="s">
+        <v>534</v>
+      </c>
+      <c r="B117" t="s">
+        <v>538</v>
+      </c>
+      <c r="C117" t="s">
+        <v>539</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" t="s">
+        <v>534</v>
+      </c>
+      <c r="B118" t="s">
+        <v>541</v>
+      </c>
+      <c r="C118" t="s">
+        <v>542</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" t="s">
+        <v>534</v>
+      </c>
+      <c r="B119" t="s">
+        <v>544</v>
+      </c>
+      <c r="C119" t="s">
+        <v>545</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" t="s">
+        <v>534</v>
+      </c>
+      <c r="B120" t="s">
+        <v>547</v>
+      </c>
+      <c r="C120" t="s">
+        <v>548</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" t="s">
+        <v>534</v>
+      </c>
+      <c r="B121" t="s">
+        <v>550</v>
+      </c>
+      <c r="C121" t="s">
+        <v>551</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" t="s">
+        <v>534</v>
+      </c>
+      <c r="B122" t="s">
+        <v>553</v>
+      </c>
+      <c r="C122" t="s">
+        <v>554</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" t="s">
+        <v>534</v>
+      </c>
+      <c r="B123" t="s">
+        <v>556</v>
+      </c>
+      <c r="C123" t="s">
+        <v>557</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" t="s">
+        <v>534</v>
+      </c>
+      <c r="B124" t="s">
+        <v>559</v>
+      </c>
+      <c r="C124" t="s">
+        <v>560</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" t="s">
+        <v>534</v>
+      </c>
+      <c r="B125" t="s">
+        <v>562</v>
+      </c>
+      <c r="C125" t="s">
+        <v>563</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" t="s">
+        <v>534</v>
+      </c>
+      <c r="B126" t="s">
+        <v>565</v>
+      </c>
+      <c r="C126" t="s">
+        <v>566</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" t="s">
+        <v>534</v>
+      </c>
+      <c r="B127" t="s">
+        <v>568</v>
+      </c>
+      <c r="C127" t="s">
+        <v>569</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" t="s">
+        <v>534</v>
+      </c>
+      <c r="B128" t="s">
+        <v>571</v>
+      </c>
+      <c r="C128" t="s">
+        <v>572</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" t="s">
+        <v>534</v>
+      </c>
+      <c r="B129" t="s">
+        <v>574</v>
+      </c>
+      <c r="C129" t="s">
+        <v>575</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" t="s">
+        <v>534</v>
+      </c>
+      <c r="B130" t="s">
+        <v>577</v>
+      </c>
+      <c r="C130" t="s">
+        <v>578</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" t="s">
+        <v>534</v>
+      </c>
+      <c r="B131" t="s">
+        <v>580</v>
+      </c>
+      <c r="C131" t="s">
+        <v>581</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" t="s">
+        <v>534</v>
+      </c>
+      <c r="B132" t="s">
+        <v>583</v>
+      </c>
+      <c r="C132" t="s">
+        <v>584</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" t="s">
+        <v>534</v>
+      </c>
+      <c r="B133" t="s">
+        <v>586</v>
+      </c>
+      <c r="C133" t="s">
+        <v>587</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" t="s">
+        <v>534</v>
+      </c>
+      <c r="B134" t="s">
+        <v>589</v>
+      </c>
+      <c r="C134" t="s">
+        <v>590</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" t="s">
+        <v>534</v>
+      </c>
+      <c r="B135" t="s">
+        <v>592</v>
+      </c>
+      <c r="C135" t="s">
+        <v>593</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" t="s">
+        <v>595</v>
+      </c>
+      <c r="B136" t="s">
+        <v>596</v>
+      </c>
+      <c r="C136" t="s">
+        <v>597</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" t="s">
+        <v>595</v>
+      </c>
+      <c r="B137" t="s">
+        <v>599</v>
+      </c>
+      <c r="C137" t="s">
+        <v>600</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" t="s">
+        <v>595</v>
+      </c>
+      <c r="B138" t="s">
+        <v>602</v>
+      </c>
+      <c r="C138" t="s">
+        <v>603</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" t="s">
+        <v>595</v>
+      </c>
+      <c r="B139" t="s">
+        <v>605</v>
+      </c>
+      <c r="C139" t="s">
+        <v>606</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" t="s">
+        <v>595</v>
+      </c>
+      <c r="B140" t="s">
+        <v>608</v>
+      </c>
+      <c r="C140" t="s">
+        <v>609</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" t="s">
+        <v>595</v>
+      </c>
+      <c r="B141" t="s">
+        <v>611</v>
+      </c>
+      <c r="C141" t="s">
+        <v>612</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" t="s">
+        <v>595</v>
+      </c>
+      <c r="B142" t="s">
+        <v>614</v>
+      </c>
+      <c r="C142" t="s">
+        <v>615</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" t="s">
+        <v>595</v>
+      </c>
+      <c r="B143" t="s">
+        <v>617</v>
+      </c>
+      <c r="C143" t="s">
+        <v>618</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" t="s">
+        <v>595</v>
+      </c>
+      <c r="B144" t="s">
+        <v>620</v>
+      </c>
+      <c r="C144" t="s">
+        <v>621</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" t="s">
+        <v>595</v>
+      </c>
+      <c r="B145" t="s">
+        <v>623</v>
+      </c>
+      <c r="C145" t="s">
+        <v>624</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" t="s">
+        <v>595</v>
+      </c>
+      <c r="B146" t="s">
+        <v>626</v>
+      </c>
+      <c r="C146" t="s">
+        <v>627</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" t="s">
+        <v>595</v>
+      </c>
+      <c r="B147" t="s">
+        <v>629</v>
+      </c>
+      <c r="C147" t="s">
+        <v>630</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" t="s">
+        <v>595</v>
+      </c>
+      <c r="B148" t="s">
+        <v>632</v>
+      </c>
+      <c r="C148" t="s">
+        <v>633</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" t="s">
+        <v>595</v>
+      </c>
+      <c r="B149" t="s">
+        <v>635</v>
+      </c>
+      <c r="C149" t="s">
+        <v>636</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" t="s">
+        <v>595</v>
+      </c>
+      <c r="B150" t="s">
+        <v>638</v>
+      </c>
+      <c r="C150" t="s">
+        <v>639</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" t="s">
+        <v>595</v>
+      </c>
+      <c r="B151" t="s">
+        <v>641</v>
+      </c>
+      <c r="C151" t="s">
+        <v>642</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" t="s">
+        <v>595</v>
+      </c>
+      <c r="B152" t="s">
+        <v>629</v>
+      </c>
+      <c r="C152" t="s">
+        <v>630</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" t="s">
+        <v>595</v>
+      </c>
+      <c r="B153" t="s">
+        <v>645</v>
+      </c>
+      <c r="C153" t="s">
+        <v>646</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" t="s">
+        <v>595</v>
+      </c>
+      <c r="B154" t="s">
+        <v>648</v>
+      </c>
+      <c r="C154" t="s">
+        <v>649</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" t="s">
+        <v>595</v>
+      </c>
+      <c r="B155" t="s">
+        <v>651</v>
+      </c>
+      <c r="C155" t="s">
+        <v>652</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" t="s">
+        <v>654</v>
+      </c>
+      <c r="B156" t="s">
+        <v>655</v>
+      </c>
+      <c r="C156" t="s">
+        <v>656</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" t="s">
+        <v>654</v>
+      </c>
+      <c r="B157" t="s">
+        <v>658</v>
+      </c>
+      <c r="C157" t="s">
+        <v>659</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" t="s">
+        <v>654</v>
+      </c>
+      <c r="B158" t="s">
+        <v>661</v>
+      </c>
+      <c r="C158" t="s">
+        <v>662</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" t="s">
+        <v>654</v>
+      </c>
+      <c r="B159" t="s">
+        <v>664</v>
+      </c>
+      <c r="C159" t="s">
+        <v>665</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" t="s">
+        <v>654</v>
+      </c>
+      <c r="B160" t="s">
+        <v>667</v>
+      </c>
+      <c r="C160" t="s">
+        <v>668</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" t="s">
+        <v>654</v>
+      </c>
+      <c r="B161" t="s">
+        <v>670</v>
+      </c>
+      <c r="C161" t="s">
+        <v>671</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" t="s">
+        <v>654</v>
+      </c>
+      <c r="B162" t="s">
+        <v>673</v>
+      </c>
+      <c r="C162" t="s">
+        <v>674</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" t="s">
+        <v>654</v>
+      </c>
+      <c r="B163" t="s">
+        <v>676</v>
+      </c>
+      <c r="C163" t="s">
+        <v>677</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" t="s">
+        <v>654</v>
+      </c>
+      <c r="B164" t="s">
+        <v>679</v>
+      </c>
+      <c r="C164" t="s">
+        <v>680</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" t="s">
+        <v>654</v>
+      </c>
+      <c r="B165" t="s">
+        <v>682</v>
+      </c>
+      <c r="C165" t="s">
+        <v>683</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" t="s">
+        <v>654</v>
+      </c>
+      <c r="B166" t="s">
+        <v>685</v>
+      </c>
+      <c r="C166" t="s">
+        <v>686</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" t="s">
+        <v>654</v>
+      </c>
+      <c r="B167" t="s">
+        <v>688</v>
+      </c>
+      <c r="C167" t="s">
+        <v>689</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" t="s">
+        <v>654</v>
+      </c>
+      <c r="B168" t="s">
+        <v>691</v>
+      </c>
+      <c r="C168" t="s">
+        <v>692</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" t="s">
+        <v>694</v>
+      </c>
+      <c r="B169" t="s">
+        <v>695</v>
+      </c>
+      <c r="C169" t="s">
+        <v>696</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" t="s">
+        <v>694</v>
+      </c>
+      <c r="B170" t="s">
+        <v>698</v>
+      </c>
+      <c r="C170" t="s">
+        <v>699</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" t="s">
+        <v>694</v>
+      </c>
+      <c r="B171" t="s">
+        <v>701</v>
+      </c>
+      <c r="C171" t="s">
+        <v>702</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" t="s">
+        <v>694</v>
+      </c>
+      <c r="B172" t="s">
+        <v>704</v>
+      </c>
+      <c r="C172" t="s">
+        <v>705</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" t="s">
+        <v>694</v>
+      </c>
+      <c r="B173" t="s">
+        <v>707</v>
+      </c>
+      <c r="C173" t="s">
+        <v>708</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" t="s">
+        <v>694</v>
+      </c>
+      <c r="B174" t="s">
+        <v>710</v>
+      </c>
+      <c r="C174" t="s">
+        <v>711</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" t="s">
+        <v>694</v>
+      </c>
+      <c r="B175" t="s">
+        <v>713</v>
+      </c>
+      <c r="C175" t="s">
+        <v>714</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" t="s">
+        <v>694</v>
+      </c>
+      <c r="B176" t="s">
+        <v>716</v>
+      </c>
+      <c r="C176" t="s">
+        <v>717</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" t="s">
+        <v>694</v>
+      </c>
+      <c r="B177" t="s">
+        <v>719</v>
+      </c>
+      <c r="C177" t="s">
+        <v>720</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" t="s">
+        <v>694</v>
+      </c>
+      <c r="B178" t="s">
+        <v>722</v>
+      </c>
+      <c r="C178" t="s">
+        <v>723</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" t="s">
+        <v>694</v>
+      </c>
+      <c r="B179" t="s">
+        <v>725</v>
+      </c>
+      <c r="C179" t="s">
+        <v>726</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" t="s">
+        <v>694</v>
+      </c>
+      <c r="B180" t="s">
+        <v>728</v>
+      </c>
+      <c r="C180" t="s">
+        <v>729</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" t="s">
+        <v>694</v>
+      </c>
+      <c r="B181" t="s">
+        <v>731</v>
+      </c>
+      <c r="C181" t="s">
+        <v>732</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" t="s">
+        <v>694</v>
+      </c>
+      <c r="B182" t="s">
+        <v>734</v>
+      </c>
+      <c r="C182" t="s">
+        <v>735</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" t="s">
+        <v>694</v>
+      </c>
+      <c r="B183" t="s">
+        <v>737</v>
+      </c>
+      <c r="C183" t="s">
+        <v>738</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" t="s">
+        <v>694</v>
+      </c>
+      <c r="B184" t="s">
+        <v>740</v>
+      </c>
+      <c r="C184" t="s">
+        <v>741</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185" t="s">
+        <v>694</v>
+      </c>
+      <c r="B185" t="s">
+        <v>743</v>
+      </c>
+      <c r="C185" t="s">
+        <v>744</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186" t="s">
+        <v>694</v>
+      </c>
+      <c r="B186" t="s">
+        <v>746</v>
+      </c>
+      <c r="C186" t="s">
+        <v>747</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187" t="s">
+        <v>694</v>
+      </c>
+      <c r="B187" t="s">
+        <v>749</v>
+      </c>
+      <c r="C187" t="s">
+        <v>750</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" t="s">
+        <v>694</v>
+      </c>
+      <c r="B188" t="s">
+        <v>752</v>
+      </c>
+      <c r="C188" t="s">
+        <v>753</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" t="s">
+        <v>755</v>
+      </c>
+      <c r="B189" t="s">
+        <v>756</v>
+      </c>
+      <c r="C189" t="s">
+        <v>757</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" t="s">
+        <v>755</v>
+      </c>
+      <c r="B190" t="s">
+        <v>759</v>
+      </c>
+      <c r="C190" t="s">
+        <v>760</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" t="s">
+        <v>755</v>
+      </c>
+      <c r="B191" t="s">
+        <v>762</v>
+      </c>
+      <c r="C191" t="s">
+        <v>763</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192" t="s">
+        <v>755</v>
+      </c>
+      <c r="B192" t="s">
+        <v>474</v>
+      </c>
+      <c r="C192" t="s">
+        <v>765</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193" t="s">
+        <v>755</v>
+      </c>
+      <c r="B193" t="s">
+        <v>767</v>
+      </c>
+      <c r="C193" t="s">
+        <v>768</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" t="s">
+        <v>755</v>
+      </c>
+      <c r="B194" t="s">
+        <v>770</v>
+      </c>
+      <c r="C194" t="s">
+        <v>771</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" t="s">
+        <v>755</v>
+      </c>
+      <c r="B195" t="s">
+        <v>773</v>
+      </c>
+      <c r="C195" t="s">
+        <v>774</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" t="s">
+        <v>755</v>
+      </c>
+      <c r="B196" t="s">
+        <v>756</v>
+      </c>
+      <c r="C196" t="s">
+        <v>776</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" t="s">
+        <v>755</v>
+      </c>
+      <c r="B197" t="s">
+        <v>778</v>
+      </c>
+      <c r="C197" t="s">
+        <v>779</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" t="s">
+        <v>755</v>
+      </c>
+      <c r="B198" t="s">
+        <v>781</v>
+      </c>
+      <c r="C198" t="s">
+        <v>782</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" t="s">
+        <v>755</v>
+      </c>
+      <c r="B199" t="s">
+        <v>784</v>
+      </c>
+      <c r="C199" t="s">
+        <v>785</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" t="s">
+        <v>755</v>
+      </c>
+      <c r="B200" t="s">
+        <v>787</v>
+      </c>
+      <c r="C200" t="s">
+        <v>788</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" t="s">
+        <v>755</v>
+      </c>
+      <c r="B201" t="s">
+        <v>790</v>
+      </c>
+      <c r="C201" t="s">
+        <v>791</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" t="s">
+        <v>755</v>
+      </c>
+      <c r="B202" t="s">
+        <v>793</v>
+      </c>
+      <c r="C202" t="s">
+        <v>794</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" t="s">
+        <v>755</v>
+      </c>
+      <c r="B203" t="s">
+        <v>796</v>
+      </c>
+      <c r="C203" t="s">
+        <v>797</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" t="s">
+        <v>755</v>
+      </c>
+      <c r="B204" t="s">
+        <v>799</v>
+      </c>
+      <c r="C204" t="s">
+        <v>800</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" t="s">
+        <v>755</v>
+      </c>
+      <c r="B205" t="s">
+        <v>802</v>
+      </c>
+      <c r="C205" t="s">
+        <v>803</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" t="s">
+        <v>755</v>
+      </c>
+      <c r="B206" t="s">
+        <v>805</v>
+      </c>
+      <c r="C206" t="s">
+        <v>806</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" t="s">
+        <v>755</v>
+      </c>
+      <c r="B207" t="s">
+        <v>808</v>
+      </c>
+      <c r="C207" t="s">
+        <v>809</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" t="s">
+        <v>755</v>
+      </c>
+      <c r="B208" t="s">
+        <v>811</v>
+      </c>
+      <c r="C208" t="s">
+        <v>812</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" t="s">
+        <v>814</v>
+      </c>
+      <c r="B209" t="s">
+        <v>815</v>
+      </c>
+      <c r="C209" t="s">
+        <v>816</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" t="s">
+        <v>814</v>
+      </c>
+      <c r="B210" t="s">
+        <v>818</v>
+      </c>
+      <c r="C210" t="s">
+        <v>819</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" t="s">
+        <v>814</v>
+      </c>
+      <c r="B211" t="s">
+        <v>821</v>
+      </c>
+      <c r="C211" t="s">
+        <v>822</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" t="s">
+        <v>814</v>
+      </c>
+      <c r="B212" t="s">
+        <v>824</v>
+      </c>
+      <c r="C212" t="s">
+        <v>825</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" t="s">
+        <v>814</v>
+      </c>
+      <c r="B213" t="s">
+        <v>827</v>
+      </c>
+      <c r="C213" t="s">
+        <v>828</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" t="s">
+        <v>814</v>
+      </c>
+      <c r="B214" t="s">
+        <v>830</v>
+      </c>
+      <c r="C214" t="s">
+        <v>831</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" t="s">
+        <v>814</v>
+      </c>
+      <c r="B215" t="s">
+        <v>833</v>
+      </c>
+      <c r="C215" t="s">
+        <v>834</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" t="s">
+        <v>814</v>
+      </c>
+      <c r="B216" t="s">
+        <v>836</v>
+      </c>
+      <c r="C216" t="s">
+        <v>837</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" t="s">
+        <v>814</v>
+      </c>
+      <c r="B217" t="s">
+        <v>839</v>
+      </c>
+      <c r="C217" t="s">
+        <v>840</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" t="s">
+        <v>814</v>
+      </c>
+      <c r="B218" t="s">
+        <v>842</v>
+      </c>
+      <c r="C218" t="s">
+        <v>843</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" t="s">
+        <v>814</v>
+      </c>
+      <c r="B219" t="s">
+        <v>845</v>
+      </c>
+      <c r="C219" t="s">
+        <v>846</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" t="s">
+        <v>814</v>
+      </c>
+      <c r="B220" t="s">
+        <v>848</v>
+      </c>
+      <c r="C220" t="s">
+        <v>849</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" t="s">
+        <v>814</v>
+      </c>
+      <c r="B221" t="s">
+        <v>851</v>
+      </c>
+      <c r="C221" t="s">
+        <v>852</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" t="s">
+        <v>814</v>
+      </c>
+      <c r="B222" t="s">
+        <v>854</v>
+      </c>
+      <c r="C222" t="s">
+        <v>855</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" t="s">
+        <v>814</v>
+      </c>
+      <c r="B223" t="s">
+        <v>857</v>
+      </c>
+      <c r="C223" t="s">
+        <v>858</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" t="s">
+        <v>814</v>
+      </c>
+      <c r="B224" t="s">
+        <v>860</v>
+      </c>
+      <c r="C224" t="s">
+        <v>861</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" t="s">
+        <v>814</v>
+      </c>
+      <c r="B225" t="s">
+        <v>863</v>
+      </c>
+      <c r="C225" t="s">
+        <v>864</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" t="s">
+        <v>814</v>
+      </c>
+      <c r="B226" t="s">
+        <v>866</v>
+      </c>
+      <c r="C226" t="s">
+        <v>867</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" t="s">
+        <v>814</v>
+      </c>
+      <c r="B227" t="s">
+        <v>869</v>
+      </c>
+      <c r="C227" t="s">
+        <v>870</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" t="s">
+        <v>814</v>
+      </c>
+      <c r="B228" t="s">
+        <v>872</v>
+      </c>
+      <c r="C228" t="s">
+        <v>873</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" t="s">
+        <v>875</v>
+      </c>
+      <c r="B229" t="s">
+        <v>876</v>
+      </c>
+      <c r="C229" t="s">
+        <v>877</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" t="s">
+        <v>875</v>
+      </c>
+      <c r="B230" t="s">
+        <v>879</v>
+      </c>
+      <c r="C230" t="s">
+        <v>880</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" t="s">
+        <v>875</v>
+      </c>
+      <c r="B231" t="s">
+        <v>882</v>
+      </c>
+      <c r="C231" t="s">
+        <v>883</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" t="s">
+        <v>875</v>
+      </c>
+      <c r="B232" t="s">
+        <v>885</v>
+      </c>
+      <c r="C232" t="s">
+        <v>886</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" t="s">
+        <v>875</v>
+      </c>
+      <c r="B233" t="s">
+        <v>888</v>
+      </c>
+      <c r="C233" t="s">
+        <v>889</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" t="s">
+        <v>875</v>
+      </c>
+      <c r="B234" t="s">
+        <v>891</v>
+      </c>
+      <c r="C234" t="s">
+        <v>892</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" t="s">
+        <v>875</v>
+      </c>
+      <c r="B235" t="s">
+        <v>894</v>
+      </c>
+      <c r="C235" t="s">
+        <v>895</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" t="s">
+        <v>875</v>
+      </c>
+      <c r="B236" t="s">
+        <v>897</v>
+      </c>
+      <c r="C236" t="s">
+        <v>898</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" t="s">
+        <v>875</v>
+      </c>
+      <c r="B237" t="s">
+        <v>900</v>
+      </c>
+      <c r="C237" t="s">
+        <v>901</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" t="s">
+        <v>875</v>
+      </c>
+      <c r="B238" t="s">
+        <v>903</v>
+      </c>
+      <c r="C238" t="s">
+        <v>904</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" t="s">
+        <v>875</v>
+      </c>
+      <c r="B239" t="s">
+        <v>906</v>
+      </c>
+      <c r="C239" t="s">
+        <v>907</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" t="s">
+        <v>875</v>
+      </c>
+      <c r="B240" t="s">
+        <v>909</v>
+      </c>
+      <c r="C240" t="s">
+        <v>910</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" t="s">
+        <v>912</v>
+      </c>
+      <c r="B241" t="s">
+        <v>913</v>
+      </c>
+      <c r="C241" t="s">
+        <v>914</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" t="s">
+        <v>912</v>
+      </c>
+      <c r="B242" t="s">
+        <v>916</v>
+      </c>
+      <c r="C242" t="s">
+        <v>917</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" t="s">
+        <v>912</v>
+      </c>
+      <c r="B243" t="s">
+        <v>919</v>
+      </c>
+      <c r="C243" t="s">
+        <v>920</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" t="s">
+        <v>912</v>
+      </c>
+      <c r="B244" t="s">
+        <v>922</v>
+      </c>
+      <c r="C244" t="s">
+        <v>923</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" t="s">
+        <v>912</v>
+      </c>
+      <c r="B245" t="s">
+        <v>925</v>
+      </c>
+      <c r="C245" t="s">
+        <v>926</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" t="s">
+        <v>912</v>
+      </c>
+      <c r="B246" t="s">
+        <v>928</v>
+      </c>
+      <c r="C246" t="s">
+        <v>929</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" t="s">
+        <v>912</v>
+      </c>
+      <c r="B247" t="s">
+        <v>931</v>
+      </c>
+      <c r="C247" t="s">
+        <v>932</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" t="s">
+        <v>912</v>
+      </c>
+      <c r="B248" t="s">
+        <v>934</v>
+      </c>
+      <c r="C248" t="s">
+        <v>935</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" t="s">
+        <v>912</v>
+      </c>
+      <c r="B249" t="s">
+        <v>937</v>
+      </c>
+      <c r="C249" t="s">
+        <v>938</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" t="s">
+        <v>912</v>
+      </c>
+      <c r="B250" t="s">
+        <v>940</v>
+      </c>
+      <c r="C250" t="s">
+        <v>941</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" t="s">
+        <v>912</v>
+      </c>
+      <c r="B251" t="s">
+        <v>943</v>
+      </c>
+      <c r="C251" t="s">
+        <v>944</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" t="s">
+        <v>912</v>
+      </c>
+      <c r="B252" t="s">
+        <v>946</v>
+      </c>
+      <c r="C252" t="s">
+        <v>947</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" t="s">
+        <v>912</v>
+      </c>
+      <c r="B253" t="s">
+        <v>949</v>
+      </c>
+      <c r="C253" t="s">
+        <v>950</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" t="s">
+        <v>912</v>
+      </c>
+      <c r="B254" t="s">
+        <v>952</v>
+      </c>
+      <c r="C254" t="s">
+        <v>953</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" t="s">
+        <v>912</v>
+      </c>
+      <c r="B255" t="s">
+        <v>955</v>
+      </c>
+      <c r="C255" t="s">
+        <v>956</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" t="s">
+        <v>912</v>
+      </c>
+      <c r="B256" t="s">
+        <v>958</v>
+      </c>
+      <c r="C256" t="s">
+        <v>959</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" t="s">
+        <v>912</v>
+      </c>
+      <c r="B257" t="s">
+        <v>961</v>
+      </c>
+      <c r="C257" t="s">
+        <v>962</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" t="s">
+        <v>912</v>
+      </c>
+      <c r="B258" t="s">
+        <v>964</v>
+      </c>
+      <c r="C258" t="s">
+        <v>965</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" t="s">
+        <v>912</v>
+      </c>
+      <c r="B259" t="s">
+        <v>967</v>
+      </c>
+      <c r="C259" t="s">
+        <v>968</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" t="s">
+        <v>912</v>
+      </c>
+      <c r="B260" t="s">
+        <v>970</v>
+      </c>
+      <c r="C260" t="s">
+        <v>971</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>972</v>
       </c>
     </row>
   </sheetData>
@@ -4443,7 +8374,170 @@
     <hyperlink ref="D95" r:id="rId187"/>
     <hyperlink ref="F95" r:id="rId188"/>
     <hyperlink ref="D96" r:id="rId189"/>
-    <hyperlink ref="F96" r:id="rId190"/>
+    <hyperlink ref="D97" r:id="rId190"/>
+    <hyperlink ref="D98" r:id="rId191"/>
+    <hyperlink ref="D99" r:id="rId192"/>
+    <hyperlink ref="D100" r:id="rId193"/>
+    <hyperlink ref="D101" r:id="rId194"/>
+    <hyperlink ref="D102" r:id="rId195"/>
+    <hyperlink ref="D103" r:id="rId196"/>
+    <hyperlink ref="D104" r:id="rId197"/>
+    <hyperlink ref="D105" r:id="rId198"/>
+    <hyperlink ref="D106" r:id="rId199"/>
+    <hyperlink ref="D107" r:id="rId200"/>
+    <hyperlink ref="D108" r:id="rId201"/>
+    <hyperlink ref="D109" r:id="rId202"/>
+    <hyperlink ref="D110" r:id="rId203"/>
+    <hyperlink ref="D111" r:id="rId204"/>
+    <hyperlink ref="D112" r:id="rId205"/>
+    <hyperlink ref="D113" r:id="rId206"/>
+    <hyperlink ref="D114" r:id="rId207"/>
+    <hyperlink ref="D115" r:id="rId208"/>
+    <hyperlink ref="D116" r:id="rId209"/>
+    <hyperlink ref="D117" r:id="rId210"/>
+    <hyperlink ref="D118" r:id="rId211"/>
+    <hyperlink ref="D119" r:id="rId212"/>
+    <hyperlink ref="D120" r:id="rId213"/>
+    <hyperlink ref="D121" r:id="rId214"/>
+    <hyperlink ref="D122" r:id="rId215"/>
+    <hyperlink ref="D123" r:id="rId216"/>
+    <hyperlink ref="D124" r:id="rId217"/>
+    <hyperlink ref="D125" r:id="rId218"/>
+    <hyperlink ref="D126" r:id="rId219"/>
+    <hyperlink ref="D127" r:id="rId220"/>
+    <hyperlink ref="D128" r:id="rId221"/>
+    <hyperlink ref="D129" r:id="rId222"/>
+    <hyperlink ref="D130" r:id="rId223"/>
+    <hyperlink ref="D131" r:id="rId224"/>
+    <hyperlink ref="D132" r:id="rId225"/>
+    <hyperlink ref="D133" r:id="rId226"/>
+    <hyperlink ref="D134" r:id="rId227"/>
+    <hyperlink ref="D135" r:id="rId228"/>
+    <hyperlink ref="D136" r:id="rId229"/>
+    <hyperlink ref="D137" r:id="rId230"/>
+    <hyperlink ref="D138" r:id="rId231"/>
+    <hyperlink ref="D139" r:id="rId232"/>
+    <hyperlink ref="D140" r:id="rId233"/>
+    <hyperlink ref="D141" r:id="rId234"/>
+    <hyperlink ref="D142" r:id="rId235"/>
+    <hyperlink ref="D143" r:id="rId236"/>
+    <hyperlink ref="D144" r:id="rId237"/>
+    <hyperlink ref="D145" r:id="rId238"/>
+    <hyperlink ref="D146" r:id="rId239"/>
+    <hyperlink ref="D147" r:id="rId240"/>
+    <hyperlink ref="D148" r:id="rId241"/>
+    <hyperlink ref="D149" r:id="rId242"/>
+    <hyperlink ref="D150" r:id="rId243"/>
+    <hyperlink ref="D151" r:id="rId244"/>
+    <hyperlink ref="D152" r:id="rId245"/>
+    <hyperlink ref="D153" r:id="rId246"/>
+    <hyperlink ref="D154" r:id="rId247"/>
+    <hyperlink ref="D155" r:id="rId248"/>
+    <hyperlink ref="D156" r:id="rId249"/>
+    <hyperlink ref="D157" r:id="rId250"/>
+    <hyperlink ref="D158" r:id="rId251"/>
+    <hyperlink ref="D159" r:id="rId252"/>
+    <hyperlink ref="D160" r:id="rId253"/>
+    <hyperlink ref="D161" r:id="rId254"/>
+    <hyperlink ref="D162" r:id="rId255"/>
+    <hyperlink ref="D163" r:id="rId256"/>
+    <hyperlink ref="D164" r:id="rId257"/>
+    <hyperlink ref="D165" r:id="rId258"/>
+    <hyperlink ref="D166" r:id="rId259"/>
+    <hyperlink ref="D167" r:id="rId260"/>
+    <hyperlink ref="D168" r:id="rId261"/>
+    <hyperlink ref="D169" r:id="rId262"/>
+    <hyperlink ref="D170" r:id="rId263"/>
+    <hyperlink ref="D171" r:id="rId264"/>
+    <hyperlink ref="D172" r:id="rId265"/>
+    <hyperlink ref="D173" r:id="rId266"/>
+    <hyperlink ref="D174" r:id="rId267"/>
+    <hyperlink ref="D175" r:id="rId268"/>
+    <hyperlink ref="D176" r:id="rId269"/>
+    <hyperlink ref="D177" r:id="rId270"/>
+    <hyperlink ref="D178" r:id="rId271"/>
+    <hyperlink ref="D179" r:id="rId272"/>
+    <hyperlink ref="D180" r:id="rId273"/>
+    <hyperlink ref="D181" r:id="rId274"/>
+    <hyperlink ref="D182" r:id="rId275"/>
+    <hyperlink ref="D183" r:id="rId276"/>
+    <hyperlink ref="D184" r:id="rId277"/>
+    <hyperlink ref="D185" r:id="rId278"/>
+    <hyperlink ref="D186" r:id="rId279"/>
+    <hyperlink ref="D187" r:id="rId280"/>
+    <hyperlink ref="D188" r:id="rId281"/>
+    <hyperlink ref="D189" r:id="rId282"/>
+    <hyperlink ref="D190" r:id="rId283"/>
+    <hyperlink ref="D191" r:id="rId284"/>
+    <hyperlink ref="D192" r:id="rId285"/>
+    <hyperlink ref="D193" r:id="rId286"/>
+    <hyperlink ref="D194" r:id="rId287"/>
+    <hyperlink ref="D195" r:id="rId288"/>
+    <hyperlink ref="D196" r:id="rId289"/>
+    <hyperlink ref="D197" r:id="rId290"/>
+    <hyperlink ref="D198" r:id="rId291"/>
+    <hyperlink ref="D199" r:id="rId292"/>
+    <hyperlink ref="D200" r:id="rId293"/>
+    <hyperlink ref="D201" r:id="rId294"/>
+    <hyperlink ref="D202" r:id="rId295"/>
+    <hyperlink ref="D203" r:id="rId296"/>
+    <hyperlink ref="D204" r:id="rId297"/>
+    <hyperlink ref="D205" r:id="rId298"/>
+    <hyperlink ref="D206" r:id="rId299"/>
+    <hyperlink ref="D207" r:id="rId300"/>
+    <hyperlink ref="D208" r:id="rId301"/>
+    <hyperlink ref="D209" r:id="rId302"/>
+    <hyperlink ref="D210" r:id="rId303"/>
+    <hyperlink ref="D211" r:id="rId304"/>
+    <hyperlink ref="D212" r:id="rId305"/>
+    <hyperlink ref="D213" r:id="rId306"/>
+    <hyperlink ref="D214" r:id="rId307"/>
+    <hyperlink ref="D215" r:id="rId308"/>
+    <hyperlink ref="D216" r:id="rId309"/>
+    <hyperlink ref="D217" r:id="rId310"/>
+    <hyperlink ref="D218" r:id="rId311"/>
+    <hyperlink ref="D219" r:id="rId312"/>
+    <hyperlink ref="D220" r:id="rId313"/>
+    <hyperlink ref="D221" r:id="rId314"/>
+    <hyperlink ref="D222" r:id="rId315"/>
+    <hyperlink ref="D223" r:id="rId316"/>
+    <hyperlink ref="D224" r:id="rId317"/>
+    <hyperlink ref="D225" r:id="rId318"/>
+    <hyperlink ref="D226" r:id="rId319"/>
+    <hyperlink ref="D227" r:id="rId320"/>
+    <hyperlink ref="D228" r:id="rId321"/>
+    <hyperlink ref="D229" r:id="rId322"/>
+    <hyperlink ref="D230" r:id="rId323"/>
+    <hyperlink ref="D231" r:id="rId324"/>
+    <hyperlink ref="D232" r:id="rId325"/>
+    <hyperlink ref="D233" r:id="rId326"/>
+    <hyperlink ref="D234" r:id="rId327"/>
+    <hyperlink ref="D235" r:id="rId328"/>
+    <hyperlink ref="D236" r:id="rId329"/>
+    <hyperlink ref="D237" r:id="rId330"/>
+    <hyperlink ref="D238" r:id="rId331"/>
+    <hyperlink ref="D239" r:id="rId332"/>
+    <hyperlink ref="D240" r:id="rId333"/>
+    <hyperlink ref="D241" r:id="rId334"/>
+    <hyperlink ref="D242" r:id="rId335"/>
+    <hyperlink ref="D243" r:id="rId336"/>
+    <hyperlink ref="D244" r:id="rId337"/>
+    <hyperlink ref="D245" r:id="rId338"/>
+    <hyperlink ref="D246" r:id="rId339"/>
+    <hyperlink ref="D247" r:id="rId340"/>
+    <hyperlink ref="D248" r:id="rId341"/>
+    <hyperlink ref="D249" r:id="rId342"/>
+    <hyperlink ref="D250" r:id="rId343"/>
+    <hyperlink ref="D251" r:id="rId344"/>
+    <hyperlink ref="D252" r:id="rId345"/>
+    <hyperlink ref="D253" r:id="rId346"/>
+    <hyperlink ref="D254" r:id="rId347"/>
+    <hyperlink ref="D255" r:id="rId348"/>
+    <hyperlink ref="D256" r:id="rId349"/>
+    <hyperlink ref="D257" r:id="rId350"/>
+    <hyperlink ref="D258" r:id="rId351"/>
+    <hyperlink ref="D259" r:id="rId352"/>
+    <hyperlink ref="D260" r:id="rId353"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
